--- a/tracking/picks.xlsx
+++ b/tracking/picks.xlsx
@@ -7,8 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Picks" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Picks" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Season Results" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Moneyline" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totals" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hitter TB" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pitcher Outs" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NRFI-YRFI" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,10 +500,17 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>pnl_50</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>20260325</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -538,10 +550,13 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>20260325</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -583,10 +598,13 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>20260325</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -622,16 +640,25 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>62.7</v>
+      </c>
       <c r="M4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>31.35</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>20260325</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -667,16 +694,25 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>95.23999999999999</v>
+      </c>
       <c r="M5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>47.62</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>20260325</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -712,16 +748,25 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-100</v>
+      </c>
       <c r="M6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>20260325</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -757,16 +802,25 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" t="n">
+        <v>60.61</v>
+      </c>
       <c r="M7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>30.3</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>20260325</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -802,16 +856,25 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>86.95999999999999</v>
+      </c>
       <c r="M8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>43.48</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>20260325</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -847,16 +910,25 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-100</v>
+      </c>
       <c r="M9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>20260325</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -892,16 +964,25 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>19</v>
+      </c>
+      <c r="L10" t="n">
+        <v>100</v>
+      </c>
       <c r="M10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>20260325</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -941,10 +1022,13 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>20260325</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -984,10 +1068,13 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>20260325</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1029,10 +1116,13 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>20260325</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1068,16 +1158,25 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L14" t="n">
+        <v>62.7</v>
+      </c>
       <c r="M14" t="inlineStr"/>
+      <c r="N14" t="n">
+        <v>31.35</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>20260325</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1113,16 +1212,25 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>95.23999999999999</v>
+      </c>
       <c r="M15" t="inlineStr"/>
+      <c r="N15" t="n">
+        <v>47.62</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>20260325</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1158,16 +1266,25 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-100</v>
+      </c>
       <c r="M16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>20260325</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1203,16 +1320,25 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L17" t="n">
+        <v>60.61</v>
+      </c>
       <c r="M17" t="inlineStr"/>
+      <c r="N17" t="n">
+        <v>30.3</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>20260325</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1248,16 +1374,25 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>86.95999999999999</v>
+      </c>
       <c r="M18" t="inlineStr"/>
+      <c r="N18" t="n">
+        <v>43.48</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>20260325</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1293,16 +1428,25 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-100</v>
+      </c>
       <c r="M19" t="inlineStr"/>
+      <c r="N19" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>20260325</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1338,16 +1482,25 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>19</v>
+      </c>
+      <c r="L20" t="n">
+        <v>100</v>
+      </c>
       <c r="M20" t="inlineStr"/>
+      <c r="N20" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>20260325</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1387,6 +1540,7 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1432,6 +1586,7 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1479,6 +1634,7 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1520,12 +1676,19 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>4000</v>
+      </c>
       <c r="M24" t="inlineStr"/>
+      <c r="N24" t="n">
+        <v>2000</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1567,12 +1730,19 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>2</v>
+      </c>
+      <c r="L25" t="n">
+        <v>62.89</v>
+      </c>
       <c r="M25" t="inlineStr"/>
+      <c r="N25" t="n">
+        <v>31.45</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1614,12 +1784,19 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>62.11</v>
+      </c>
       <c r="M26" t="inlineStr"/>
+      <c r="N26" t="n">
+        <v>31.06</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1661,12 +1838,19 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>15</v>
+      </c>
+      <c r="L27" t="n">
+        <v>10000</v>
+      </c>
       <c r="M27" t="inlineStr"/>
+      <c r="N27" t="n">
+        <v>5000</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1712,6 +1896,7 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1724,7 +1909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1793,6 +1978,2805 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>pnl_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SFG vs NYY</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Giancarlo Stanton</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-159.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.6656</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L2" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>31.35</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NYY vs SFG</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Patrick Bailey</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-105</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.5429</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.06950000000000001</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>95.23999999999999</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>47.62</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NYY vs SFG</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Rafael Devers</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>144</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.4371</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.0544</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SFG vs NYY</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Trent Grisham</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-165</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.6313</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.0532</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>60.61</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SFG vs NYY</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Ryan McMahon</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.5377</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.0426</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>86.95999999999999</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>43.48</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SFG vs NYY</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Cody Bellinger</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>135</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.4371</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SFG vs NYY</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Giancarlo Stanton</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-159.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.6656</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>31.35</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NYY vs SFG</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Patrick Bailey</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-105</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.5429</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.06950000000000001</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>95.23999999999999</v>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>47.62</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NYY vs SFG</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Rafael Devers</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>144</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.4371</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.0544</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SFG vs NYY</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Trent Grisham</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-165</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.6313</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.0532</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>60.61</v>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="n">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SFG vs NYY</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Ryan McMahon</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.5377</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.0426</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>86.95999999999999</v>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="n">
+        <v>43.48</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SFG vs NYY</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Cody Bellinger</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>135</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.4371</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NYY vs SFG</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Harrison Bader</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.4608</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>4000</v>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SFG vs NYY</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Giancarlo Stanton</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-159</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.6656</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.09429999999999999</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>62.89</v>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="n">
+        <v>31.45</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NYY vs SFG</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Rafael Devers</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-161</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.6611</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.0876</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>62.11</v>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>31.06</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SFG vs NYY</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Max Fried</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>100</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.1454</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>19</v>
+      </c>
+      <c r="L17" t="n">
+        <v>100</v>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SFG vs NYY</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Max Fried</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G18" t="n">
+        <v>100</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.1454</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>19</v>
+      </c>
+      <c r="L18" t="n">
+        <v>100</v>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NYY vs SFG</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Logan Webb</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.4107</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>15</v>
+      </c>
+      <c r="L19" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>pick_date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>game</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>subject</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>bet_type</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>odds</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>model_prob</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>result</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>pnl</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>pnl_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NYY @ SFG</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>SFG</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.5715</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.09370000000000001</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NYY @ SFG</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SFG</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>100</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.5715</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.09370000000000001</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NYY @ SFG</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SFG</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>102</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.5715</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.09669999999999999</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>pick_date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>game</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>subject</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>bet_type</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>odds</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>model_prob</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>result</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>pnl</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>pnl_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NYY @ SFG</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>NYY @ SFG</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-114</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.6329</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1248</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NYY @ SFG</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NYY @ SFG</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-114</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.6329</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.1248</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NYY @ SFG</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NYY @ SFG</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-114</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.6329</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.1259</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>pick_date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>game</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>subject</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>bet_type</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>odds</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>model_prob</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>result</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>pnl</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>pnl_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SFG vs NYY</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Giancarlo Stanton</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-159.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.6656</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L2" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>31.35</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NYY vs SFG</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Patrick Bailey</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-105</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.5429</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.06950000000000001</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>95.23999999999999</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>47.62</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NYY vs SFG</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Rafael Devers</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>144</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.4371</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.0544</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SFG vs NYY</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Trent Grisham</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-165</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.6313</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.0532</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>60.61</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SFG vs NYY</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Ryan McMahon</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.5377</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.0426</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>86.95999999999999</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>43.48</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SFG vs NYY</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Cody Bellinger</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>135</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.4371</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SFG vs NYY</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Giancarlo Stanton</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-159.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.6656</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>31.35</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NYY vs SFG</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Patrick Bailey</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-105</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.5429</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.06950000000000001</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>95.23999999999999</v>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>47.62</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NYY vs SFG</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Rafael Devers</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>144</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.4371</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.0544</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SFG vs NYY</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Trent Grisham</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-165</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.6313</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.0532</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>60.61</v>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="n">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SFG vs NYY</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Ryan McMahon</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.5377</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.0426</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>86.95999999999999</v>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="n">
+        <v>43.48</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SFG vs NYY</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Cody Bellinger</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>135</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.4371</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NYY vs SFG</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Harrison Bader</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.4608</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>4000</v>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SFG vs NYY</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Giancarlo Stanton</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-159</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.6656</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.09429999999999999</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>62.89</v>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="n">
+        <v>31.45</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NYY vs SFG</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Rafael Devers</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-161</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.6611</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.0876</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>62.11</v>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>31.06</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>pick_date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>game</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>subject</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>bet_type</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>odds</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>model_prob</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>result</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>pnl</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>pnl_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SFG vs NYY</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Max Fried</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1454</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>19</v>
+      </c>
+      <c r="L2" t="n">
+        <v>100</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SFG vs NYY</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Max Fried</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>100</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.1454</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>19</v>
+      </c>
+      <c r="L3" t="n">
+        <v>100</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NYY vs SFG</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Logan Webb</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.4107</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>15</v>
+      </c>
+      <c r="L4" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>pick_date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>game</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>subject</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>bet_type</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>odds</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>model_prob</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>result</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>pnl</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>pnl_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NYY @ SFG</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>NYY @ SFG</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>NRFI</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>-157.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-0.5764</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NYY @ SFG</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NYY @ SFG</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>NRFI</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>-157.5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-0.5764</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NYY @ SFG</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NYY @ SFG</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>YRFI</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>120</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.5734</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tracking/picks.xlsx
+++ b/tracking/picks.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N28"/>
+  <dimension ref="A1:N54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1032,43 +1032,51 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Hitter TB</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NYY @ SFG</t>
+          <t>NYY vs SFG</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SFG</t>
+          <t>Harrison Bader</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>HOME</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0.5</v>
+      </c>
       <c r="G12" t="n">
-        <v>100</v>
+        <v>-2.5</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5715</v>
+        <v>0.4608</v>
       </c>
       <c r="I12" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.42</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>4000</v>
+      </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="N12" t="n">
+        <v>2000</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1078,17 +1086,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Totals</t>
+          <t>Hitter TB</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NYY @ SFG</t>
+          <t>NYY vs SFG</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NYY @ SFG</t>
+          <t>Rafael Devers</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1097,26 +1105,32 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>8.5</v>
+        <v>0.5</v>
       </c>
       <c r="G13" t="n">
-        <v>-114</v>
+        <v>-161</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6329</v>
+        <v>0.6611</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1248</v>
+        <v>0.0876</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>62.11</v>
+      </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="N13" t="n">
+        <v>31.06</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1126,35 +1140,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hitter TB</t>
+          <t>Pitcher Outs</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SFG vs NYY</t>
+          <t>NYY vs SFG</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Giancarlo Stanton</t>
+          <t>Logan Webb</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.5</v>
+        <v>16.5</v>
       </c>
       <c r="G14" t="n">
-        <v>-159.5</v>
+        <v>-1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6656</v>
+        <v>0.4107</v>
       </c>
       <c r="I14" t="n">
-        <v>0.094</v>
+        <v>0.394</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1162,14 +1176,14 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="L14" t="n">
-        <v>62.7</v>
+        <v>10000</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
-        <v>31.35</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="15">
@@ -1180,179 +1194,155 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hitter TB</t>
+          <t>NRFI/YRFI</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NYY vs SFG</t>
+          <t>NYY @ SFG</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>NYY @ SFG</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>0.5</v>
-      </c>
+          <t>YRFI</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>-105</v>
+        <v>120</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5429</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.5734</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>95.23999999999999</v>
-      </c>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="n">
-        <v>47.62</v>
-      </c>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260325</t>
+          <t>20260326</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hitter TB</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NYY vs SFG</t>
+          <t>MIN @ BAL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Rafael Devers</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>1.5</v>
-      </c>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>144</v>
+        <v>-141.5</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4371</v>
+        <v>0.649</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0544</v>
+        <v>0.0881</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>-100</v>
-      </c>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="n">
-        <v>-50</v>
-      </c>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260325</t>
+          <t>20260326</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hitter TB</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SFG vs NYY</t>
+          <t>PIT @ NYM</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Trent Grisham</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>0.5</v>
-      </c>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
-        <v>-165</v>
+        <v>-121</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6313</v>
+        <v>0.5858</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0532</v>
+        <v>0.0619</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>3</v>
-      </c>
-      <c r="L17" t="n">
-        <v>60.61</v>
-      </c>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="n">
-        <v>30.3</v>
-      </c>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260325</t>
+          <t>20260326</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hitter TB</t>
+          <t>Totals</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SFG vs NYY</t>
+          <t>CWS @ MIL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Ryan McMahon</t>
+          <t>CWS @ MIL</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1361,52 +1351,46 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.5</v>
+        <v>8</v>
       </c>
       <c r="G18" t="n">
-        <v>-115</v>
+        <v>-105</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5377</v>
+        <v>0.7967</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0426</v>
+        <v>0.3076</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>86.95999999999999</v>
-      </c>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="n">
-        <v>43.48</v>
-      </c>
+      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260325</t>
+          <t>20260326</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hitter TB</t>
+          <t>Totals</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SFG vs NYY</t>
+          <t>PIT @ NYM</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cody Bellinger</t>
+          <t>PIT @ NYM</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1415,52 +1399,46 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.5</v>
+        <v>7</v>
       </c>
       <c r="G19" t="n">
-        <v>135</v>
+        <v>-121</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4371</v>
+        <v>0.7237</v>
       </c>
       <c r="I19" t="n">
-        <v>0.042</v>
+        <v>0.3699</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>-100</v>
-      </c>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="n">
-        <v>-50</v>
-      </c>
+      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260325</t>
+          <t>20260326</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pitcher Outs</t>
+          <t>Totals</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SFG vs NYY</t>
+          <t>WSN @ CHC</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Max Fried</t>
+          <t>WSN @ CHC</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1469,68 +1447,64 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>16.5</v>
+        <v>7</v>
       </c>
       <c r="G20" t="n">
-        <v>100</v>
+        <v>-106</v>
       </c>
       <c r="H20" t="n">
-        <v>0.607</v>
+        <v>0.6821</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1454</v>
+        <v>0.1918</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>19</v>
-      </c>
-      <c r="L20" t="n">
-        <v>100</v>
-      </c>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="n">
-        <v>50</v>
-      </c>
+      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260325</t>
+          <t>20260326</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NRFI/YRFI</t>
+          <t>Totals</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NYY @ SFG</t>
+          <t>MIN @ BAL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NYY @ SFG</t>
+          <t>MIN @ BAL</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>NRFI</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>8.5</v>
+      </c>
       <c r="G21" t="n">
-        <v>-157.5</v>
+        <v>-115</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>0.5743</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5764</v>
+        <v>0.0634</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1545,38 +1519,40 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260325</t>
+          <t>20260326</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Hitter TB</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NYY @ SFG</t>
+          <t>NYM vs PIT</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SFG</t>
+          <t>Jared Triolo</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>HOME</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0.5</v>
+      </c>
       <c r="G22" t="n">
-        <v>102</v>
+        <v>-5</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5715</v>
+        <v>0.488</v>
       </c>
       <c r="I22" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.4119</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1591,22 +1567,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260325</t>
+          <t>20260326</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Totals</t>
+          <t>Hitter TB</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NYY @ SFG</t>
+          <t>MIL vs CWS</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NYY @ SFG</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1615,16 +1591,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>8.5</v>
+        <v>0.5</v>
       </c>
       <c r="G23" t="n">
-        <v>-114</v>
+        <v>-134.5</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6329</v>
+        <v>0.6704</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1259</v>
+        <v>0.1361</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1639,7 +1615,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260325</t>
+          <t>20260326</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1649,12 +1625,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NYY vs SFG</t>
+          <t>TBR vs STL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Harrison Bader</t>
+          <t>Jordan Walker</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1666,34 +1642,28 @@
         <v>0.5</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.5</v>
+        <v>128.5</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4608</v>
+        <v>0.5208</v>
       </c>
       <c r="I24" t="n">
-        <v>0.42</v>
+        <v>0.1146</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>4000</v>
-      </c>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="n">
-        <v>2000</v>
-      </c>
+      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260325</t>
+          <t>20260326</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1703,12 +1673,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SFG vs NYY</t>
+          <t>PIT vs NYM</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Giancarlo Stanton</t>
+          <t>Jorge Polanco</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1720,34 +1690,28 @@
         <v>0.5</v>
       </c>
       <c r="G25" t="n">
-        <v>-159</v>
+        <v>-141</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6656</v>
+        <v>0.65</v>
       </c>
       <c r="I25" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.1053</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>2</v>
-      </c>
-      <c r="L25" t="n">
-        <v>62.89</v>
-      </c>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="n">
-        <v>31.45</v>
-      </c>
+      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260325</t>
+          <t>20260326</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1757,136 +1721,126 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NYY vs SFG</t>
+          <t>CHC vs WSN</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Rafael Devers</t>
+          <t>Jacob Young</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>0.5</v>
       </c>
       <c r="G26" t="n">
-        <v>-161</v>
+        <v>-110</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6611</v>
+        <v>0.5992</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0876</v>
+        <v>0.1134</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K26" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" t="n">
-        <v>62.11</v>
-      </c>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="n">
-        <v>31.06</v>
-      </c>
+      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260325</t>
+          <t>20260326</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pitcher Outs</t>
+          <t>Hitter TB</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NYY vs SFG</t>
+          <t>CHC vs WSN</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Logan Webb</t>
+          <t>James Wood</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>16.5</v>
+        <v>0.5</v>
       </c>
       <c r="G27" t="n">
-        <v>-1</v>
+        <v>-161</v>
       </c>
       <c r="H27" t="n">
-        <v>0.4107</v>
+        <v>0.6791</v>
       </c>
       <c r="I27" t="n">
-        <v>0.394</v>
+        <v>0.1056</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K27" t="n">
-        <v>15</v>
-      </c>
-      <c r="L27" t="n">
-        <v>10000</v>
-      </c>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" t="n">
-        <v>5000</v>
-      </c>
+      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260325</t>
+          <t>20260326</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NRFI/YRFI</t>
+          <t>Hitter TB</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NYY @ SFG</t>
+          <t>PIT vs NYM</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NYY @ SFG</t>
+          <t>Juan Soto</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>YRFI</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>0.5</v>
+      </c>
       <c r="G28" t="n">
-        <v>120</v>
+        <v>-153.5</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5734</v>
+        <v>0.1028</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1897,6 +1851,1246 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CWS vs MIL</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>David Hamilton</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-118</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.6207</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.1178</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NYM vs PIT</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Brandon Lowe</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-150</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.6529</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>MIN vs BAL</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Tyler O'Neill</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-175</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.6989</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CHC vs WSN</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CJ Abrams</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-135.5</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.6195000000000001</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.0832</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>PIT vs NYM</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Francisco Lindor</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-180.5</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.6811</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.0843</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CIN vs BOS</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Ceddanne Rafaela</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-178</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.6949</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.09719999999999999</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>NYM vs PIT</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Spencer Horwitz</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-126</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.5911999999999999</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.0756</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>MIL vs CWS</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Andrew Benintendi</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-141.5</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.6186</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.0741</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>MIL vs CWS</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Miguel Vargas</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-145</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.6219</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.0713</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>MIN vs BAL</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Samuel Basallo</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-185</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.6848</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.0808</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>MIN vs BAL</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Gunnar Henderson</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-125</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.5917</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.07480000000000001</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>MIN vs BAL</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Adley Rutschman</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-172</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.6712</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.0818</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>BAL vs MIN</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Austin Martin</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-170</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.6679</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.08169999999999999</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CWS vs MIL</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-175</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.7971</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.2083</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>BAL vs MIN</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Joe Ryan</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G43" t="n">
+        <v>145</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.7798</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.4004</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>NYM vs PIT</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Paul Skenes</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-104.5</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.7044</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.2317</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>MIN vs BAL</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Trevor Rogers</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.7123</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.2247</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>PIT vs NYM</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G46" t="n">
+        <v>140.5</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.6554</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.2699</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CHC vs WSN</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Cade Cavalli</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.1997</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.1827</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>STL vs TBR</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-167.5</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.7352</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.1525</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>WSN vs CHC</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Matthew Boyd</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.6491</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.1491</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>MIL vs CWS</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Shane Smith</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-155</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.7044</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.1431</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>PIT @ NYM</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>PIT @ NYM</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>YRFI</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="n">
+        <v>120</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.5746</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>CWS @ MIL</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>CWS @ MIL</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>YRFI</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="n">
+        <v>-102</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.5314</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>MIN @ BAL</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>MIN @ BAL</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>YRFI</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="n">
+        <v>-112</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.5061</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>WSN @ CHC</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>WSN @ CHC</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>YRFI</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="n">
+        <v>106</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.5887</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.1338</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1909,7 +3103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2321,30 +3515,30 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SFG vs NYY</t>
+          <t>NYY vs SFG</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Giancarlo Stanton</t>
+          <t>Harrison Bader</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>0.5</v>
       </c>
       <c r="G8" t="n">
-        <v>-159.5</v>
+        <v>-2.5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6656</v>
+        <v>0.4608</v>
       </c>
       <c r="I8" t="n">
-        <v>0.094</v>
+        <v>0.42</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -2352,14 +3546,14 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>62.7</v>
+        <v>4000</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>31.35</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="9">
@@ -2380,25 +3574,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Rafael Devers</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>0.5</v>
       </c>
       <c r="G9" t="n">
-        <v>-105</v>
+        <v>-161</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5429</v>
+        <v>0.6611</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.0876</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -2406,14 +3600,14 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>95.23999999999999</v>
+        <v>62.11</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>47.62</v>
+        <v>31.06</v>
       </c>
     </row>
     <row r="10">
@@ -2424,17 +3618,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hitter TB</t>
+          <t>Pitcher Outs</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NYY vs SFG</t>
+          <t>SFG vs NYY</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Rafael Devers</t>
+          <t>Max Fried</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2443,31 +3637,31 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.5</v>
+        <v>16.5</v>
       </c>
       <c r="G10" t="n">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4371</v>
+        <v>0.607</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0544</v>
+        <v>0.1454</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="L10" t="n">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>-50</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
@@ -2478,35 +3672,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hitter TB</t>
+          <t>Pitcher Outs</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SFG vs NYY</t>
+          <t>NYY vs SFG</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Trent Grisham</t>
+          <t>Logan Webb</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.5</v>
+        <v>16.5</v>
       </c>
       <c r="G11" t="n">
-        <v>-165</v>
+        <v>-1</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6313</v>
+        <v>0.4107</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0532</v>
+        <v>0.394</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -2514,445 +3708,13 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="L11" t="n">
-        <v>60.61</v>
+        <v>10000</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
-        <v>30.3</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>20260325</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>SFG vs NYY</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Ryan McMahon</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-115</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.5377</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.0426</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>86.95999999999999</v>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="n">
-        <v>43.48</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>20260325</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>SFG vs NYY</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Cody Bellinger</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G13" t="n">
-        <v>135</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.4371</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="n">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>20260325</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>NYY vs SFG</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Harrison Bader</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.4608</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>4000</v>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>20260325</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>SFG vs NYY</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Giancarlo Stanton</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-159</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.6656</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.09429999999999999</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L15" t="n">
-        <v>62.89</v>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="n">
-        <v>31.45</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>20260325</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>NYY vs SFG</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Rafael Devers</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-161</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.6611</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.0876</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>62.11</v>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="n">
-        <v>31.06</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>20260325</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Pitcher Outs</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>SFG vs NYY</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Max Fried</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="G17" t="n">
-        <v>100</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.607</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.1454</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>19</v>
-      </c>
-      <c r="L17" t="n">
-        <v>100</v>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>20260325</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Pitcher Outs</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>SFG vs NYY</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Max Fried</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="G18" t="n">
-        <v>100</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.607</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.1454</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>19</v>
-      </c>
-      <c r="L18" t="n">
-        <v>100</v>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>20260325</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Pitcher Outs</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>NYY vs SFG</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Logan Webb</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="G19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.4107</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.394</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>15</v>
-      </c>
-      <c r="L19" t="n">
-        <v>10000</v>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="n">
         <v>5000</v>
       </c>
     </row>
@@ -3091,7 +3853,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260325</t>
+          <t>20260326</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3101,12 +3863,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NYY @ SFG</t>
+          <t>MIN @ BAL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SFG</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -3116,13 +3878,13 @@
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>100</v>
+        <v>-141.5</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5715</v>
+        <v>0.649</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.0881</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -3137,7 +3899,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260325</t>
+          <t>20260326</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3147,12 +3909,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NYY @ SFG</t>
+          <t>PIT @ NYM</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SFG</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3162,13 +3924,13 @@
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>102</v>
+        <v>-121</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5715</v>
+        <v>0.5858</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.0619</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -3191,7 +3953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3317,7 +4079,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260325</t>
+          <t>20260326</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3327,12 +4089,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NYY @ SFG</t>
+          <t>CWS @ MIL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NYY @ SFG</t>
+          <t>CWS @ MIL</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -3341,16 +4103,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="G3" t="n">
-        <v>-114</v>
+        <v>-105</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6329</v>
+        <v>0.7967</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1248</v>
+        <v>0.3076</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -3365,7 +4127,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260325</t>
+          <t>20260326</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3375,12 +4137,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NYY @ SFG</t>
+          <t>PIT @ NYM</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NYY @ SFG</t>
+          <t>PIT @ NYM</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3389,16 +4151,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="G4" t="n">
-        <v>-114</v>
+        <v>-121</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6329</v>
+        <v>0.7237</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1259</v>
+        <v>0.3699</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -3409,6 +4171,102 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>WSN @ CHC</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>WSN @ CHC</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-106</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.6821</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.1918</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>MIN @ BAL</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MIN @ BAL</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.5743</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.0634</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3421,7 +4279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3833,30 +4691,30 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SFG vs NYY</t>
+          <t>NYY vs SFG</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Giancarlo Stanton</t>
+          <t>Harrison Bader</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>0.5</v>
       </c>
       <c r="G8" t="n">
-        <v>-159.5</v>
+        <v>-2.5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6656</v>
+        <v>0.4608</v>
       </c>
       <c r="I8" t="n">
-        <v>0.094</v>
+        <v>0.42</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -3864,14 +4722,14 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>62.7</v>
+        <v>4000</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>31.35</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="9">
@@ -3892,25 +4750,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Rafael Devers</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>0.5</v>
       </c>
       <c r="G9" t="n">
-        <v>-105</v>
+        <v>-161</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5429</v>
+        <v>0.6611</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.0876</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -3918,20 +4776,20 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>95.23999999999999</v>
+        <v>62.11</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>47.62</v>
+        <v>31.06</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260325</t>
+          <t>20260326</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3941,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NYY vs SFG</t>
+          <t>PIT vs NYM</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Rafael Devers</t>
+          <t>Francisco Lindor</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -3955,37 +4813,31 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G10" t="n">
-        <v>144</v>
+        <v>-180.5</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4371</v>
+        <v>0.6811</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0544</v>
+        <v>0.0843</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>-100</v>
-      </c>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="n">
-        <v>-50</v>
-      </c>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260325</t>
+          <t>20260326</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3995,51 +4847,45 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SFG vs NYY</t>
+          <t>CIN vs BOS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Trent Grisham</t>
+          <t>Ceddanne Rafaela</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G11" t="n">
-        <v>-165</v>
+        <v>-178</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6313</v>
+        <v>0.6949</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0532</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>3</v>
-      </c>
-      <c r="L11" t="n">
-        <v>60.61</v>
-      </c>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="n">
-        <v>30.3</v>
-      </c>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260325</t>
+          <t>20260326</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4049,12 +4895,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SFG vs NYY</t>
+          <t>NYM vs PIT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ryan McMahon</t>
+          <t>Spencer Horwitz</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -4066,34 +4912,28 @@
         <v>0.5</v>
       </c>
       <c r="G12" t="n">
-        <v>-115</v>
+        <v>-126</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5377</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0426</v>
+        <v>0.0756</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>86.95999999999999</v>
-      </c>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="n">
-        <v>43.48</v>
-      </c>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260325</t>
+          <t>20260326</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4103,51 +4943,45 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SFG vs NYY</t>
+          <t>MIN vs BAL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Cody Bellinger</t>
+          <t>Gunnar Henderson</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>1.5</v>
       </c>
       <c r="G13" t="n">
-        <v>135</v>
+        <v>-125</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4371</v>
+        <v>0.5917</v>
       </c>
       <c r="I13" t="n">
-        <v>0.042</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>-100</v>
-      </c>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="n">
-        <v>-50</v>
-      </c>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260325</t>
+          <t>20260326</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4157,51 +4991,45 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NYY vs SFG</t>
+          <t>MIL vs CWS</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Harrison Bader</t>
+          <t>Miguel Vargas</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>0.5</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.5</v>
+        <v>-145</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4608</v>
+        <v>0.6219</v>
       </c>
       <c r="I14" t="n">
-        <v>0.42</v>
+        <v>0.0713</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>4000</v>
-      </c>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="n">
-        <v>2000</v>
-      </c>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260325</t>
+          <t>20260326</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4211,51 +5039,45 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SFG vs NYY</t>
+          <t>MIN vs BAL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Giancarlo Stanton</t>
+          <t>Samuel Basallo</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G15" t="n">
-        <v>-159</v>
+        <v>-185</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6656</v>
+        <v>0.6848</v>
       </c>
       <c r="I15" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.0808</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L15" t="n">
-        <v>62.89</v>
-      </c>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="n">
-        <v>31.45</v>
-      </c>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260325</t>
+          <t>20260326</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4265,12 +5087,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NYY vs SFG</t>
+          <t>CHC vs WSN</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Rafael Devers</t>
+          <t>CJ Abrams</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -4282,29 +5104,647 @@
         <v>0.5</v>
       </c>
       <c r="G16" t="n">
+        <v>-135.5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.6195000000000001</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.0832</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MIL vs CWS</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Andrew Benintendi</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-141.5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.6186</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.0741</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MIN vs BAL</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Tyler O'Neill</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-175</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.6989</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CHC vs WSN</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>James Wood</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G19" t="n">
         <v>-161</v>
       </c>
-      <c r="H16" t="n">
-        <v>0.6611</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.0876</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>62.11</v>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="n">
-        <v>31.06</v>
-      </c>
+      <c r="H19" t="n">
+        <v>0.6791</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.1056</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CWS vs MIL</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>David Hamilton</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-118</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.6207</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.1178</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>PIT vs NYM</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Juan Soto</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-153.5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.1028</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>MIN vs BAL</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Adley Rutschman</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-172</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.6712</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.0818</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CHC vs WSN</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Jacob Young</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.5992</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.1134</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>PIT vs NYM</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Jorge Polanco</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-141</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.1053</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>TBR vs STL</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Jordan Walker</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G25" t="n">
+        <v>128.5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.5208</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.1146</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>MIL vs CWS</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Colson Montgomery</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-134.5</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.6704</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.1361</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NYM vs PIT</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Jared Triolo</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.488</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.4119</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NYM vs PIT</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Brandon Lowe</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-150</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.6529</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BAL vs MIN</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Austin Martin</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-170</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.6679</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.08169999999999999</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4317,7 +5757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4459,30 +5899,30 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SFG vs NYY</t>
+          <t>NYY vs SFG</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Max Fried</t>
+          <t>Logan Webb</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>16.5</v>
       </c>
       <c r="G3" t="n">
-        <v>100</v>
+        <v>-1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.607</v>
+        <v>0.4107</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1454</v>
+        <v>0.394</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -4490,20 +5930,20 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="L3" t="n">
-        <v>100</v>
+        <v>10000</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>50</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260325</t>
+          <t>20260326</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4513,46 +5953,424 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NYY vs SFG</t>
+          <t>CWS vs MIL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Logan Webb</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-175</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.7971</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.2083</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BAL vs MIN</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Joe Ryan</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>145</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.7798</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.4004</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NYM vs PIT</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Paul Skenes</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-104.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.7044</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.2317</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>MIN vs BAL</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Trevor Rogers</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.7123</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.2247</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PIT vs NYM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>140.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.6554</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.2699</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CHC vs WSN</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Cade Cavalli</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="F9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G9" t="n">
         <v>-1</v>
       </c>
-      <c r="H4" t="n">
-        <v>0.4107</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.394</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>15</v>
-      </c>
-      <c r="L4" t="n">
-        <v>10000</v>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="n">
-        <v>5000</v>
-      </c>
+      <c r="H9" t="n">
+        <v>0.1997</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1827</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>STL vs TBR</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-167.5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.7352</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.1525</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>WSN vs CHC</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Matthew Boyd</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.6491</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1491</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>MIL vs CWS</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Shane Smith</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-155</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.7044</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.1431</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4565,7 +6383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4709,18 +6527,18 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>NRFI</t>
+          <t>YRFI</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>-157.5</v>
+        <v>120</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5764</v>
+        <v>0.5734</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -4735,7 +6553,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260325</t>
+          <t>20260326</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4745,12 +6563,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NYY @ SFG</t>
+          <t>PIT @ NYM</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NYY @ SFG</t>
+          <t>PIT @ NYM</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -4766,7 +6584,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5734</v>
+        <v>0.5746</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -4778,6 +6596,144 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CWS @ MIL</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CWS @ MIL</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>YRFI</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>-102</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.5314</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>MIN @ BAL</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MIN @ BAL</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>YRFI</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>-112</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.5061</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>WSN @ CHC</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>WSN @ CHC</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>YRFI</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>106</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.5887</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1338</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tracking/picks.xlsx
+++ b/tracking/picks.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N54"/>
+  <dimension ref="A1:N82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3091,6 +3091,1334 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>TEX @ PHI</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="n">
+        <v>-156.5</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.8207</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.2357</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>BOS @ CIN</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="n">
+        <v>135</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.6636</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.2548</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>DET @ SDP</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>SDP</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="n">
+        <v>107</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.5977</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.1335</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>LAA @ HOU</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LAA @ HOU</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>8</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-114</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.2154</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>DET @ SDP</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>DET @ SDP</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>7</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.7019</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.203</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>TEX @ PHI</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>TEX @ PHI</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>8</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-105</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.6418</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.1516</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>BOS @ CIN</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>BOS @ CIN</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>8</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.5835</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.0727</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>BOS @ CIN</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>BOS @ CIN</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>8</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-105</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.5555</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.0663</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>PHI vs TEX</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Wyatt Langford</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-20</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.6369</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.2456</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>CHC vs WSN</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Keibert Ruiz</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.5118</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.4948</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>BOS vs CIN</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Ke'Bryan Hayes</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G65" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.5485</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.1263</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>CIN vs BOS</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Isiah Kiner-Falefa</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G66" t="n">
+        <v>-185</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.7533</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.1467</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>PHI vs TEX</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Sam Haggerty</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G67" t="n">
+        <v>106</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.5615</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.1109</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>HOU vs LAA</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Oswald Peraza</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G68" t="n">
+        <v>-125</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.6553</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.1406</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>LAA vs HOU</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Jake Meyers</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G69" t="n">
+        <v>126.5</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.5076000000000001</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.0975</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>HOU vs LAA</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Zach Neto</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G70" t="n">
+        <v>-183.5</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.6847</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>DET vs SDP</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Manny Machado</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G71" t="n">
+        <v>-164.5</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.6501</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.0707</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>LAA vs HOU</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Yainer Diaz</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G72" t="n">
+        <v>-182</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.6797</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>DET vs SDP</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Nick Pivetta</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G73" t="n">
+        <v>-116.5</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.8866000000000001</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.3851</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>PHI vs TEX</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Nathan Eovaldi</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G74" t="n">
+        <v>-125</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.8067</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>BOS vs CIN</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Andrew Abbott</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G75" t="n">
+        <v>125</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.2242</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>CIN vs BOS</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Garrett Crochet</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G76" t="n">
+        <v>-125</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.6627999999999999</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>LAA vs HOU</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Hunter Brown</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G77" t="n">
+        <v>-110.5</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.6015</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>LAA @ HOU</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LAA @ HOU</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>YRFI</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="n">
+        <v>102</v>
+      </c>
+      <c r="H78" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.5347</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>CWS @ MIL</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>CWS @ MIL</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>NRFI</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="n">
+        <v>-129</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
+        <v>-0.5273</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>BOS @ CIN</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>BOS @ CIN</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>NRFI</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="n">
+        <v>-155</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.3829</v>
+      </c>
+      <c r="I80" t="n">
+        <v>-0.1836</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>DET @ SDP</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>DET @ SDP</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>YRFI</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="n">
+        <v>118</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.5887</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>TEX @ PHI</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>TEX @ PHI</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>YRFI</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="n">
+        <v>-106</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.5887</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0.1079</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3729,7 +5057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3941,6 +5269,144 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TEX @ PHI</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>-156.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.8207</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.2357</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BOS @ CIN</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>135</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.6636</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.2548</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DET @ SDP</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SDP</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>107</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.5977</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1335</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3953,7 +5419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4267,6 +5733,246 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>LAA @ HOU</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LAA @ HOU</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-114</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.2154</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DET @ SDP</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>DET @ SDP</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.7019</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.203</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>TEX @ PHI</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TEX @ PHI</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-105</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.6418</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1516</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BOS @ CIN</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>BOS @ CIN</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.5835</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.0727</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BOS @ CIN</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>BOS @ CIN</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>8</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-105</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.5555</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.0663</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4279,7 +5985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N29"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4799,30 +6505,30 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PIT vs NYM</t>
+          <t>MIN vs BAL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Francisco Lindor</t>
+          <t>Samuel Basallo</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G10" t="n">
-        <v>-180.5</v>
+        <v>-185</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6811</v>
+        <v>0.6848</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0843</v>
+        <v>0.0808</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -4847,12 +6553,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CIN vs BOS</t>
+          <t>MIN vs BAL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ceddanne Rafaela</t>
+          <t>Gunnar Henderson</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4864,13 +6570,13 @@
         <v>1.5</v>
       </c>
       <c r="G11" t="n">
-        <v>-178</v>
+        <v>-125</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6949</v>
+        <v>0.5917</v>
       </c>
       <c r="I11" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -4895,30 +6601,30 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NYM vs PIT</t>
+          <t>MIN vs BAL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Spencer Horwitz</t>
+          <t>Adley Rutschman</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G12" t="n">
-        <v>-126</v>
+        <v>-172</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5911999999999999</v>
+        <v>0.6712</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0756</v>
+        <v>0.0818</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -4943,12 +6649,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MIN vs BAL</t>
+          <t>BAL vs MIN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Gunnar Henderson</t>
+          <t>Austin Martin</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -4960,13 +6666,13 @@
         <v>1.5</v>
       </c>
       <c r="G13" t="n">
-        <v>-125</v>
+        <v>-170</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5917</v>
+        <v>0.6679</v>
       </c>
       <c r="I13" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -4991,12 +6697,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MIL vs CWS</t>
+          <t>PHI vs TEX</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Miguel Vargas</t>
+          <t>Wyatt Langford</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -5008,13 +6714,13 @@
         <v>0.5</v>
       </c>
       <c r="G14" t="n">
-        <v>-145</v>
+        <v>-20</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6219</v>
+        <v>0.6369</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0713</v>
+        <v>0.2456</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -5039,12 +6745,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MIN vs BAL</t>
+          <t>CHC vs WSN</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Samuel Basallo</t>
+          <t>Keibert Ruiz</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -5053,16 +6759,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G15" t="n">
-        <v>-185</v>
+        <v>-1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6848</v>
+        <v>0.5118</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0808</v>
+        <v>0.4948</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -5087,30 +6793,30 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CHC vs WSN</t>
+          <t>HOU vs LAA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CJ Abrams</t>
+          <t>Oswald Peraza</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>0.5</v>
       </c>
       <c r="G16" t="n">
-        <v>-135.5</v>
+        <v>-125</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6195000000000001</v>
+        <v>0.6553</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0832</v>
+        <v>0.1406</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -5135,30 +6841,30 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MIL vs CWS</t>
+          <t>CIN vs BOS</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Andrew Benintendi</t>
+          <t>Isiah Kiner-Falefa</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G17" t="n">
-        <v>-141.5</v>
+        <v>-185</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6186</v>
+        <v>0.7533</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0741</v>
+        <v>0.1467</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -5183,12 +6889,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MIN vs BAL</t>
+          <t>PHI vs TEX</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tyler O'Neill</t>
+          <t>Sam Haggerty</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -5197,16 +6903,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G18" t="n">
-        <v>-175</v>
+        <v>106</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6989</v>
+        <v>0.5615</v>
       </c>
       <c r="I18" t="n">
-        <v>0.108</v>
+        <v>0.1109</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -5231,12 +6937,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CHC vs WSN</t>
+          <t>MIL vs CWS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>James Wood</t>
+          <t>Miguel Vargas</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -5248,13 +6954,13 @@
         <v>0.5</v>
       </c>
       <c r="G19" t="n">
-        <v>-161</v>
+        <v>-145</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6791</v>
+        <v>0.6219</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1056</v>
+        <v>0.0713</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -5279,12 +6985,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CWS vs MIL</t>
+          <t>LAA vs HOU</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Jake Meyers</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -5296,13 +7002,13 @@
         <v>0.5</v>
       </c>
       <c r="G20" t="n">
-        <v>-118</v>
+        <v>126.5</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6207</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1178</v>
+        <v>0.0975</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -5327,12 +7033,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PIT vs NYM</t>
+          <t>HOU vs LAA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Juan Soto</t>
+          <t>Zach Neto</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -5344,13 +7050,13 @@
         <v>0.5</v>
       </c>
       <c r="G21" t="n">
-        <v>-153.5</v>
+        <v>-183.5</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6667</v>
+        <v>0.6847</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1028</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -5375,12 +7081,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MIN vs BAL</t>
+          <t>BOS vs CIN</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Adley Rutschman</t>
+          <t>Ke'Bryan Hayes</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -5389,16 +7095,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G22" t="n">
-        <v>-172</v>
+        <v>120.5</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6712</v>
+        <v>0.5485</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0818</v>
+        <v>0.1263</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -5423,30 +7129,30 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CHC vs WSN</t>
+          <t>MIL vs CWS</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Jacob Young</t>
+          <t>Andrew Benintendi</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>0.5</v>
       </c>
       <c r="G23" t="n">
-        <v>-110</v>
+        <v>-141.5</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5992</v>
+        <v>0.6186</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1134</v>
+        <v>0.0741</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -5471,12 +7177,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PIT vs NYM</t>
+          <t>CHC vs WSN</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Jorge Polanco</t>
+          <t>CJ Abrams</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -5488,13 +7194,13 @@
         <v>0.5</v>
       </c>
       <c r="G24" t="n">
-        <v>-141</v>
+        <v>-135.5</v>
       </c>
       <c r="H24" t="n">
-        <v>0.65</v>
+        <v>0.6195000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1053</v>
+        <v>0.0832</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -5519,12 +7225,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TBR vs STL</t>
+          <t>CIN vs BOS</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Jordan Walker</t>
+          <t>Ceddanne Rafaela</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -5533,16 +7239,16 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G25" t="n">
-        <v>128.5</v>
+        <v>-178</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5208</v>
+        <v>0.6949</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1146</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -5567,12 +7273,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MIL vs CWS</t>
+          <t>PIT vs NYM</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Colson Montgomery</t>
+          <t>Francisco Lindor</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -5584,13 +7290,13 @@
         <v>0.5</v>
       </c>
       <c r="G26" t="n">
-        <v>-134.5</v>
+        <v>-180.5</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6704</v>
+        <v>0.6811</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1361</v>
+        <v>0.0843</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -5615,30 +7321,30 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NYM vs PIT</t>
+          <t>DET vs SDP</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Jared Triolo</t>
+          <t>Manny Machado</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>0.5</v>
       </c>
       <c r="G27" t="n">
-        <v>-5</v>
+        <v>-164.5</v>
       </c>
       <c r="H27" t="n">
-        <v>0.488</v>
+        <v>0.6501</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4119</v>
+        <v>0.0707</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -5663,30 +7369,30 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NYM vs PIT</t>
+          <t>MIN vs BAL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Brandon Lowe</t>
+          <t>Tyler O'Neill</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G28" t="n">
-        <v>-150</v>
+        <v>-175</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6529</v>
+        <v>0.6989</v>
       </c>
       <c r="I28" t="n">
-        <v>0.096</v>
+        <v>0.108</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -5711,30 +7417,30 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BAL vs MIN</t>
+          <t>NYM vs PIT</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Austin Martin</t>
+          <t>Brandon Lowe</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G29" t="n">
-        <v>-170</v>
+        <v>-150</v>
       </c>
       <c r="H29" t="n">
-        <v>0.6679</v>
+        <v>0.6529</v>
       </c>
       <c r="I29" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.096</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -5745,6 +7451,486 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CWS vs MIL</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>David Hamilton</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-118</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.6207</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.1178</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PIT vs NYM</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Juan Soto</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-153.5</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.1028</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CHC vs WSN</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>James Wood</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-161</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.6791</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.1056</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CHC vs WSN</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Jacob Young</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.5992</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.1134</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>PIT vs NYM</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Jorge Polanco</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-141</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.1053</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>TBR vs STL</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Jordan Walker</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G35" t="n">
+        <v>128.5</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.5208</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.1146</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>MIL vs CWS</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Colson Montgomery</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-134.5</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.6704</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.1361</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>NYM vs PIT</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Jared Triolo</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.488</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.4119</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>NYM vs PIT</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Spencer Horwitz</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-126</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.5911999999999999</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.0756</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>LAA vs HOU</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Yainer Diaz</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-182</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.6797</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5757,7 +7943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6371,6 +8557,246 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DET vs SDP</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Nick Pivetta</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-116.5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.8866000000000001</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.3851</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PHI vs TEX</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Nathan Eovaldi</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-125</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.8067</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BOS vs CIN</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Andrew Abbott</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>125</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.2242</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CIN vs BOS</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Garrett Crochet</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-125</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.6627999999999999</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>LAA vs HOU</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Hunter Brown</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-110.5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.6015</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6383,7 +8809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6734,6 +9160,236 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>LAA @ HOU</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LAA @ HOU</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>YRFI</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>102</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.5347</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CWS @ MIL</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CWS @ MIL</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>NRFI</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>-129</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-0.5273</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BOS @ CIN</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>BOS @ CIN</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>NRFI</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>-155</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.3829</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.1836</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>DET @ SDP</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>DET @ SDP</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>YRFI</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>118</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.5887</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>TEX @ PHI</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TEX @ PHI</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>YRFI</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>-106</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.5887</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.1079</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tracking/picks.xlsx
+++ b/tracking/picks.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N82"/>
+  <dimension ref="A1:N92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4419,6 +4419,482 @@
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>TBR @ STL</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.6141</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>CWS @ MIL</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>CWS @ MIL</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G84" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0.7967</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.2967</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>TBR @ STL</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>TBR @ STL</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="G85" t="n">
+        <v>-105</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0.7002</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0.2111</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>STL vs TBR</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Nick Fortes</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G86" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0.5552</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>STL vs TBR</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Ben Williamson</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G87" t="n">
+        <v>-195.5</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0.7428</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.1248</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>STL vs TBR</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Carson Williams</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G88" t="n">
+        <v>110</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0.5195</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>SDP vs DET</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Spencer Torkelson</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G89" t="n">
+        <v>-145</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0.6225000000000001</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0.07190000000000001</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>BAL vs MIN</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Matt Wallner</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G90" t="n">
+        <v>-143.5</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0.6172</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.0706</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>TBR vs STL</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Matthew Liberatore</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G91" t="n">
+        <v>-183.5</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0.7463</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0.1529</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>TBR @ STL</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>TBR @ STL</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>YRFI</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="n">
+        <v>100</v>
+      </c>
+      <c r="H92" t="n">
+        <v>1</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0.5306</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5057,7 +5533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5407,6 +5883,52 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>TBR @ STL</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.6141</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5419,7 +5941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5973,6 +6495,102 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CWS @ MIL</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CWS @ MIL</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.7967</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.2967</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>TBR @ STL</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TBR @ STL</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-105</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.7002</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.2111</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5985,7 +6603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N39"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6505,12 +7123,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MIN vs BAL</t>
+          <t>BAL vs MIN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Samuel Basallo</t>
+          <t>Austin Martin</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -6522,13 +7140,13 @@
         <v>1.5</v>
       </c>
       <c r="G10" t="n">
-        <v>-185</v>
+        <v>-170</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6848</v>
+        <v>0.6679</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0808</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -6553,30 +7171,30 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MIN vs BAL</t>
+          <t>PHI vs TEX</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Gunnar Henderson</t>
+          <t>Wyatt Langford</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G11" t="n">
-        <v>-125</v>
+        <v>-20</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5917</v>
+        <v>0.6369</v>
       </c>
       <c r="I11" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.2456</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -6601,12 +7219,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MIN vs BAL</t>
+          <t>CHC vs WSN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Adley Rutschman</t>
+          <t>Keibert Ruiz</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -6615,16 +7233,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G12" t="n">
-        <v>-172</v>
+        <v>-1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6712</v>
+        <v>0.5118</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0818</v>
+        <v>0.4948</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -6649,12 +7267,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BAL vs MIN</t>
+          <t>BOS vs CIN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Austin Martin</t>
+          <t>Ke'Bryan Hayes</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6663,16 +7281,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G13" t="n">
-        <v>-170</v>
+        <v>120.5</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6679</v>
+        <v>0.5485</v>
       </c>
       <c r="I13" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.1263</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -6697,30 +7315,30 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PHI vs TEX</t>
+          <t>CIN vs BOS</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Wyatt Langford</t>
+          <t>Isiah Kiner-Falefa</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G14" t="n">
-        <v>-20</v>
+        <v>-185</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6369</v>
+        <v>0.7533</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2456</v>
+        <v>0.1467</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -6745,12 +7363,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CHC vs WSN</t>
+          <t>PHI vs TEX</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Keibert Ruiz</t>
+          <t>Sam Haggerty</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6762,13 +7380,13 @@
         <v>0.5</v>
       </c>
       <c r="G15" t="n">
-        <v>-1</v>
+        <v>106</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5118</v>
+        <v>0.5615</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4948</v>
+        <v>0.1109</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -6841,12 +7459,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CIN vs BOS</t>
+          <t>LAA vs HOU</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Isiah Kiner-Falefa</t>
+          <t>Yainer Diaz</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -6858,13 +7476,13 @@
         <v>1.5</v>
       </c>
       <c r="G17" t="n">
-        <v>-185</v>
+        <v>-182</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7533</v>
+        <v>0.6797</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1467</v>
+        <v>0.077</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -6889,30 +7507,30 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PHI vs TEX</t>
+          <t>HOU vs LAA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sam Haggerty</t>
+          <t>Zach Neto</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>0.5</v>
       </c>
       <c r="G18" t="n">
-        <v>106</v>
+        <v>-183.5</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5615</v>
+        <v>0.6847</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1109</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -6937,12 +7555,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MIL vs CWS</t>
+          <t>DET vs SDP</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Miguel Vargas</t>
+          <t>Manny Machado</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -6954,13 +7572,13 @@
         <v>0.5</v>
       </c>
       <c r="G19" t="n">
-        <v>-145</v>
+        <v>-164.5</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6219</v>
+        <v>0.6501</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0713</v>
+        <v>0.0707</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -6985,12 +7603,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LAA vs HOU</t>
+          <t>MIN vs BAL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Jake Meyers</t>
+          <t>Adley Rutschman</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -6999,16 +7617,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G20" t="n">
-        <v>126.5</v>
+        <v>-172</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.6712</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0975</v>
+        <v>0.0818</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -7033,30 +7651,30 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HOU vs LAA</t>
+          <t>STL vs TBR</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Zach Neto</t>
+          <t>Nick Fortes</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>0.5</v>
       </c>
       <c r="G21" t="n">
-        <v>-183.5</v>
+        <v>119.5</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6847</v>
+        <v>0.5552</v>
       </c>
       <c r="I21" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.131</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -7081,12 +7699,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BOS vs CIN</t>
+          <t>STL vs TBR</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ke'Bryan Hayes</t>
+          <t>Ben Williamson</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -7095,16 +7713,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G22" t="n">
-        <v>120.5</v>
+        <v>-195.5</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5485</v>
+        <v>0.7428</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1263</v>
+        <v>0.1248</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -7129,30 +7747,30 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MIL vs CWS</t>
+          <t>STL vs TBR</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Andrew Benintendi</t>
+          <t>Carson Williams</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>0.5</v>
       </c>
       <c r="G23" t="n">
-        <v>-141.5</v>
+        <v>110</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6186</v>
+        <v>0.5195</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0741</v>
+        <v>0.077</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -7177,30 +7795,30 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CHC vs WSN</t>
+          <t>LAA vs HOU</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CJ Abrams</t>
+          <t>Jake Meyers</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>0.5</v>
       </c>
       <c r="G24" t="n">
-        <v>-135.5</v>
+        <v>126.5</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6195000000000001</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0832</v>
+        <v>0.0975</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -7225,12 +7843,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CIN vs BOS</t>
+          <t>MIN vs BAL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ceddanne Rafaela</t>
+          <t>Gunnar Henderson</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -7242,13 +7860,13 @@
         <v>1.5</v>
       </c>
       <c r="G25" t="n">
-        <v>-178</v>
+        <v>-125</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6949</v>
+        <v>0.5917</v>
       </c>
       <c r="I25" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -7273,12 +7891,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PIT vs NYM</t>
+          <t>NYM vs PIT</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Francisco Lindor</t>
+          <t>Spencer Horwitz</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -7290,13 +7908,13 @@
         <v>0.5</v>
       </c>
       <c r="G26" t="n">
-        <v>-180.5</v>
+        <v>-126</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6811</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0843</v>
+        <v>0.0756</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -7321,12 +7939,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DET vs SDP</t>
+          <t>MIL vs CWS</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Manny Machado</t>
+          <t>Miguel Vargas</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -7338,13 +7956,13 @@
         <v>0.5</v>
       </c>
       <c r="G27" t="n">
-        <v>-164.5</v>
+        <v>-145</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6501</v>
+        <v>0.6219</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0707</v>
+        <v>0.0713</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -7369,12 +7987,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MIN vs BAL</t>
+          <t>NYM vs PIT</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Tyler O'Neill</t>
+          <t>Jared Triolo</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -7383,16 +8001,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G28" t="n">
-        <v>-175</v>
+        <v>-5</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6989</v>
+        <v>0.488</v>
       </c>
       <c r="I28" t="n">
-        <v>0.108</v>
+        <v>0.4119</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -7417,12 +8035,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NYM vs PIT</t>
+          <t>MIL vs CWS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Brandon Lowe</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -7434,13 +8052,13 @@
         <v>0.5</v>
       </c>
       <c r="G29" t="n">
-        <v>-150</v>
+        <v>-134.5</v>
       </c>
       <c r="H29" t="n">
-        <v>0.6529</v>
+        <v>0.6704</v>
       </c>
       <c r="I29" t="n">
-        <v>0.096</v>
+        <v>0.1361</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -7465,12 +8083,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CWS vs MIL</t>
+          <t>TBR vs STL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Jordan Walker</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -7482,13 +8100,13 @@
         <v>0.5</v>
       </c>
       <c r="G30" t="n">
-        <v>-118</v>
+        <v>128.5</v>
       </c>
       <c r="H30" t="n">
-        <v>0.6207</v>
+        <v>0.5208</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1178</v>
+        <v>0.1146</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -7518,7 +8136,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Juan Soto</t>
+          <t>Jorge Polanco</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -7530,13 +8148,13 @@
         <v>0.5</v>
       </c>
       <c r="G31" t="n">
-        <v>-153.5</v>
+        <v>-141</v>
       </c>
       <c r="H31" t="n">
-        <v>0.6667</v>
+        <v>0.65</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1028</v>
+        <v>0.1053</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -7566,25 +8184,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>James Wood</t>
+          <t>Jacob Young</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>0.5</v>
       </c>
       <c r="G32" t="n">
-        <v>-161</v>
+        <v>-110</v>
       </c>
       <c r="H32" t="n">
-        <v>0.6791</v>
+        <v>0.5992</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1056</v>
+        <v>0.1134</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -7614,25 +8232,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Jacob Young</t>
+          <t>James Wood</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>0.5</v>
       </c>
       <c r="G33" t="n">
-        <v>-110</v>
+        <v>-161</v>
       </c>
       <c r="H33" t="n">
-        <v>0.5992</v>
+        <v>0.6791</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1134</v>
+        <v>0.1056</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -7662,7 +8280,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Jorge Polanco</t>
+          <t>Juan Soto</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -7674,13 +8292,13 @@
         <v>0.5</v>
       </c>
       <c r="G34" t="n">
-        <v>-141</v>
+        <v>-153.5</v>
       </c>
       <c r="H34" t="n">
-        <v>0.65</v>
+        <v>0.6667</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1053</v>
+        <v>0.1028</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -7705,12 +8323,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>TBR vs STL</t>
+          <t>CWS vs MIL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Jordan Walker</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -7722,13 +8340,13 @@
         <v>0.5</v>
       </c>
       <c r="G35" t="n">
-        <v>128.5</v>
+        <v>-118</v>
       </c>
       <c r="H35" t="n">
-        <v>0.5208</v>
+        <v>0.6207</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1146</v>
+        <v>0.1178</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -7753,12 +8371,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MIL vs CWS</t>
+          <t>NYM vs PIT</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Colson Montgomery</t>
+          <t>Brandon Lowe</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -7770,13 +8388,13 @@
         <v>0.5</v>
       </c>
       <c r="G36" t="n">
-        <v>-134.5</v>
+        <v>-150</v>
       </c>
       <c r="H36" t="n">
-        <v>0.6704</v>
+        <v>0.6529</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1361</v>
+        <v>0.096</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -7801,12 +8419,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NYM vs PIT</t>
+          <t>MIN vs BAL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Jared Triolo</t>
+          <t>Tyler O'Neill</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -7815,16 +8433,16 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G37" t="n">
-        <v>-5</v>
+        <v>-175</v>
       </c>
       <c r="H37" t="n">
-        <v>0.488</v>
+        <v>0.6989</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4119</v>
+        <v>0.108</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -7849,12 +8467,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NYM vs PIT</t>
+          <t>CHC vs WSN</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Spencer Horwitz</t>
+          <t>CJ Abrams</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -7866,13 +8484,13 @@
         <v>0.5</v>
       </c>
       <c r="G38" t="n">
-        <v>-126</v>
+        <v>-135.5</v>
       </c>
       <c r="H38" t="n">
-        <v>0.5911999999999999</v>
+        <v>0.6195000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0756</v>
+        <v>0.0832</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -7897,30 +8515,30 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>LAA vs HOU</t>
+          <t>PIT vs NYM</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Yainer Diaz</t>
+          <t>Francisco Lindor</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G39" t="n">
-        <v>-182</v>
+        <v>-180.5</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6797</v>
+        <v>0.6811</v>
       </c>
       <c r="I39" t="n">
-        <v>0.077</v>
+        <v>0.0843</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -7931,6 +8549,246 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CIN vs BOS</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Ceddanne Rafaela</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-178</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.6949</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.09719999999999999</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>SDP vs DET</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Spencer Torkelson</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-145</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.6225000000000001</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.07190000000000001</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>MIL vs CWS</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Andrew Benintendi</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-141.5</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.6186</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.0741</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>MIN vs BAL</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Samuel Basallo</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-185</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.6848</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.0808</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>BAL vs MIN</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Matt Wallner</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-143.5</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.6172</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.0706</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7943,7 +8801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8139,12 +8997,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CWS vs MIL</t>
+          <t>CIN vs BOS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Garrett Crochet</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -8153,16 +9011,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="G4" t="n">
-        <v>-175</v>
+        <v>-125</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7971</v>
+        <v>0.6627999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2083</v>
+        <v>0.147</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -8187,12 +9045,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BAL vs MIN</t>
+          <t>BOS vs CIN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Joe Ryan</t>
+          <t>Andrew Abbott</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -8204,13 +9062,13 @@
         <v>15.5</v>
       </c>
       <c r="G5" t="n">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7798</v>
+        <v>0.632</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4004</v>
+        <v>0.2242</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -8235,12 +9093,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NYM vs PIT</t>
+          <t>PHI vs TEX</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Paul Skenes</t>
+          <t>Nathan Eovaldi</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -8249,16 +9107,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="G6" t="n">
-        <v>-104.5</v>
+        <v>-125</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7044</v>
+        <v>0.8067</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2317</v>
+        <v>0.2972</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -8283,12 +9141,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MIN vs BAL</t>
+          <t>DET vs SDP</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Trevor Rogers</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -8297,16 +9155,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="G7" t="n">
-        <v>-110</v>
+        <v>-116.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7123</v>
+        <v>0.8866000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2247</v>
+        <v>0.3851</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -8331,12 +9189,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PIT vs NYM</t>
+          <t>MIL vs CWS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Shane Smith</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -8345,16 +9203,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="G8" t="n">
-        <v>140.5</v>
+        <v>-155</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6554</v>
+        <v>0.7044</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2699</v>
+        <v>0.1431</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -8379,30 +9237,30 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CHC vs WSN</t>
+          <t>WSN vs CHC</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Cade Cavalli</t>
+          <t>Matthew Boyd</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="G9" t="n">
-        <v>-1</v>
+        <v>-115</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1997</v>
+        <v>0.6491</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1827</v>
+        <v>0.1491</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -8475,30 +9333,30 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>WSN vs CHC</t>
+          <t>CHC vs WSN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Matthew Boyd</t>
+          <t>Cade Cavalli</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="G11" t="n">
-        <v>-115</v>
+        <v>-1</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6491</v>
+        <v>0.1997</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1491</v>
+        <v>0.1827</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -8523,12 +9381,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MIL vs CWS</t>
+          <t>PIT vs NYM</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Shane Smith</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -8537,16 +9395,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="G12" t="n">
-        <v>-155</v>
+        <v>140.5</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7044</v>
+        <v>0.6554</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1431</v>
+        <v>0.2699</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -8571,12 +9429,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DET vs SDP</t>
+          <t>MIN vs BAL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Nick Pivetta</t>
+          <t>Trevor Rogers</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -8585,16 +9443,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="G13" t="n">
-        <v>-116.5</v>
+        <v>-110</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8866000000000001</v>
+        <v>0.7123</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3851</v>
+        <v>0.2247</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -8619,12 +9477,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PHI vs TEX</t>
+          <t>NYM vs PIT</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Nathan Eovaldi</t>
+          <t>Paul Skenes</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -8633,16 +9491,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="G14" t="n">
-        <v>-125</v>
+        <v>-104.5</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8067</v>
+        <v>0.7044</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2972</v>
+        <v>0.2317</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -8667,12 +9525,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BOS vs CIN</t>
+          <t>BAL vs MIN</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Andrew Abbott</t>
+          <t>Joe Ryan</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -8684,13 +9542,13 @@
         <v>15.5</v>
       </c>
       <c r="G15" t="n">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="H15" t="n">
-        <v>0.632</v>
+        <v>0.7798</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2242</v>
+        <v>0.4004</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -8715,12 +9573,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CIN vs BOS</t>
+          <t>CWS vs MIL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Garrett Crochet</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -8729,16 +9587,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="G16" t="n">
-        <v>-125</v>
+        <v>-175</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6627999999999999</v>
+        <v>0.7971</v>
       </c>
       <c r="I16" t="n">
-        <v>0.147</v>
+        <v>0.2083</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -8797,6 +9655,54 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>TBR vs STL</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Matthew Liberatore</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-183.5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.7463</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.1529</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8809,7 +9715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9390,6 +10296,52 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>TBR @ STL</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TBR @ STL</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>YRFI</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="n">
+        <v>100</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.5306</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tracking/picks.xlsx
+++ b/tracking/picks.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N92"/>
+  <dimension ref="A1:N96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4895,6 +4895,196 @@
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>TBR @ STL</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>TBR @ STL</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>8</v>
+      </c>
+      <c r="G93" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0.7002</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0.1997</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>TBR vs STL</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Masyn Winn</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G94" t="n">
+        <v>-20</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0.5832000000000001</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>CHC vs WSN</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Cade Cavalli</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G95" t="n">
+        <v>-140.5</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0.8003</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0.4224</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>DET @ SDP</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>DET @ SDP</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>NRFI</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="n">
+        <v>-162</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0.4113</v>
+      </c>
+      <c r="I96" t="n">
+        <v>-0.1628</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5941,7 +6131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6591,6 +6781,54 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>TBR @ STL</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TBR @ STL</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>8</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.7002</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.1997</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6603,7 +6841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:N45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7795,30 +8033,30 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>LAA vs HOU</t>
+          <t>SDP vs DET</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Jake Meyers</t>
+          <t>Spencer Torkelson</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>0.5</v>
       </c>
       <c r="G24" t="n">
-        <v>126.5</v>
+        <v>-145</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0975</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -7843,12 +8081,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MIN vs BAL</t>
+          <t>LAA vs HOU</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Gunnar Henderson</t>
+          <t>Jake Meyers</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -7857,16 +8095,16 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G25" t="n">
-        <v>-125</v>
+        <v>126.5</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5917</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.0975</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -7891,30 +8129,30 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NYM vs PIT</t>
+          <t>MIN vs BAL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Spencer Horwitz</t>
+          <t>Gunnar Henderson</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G26" t="n">
-        <v>-126</v>
+        <v>-125</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5911999999999999</v>
+        <v>0.5917</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0756</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -7939,12 +8177,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MIL vs CWS</t>
+          <t>NYM vs PIT</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Miguel Vargas</t>
+          <t>Spencer Horwitz</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -7956,13 +8194,13 @@
         <v>0.5</v>
       </c>
       <c r="G27" t="n">
-        <v>-145</v>
+        <v>-126</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6219</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0713</v>
+        <v>0.0756</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -7987,30 +8225,30 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NYM vs PIT</t>
+          <t>MIL vs CWS</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Jared Triolo</t>
+          <t>Miguel Vargas</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>0.5</v>
       </c>
       <c r="G28" t="n">
-        <v>-5</v>
+        <v>-145</v>
       </c>
       <c r="H28" t="n">
-        <v>0.488</v>
+        <v>0.6219</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4119</v>
+        <v>0.0713</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -8035,30 +8273,30 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MIL vs CWS</t>
+          <t>NYM vs PIT</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Colson Montgomery</t>
+          <t>Jared Triolo</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>0.5</v>
       </c>
       <c r="G29" t="n">
-        <v>-134.5</v>
+        <v>-5</v>
       </c>
       <c r="H29" t="n">
-        <v>0.6704</v>
+        <v>0.488</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1361</v>
+        <v>0.4119</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -8083,30 +8321,30 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>TBR vs STL</t>
+          <t>MIL vs CWS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Jordan Walker</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>0.5</v>
       </c>
       <c r="G30" t="n">
-        <v>128.5</v>
+        <v>-134.5</v>
       </c>
       <c r="H30" t="n">
-        <v>0.5208</v>
+        <v>0.6704</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1146</v>
+        <v>0.1361</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -8131,30 +8369,30 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PIT vs NYM</t>
+          <t>TBR vs STL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Jorge Polanco</t>
+          <t>Jordan Walker</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>0.5</v>
       </c>
       <c r="G31" t="n">
-        <v>-141</v>
+        <v>128.5</v>
       </c>
       <c r="H31" t="n">
-        <v>0.65</v>
+        <v>0.5208</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1053</v>
+        <v>0.1146</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -8179,30 +8417,30 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CHC vs WSN</t>
+          <t>PIT vs NYM</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Jacob Young</t>
+          <t>Jorge Polanco</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>0.5</v>
       </c>
       <c r="G32" t="n">
-        <v>-110</v>
+        <v>-141</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5992</v>
+        <v>0.65</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1134</v>
+        <v>0.1053</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -8232,25 +8470,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>James Wood</t>
+          <t>Jacob Young</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>0.5</v>
       </c>
       <c r="G33" t="n">
-        <v>-161</v>
+        <v>-110</v>
       </c>
       <c r="H33" t="n">
-        <v>0.6791</v>
+        <v>0.5992</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1056</v>
+        <v>0.1134</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -8275,12 +8513,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>PIT vs NYM</t>
+          <t>CHC vs WSN</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Juan Soto</t>
+          <t>James Wood</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -8292,13 +8530,13 @@
         <v>0.5</v>
       </c>
       <c r="G34" t="n">
-        <v>-153.5</v>
+        <v>-161</v>
       </c>
       <c r="H34" t="n">
-        <v>0.6667</v>
+        <v>0.6791</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1028</v>
+        <v>0.1056</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -8323,30 +8561,30 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CWS vs MIL</t>
+          <t>PIT vs NYM</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Juan Soto</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>0.5</v>
       </c>
       <c r="G35" t="n">
-        <v>-118</v>
+        <v>-153.5</v>
       </c>
       <c r="H35" t="n">
-        <v>0.6207</v>
+        <v>0.6667</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1178</v>
+        <v>0.1028</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -8371,30 +8609,30 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NYM vs PIT</t>
+          <t>CWS vs MIL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Brandon Lowe</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>0.5</v>
       </c>
       <c r="G36" t="n">
-        <v>-150</v>
+        <v>-118</v>
       </c>
       <c r="H36" t="n">
-        <v>0.6529</v>
+        <v>0.6207</v>
       </c>
       <c r="I36" t="n">
-        <v>0.096</v>
+        <v>0.1178</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -8419,30 +8657,30 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MIN vs BAL</t>
+          <t>NYM vs PIT</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Tyler O'Neill</t>
+          <t>Brandon Lowe</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G37" t="n">
-        <v>-175</v>
+        <v>-150</v>
       </c>
       <c r="H37" t="n">
-        <v>0.6989</v>
+        <v>0.6529</v>
       </c>
       <c r="I37" t="n">
-        <v>0.108</v>
+        <v>0.096</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -8467,30 +8705,30 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CHC vs WSN</t>
+          <t>MIN vs BAL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CJ Abrams</t>
+          <t>Tyler O'Neill</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G38" t="n">
-        <v>-135.5</v>
+        <v>-175</v>
       </c>
       <c r="H38" t="n">
-        <v>0.6195000000000001</v>
+        <v>0.6989</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0832</v>
+        <v>0.108</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -8515,12 +8753,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PIT vs NYM</t>
+          <t>CHC vs WSN</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Francisco Lindor</t>
+          <t>CJ Abrams</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -8532,13 +8770,13 @@
         <v>0.5</v>
       </c>
       <c r="G39" t="n">
-        <v>-180.5</v>
+        <v>-135.5</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6811</v>
+        <v>0.6195000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0843</v>
+        <v>0.0832</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -8563,30 +8801,30 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CIN vs BOS</t>
+          <t>PIT vs NYM</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ceddanne Rafaela</t>
+          <t>Francisco Lindor</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G40" t="n">
-        <v>-178</v>
+        <v>-180.5</v>
       </c>
       <c r="H40" t="n">
-        <v>0.6949</v>
+        <v>0.6811</v>
       </c>
       <c r="I40" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.0843</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -8611,30 +8849,30 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SDP vs DET</t>
+          <t>CIN vs BOS</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Spencer Torkelson</t>
+          <t>Ceddanne Rafaela</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G41" t="n">
-        <v>-145</v>
+        <v>-178</v>
       </c>
       <c r="H41" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.6949</v>
       </c>
       <c r="I41" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -8659,12 +8897,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MIL vs CWS</t>
+          <t>BAL vs MIN</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Andrew Benintendi</t>
+          <t>Matt Wallner</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -8676,13 +8914,13 @@
         <v>0.5</v>
       </c>
       <c r="G42" t="n">
-        <v>-141.5</v>
+        <v>-143.5</v>
       </c>
       <c r="H42" t="n">
-        <v>0.6186</v>
+        <v>0.6172</v>
       </c>
       <c r="I42" t="n">
-        <v>0.0741</v>
+        <v>0.0706</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -8707,30 +8945,30 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MIN vs BAL</t>
+          <t>MIL vs CWS</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Samuel Basallo</t>
+          <t>Andrew Benintendi</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G43" t="n">
-        <v>-185</v>
+        <v>-141.5</v>
       </c>
       <c r="H43" t="n">
-        <v>0.6848</v>
+        <v>0.6186</v>
       </c>
       <c r="I43" t="n">
-        <v>0.0808</v>
+        <v>0.0741</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -8755,30 +8993,30 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>BAL vs MIN</t>
+          <t>MIN vs BAL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Matt Wallner</t>
+          <t>Samuel Basallo</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G44" t="n">
-        <v>-143.5</v>
+        <v>-185</v>
       </c>
       <c r="H44" t="n">
-        <v>0.6172</v>
+        <v>0.6848</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0706</v>
+        <v>0.0808</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -8789,6 +9027,54 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>TBR vs STL</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Masyn Winn</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-20</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.5832000000000001</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8801,7 +9087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8997,12 +9283,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CIN vs BOS</t>
+          <t>LAA vs HOU</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Garrett Crochet</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -9014,13 +9300,13 @@
         <v>17.5</v>
       </c>
       <c r="G4" t="n">
-        <v>-125</v>
+        <v>-110.5</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6627999999999999</v>
+        <v>0.6015</v>
       </c>
       <c r="I4" t="n">
-        <v>0.147</v>
+        <v>0.112</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -9045,12 +9331,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BOS vs CIN</t>
+          <t>CIN vs BOS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Andrew Abbott</t>
+          <t>Garrett Crochet</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -9059,16 +9345,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="G5" t="n">
-        <v>125</v>
+        <v>-125</v>
       </c>
       <c r="H5" t="n">
-        <v>0.632</v>
+        <v>0.6627999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2242</v>
+        <v>0.147</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -9093,12 +9379,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PHI vs TEX</t>
+          <t>BOS vs CIN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Nathan Eovaldi</t>
+          <t>Andrew Abbott</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -9107,16 +9393,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="G6" t="n">
-        <v>-125</v>
+        <v>125</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8067</v>
+        <v>0.632</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2972</v>
+        <v>0.2242</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -9141,12 +9427,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DET vs SDP</t>
+          <t>PHI vs TEX</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Nick Pivetta</t>
+          <t>Nathan Eovaldi</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -9155,16 +9441,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="G7" t="n">
-        <v>-116.5</v>
+        <v>-125</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8866000000000001</v>
+        <v>0.8067</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3851</v>
+        <v>0.2972</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -9189,12 +9475,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MIL vs CWS</t>
+          <t>DET vs SDP</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Shane Smith</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -9203,16 +9489,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="G8" t="n">
-        <v>-155</v>
+        <v>-116.5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7044</v>
+        <v>0.8866000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1431</v>
+        <v>0.3851</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -9237,12 +9523,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>WSN vs CHC</t>
+          <t>MIL vs CWS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Matthew Boyd</t>
+          <t>Shane Smith</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -9251,16 +9537,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="G9" t="n">
-        <v>-115</v>
+        <v>-155</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6491</v>
+        <v>0.7044</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1491</v>
+        <v>0.1431</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -9285,12 +9571,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>STL vs TBR</t>
+          <t>WSN vs CHC</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Matthew Boyd</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -9299,16 +9585,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="G10" t="n">
-        <v>-167.5</v>
+        <v>-115</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7352</v>
+        <v>0.6491</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1525</v>
+        <v>0.1491</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -9333,30 +9619,30 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CHC vs WSN</t>
+          <t>STL vs TBR</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Cade Cavalli</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>14.5</v>
       </c>
       <c r="G11" t="n">
-        <v>-1</v>
+        <v>-167.5</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1997</v>
+        <v>0.7352</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1827</v>
+        <v>0.1525</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -9381,30 +9667,30 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PIT vs NYM</t>
+          <t>CHC vs WSN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Cade Cavalli</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="G12" t="n">
-        <v>140.5</v>
+        <v>-1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6554</v>
+        <v>0.1997</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2699</v>
+        <v>0.1827</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -9429,12 +9715,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MIN vs BAL</t>
+          <t>PIT vs NYM</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Trevor Rogers</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -9443,16 +9729,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="G13" t="n">
-        <v>-110</v>
+        <v>140.5</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7123</v>
+        <v>0.6554</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2247</v>
+        <v>0.2699</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -9477,12 +9763,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NYM vs PIT</t>
+          <t>MIN vs BAL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Paul Skenes</t>
+          <t>Trevor Rogers</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -9491,16 +9777,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="G14" t="n">
-        <v>-104.5</v>
+        <v>-110</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7044</v>
+        <v>0.7123</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2317</v>
+        <v>0.2247</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -9525,12 +9811,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BAL vs MIN</t>
+          <t>NYM vs PIT</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Joe Ryan</t>
+          <t>Paul Skenes</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -9542,13 +9828,13 @@
         <v>15.5</v>
       </c>
       <c r="G15" t="n">
-        <v>145</v>
+        <v>-104.5</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7798</v>
+        <v>0.7044</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4004</v>
+        <v>0.2317</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -9573,12 +9859,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CWS vs MIL</t>
+          <t>BAL vs MIN</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Joe Ryan</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -9587,16 +9873,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="G16" t="n">
-        <v>-175</v>
+        <v>145</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7971</v>
+        <v>0.7798</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2083</v>
+        <v>0.4004</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -9621,12 +9907,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LAA vs HOU</t>
+          <t>CWS vs MIL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -9635,16 +9921,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="G17" t="n">
-        <v>-110.5</v>
+        <v>-175</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6015</v>
+        <v>0.7971</v>
       </c>
       <c r="I17" t="n">
-        <v>0.112</v>
+        <v>0.2083</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -9703,6 +9989,54 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CHC vs WSN</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Cade Cavalli</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-140.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.8003</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.4224</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9715,7 +10049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10342,6 +10676,52 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DET @ SDP</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>DET @ SDP</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>NRFI</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>-162</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.4113</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-0.1628</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tracking/picks.xlsx
+++ b/tracking/picks.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N96"/>
+  <dimension ref="A1:N118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5085,6 +5085,1054 @@
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>ARI @ LAD</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>ARI</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="n">
+        <v>217.5</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0.3725</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0.07049999999999999</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>CLE @ SEA</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>CLE @ SEA</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G98" t="n">
+        <v>-121.5</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0.8472</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>ARI @ LAD</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>ARI @ LAD</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>9</v>
+      </c>
+      <c r="G99" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0.6322</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0.1214</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>MIN vs BAL</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Colton Cowser</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G100" t="n">
+        <v>250</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0.5614</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0.2085</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>BAL vs MIN</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Royce Lewis</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G101" t="n">
+        <v>-50</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0.4602</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0.2055</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>CLE vs SEA</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Cal Raleigh</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G102" t="n">
+        <v>-147.5</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0.7043</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>BAL vs MIN</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Josh Bell</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G103" t="n">
+        <v>-52.5</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0.4279</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0.1718</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>MIN vs BAL</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Gunnar Henderson</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G104" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0.4083</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>SEA vs CLE</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Kyle Manzardo</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G105" t="n">
+        <v>-108</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0.6057</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0.1269</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>LAD vs ARI</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Pavin Smith</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G106" t="n">
+        <v>101</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0.5637</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0.1034</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>CLE vs SEA</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Randy Arozarena</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G107" t="n">
+        <v>-124</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0.6155</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0.1069</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>SEA vs CLE</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Rhys Hoskins</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G108" t="n">
+        <v>100</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0.5556</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>SEA vs CLE</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Gabriel Arias</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G109" t="n">
+        <v>115</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0.5197000000000001</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>ARI vs LAD</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Miguel Rojas</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G110" t="n">
+        <v>113</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0.5123</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0.0765</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>CLE vs SEA</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Dominic Canzone</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G111" t="n">
+        <v>-118</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0.5725</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0.0725</v>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>LAA vs HOU</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Yordan Alvarez</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G112" t="n">
+        <v>-138</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0.6188</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>LAD vs ARI</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Zac Gallen</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G113" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0.3257</v>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>ARI vs LAD</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Yoshinobu Yamamoto</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G114" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0.2304</v>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>CIN vs BOS</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Garrett Crochet</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G115" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0.2589</v>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>PIT @ NYM</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>PIT @ NYM</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>NRFI</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="n">
+        <v>-162</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" t="n">
+        <v>-0.5818</v>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>ARI @ LAD</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>ARI @ LAD</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>YRFI</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="n">
+        <v>-119</v>
+      </c>
+      <c r="H117" t="n">
+        <v>1</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.4875</v>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>CLE @ SEA</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>CLE @ SEA</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>NRFI</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="n">
+        <v>-155</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.4113</v>
+      </c>
+      <c r="I118" t="n">
+        <v>-0.1552</v>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5723,7 +6771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6119,6 +7167,52 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ARI @ LAD</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ARI</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>217.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.3725</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.07049999999999999</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6131,7 +7225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6829,6 +7923,102 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLE @ SEA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CLE @ SEA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-121.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.8472</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ARI @ LAD</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ARI @ LAD</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>9</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.6322</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.1214</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6841,7 +8031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N45"/>
+  <dimension ref="A1:N58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7361,30 +8551,30 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BAL vs MIN</t>
+          <t>SDP vs DET</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Austin Martin</t>
+          <t>Spencer Torkelson</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G10" t="n">
-        <v>-170</v>
+        <v>-145</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6679</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -7409,30 +8599,30 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PHI vs TEX</t>
+          <t>STL vs TBR</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Wyatt Langford</t>
+          <t>Carson Williams</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>0.5</v>
       </c>
       <c r="G11" t="n">
-        <v>-20</v>
+        <v>110</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6369</v>
+        <v>0.5195</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2456</v>
+        <v>0.077</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -7457,12 +8647,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CHC vs WSN</t>
+          <t>STL vs TBR</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Keibert Ruiz</t>
+          <t>Ben Williamson</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -7471,16 +8661,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G12" t="n">
-        <v>-1</v>
+        <v>-195.5</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5118</v>
+        <v>0.7428</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4948</v>
+        <v>0.1248</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -7505,12 +8695,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BOS vs CIN</t>
+          <t>STL vs TBR</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ke'Bryan Hayes</t>
+          <t>Nick Fortes</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -7522,13 +8712,13 @@
         <v>0.5</v>
       </c>
       <c r="G13" t="n">
-        <v>120.5</v>
+        <v>119.5</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5485</v>
+        <v>0.5552</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1263</v>
+        <v>0.131</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -7553,12 +8743,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CIN vs BOS</t>
+          <t>LAA vs HOU</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Isiah Kiner-Falefa</t>
+          <t>Jake Meyers</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -7567,16 +8757,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G14" t="n">
-        <v>-185</v>
+        <v>126.5</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7533</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1467</v>
+        <v>0.0975</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -7601,30 +8791,30 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PHI vs TEX</t>
+          <t>DET vs SDP</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sam Haggerty</t>
+          <t>Manny Machado</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>0.5</v>
       </c>
       <c r="G15" t="n">
-        <v>106</v>
+        <v>-164.5</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5615</v>
+        <v>0.6501</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1109</v>
+        <v>0.0707</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -7654,25 +8844,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Oswald Peraza</t>
+          <t>Zach Neto</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>0.5</v>
       </c>
       <c r="G16" t="n">
-        <v>-125</v>
+        <v>-183.5</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6553</v>
+        <v>0.6847</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1406</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -7697,30 +8887,30 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LAA vs HOU</t>
+          <t>BAL vs MIN</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Yainer Diaz</t>
+          <t>Matt Wallner</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G17" t="n">
-        <v>-182</v>
+        <v>-143.5</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6797</v>
+        <v>0.6172</v>
       </c>
       <c r="I17" t="n">
-        <v>0.077</v>
+        <v>0.0706</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -7745,30 +8935,30 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>HOU vs LAA</t>
+          <t>LAA vs HOU</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Zach Neto</t>
+          <t>Yainer Diaz</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G18" t="n">
-        <v>-183.5</v>
+        <v>-182</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6847</v>
+        <v>0.6797</v>
       </c>
       <c r="I18" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.077</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -7793,12 +8983,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DET vs SDP</t>
+          <t>TBR vs STL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Manny Machado</t>
+          <t>Masyn Winn</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -7810,13 +9000,13 @@
         <v>0.5</v>
       </c>
       <c r="G19" t="n">
-        <v>-164.5</v>
+        <v>-20</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6501</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0707</v>
+        <v>0.1919</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -7841,12 +9031,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MIN vs BAL</t>
+          <t>BAL vs MIN</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Adley Rutschman</t>
+          <t>Josh Bell</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -7855,16 +9045,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G20" t="n">
-        <v>-172</v>
+        <v>-52.5</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6712</v>
+        <v>0.4279</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0818</v>
+        <v>0.1718</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -7889,12 +9079,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>STL vs TBR</t>
+          <t>BAL vs MIN</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Royce Lewis</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -7906,13 +9096,13 @@
         <v>0.5</v>
       </c>
       <c r="G21" t="n">
-        <v>119.5</v>
+        <v>-50</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5552</v>
+        <v>0.4602</v>
       </c>
       <c r="I21" t="n">
-        <v>0.131</v>
+        <v>0.2055</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -7937,30 +9127,30 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>STL vs TBR</t>
+          <t>CLE vs SEA</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ben Williamson</t>
+          <t>Cal Raleigh</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G22" t="n">
-        <v>-195.5</v>
+        <v>-147.5</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7428</v>
+        <v>0.7043</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1248</v>
+        <v>0.152</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -7985,12 +9175,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>STL vs TBR</t>
+          <t>HOU vs LAA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Carson Williams</t>
+          <t>Oswald Peraza</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -8002,13 +9192,13 @@
         <v>0.5</v>
       </c>
       <c r="G23" t="n">
-        <v>110</v>
+        <v>-125</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5195</v>
+        <v>0.6553</v>
       </c>
       <c r="I23" t="n">
-        <v>0.077</v>
+        <v>0.1406</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -8033,12 +9223,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SDP vs DET</t>
+          <t>MIN vs BAL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Spencer Torkelson</t>
+          <t>Gunnar Henderson</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -8047,16 +9237,16 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G24" t="n">
-        <v>-145</v>
+        <v>-3.5</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.4083</v>
       </c>
       <c r="I24" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.3519</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -8081,30 +9271,30 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>LAA vs HOU</t>
+          <t>SEA vs CLE</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Jake Meyers</t>
+          <t>Kyle Manzardo</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>0.5</v>
       </c>
       <c r="G25" t="n">
-        <v>126.5</v>
+        <v>-108</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.6057</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0975</v>
+        <v>0.1269</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -8129,30 +9319,30 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MIN vs BAL</t>
+          <t>LAD vs ARI</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Gunnar Henderson</t>
+          <t>Pavin Smith</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G26" t="n">
-        <v>-125</v>
+        <v>101</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5917</v>
+        <v>0.5637</v>
       </c>
       <c r="I26" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.1034</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -8177,12 +9367,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NYM vs PIT</t>
+          <t>CLE vs SEA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Spencer Horwitz</t>
+          <t>Randy Arozarena</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -8194,13 +9384,13 @@
         <v>0.5</v>
       </c>
       <c r="G27" t="n">
-        <v>-126</v>
+        <v>-124</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5911999999999999</v>
+        <v>0.6155</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0756</v>
+        <v>0.1069</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -8225,12 +9415,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MIL vs CWS</t>
+          <t>SEA vs CLE</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Miguel Vargas</t>
+          <t>Rhys Hoskins</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -8242,13 +9432,13 @@
         <v>0.5</v>
       </c>
       <c r="G28" t="n">
-        <v>-145</v>
+        <v>100</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6219</v>
+        <v>0.5556</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0713</v>
+        <v>0.094</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -8273,30 +9463,30 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NYM vs PIT</t>
+          <t>SEA vs CLE</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Jared Triolo</t>
+          <t>Gabriel Arias</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>0.5</v>
       </c>
       <c r="G29" t="n">
-        <v>-5</v>
+        <v>115</v>
       </c>
       <c r="H29" t="n">
-        <v>0.488</v>
+        <v>0.5197000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4119</v>
+        <v>0.083</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -8321,30 +9511,30 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MIL vs CWS</t>
+          <t>ARI vs LAD</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Colson Montgomery</t>
+          <t>Miguel Rojas</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>0.5</v>
       </c>
       <c r="G30" t="n">
-        <v>-134.5</v>
+        <v>113</v>
       </c>
       <c r="H30" t="n">
-        <v>0.6704</v>
+        <v>0.5123</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1361</v>
+        <v>0.0765</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -8369,30 +9559,30 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>TBR vs STL</t>
+          <t>MIN vs BAL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Jordan Walker</t>
+          <t>Colton Cowser</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>0.5</v>
       </c>
       <c r="G31" t="n">
-        <v>128.5</v>
+        <v>250</v>
       </c>
       <c r="H31" t="n">
-        <v>0.5208</v>
+        <v>0.5614</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1146</v>
+        <v>0.2085</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -8417,30 +9607,30 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PIT vs NYM</t>
+          <t>PHI vs TEX</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Jorge Polanco</t>
+          <t>Sam Haggerty</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>0.5</v>
       </c>
       <c r="G32" t="n">
-        <v>-141</v>
+        <v>106</v>
       </c>
       <c r="H32" t="n">
-        <v>0.65</v>
+        <v>0.5615</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1053</v>
+        <v>0.1109</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -8465,30 +9655,30 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CHC vs WSN</t>
+          <t>PHI vs TEX</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Jacob Young</t>
+          <t>Wyatt Langford</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>0.5</v>
       </c>
       <c r="G33" t="n">
-        <v>-110</v>
+        <v>-20</v>
       </c>
       <c r="H33" t="n">
-        <v>0.5992</v>
+        <v>0.6369</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1134</v>
+        <v>0.2456</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -8513,30 +9703,30 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CHC vs WSN</t>
+          <t>BOS vs CIN</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>James Wood</t>
+          <t>Ke'Bryan Hayes</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>0.5</v>
       </c>
       <c r="G34" t="n">
-        <v>-161</v>
+        <v>120.5</v>
       </c>
       <c r="H34" t="n">
-        <v>0.6791</v>
+        <v>0.5485</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1056</v>
+        <v>0.1263</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -8561,30 +9751,30 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PIT vs NYM</t>
+          <t>NYM vs PIT</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Juan Soto</t>
+          <t>Jared Triolo</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>0.5</v>
       </c>
       <c r="G35" t="n">
-        <v>-153.5</v>
+        <v>-5</v>
       </c>
       <c r="H35" t="n">
-        <v>0.6667</v>
+        <v>0.488</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1028</v>
+        <v>0.4119</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -8609,30 +9799,30 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CWS vs MIL</t>
+          <t>MIL vs CWS</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>0.5</v>
       </c>
       <c r="G36" t="n">
-        <v>-118</v>
+        <v>-134.5</v>
       </c>
       <c r="H36" t="n">
-        <v>0.6207</v>
+        <v>0.6704</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1178</v>
+        <v>0.1361</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -8657,30 +9847,30 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NYM vs PIT</t>
+          <t>TBR vs STL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Brandon Lowe</t>
+          <t>Jordan Walker</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>0.5</v>
       </c>
       <c r="G37" t="n">
-        <v>-150</v>
+        <v>128.5</v>
       </c>
       <c r="H37" t="n">
-        <v>0.6529</v>
+        <v>0.5208</v>
       </c>
       <c r="I37" t="n">
-        <v>0.096</v>
+        <v>0.1146</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -8705,30 +9895,30 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MIN vs BAL</t>
+          <t>PIT vs NYM</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Tyler O'Neill</t>
+          <t>Jorge Polanco</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G38" t="n">
-        <v>-175</v>
+        <v>-141</v>
       </c>
       <c r="H38" t="n">
-        <v>0.6989</v>
+        <v>0.65</v>
       </c>
       <c r="I38" t="n">
-        <v>0.108</v>
+        <v>0.1053</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -8758,25 +9948,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CJ Abrams</t>
+          <t>Jacob Young</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>0.5</v>
       </c>
       <c r="G39" t="n">
-        <v>-135.5</v>
+        <v>-110</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6195000000000001</v>
+        <v>0.5992</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0832</v>
+        <v>0.1134</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -8801,12 +9991,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PIT vs NYM</t>
+          <t>CHC vs WSN</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Francisco Lindor</t>
+          <t>James Wood</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -8818,13 +10008,13 @@
         <v>0.5</v>
       </c>
       <c r="G40" t="n">
-        <v>-180.5</v>
+        <v>-161</v>
       </c>
       <c r="H40" t="n">
-        <v>0.6811</v>
+        <v>0.6791</v>
       </c>
       <c r="I40" t="n">
-        <v>0.0843</v>
+        <v>0.1056</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -8849,30 +10039,30 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CIN vs BOS</t>
+          <t>PIT vs NYM</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Ceddanne Rafaela</t>
+          <t>Juan Soto</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G41" t="n">
-        <v>-178</v>
+        <v>-153.5</v>
       </c>
       <c r="H41" t="n">
-        <v>0.6949</v>
+        <v>0.6667</v>
       </c>
       <c r="I41" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.1028</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -8897,30 +10087,30 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BAL vs MIN</t>
+          <t>CWS vs MIL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Matt Wallner</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>0.5</v>
       </c>
       <c r="G42" t="n">
-        <v>-143.5</v>
+        <v>-118</v>
       </c>
       <c r="H42" t="n">
-        <v>0.6172</v>
+        <v>0.6207</v>
       </c>
       <c r="I42" t="n">
-        <v>0.0706</v>
+        <v>0.1178</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -8945,12 +10135,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MIL vs CWS</t>
+          <t>NYM vs PIT</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Andrew Benintendi</t>
+          <t>Brandon Lowe</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -8962,13 +10152,13 @@
         <v>0.5</v>
       </c>
       <c r="G43" t="n">
-        <v>-141.5</v>
+        <v>-150</v>
       </c>
       <c r="H43" t="n">
-        <v>0.6186</v>
+        <v>0.6529</v>
       </c>
       <c r="I43" t="n">
-        <v>0.0741</v>
+        <v>0.096</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -8998,7 +10188,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Samuel Basallo</t>
+          <t>Tyler O'Neill</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -9010,13 +10200,13 @@
         <v>1.5</v>
       </c>
       <c r="G44" t="n">
-        <v>-185</v>
+        <v>-175</v>
       </c>
       <c r="H44" t="n">
-        <v>0.6848</v>
+        <v>0.6989</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0808</v>
+        <v>0.108</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -9041,30 +10231,30 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>TBR vs STL</t>
+          <t>CIN vs BOS</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Masyn Winn</t>
+          <t>Isiah Kiner-Falefa</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G45" t="n">
-        <v>-20</v>
+        <v>-185</v>
       </c>
       <c r="H45" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.7533</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1919</v>
+        <v>0.1467</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -9075,6 +10265,630 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CHC vs WSN</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>CJ Abrams</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-135.5</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.6195000000000001</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.0832</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CIN vs BOS</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Ceddanne Rafaela</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-178</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.6949</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.09719999999999999</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>NYM vs PIT</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Spencer Horwitz</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-126</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.5911999999999999</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.0756</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>MIL vs CWS</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Andrew Benintendi</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-141.5</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.6186</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.0741</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>MIL vs CWS</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Miguel Vargas</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-145</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.6219</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.0713</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>MIN vs BAL</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Samuel Basallo</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-185</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.6848</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.0808</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>MIN vs BAL</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Gunnar Henderson</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-125</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.5917</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.07480000000000001</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>MIN vs BAL</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Adley Rutschman</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-172</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.6712</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.0818</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>BAL vs MIN</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Austin Martin</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-170</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.6679</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.08169999999999999</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>CLE vs SEA</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Dominic Canzone</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-118</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.5725</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.0725</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>CHC vs WSN</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Keibert Ruiz</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.5118</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.4948</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>PIT vs NYM</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Francisco Lindor</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-180.5</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.6811</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.0843</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>LAA vs HOU</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Yordan Alvarez</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-138</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.6188</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9087,7 +10901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9283,30 +11097,30 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LAA vs HOU</t>
+          <t>LAD vs ARI</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Zac Gallen</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="G4" t="n">
-        <v>-110.5</v>
+        <v>-0.5</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6015</v>
+        <v>0.3341</v>
       </c>
       <c r="I4" t="n">
-        <v>0.112</v>
+        <v>0.3257</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -9331,12 +11145,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CIN vs BOS</t>
+          <t>CHC vs WSN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Garrett Crochet</t>
+          <t>Cade Cavalli</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -9345,16 +11159,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="G5" t="n">
-        <v>-125</v>
+        <v>-140.5</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6627999999999999</v>
+        <v>0.8003</v>
       </c>
       <c r="I5" t="n">
-        <v>0.147</v>
+        <v>0.4224</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -9379,12 +11193,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BOS vs CIN</t>
+          <t>TBR vs STL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Andrew Abbott</t>
+          <t>Matthew Liberatore</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -9393,16 +11207,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="G6" t="n">
-        <v>125</v>
+        <v>-183.5</v>
       </c>
       <c r="H6" t="n">
-        <v>0.632</v>
+        <v>0.7463</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2242</v>
+        <v>0.1529</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -9427,12 +11241,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PHI vs TEX</t>
+          <t>LAA vs HOU</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Nathan Eovaldi</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -9441,16 +11255,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="G7" t="n">
-        <v>-125</v>
+        <v>-110.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8067</v>
+        <v>0.6015</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2972</v>
+        <v>0.112</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -9475,12 +11289,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DET vs SDP</t>
+          <t>CIN vs BOS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Nick Pivetta</t>
+          <t>Garrett Crochet</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -9489,16 +11303,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="G8" t="n">
-        <v>-116.5</v>
+        <v>-125</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8866000000000001</v>
+        <v>0.6627999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3851</v>
+        <v>0.147</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -9523,12 +11337,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MIL vs CWS</t>
+          <t>BOS vs CIN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Shane Smith</t>
+          <t>Andrew Abbott</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -9537,16 +11351,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="G9" t="n">
-        <v>-155</v>
+        <v>125</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7044</v>
+        <v>0.632</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1431</v>
+        <v>0.2242</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -9571,12 +11385,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>WSN vs CHC</t>
+          <t>PHI vs TEX</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Matthew Boyd</t>
+          <t>Nathan Eovaldi</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -9585,16 +11399,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="G10" t="n">
-        <v>-115</v>
+        <v>-125</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6491</v>
+        <v>0.8067</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1491</v>
+        <v>0.2972</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -9619,12 +11433,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>STL vs TBR</t>
+          <t>DET vs SDP</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -9633,16 +11447,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="G11" t="n">
-        <v>-167.5</v>
+        <v>-116.5</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7352</v>
+        <v>0.8866000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1525</v>
+        <v>0.3851</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -9667,30 +11481,30 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CHC vs WSN</t>
+          <t>MIL vs CWS</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cade Cavalli</t>
+          <t>Shane Smith</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>14.5</v>
       </c>
       <c r="G12" t="n">
-        <v>-1</v>
+        <v>-155</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1997</v>
+        <v>0.7044</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1827</v>
+        <v>0.1431</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -9715,12 +11529,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PIT vs NYM</t>
+          <t>WSN vs CHC</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Matthew Boyd</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -9732,13 +11546,13 @@
         <v>15.5</v>
       </c>
       <c r="G13" t="n">
-        <v>140.5</v>
+        <v>-115</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6554</v>
+        <v>0.6491</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2699</v>
+        <v>0.1491</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -9763,12 +11577,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MIN vs BAL</t>
+          <t>STL vs TBR</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Trevor Rogers</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -9777,16 +11591,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="G14" t="n">
-        <v>-110</v>
+        <v>-167.5</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7123</v>
+        <v>0.7352</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2247</v>
+        <v>0.1525</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -9811,30 +11625,30 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NYM vs PIT</t>
+          <t>CHC vs WSN</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Paul Skenes</t>
+          <t>Cade Cavalli</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="G15" t="n">
-        <v>-104.5</v>
+        <v>-1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7044</v>
+        <v>0.1997</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2317</v>
+        <v>0.1827</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -9859,12 +11673,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BAL vs MIN</t>
+          <t>PIT vs NYM</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Joe Ryan</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -9876,13 +11690,13 @@
         <v>15.5</v>
       </c>
       <c r="G16" t="n">
-        <v>145</v>
+        <v>140.5</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7798</v>
+        <v>0.6554</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4004</v>
+        <v>0.2699</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -9907,12 +11721,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CWS vs MIL</t>
+          <t>MIN vs BAL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Trevor Rogers</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -9921,16 +11735,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="G17" t="n">
-        <v>-175</v>
+        <v>-110</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7971</v>
+        <v>0.7123</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2083</v>
+        <v>0.2247</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -9955,12 +11769,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TBR vs STL</t>
+          <t>NYM vs PIT</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Matthew Liberatore</t>
+          <t>Paul Skenes</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -9969,16 +11783,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="G18" t="n">
-        <v>-183.5</v>
+        <v>-104.5</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7463</v>
+        <v>0.7044</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1529</v>
+        <v>0.2317</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -10003,12 +11817,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CHC vs WSN</t>
+          <t>BAL vs MIN</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cade Cavalli</t>
+          <t>Joe Ryan</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -10017,16 +11831,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="G19" t="n">
-        <v>-140.5</v>
+        <v>145</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8003</v>
+        <v>0.7798</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4224</v>
+        <v>0.4004</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -10037,6 +11851,150 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CWS vs MIL</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-175</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.7971</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.2083</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ARI vs LAD</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Yoshinobu Yamamoto</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G21" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.2304</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CIN vs BOS</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Garrett Crochet</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.2589</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10049,7 +12007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10722,6 +12680,144 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PIT @ NYM</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>PIT @ NYM</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>NRFI</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>-162</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-0.5818</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ARI @ LAD</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ARI @ LAD</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>YRFI</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>-119</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.4875</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLE @ SEA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CLE @ SEA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>NRFI</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>-155</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.4113</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-0.1552</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tracking/picks.xlsx
+++ b/tracking/picks.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N118"/>
+  <dimension ref="A1:N122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6133,6 +6133,196 @@
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>ARI vs LAD</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Miguel Rojas</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G119" t="n">
+        <v>-260</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.7621</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>ARI vs LAD</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Max Muncy</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G120" t="n">
+        <v>-210</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.7116</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.07149999999999999</v>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>LAD vs ARI</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Zac Gallen</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G121" t="n">
+        <v>-155</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.6659</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.0977</v>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>ARI @ LAD</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>ARI @ LAD</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>NRFI</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="n">
+        <v>-105</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" t="n">
+        <v>-0.4852</v>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8031,7 +8221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N58"/>
+  <dimension ref="A1:N60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8551,12 +8741,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SDP vs DET</t>
+          <t>TBR vs STL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Spencer Torkelson</t>
+          <t>Masyn Winn</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -8568,13 +8758,13 @@
         <v>0.5</v>
       </c>
       <c r="G10" t="n">
-        <v>-145</v>
+        <v>-20</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.1919</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -8599,30 +8789,30 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>STL vs TBR</t>
+          <t>BAL vs MIN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Carson Williams</t>
+          <t>Matt Wallner</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>0.5</v>
       </c>
       <c r="G11" t="n">
-        <v>110</v>
+        <v>-143.5</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5195</v>
+        <v>0.6172</v>
       </c>
       <c r="I11" t="n">
-        <v>0.077</v>
+        <v>0.0706</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -8647,30 +8837,30 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>STL vs TBR</t>
+          <t>SDP vs DET</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ben Williamson</t>
+          <t>Spencer Torkelson</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G12" t="n">
-        <v>-195.5</v>
+        <v>-145</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7428</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1248</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -8700,7 +8890,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Carson Williams</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -8712,13 +8902,13 @@
         <v>0.5</v>
       </c>
       <c r="G13" t="n">
-        <v>119.5</v>
+        <v>110</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5552</v>
+        <v>0.5195</v>
       </c>
       <c r="I13" t="n">
-        <v>0.131</v>
+        <v>0.077</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -8743,30 +8933,30 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LAA vs HOU</t>
+          <t>DET vs SDP</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Jake Meyers</t>
+          <t>Manny Machado</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>0.5</v>
       </c>
       <c r="G14" t="n">
-        <v>126.5</v>
+        <v>-164.5</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.6501</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0975</v>
+        <v>0.0707</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -8791,30 +8981,30 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DET vs SDP</t>
+          <t>STL vs TBR</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Manny Machado</t>
+          <t>Nick Fortes</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>0.5</v>
       </c>
       <c r="G15" t="n">
-        <v>-164.5</v>
+        <v>119.5</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6501</v>
+        <v>0.5552</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0707</v>
+        <v>0.131</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -8839,30 +9029,30 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>HOU vs LAA</t>
+          <t>LAA vs HOU</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Zach Neto</t>
+          <t>Yainer Diaz</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G16" t="n">
-        <v>-183.5</v>
+        <v>-182</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6847</v>
+        <v>0.6797</v>
       </c>
       <c r="I16" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.077</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -8887,12 +9077,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BAL vs MIN</t>
+          <t>MIN vs BAL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Matt Wallner</t>
+          <t>Colton Cowser</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8904,13 +9094,13 @@
         <v>0.5</v>
       </c>
       <c r="G17" t="n">
-        <v>-143.5</v>
+        <v>250</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6172</v>
+        <v>0.5614</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0706</v>
+        <v>0.2085</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -8935,30 +9125,30 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LAA vs HOU</t>
+          <t>HOU vs LAA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Yainer Diaz</t>
+          <t>Zach Neto</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G18" t="n">
-        <v>-182</v>
+        <v>-183.5</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6797</v>
+        <v>0.6847</v>
       </c>
       <c r="I18" t="n">
-        <v>0.077</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -8983,30 +9173,30 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TBR vs STL</t>
+          <t>STL vs TBR</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Masyn Winn</t>
+          <t>Ben Williamson</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G19" t="n">
-        <v>-20</v>
+        <v>-195.5</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.7428</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1919</v>
+        <v>0.1248</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -9036,7 +9226,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Josh Bell</t>
+          <t>Royce Lewis</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9048,13 +9238,13 @@
         <v>0.5</v>
       </c>
       <c r="G20" t="n">
-        <v>-52.5</v>
+        <v>-50</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4279</v>
+        <v>0.4602</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1718</v>
+        <v>0.2055</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -9079,30 +9269,30 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BAL vs MIN</t>
+          <t>SEA vs CLE</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Royce Lewis</t>
+          <t>Kyle Manzardo</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>0.5</v>
       </c>
       <c r="G21" t="n">
-        <v>-50</v>
+        <v>-108</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4602</v>
+        <v>0.6057</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2055</v>
+        <v>0.1269</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -9127,30 +9317,30 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLE vs SEA</t>
+          <t>BAL vs MIN</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cal Raleigh</t>
+          <t>Josh Bell</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>0.5</v>
       </c>
       <c r="G22" t="n">
-        <v>-147.5</v>
+        <v>-52.5</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7043</v>
+        <v>0.4279</v>
       </c>
       <c r="I22" t="n">
-        <v>0.152</v>
+        <v>0.1718</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -9175,30 +9365,30 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HOU vs LAA</t>
+          <t>MIN vs BAL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Oswald Peraza</t>
+          <t>Gunnar Henderson</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G23" t="n">
-        <v>-125</v>
+        <v>-3.5</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6553</v>
+        <v>0.4083</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1406</v>
+        <v>0.3519</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -9223,30 +9413,30 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MIN vs BAL</t>
+          <t>LAA vs HOU</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Gunnar Henderson</t>
+          <t>Jake Meyers</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.5</v>
+        <v>126.5</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4083</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3519</v>
+        <v>0.0975</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -9271,12 +9461,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SEA vs CLE</t>
+          <t>LAD vs ARI</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Kyle Manzardo</t>
+          <t>Pavin Smith</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -9288,13 +9478,13 @@
         <v>0.5</v>
       </c>
       <c r="G25" t="n">
-        <v>-108</v>
+        <v>101</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6057</v>
+        <v>0.5637</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1269</v>
+        <v>0.1034</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -9319,12 +9509,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>LAD vs ARI</t>
+          <t>CLE vs SEA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Pavin Smith</t>
+          <t>Randy Arozarena</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -9336,13 +9526,13 @@
         <v>0.5</v>
       </c>
       <c r="G26" t="n">
-        <v>101</v>
+        <v>-124</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5637</v>
+        <v>0.6155</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1034</v>
+        <v>0.1069</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -9367,12 +9557,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLE vs SEA</t>
+          <t>SEA vs CLE</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Randy Arozarena</t>
+          <t>Rhys Hoskins</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -9384,13 +9574,13 @@
         <v>0.5</v>
       </c>
       <c r="G27" t="n">
-        <v>-124</v>
+        <v>100</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6155</v>
+        <v>0.5556</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1069</v>
+        <v>0.094</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -9420,7 +9610,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Rhys Hoskins</t>
+          <t>Gabriel Arias</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -9432,13 +9622,13 @@
         <v>0.5</v>
       </c>
       <c r="G28" t="n">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="H28" t="n">
-        <v>0.5556</v>
+        <v>0.5197000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>0.094</v>
+        <v>0.083</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -9463,30 +9653,30 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SEA vs CLE</t>
+          <t>ARI vs LAD</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Gabriel Arias</t>
+          <t>Miguel Rojas</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>0.5</v>
       </c>
       <c r="G29" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.5123</v>
       </c>
       <c r="I29" t="n">
-        <v>0.083</v>
+        <v>0.0765</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -9511,30 +9701,30 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ARI vs LAD</t>
+          <t>CLE vs SEA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Miguel Rojas</t>
+          <t>Dominic Canzone</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>0.5</v>
       </c>
       <c r="G30" t="n">
-        <v>113</v>
+        <v>-118</v>
       </c>
       <c r="H30" t="n">
-        <v>0.5123</v>
+        <v>0.5725</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0765</v>
+        <v>0.0725</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -9559,30 +9749,30 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MIN vs BAL</t>
+          <t>LAA vs HOU</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Colton Cowser</t>
+          <t>Yordan Alvarez</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G31" t="n">
-        <v>250</v>
+        <v>-138</v>
       </c>
       <c r="H31" t="n">
-        <v>0.5614</v>
+        <v>0.6188</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2085</v>
+        <v>0.0769</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -9607,30 +9797,30 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PHI vs TEX</t>
+          <t>CLE vs SEA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sam Haggerty</t>
+          <t>Cal Raleigh</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>0.5</v>
       </c>
       <c r="G32" t="n">
-        <v>106</v>
+        <v>-147.5</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5615</v>
+        <v>0.7043</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1109</v>
+        <v>0.152</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -9655,30 +9845,30 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PHI vs TEX</t>
+          <t>HOU vs LAA</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Wyatt Langford</t>
+          <t>Oswald Peraza</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>0.5</v>
       </c>
       <c r="G33" t="n">
-        <v>-20</v>
+        <v>-125</v>
       </c>
       <c r="H33" t="n">
-        <v>0.6369</v>
+        <v>0.6553</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2456</v>
+        <v>0.1406</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -9703,12 +9893,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BOS vs CIN</t>
+          <t>CHC vs WSN</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Ke'Bryan Hayes</t>
+          <t>Keibert Ruiz</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -9720,13 +9910,13 @@
         <v>0.5</v>
       </c>
       <c r="G34" t="n">
-        <v>120.5</v>
+        <v>-1</v>
       </c>
       <c r="H34" t="n">
-        <v>0.5485</v>
+        <v>0.5118</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1263</v>
+        <v>0.4948</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -9751,12 +9941,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NYM vs PIT</t>
+          <t>CIN vs BOS</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Jared Triolo</t>
+          <t>Isiah Kiner-Falefa</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -9765,16 +9955,16 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G35" t="n">
-        <v>-5</v>
+        <v>-185</v>
       </c>
       <c r="H35" t="n">
-        <v>0.488</v>
+        <v>0.7533</v>
       </c>
       <c r="I35" t="n">
-        <v>0.4119</v>
+        <v>0.1467</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -9799,30 +9989,30 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MIL vs CWS</t>
+          <t>NYM vs PIT</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Colson Montgomery</t>
+          <t>Jared Triolo</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>0.5</v>
       </c>
       <c r="G36" t="n">
-        <v>-134.5</v>
+        <v>-5</v>
       </c>
       <c r="H36" t="n">
-        <v>0.6704</v>
+        <v>0.488</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1361</v>
+        <v>0.4119</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -9847,30 +10037,30 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>TBR vs STL</t>
+          <t>MIL vs CWS</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Jordan Walker</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>0.5</v>
       </c>
       <c r="G37" t="n">
-        <v>128.5</v>
+        <v>-134.5</v>
       </c>
       <c r="H37" t="n">
-        <v>0.5208</v>
+        <v>0.6704</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1146</v>
+        <v>0.1361</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -9895,30 +10085,30 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PIT vs NYM</t>
+          <t>TBR vs STL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Jorge Polanco</t>
+          <t>Jordan Walker</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>0.5</v>
       </c>
       <c r="G38" t="n">
-        <v>-141</v>
+        <v>128.5</v>
       </c>
       <c r="H38" t="n">
-        <v>0.65</v>
+        <v>0.5208</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1053</v>
+        <v>0.1146</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -9943,30 +10133,30 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CHC vs WSN</t>
+          <t>PIT vs NYM</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Jacob Young</t>
+          <t>Jorge Polanco</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>0.5</v>
       </c>
       <c r="G39" t="n">
-        <v>-110</v>
+        <v>-141</v>
       </c>
       <c r="H39" t="n">
-        <v>0.5992</v>
+        <v>0.65</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1134</v>
+        <v>0.1053</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -9996,25 +10186,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>James Wood</t>
+          <t>Jacob Young</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>0.5</v>
       </c>
       <c r="G40" t="n">
-        <v>-161</v>
+        <v>-110</v>
       </c>
       <c r="H40" t="n">
-        <v>0.6791</v>
+        <v>0.5992</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1056</v>
+        <v>0.1134</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -10039,12 +10229,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PIT vs NYM</t>
+          <t>CHC vs WSN</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Juan Soto</t>
+          <t>James Wood</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -10056,13 +10246,13 @@
         <v>0.5</v>
       </c>
       <c r="G41" t="n">
-        <v>-153.5</v>
+        <v>-161</v>
       </c>
       <c r="H41" t="n">
-        <v>0.6667</v>
+        <v>0.6791</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1028</v>
+        <v>0.1056</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -10087,30 +10277,30 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CWS vs MIL</t>
+          <t>PIT vs NYM</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Juan Soto</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>0.5</v>
       </c>
       <c r="G42" t="n">
-        <v>-118</v>
+        <v>-153.5</v>
       </c>
       <c r="H42" t="n">
-        <v>0.6207</v>
+        <v>0.6667</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1178</v>
+        <v>0.1028</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -10135,30 +10325,30 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NYM vs PIT</t>
+          <t>CWS vs MIL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Brandon Lowe</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F43" t="n">
         <v>0.5</v>
       </c>
       <c r="G43" t="n">
-        <v>-150</v>
+        <v>-118</v>
       </c>
       <c r="H43" t="n">
-        <v>0.6529</v>
+        <v>0.6207</v>
       </c>
       <c r="I43" t="n">
-        <v>0.096</v>
+        <v>0.1178</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -10183,30 +10373,30 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MIN vs BAL</t>
+          <t>NYM vs PIT</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Tyler O'Neill</t>
+          <t>Brandon Lowe</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G44" t="n">
-        <v>-175</v>
+        <v>-150</v>
       </c>
       <c r="H44" t="n">
-        <v>0.6989</v>
+        <v>0.6529</v>
       </c>
       <c r="I44" t="n">
-        <v>0.108</v>
+        <v>0.096</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -10231,12 +10421,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CIN vs BOS</t>
+          <t>MIN vs BAL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Isiah Kiner-Falefa</t>
+          <t>Tyler O'Neill</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -10248,13 +10438,13 @@
         <v>1.5</v>
       </c>
       <c r="G45" t="n">
-        <v>-185</v>
+        <v>-175</v>
       </c>
       <c r="H45" t="n">
-        <v>0.7533</v>
+        <v>0.6989</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1467</v>
+        <v>0.108</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -10327,30 +10517,30 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CIN vs BOS</t>
+          <t>PIT vs NYM</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Ceddanne Rafaela</t>
+          <t>Francisco Lindor</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G47" t="n">
-        <v>-178</v>
+        <v>-180.5</v>
       </c>
       <c r="H47" t="n">
-        <v>0.6949</v>
+        <v>0.6811</v>
       </c>
       <c r="I47" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.0843</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -10375,30 +10565,30 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NYM vs PIT</t>
+          <t>CIN vs BOS</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Spencer Horwitz</t>
+          <t>Ceddanne Rafaela</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G48" t="n">
-        <v>-126</v>
+        <v>-178</v>
       </c>
       <c r="H48" t="n">
-        <v>0.5911999999999999</v>
+        <v>0.6949</v>
       </c>
       <c r="I48" t="n">
-        <v>0.0756</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -10423,12 +10613,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MIL vs CWS</t>
+          <t>NYM vs PIT</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Andrew Benintendi</t>
+          <t>Spencer Horwitz</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -10440,13 +10630,13 @@
         <v>0.5</v>
       </c>
       <c r="G49" t="n">
-        <v>-141.5</v>
+        <v>-126</v>
       </c>
       <c r="H49" t="n">
-        <v>0.6186</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>0.0741</v>
+        <v>0.0756</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -10476,7 +10666,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Miguel Vargas</t>
+          <t>Andrew Benintendi</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -10488,13 +10678,13 @@
         <v>0.5</v>
       </c>
       <c r="G50" t="n">
-        <v>-145</v>
+        <v>-141.5</v>
       </c>
       <c r="H50" t="n">
-        <v>0.6219</v>
+        <v>0.6186</v>
       </c>
       <c r="I50" t="n">
-        <v>0.0713</v>
+        <v>0.0741</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -10519,30 +10709,30 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MIN vs BAL</t>
+          <t>MIL vs CWS</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Samuel Basallo</t>
+          <t>Miguel Vargas</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G51" t="n">
-        <v>-185</v>
+        <v>-145</v>
       </c>
       <c r="H51" t="n">
-        <v>0.6848</v>
+        <v>0.6219</v>
       </c>
       <c r="I51" t="n">
-        <v>0.0808</v>
+        <v>0.0713</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -10572,7 +10762,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Gunnar Henderson</t>
+          <t>Samuel Basallo</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -10584,13 +10774,13 @@
         <v>1.5</v>
       </c>
       <c r="G52" t="n">
-        <v>-125</v>
+        <v>-185</v>
       </c>
       <c r="H52" t="n">
-        <v>0.5917</v>
+        <v>0.6848</v>
       </c>
       <c r="I52" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.0808</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -10620,7 +10810,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Adley Rutschman</t>
+          <t>Gunnar Henderson</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -10632,13 +10822,13 @@
         <v>1.5</v>
       </c>
       <c r="G53" t="n">
-        <v>-172</v>
+        <v>-125</v>
       </c>
       <c r="H53" t="n">
-        <v>0.6712</v>
+        <v>0.5917</v>
       </c>
       <c r="I53" t="n">
-        <v>0.0818</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -10663,12 +10853,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>BAL vs MIN</t>
+          <t>MIN vs BAL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Austin Martin</t>
+          <t>Adley Rutschman</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -10680,13 +10870,13 @@
         <v>1.5</v>
       </c>
       <c r="G54" t="n">
-        <v>-170</v>
+        <v>-172</v>
       </c>
       <c r="H54" t="n">
-        <v>0.6679</v>
+        <v>0.6712</v>
       </c>
       <c r="I54" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.0818</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -10711,30 +10901,30 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CLE vs SEA</t>
+          <t>BAL vs MIN</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Dominic Canzone</t>
+          <t>Austin Martin</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G55" t="n">
-        <v>-118</v>
+        <v>-170</v>
       </c>
       <c r="H55" t="n">
-        <v>0.5725</v>
+        <v>0.6679</v>
       </c>
       <c r="I55" t="n">
-        <v>0.0725</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -10759,30 +10949,30 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CHC vs WSN</t>
+          <t>PHI vs TEX</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Keibert Ruiz</t>
+          <t>Wyatt Langford</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F56" t="n">
         <v>0.5</v>
       </c>
       <c r="G56" t="n">
-        <v>-1</v>
+        <v>-20</v>
       </c>
       <c r="H56" t="n">
-        <v>0.5118</v>
+        <v>0.6369</v>
       </c>
       <c r="I56" t="n">
-        <v>0.4948</v>
+        <v>0.2456</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -10807,30 +10997,30 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>PIT vs NYM</t>
+          <t>ARI vs LAD</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Francisco Lindor</t>
+          <t>Miguel Rojas</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G57" t="n">
-        <v>-180.5</v>
+        <v>-260</v>
       </c>
       <c r="H57" t="n">
-        <v>0.6811</v>
+        <v>0.7621</v>
       </c>
       <c r="I57" t="n">
-        <v>0.0843</v>
+        <v>0.093</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -10855,12 +11045,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>LAA vs HOU</t>
+          <t>BOS vs CIN</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Yordan Alvarez</t>
+          <t>Ke'Bryan Hayes</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -10869,16 +11059,16 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G58" t="n">
-        <v>-138</v>
+        <v>120.5</v>
       </c>
       <c r="H58" t="n">
-        <v>0.6188</v>
+        <v>0.5485</v>
       </c>
       <c r="I58" t="n">
-        <v>0.0769</v>
+        <v>0.1263</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -10889,6 +11079,102 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>PHI vs TEX</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Sam Haggerty</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G59" t="n">
+        <v>106</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.5615</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.1109</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ARI vs LAD</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Max Muncy</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-210</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.7116</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.07149999999999999</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10901,7 +11187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11097,30 +11383,30 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LAD vs ARI</t>
+          <t>ARI vs LAD</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Zac Gallen</t>
+          <t>Yoshinobu Yamamoto</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.5</v>
+        <v>109.5</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3341</v>
+        <v>0.669</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3257</v>
+        <v>0.2304</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -11145,30 +11431,30 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CHC vs WSN</t>
+          <t>LAD vs ARI</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cade Cavalli</t>
+          <t>Zac Gallen</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>14.5</v>
       </c>
       <c r="G5" t="n">
-        <v>-140.5</v>
+        <v>-0.5</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8003</v>
+        <v>0.3341</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4224</v>
+        <v>0.3257</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -11193,12 +11479,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TBR vs STL</t>
+          <t>CHC vs WSN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Matthew Liberatore</t>
+          <t>Cade Cavalli</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -11210,13 +11496,13 @@
         <v>14.5</v>
       </c>
       <c r="G6" t="n">
-        <v>-183.5</v>
+        <v>-140.5</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7463</v>
+        <v>0.8003</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1529</v>
+        <v>0.4224</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -11241,12 +11527,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LAA vs HOU</t>
+          <t>TBR vs STL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Matthew Liberatore</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -11255,16 +11541,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="G7" t="n">
-        <v>-110.5</v>
+        <v>-183.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6015</v>
+        <v>0.7463</v>
       </c>
       <c r="I7" t="n">
-        <v>0.112</v>
+        <v>0.1529</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -11289,12 +11575,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CIN vs BOS</t>
+          <t>LAA vs HOU</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Garrett Crochet</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -11306,13 +11592,13 @@
         <v>17.5</v>
       </c>
       <c r="G8" t="n">
-        <v>-125</v>
+        <v>-110.5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6627999999999999</v>
+        <v>0.6015</v>
       </c>
       <c r="I8" t="n">
-        <v>0.147</v>
+        <v>0.112</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -11337,12 +11623,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BOS vs CIN</t>
+          <t>CIN vs BOS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Andrew Abbott</t>
+          <t>Garrett Crochet</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -11351,16 +11637,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="G9" t="n">
-        <v>125</v>
+        <v>-125</v>
       </c>
       <c r="H9" t="n">
-        <v>0.632</v>
+        <v>0.6627999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2242</v>
+        <v>0.147</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -11385,12 +11671,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PHI vs TEX</t>
+          <t>BOS vs CIN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Nathan Eovaldi</t>
+          <t>Andrew Abbott</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -11399,16 +11685,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="G10" t="n">
-        <v>-125</v>
+        <v>125</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8067</v>
+        <v>0.632</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2972</v>
+        <v>0.2242</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -11433,12 +11719,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DET vs SDP</t>
+          <t>PHI vs TEX</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Nick Pivetta</t>
+          <t>Nathan Eovaldi</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -11447,16 +11733,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="G11" t="n">
-        <v>-116.5</v>
+        <v>-125</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8866000000000001</v>
+        <v>0.8067</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3851</v>
+        <v>0.2972</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -11481,12 +11767,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MIL vs CWS</t>
+          <t>DET vs SDP</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Shane Smith</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -11495,16 +11781,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="G12" t="n">
-        <v>-155</v>
+        <v>-116.5</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7044</v>
+        <v>0.8866000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1431</v>
+        <v>0.3851</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -11529,12 +11815,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>WSN vs CHC</t>
+          <t>MIL vs CWS</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Matthew Boyd</t>
+          <t>Shane Smith</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -11543,16 +11829,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="G13" t="n">
-        <v>-115</v>
+        <v>-155</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6491</v>
+        <v>0.7044</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1491</v>
+        <v>0.1431</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -11577,12 +11863,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>STL vs TBR</t>
+          <t>WSN vs CHC</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Matthew Boyd</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -11591,16 +11877,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="G14" t="n">
-        <v>-167.5</v>
+        <v>-115</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7352</v>
+        <v>0.6491</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1525</v>
+        <v>0.1491</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -11625,30 +11911,30 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CHC vs WSN</t>
+          <t>STL vs TBR</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cade Cavalli</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>14.5</v>
       </c>
       <c r="G15" t="n">
-        <v>-1</v>
+        <v>-167.5</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1997</v>
+        <v>0.7352</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1827</v>
+        <v>0.1525</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -11673,30 +11959,30 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PIT vs NYM</t>
+          <t>CHC vs WSN</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Cade Cavalli</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="G16" t="n">
-        <v>140.5</v>
+        <v>-1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6554</v>
+        <v>0.1997</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2699</v>
+        <v>0.1827</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -11721,12 +12007,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MIN vs BAL</t>
+          <t>PIT vs NYM</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Trevor Rogers</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -11735,16 +12021,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="G17" t="n">
-        <v>-110</v>
+        <v>140.5</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7123</v>
+        <v>0.6554</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2247</v>
+        <v>0.2699</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -11769,12 +12055,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NYM vs PIT</t>
+          <t>MIN vs BAL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Paul Skenes</t>
+          <t>Trevor Rogers</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -11783,16 +12069,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="G18" t="n">
-        <v>-104.5</v>
+        <v>-110</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7044</v>
+        <v>0.7123</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2317</v>
+        <v>0.2247</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -11817,12 +12103,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BAL vs MIN</t>
+          <t>NYM vs PIT</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Joe Ryan</t>
+          <t>Paul Skenes</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -11834,13 +12120,13 @@
         <v>15.5</v>
       </c>
       <c r="G19" t="n">
-        <v>145</v>
+        <v>-104.5</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7798</v>
+        <v>0.7044</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4004</v>
+        <v>0.2317</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -11865,12 +12151,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CWS vs MIL</t>
+          <t>BAL vs MIN</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Joe Ryan</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -11879,16 +12165,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="G20" t="n">
-        <v>-175</v>
+        <v>145</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7971</v>
+        <v>0.7798</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2083</v>
+        <v>0.4004</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -11913,12 +12199,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ARI vs LAD</t>
+          <t>CWS vs MIL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -11927,16 +12213,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="G21" t="n">
-        <v>109.5</v>
+        <v>-175</v>
       </c>
       <c r="H21" t="n">
-        <v>0.669</v>
+        <v>0.7971</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2304</v>
+        <v>0.2083</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -11995,6 +12281,54 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>LAD vs ARI</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Zac Gallen</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-155</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.6659</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.0977</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12007,7 +12341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12187,12 +12521,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PIT @ NYM</t>
+          <t>ARI @ LAD</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PIT @ NYM</t>
+          <t>ARI @ LAD</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -12202,13 +12536,13 @@
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>120</v>
+        <v>-119</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5746</v>
+        <v>0.4875</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -12233,28 +12567,28 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CWS @ MIL</t>
+          <t>PIT @ NYM</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CWS @ MIL</t>
+          <t>PIT @ NYM</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>YRFI</t>
+          <t>NRFI</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>-102</v>
+        <v>-162</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5314</v>
+        <v>-0.5818</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -12279,28 +12613,28 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MIN @ BAL</t>
+          <t>DET @ SDP</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MIN @ BAL</t>
+          <t>DET @ SDP</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>YRFI</t>
+          <t>NRFI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>-112</v>
+        <v>-162</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0.4113</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5061</v>
+        <v>-0.1628</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -12325,12 +12659,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>WSN @ CHC</t>
+          <t>TBR @ STL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>WSN @ CHC</t>
+          <t>TBR @ STL</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -12340,13 +12674,13 @@
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5887</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1338</v>
+        <v>0.5306</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -12371,12 +12705,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LAA @ HOU</t>
+          <t>TEX @ PHI</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LAA @ HOU</t>
+          <t>TEX @ PHI</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -12386,13 +12720,13 @@
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>102</v>
+        <v>-106</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0.5887</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5347</v>
+        <v>0.1079</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -12417,28 +12751,28 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CWS @ MIL</t>
+          <t>DET @ SDP</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CWS @ MIL</t>
+          <t>DET @ SDP</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>NRFI</t>
+          <t>YRFI</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>-129</v>
+        <v>118</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.5887</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5273</v>
+        <v>0.161</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -12509,28 +12843,28 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DET @ SDP</t>
+          <t>CWS @ MIL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DET @ SDP</t>
+          <t>CWS @ MIL</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>YRFI</t>
+          <t>NRFI</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>118</v>
+        <v>-129</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5887</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0.161</v>
+        <v>-0.5273</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -12555,12 +12889,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TEX @ PHI</t>
+          <t>LAA @ HOU</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>TEX @ PHI</t>
+          <t>LAA @ HOU</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -12570,13 +12904,13 @@
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>-106</v>
+        <v>102</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5887</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1079</v>
+        <v>0.5347</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -12601,12 +12935,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TBR @ STL</t>
+          <t>WSN @ CHC</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>TBR @ STL</t>
+          <t>WSN @ CHC</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -12616,13 +12950,13 @@
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0.5887</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5306</v>
+        <v>0.1338</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -12647,28 +12981,28 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DET @ SDP</t>
+          <t>MIN @ BAL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DET @ SDP</t>
+          <t>MIN @ BAL</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>NRFI</t>
+          <t>YRFI</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>-162</v>
+        <v>-112</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4113</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1628</v>
+        <v>0.5061</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -12693,28 +13027,28 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PIT @ NYM</t>
+          <t>CWS @ MIL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>PIT @ NYM</t>
+          <t>CWS @ MIL</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>NRFI</t>
+          <t>YRFI</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>-162</v>
+        <v>-102</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5818</v>
+        <v>0.5314</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -12739,12 +13073,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ARI @ LAD</t>
+          <t>PIT @ NYM</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ARI @ LAD</t>
+          <t>PIT @ NYM</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -12754,13 +13088,13 @@
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>-119</v>
+        <v>120</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4875</v>
+        <v>0.5746</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -12818,6 +13152,52 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ARI @ LAD</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ARI @ LAD</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>NRFI</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="n">
+        <v>-105</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-0.4852</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tracking/picks.xlsx
+++ b/tracking/picks.xlsx
@@ -1556,13 +1556,19 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-100</v>
+      </c>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="N22" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1604,13 +1610,19 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-100</v>
+      </c>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="N23" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1652,13 +1664,19 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>2</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-100</v>
+      </c>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="N24" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1700,13 +1718,19 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>70.92</v>
+      </c>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="N25" t="n">
+        <v>35.46</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1748,13 +1772,19 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>4</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-100</v>
+      </c>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="N26" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1796,13 +1826,19 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-100</v>
+      </c>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="N27" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1844,13 +1880,19 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>2</v>
+      </c>
+      <c r="L28" t="n">
+        <v>65.15000000000001</v>
+      </c>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="N28" t="n">
+        <v>32.57</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1892,13 +1934,19 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-100</v>
+      </c>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="N29" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1940,13 +1988,19 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>8</v>
+      </c>
+      <c r="L30" t="n">
+        <v>66.67</v>
+      </c>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="N30" t="n">
+        <v>33.33</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1988,13 +2042,19 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" t="n">
+        <v>57.14</v>
+      </c>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="N31" t="n">
+        <v>28.57</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2036,13 +2096,19 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" t="n">
+        <v>73.8</v>
+      </c>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="N32" t="n">
+        <v>36.9</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2084,13 +2150,19 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>-100</v>
+      </c>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="N33" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2132,13 +2204,19 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>2</v>
+      </c>
+      <c r="L34" t="n">
+        <v>-100</v>
+      </c>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="N34" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2180,13 +2258,19 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>-100</v>
+      </c>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="N35" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2228,13 +2312,19 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-100</v>
+      </c>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="N36" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2276,13 +2366,19 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>-100</v>
+      </c>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="N37" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2324,13 +2420,19 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" t="n">
+        <v>54.05</v>
+      </c>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="N38" t="n">
+        <v>27.03</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2372,13 +2474,19 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>80</v>
+      </c>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="N39" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2420,13 +2528,19 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>3</v>
+      </c>
+      <c r="L40" t="n">
+        <v>-100</v>
+      </c>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+      <c r="N40" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2468,13 +2582,19 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" t="n">
+        <v>58.82</v>
+      </c>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="N41" t="n">
+        <v>29.41</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2516,13 +2636,19 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>15</v>
+      </c>
+      <c r="L42" t="n">
+        <v>57.14</v>
+      </c>
       <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="N42" t="n">
+        <v>28.57</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2564,13 +2690,19 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>16</v>
+      </c>
+      <c r="L43" t="n">
+        <v>145</v>
+      </c>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+      <c r="N43" t="n">
+        <v>72.5</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2612,13 +2744,19 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>2</v>
+      </c>
+      <c r="L44" t="n">
+        <v>-100</v>
+      </c>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+      <c r="N44" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2660,13 +2798,19 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>21</v>
+      </c>
+      <c r="L45" t="n">
+        <v>90.91</v>
+      </c>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="N45" t="n">
+        <v>45.45</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2708,13 +2852,19 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>15</v>
+      </c>
+      <c r="L46" t="n">
+        <v>-100</v>
+      </c>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+      <c r="N46" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2756,13 +2906,19 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>11</v>
+      </c>
+      <c r="L47" t="n">
+        <v>10000</v>
+      </c>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="N47" t="n">
+        <v>5000</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2804,13 +2960,19 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>15</v>
+      </c>
+      <c r="L48" t="n">
+        <v>59.7</v>
+      </c>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="N48" t="n">
+        <v>29.85</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2852,13 +3014,19 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>11</v>
+      </c>
+      <c r="L49" t="n">
+        <v>-100</v>
+      </c>
       <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+      <c r="N49" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2900,13 +3068,19 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>5</v>
+      </c>
+      <c r="L50" t="n">
+        <v>-100</v>
+      </c>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="N50" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3510,13 +3684,19 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>-100</v>
+      </c>
       <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+      <c r="N63" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3558,13 +3738,19 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>1</v>
+      </c>
+      <c r="L64" t="n">
+        <v>-100</v>
+      </c>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+      <c r="N64" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3606,13 +3792,19 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>120.5</v>
+      </c>
       <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+      <c r="N65" t="n">
+        <v>60.25</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3654,13 +3846,19 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>54.05</v>
+      </c>
       <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+      <c r="N66" t="n">
+        <v>27.03</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3702,13 +3900,19 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>106</v>
+      </c>
       <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+      <c r="N67" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3750,13 +3954,19 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>1</v>
+      </c>
+      <c r="L68" t="n">
+        <v>-100</v>
+      </c>
       <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+      <c r="N68" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3798,13 +4008,19 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>126.5</v>
+      </c>
       <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+      <c r="N69" t="n">
+        <v>63.25</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3846,13 +4062,19 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>-100</v>
+      </c>
       <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+      <c r="N70" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3894,13 +4116,19 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>1</v>
+      </c>
+      <c r="L71" t="n">
+        <v>60.79</v>
+      </c>
       <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+      <c r="N71" t="n">
+        <v>30.4</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3942,13 +4170,19 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>54.95</v>
+      </c>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+      <c r="N72" t="n">
+        <v>27.47</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3990,13 +4224,19 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>9</v>
+      </c>
+      <c r="L73" t="n">
+        <v>-100</v>
+      </c>
       <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+      <c r="N73" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4038,13 +4278,19 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>14</v>
+      </c>
+      <c r="L74" t="n">
+        <v>-100</v>
+      </c>
       <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+      <c r="N74" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4086,13 +4332,19 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>18</v>
+      </c>
+      <c r="L75" t="n">
+        <v>125</v>
+      </c>
       <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+      <c r="N75" t="n">
+        <v>62.5</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4134,13 +4386,19 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>18</v>
+      </c>
+      <c r="L76" t="n">
+        <v>80</v>
+      </c>
       <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+      <c r="N76" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4182,13 +4440,19 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>14</v>
+      </c>
+      <c r="L77" t="n">
+        <v>-100</v>
+      </c>
       <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+      <c r="N77" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4602,13 +4866,19 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>3</v>
+      </c>
+      <c r="L86" t="n">
+        <v>-100</v>
+      </c>
       <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+      <c r="N86" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4650,13 +4920,19 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>3</v>
+      </c>
+      <c r="L87" t="n">
+        <v>-100</v>
+      </c>
       <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+      <c r="N87" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4698,13 +4974,19 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>1</v>
+      </c>
+      <c r="L88" t="n">
+        <v>-100</v>
+      </c>
       <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+      <c r="N88" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4746,13 +5028,19 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
+        <v>1</v>
+      </c>
+      <c r="L89" t="n">
+        <v>68.97</v>
+      </c>
       <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+      <c r="N89" t="n">
+        <v>34.48</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4794,13 +5082,19 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
+        <v>-100</v>
+      </c>
       <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+      <c r="N90" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4842,13 +5136,19 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>15</v>
+      </c>
+      <c r="L91" t="n">
+        <v>54.5</v>
+      </c>
       <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+      <c r="N91" t="n">
+        <v>27.25</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4984,13 +5284,19 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>2</v>
+      </c>
+      <c r="L94" t="n">
+        <v>500</v>
+      </c>
       <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+      <c r="N94" t="n">
+        <v>250</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5032,13 +5338,19 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>11</v>
+      </c>
+      <c r="L95" t="n">
+        <v>-100</v>
+      </c>
       <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+      <c r="N95" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5268,13 +5580,19 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
+        <v>-100</v>
+      </c>
       <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
+      <c r="N100" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5316,13 +5634,19 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="n">
+        <v>200</v>
+      </c>
       <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+      <c r="N101" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5364,13 +5688,19 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>-100</v>
+      </c>
       <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
+      <c r="N102" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5412,13 +5742,19 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="n">
+        <v>190.48</v>
+      </c>
       <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
+      <c r="N103" t="n">
+        <v>95.23999999999999</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5460,13 +5796,19 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="n">
+        <v>-100</v>
+      </c>
       <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
+      <c r="N104" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5508,13 +5850,19 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K105" t="n">
+        <v>1</v>
+      </c>
+      <c r="L105" t="n">
+        <v>92.59</v>
+      </c>
       <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
+      <c r="N105" t="n">
+        <v>46.3</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5604,13 +5952,19 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K107" t="n">
+        <v>2</v>
+      </c>
+      <c r="L107" t="n">
+        <v>80.65000000000001</v>
+      </c>
       <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
+      <c r="N107" t="n">
+        <v>40.32</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5652,13 +6006,19 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K108" t="n">
+        <v>4</v>
+      </c>
+      <c r="L108" t="n">
+        <v>100</v>
+      </c>
       <c r="M108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
+      <c r="N108" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5700,13 +6060,19 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K109" t="n">
+        <v>1</v>
+      </c>
+      <c r="L109" t="n">
+        <v>115</v>
+      </c>
       <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
+      <c r="N109" t="n">
+        <v>57.5</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5748,13 +6114,19 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L110" t="n">
+        <v>-100</v>
+      </c>
       <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
+      <c r="N110" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5796,13 +6168,19 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K111" t="n">
+        <v>8</v>
+      </c>
+      <c r="L111" t="n">
+        <v>84.75</v>
+      </c>
       <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
+      <c r="N111" t="n">
+        <v>42.37</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5844,13 +6222,19 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K112" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" t="n">
+        <v>72.45999999999999</v>
+      </c>
       <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
+      <c r="N112" t="n">
+        <v>36.23</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5892,13 +6276,19 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K113" t="n">
+        <v>12</v>
+      </c>
+      <c r="L113" t="n">
+        <v>20000</v>
+      </c>
       <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
+      <c r="N113" t="n">
+        <v>10000</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5940,13 +6330,19 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K114" t="n">
+        <v>18</v>
+      </c>
+      <c r="L114" t="n">
+        <v>109.5</v>
+      </c>
       <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
+      <c r="N114" t="n">
+        <v>54.75</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5988,13 +6384,19 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K115" t="n">
+        <v>18</v>
+      </c>
+      <c r="L115" t="n">
+        <v>-100</v>
+      </c>
       <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
+      <c r="N115" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6174,13 +6576,19 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K119" t="n">
+        <v>1</v>
+      </c>
+      <c r="L119" t="n">
+        <v>38.46</v>
+      </c>
       <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
+      <c r="N119" t="n">
+        <v>19.23</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6222,13 +6630,19 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K120" t="n">
+        <v>1</v>
+      </c>
+      <c r="L120" t="n">
+        <v>47.62</v>
+      </c>
       <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
+      <c r="N120" t="n">
+        <v>23.81</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6270,13 +6684,19 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K121" t="n">
+        <v>12</v>
+      </c>
+      <c r="L121" t="n">
+        <v>-100</v>
+      </c>
       <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
+      <c r="N121" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6335,7 +6755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6948,6 +7368,3786 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
         <v>5000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NYM vs PIT</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Jared Triolo</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.488</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.4119</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>MIL vs CWS</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Colson Montgomery</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-134.5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.6704</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.1361</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>TBR vs STL</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Jordan Walker</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>128.5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.5208</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.1146</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PIT vs NYM</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Jorge Polanco</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-141</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.1053</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>70.92</v>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="n">
+        <v>35.46</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CHC vs WSN</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Jacob Young</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.5992</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.1134</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>4</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CHC vs WSN</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>James Wood</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-161</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.6791</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.1056</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PIT vs NYM</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Juan Soto</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-153.5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.1028</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>65.15000000000001</v>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="n">
+        <v>32.57</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CWS vs MIL</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>David Hamilton</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-118</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.6207</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.1178</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NYM vs PIT</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Brandon Lowe</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-150</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.6529</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>8</v>
+      </c>
+      <c r="L20" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>MIN vs BAL</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Tyler O'Neill</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-175</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.6989</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="n">
+        <v>28.57</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CHC vs WSN</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CJ Abrams</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-135.5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.6195000000000001</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.0832</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="n">
+        <v>36.9</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>PIT vs NYM</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Francisco Lindor</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-180.5</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.6811</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.0843</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CIN vs BOS</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Ceddanne Rafaela</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-178</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.6949</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.09719999999999999</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>2</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NYM vs PIT</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Spencer Horwitz</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-126</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.5911999999999999</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.0756</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>MIL vs CWS</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Andrew Benintendi</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-141.5</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.6186</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.0741</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>MIL vs CWS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Miguel Vargas</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-145</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.6219</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.0713</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>MIN vs BAL</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Samuel Basallo</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-185</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.6848</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.0808</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>54.05</v>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="n">
+        <v>27.03</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>MIN vs BAL</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Gunnar Henderson</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-125</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.5917</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.07480000000000001</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>80</v>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>MIN vs BAL</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Adley Rutschman</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-172</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.6712</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.0818</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>3</v>
+      </c>
+      <c r="L30" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>BAL vs MIN</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Austin Martin</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-170</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.6679</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.08169999999999999</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" t="n">
+        <v>58.82</v>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="n">
+        <v>29.41</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>PHI vs TEX</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Wyatt Langford</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-20</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.6369</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.2456</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CHC vs WSN</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Keibert Ruiz</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.5118</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.4948</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>BOS vs CIN</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Ke'Bryan Hayes</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G34" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.5485</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.1263</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="n">
+        <v>60.25</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CIN vs BOS</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Isiah Kiner-Falefa</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-185</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.7533</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.1467</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>54.05</v>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="n">
+        <v>27.03</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>PHI vs TEX</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Sam Haggerty</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G36" t="n">
+        <v>106</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.5615</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.1109</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>106</v>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>HOU vs LAA</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Oswald Peraza</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-125</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.6553</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.1406</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>1</v>
+      </c>
+      <c r="L37" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>LAA vs HOU</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Jake Meyers</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G38" t="n">
+        <v>126.5</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.5076000000000001</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.0975</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>126.5</v>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="n">
+        <v>63.25</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>HOU vs LAA</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Zach Neto</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-183.5</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.6847</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>DET vs SDP</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Manny Machado</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-164.5</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.6501</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.0707</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" t="n">
+        <v>60.79</v>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="n">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>LAA vs HOU</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Yainer Diaz</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-182</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.6797</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>54.95</v>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="n">
+        <v>27.47</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>STL vs TBR</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Nick Fortes</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G42" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.5552</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>3</v>
+      </c>
+      <c r="L42" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>STL vs TBR</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Ben Williamson</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-195.5</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.7428</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.1248</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>3</v>
+      </c>
+      <c r="L43" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>STL vs TBR</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Carson Williams</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G44" t="n">
+        <v>110</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.5195</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SDP vs DET</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Spencer Torkelson</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-145</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.6225000000000001</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.07190000000000001</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" t="n">
+        <v>68.97</v>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="n">
+        <v>34.48</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>BAL vs MIN</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Matt Wallner</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-143.5</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.6172</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.0706</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>TBR vs STL</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Masyn Winn</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-20</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.5832000000000001</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>2</v>
+      </c>
+      <c r="L47" t="n">
+        <v>500</v>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>MIN vs BAL</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Colton Cowser</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G48" t="n">
+        <v>250</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.5614</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.2085</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>BAL vs MIN</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Royce Lewis</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-50</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.4602</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.2055</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>200</v>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>CLE vs SEA</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Cal Raleigh</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-147.5</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.7043</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>BAL vs MIN</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Josh Bell</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-52.5</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.4279</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.1718</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>190.48</v>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="n">
+        <v>95.23999999999999</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>MIN vs BAL</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Gunnar Henderson</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.4083</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>SEA vs CLE</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Kyle Manzardo</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-108</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.6057</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.1269</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>1</v>
+      </c>
+      <c r="L53" t="n">
+        <v>92.59</v>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="n">
+        <v>46.3</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>CLE vs SEA</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Randy Arozarena</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-124</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.6155</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.1069</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>2</v>
+      </c>
+      <c r="L54" t="n">
+        <v>80.65000000000001</v>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="n">
+        <v>40.32</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>SEA vs CLE</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Rhys Hoskins</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G55" t="n">
+        <v>100</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.5556</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>4</v>
+      </c>
+      <c r="L55" t="n">
+        <v>100</v>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>SEA vs CLE</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Gabriel Arias</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G56" t="n">
+        <v>115</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.5197000000000001</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>1</v>
+      </c>
+      <c r="L56" t="n">
+        <v>115</v>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ARI vs LAD</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Miguel Rojas</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G57" t="n">
+        <v>113</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.5123</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.0765</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L57" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>CLE vs SEA</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Dominic Canzone</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-118</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.5725</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.0725</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>8</v>
+      </c>
+      <c r="L58" t="n">
+        <v>84.75</v>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="n">
+        <v>42.37</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>LAA vs HOU</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Yordan Alvarez</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-138</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.6188</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>72.45999999999999</v>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="n">
+        <v>36.23</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ARI vs LAD</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Miguel Rojas</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-260</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.7621</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>1</v>
+      </c>
+      <c r="L60" t="n">
+        <v>38.46</v>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="n">
+        <v>19.23</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ARI vs LAD</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Max Muncy</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-210</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.7116</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.07149999999999999</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>1</v>
+      </c>
+      <c r="L61" t="n">
+        <v>47.62</v>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="n">
+        <v>23.81</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>CWS vs MIL</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-175</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.7971</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.2083</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>15</v>
+      </c>
+      <c r="L62" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="n">
+        <v>28.57</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>BAL vs MIN</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Joe Ryan</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G63" t="n">
+        <v>145</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.7798</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.4004</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>16</v>
+      </c>
+      <c r="L63" t="n">
+        <v>145</v>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="n">
+        <v>72.5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>NYM vs PIT</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Paul Skenes</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-104.5</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.7044</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.2317</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>2</v>
+      </c>
+      <c r="L64" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>MIN vs BAL</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Trevor Rogers</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G65" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.7123</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.2247</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>21</v>
+      </c>
+      <c r="L65" t="n">
+        <v>90.91</v>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="n">
+        <v>45.45</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>PIT vs NYM</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G66" t="n">
+        <v>140.5</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.6554</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.2699</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>15</v>
+      </c>
+      <c r="L66" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>CHC vs WSN</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Cade Cavalli</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.1997</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.1827</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>11</v>
+      </c>
+      <c r="L67" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>STL vs TBR</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G68" t="n">
+        <v>-167.5</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.7352</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.1525</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>15</v>
+      </c>
+      <c r="L68" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="n">
+        <v>29.85</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>WSN vs CHC</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Matthew Boyd</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G69" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.6491</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.1491</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>11</v>
+      </c>
+      <c r="L69" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>MIL vs CWS</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Shane Smith</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G70" t="n">
+        <v>-155</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.7044</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.1431</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>5</v>
+      </c>
+      <c r="L70" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>DET vs SDP</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Nick Pivetta</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G71" t="n">
+        <v>-116.5</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.8866000000000001</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.3851</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>9</v>
+      </c>
+      <c r="L71" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>PHI vs TEX</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Nathan Eovaldi</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G72" t="n">
+        <v>-125</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.8067</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>14</v>
+      </c>
+      <c r="L72" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>BOS vs CIN</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Andrew Abbott</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G73" t="n">
+        <v>125</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.2242</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>18</v>
+      </c>
+      <c r="L73" t="n">
+        <v>125</v>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="n">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>CIN vs BOS</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Garrett Crochet</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G74" t="n">
+        <v>-125</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.6627999999999999</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>18</v>
+      </c>
+      <c r="L74" t="n">
+        <v>80</v>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>LAA vs HOU</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Hunter Brown</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-110.5</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.6015</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>14</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>TBR vs STL</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Matthew Liberatore</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G76" t="n">
+        <v>-183.5</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.7463</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.1529</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>15</v>
+      </c>
+      <c r="L76" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="n">
+        <v>27.25</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>CHC vs WSN</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Cade Cavalli</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G77" t="n">
+        <v>-140.5</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.8003</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.4224</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>11</v>
+      </c>
+      <c r="L77" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>LAD vs ARI</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Zac Gallen</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G78" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.3257</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>12</v>
+      </c>
+      <c r="L78" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ARI vs LAD</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Yoshinobu Yamamoto</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G79" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.2304</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>18</v>
+      </c>
+      <c r="L79" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="n">
+        <v>54.75</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>CIN vs BOS</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Garrett Crochet</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G80" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.2589</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>18</v>
+      </c>
+      <c r="L80" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>LAD vs ARI</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Zac Gallen</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G81" t="n">
+        <v>-155</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.6659</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.0977</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>12</v>
+      </c>
+      <c r="L81" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="n">
+        <v>-50</v>
       </c>
     </row>
   </sheetData>
@@ -8768,13 +12968,19 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>500</v>
+      </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>250</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8816,13 +13022,19 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-100</v>
+      </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8864,13 +13076,19 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>68.97</v>
+      </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="N12" t="n">
+        <v>34.48</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8912,13 +13130,19 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-100</v>
+      </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="N13" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8960,13 +13184,19 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>60.79</v>
+      </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" t="n">
+        <v>30.4</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -9008,13 +13238,19 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-100</v>
+      </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="N15" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9056,13 +13292,19 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>54.95</v>
+      </c>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>27.47</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9104,13 +13346,19 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-100</v>
+      </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="N17" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9152,13 +13400,19 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-100</v>
+      </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="N18" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -9200,13 +13454,19 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-100</v>
+      </c>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="N19" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9248,13 +13508,19 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>200</v>
+      </c>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="N20" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -9296,13 +13562,19 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>92.59</v>
+      </c>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="N21" t="n">
+        <v>46.3</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -9344,13 +13616,19 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>190.48</v>
+      </c>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="N22" t="n">
+        <v>95.23999999999999</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -9392,13 +13670,19 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-100</v>
+      </c>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="N23" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -9440,13 +13724,19 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>126.5</v>
+      </c>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="N24" t="n">
+        <v>63.25</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -9536,13 +13826,19 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>2</v>
+      </c>
+      <c r="L26" t="n">
+        <v>80.65000000000001</v>
+      </c>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="N26" t="n">
+        <v>40.32</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -9584,13 +13880,19 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>4</v>
+      </c>
+      <c r="L27" t="n">
+        <v>100</v>
+      </c>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="N27" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -9632,13 +13934,19 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>115</v>
+      </c>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="N28" t="n">
+        <v>57.5</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -9680,13 +13988,19 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-100</v>
+      </c>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="N29" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -9728,13 +14042,19 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>8</v>
+      </c>
+      <c r="L30" t="n">
+        <v>84.75</v>
+      </c>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="N30" t="n">
+        <v>42.37</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -9776,13 +14096,19 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>72.45999999999999</v>
+      </c>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="N31" t="n">
+        <v>36.23</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -9824,13 +14150,19 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>-100</v>
+      </c>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="N32" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -9872,13 +14204,19 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" t="n">
+        <v>-100</v>
+      </c>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="N33" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -9920,13 +14258,19 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>-100</v>
+      </c>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="N34" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -9968,13 +14312,19 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>54.05</v>
+      </c>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="N35" t="n">
+        <v>27.03</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -10016,13 +14366,19 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>2</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-100</v>
+      </c>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="N36" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -10064,13 +14420,19 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>-100</v>
+      </c>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="N37" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -10112,13 +14474,19 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>2</v>
+      </c>
+      <c r="L38" t="n">
+        <v>-100</v>
+      </c>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="N38" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -10160,13 +14528,19 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" t="n">
+        <v>70.92</v>
+      </c>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="N39" t="n">
+        <v>35.46</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -10208,13 +14582,19 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>4</v>
+      </c>
+      <c r="L40" t="n">
+        <v>-100</v>
+      </c>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+      <c r="N40" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -10256,13 +14636,19 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>-100</v>
+      </c>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="N41" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -10304,13 +14690,19 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>2</v>
+      </c>
+      <c r="L42" t="n">
+        <v>65.15000000000001</v>
+      </c>
       <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="N42" t="n">
+        <v>32.57</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -10352,13 +14744,19 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>1</v>
+      </c>
+      <c r="L43" t="n">
+        <v>-100</v>
+      </c>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+      <c r="N43" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -10400,13 +14798,19 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>8</v>
+      </c>
+      <c r="L44" t="n">
+        <v>66.67</v>
+      </c>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+      <c r="N44" t="n">
+        <v>33.33</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -10448,13 +14852,19 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" t="n">
+        <v>57.14</v>
+      </c>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="N45" t="n">
+        <v>28.57</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -10496,13 +14906,19 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" t="n">
+        <v>73.8</v>
+      </c>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+      <c r="N46" t="n">
+        <v>36.9</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -10544,13 +14960,19 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>-100</v>
+      </c>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="N47" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -10592,13 +15014,19 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>2</v>
+      </c>
+      <c r="L48" t="n">
+        <v>-100</v>
+      </c>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="N48" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -10640,13 +15068,19 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>-100</v>
+      </c>
       <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+      <c r="N49" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -10688,13 +15122,19 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>-100</v>
+      </c>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="N50" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -10736,13 +15176,19 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>-100</v>
+      </c>
       <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+      <c r="N51" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -10784,13 +15230,19 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" t="n">
+        <v>54.05</v>
+      </c>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+      <c r="N52" t="n">
+        <v>27.03</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -10832,13 +15284,19 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>80</v>
+      </c>
       <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+      <c r="N53" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -10880,13 +15338,19 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>3</v>
+      </c>
+      <c r="L54" t="n">
+        <v>-100</v>
+      </c>
       <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+      <c r="N54" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -10928,13 +15392,19 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>1</v>
+      </c>
+      <c r="L55" t="n">
+        <v>58.82</v>
+      </c>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+      <c r="N55" t="n">
+        <v>29.41</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -10976,13 +15446,19 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>-100</v>
+      </c>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+      <c r="N56" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -11024,13 +15500,19 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L57" t="n">
+        <v>38.46</v>
+      </c>
       <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+      <c r="N57" t="n">
+        <v>19.23</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -11072,13 +15554,19 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>120.5</v>
+      </c>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+      <c r="N58" t="n">
+        <v>60.25</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -11120,13 +15608,19 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>106</v>
+      </c>
       <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+      <c r="N59" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -11168,13 +15662,19 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>1</v>
+      </c>
+      <c r="L60" t="n">
+        <v>47.62</v>
+      </c>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+      <c r="N60" t="n">
+        <v>23.81</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11410,13 +15910,19 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>18</v>
+      </c>
+      <c r="L4" t="n">
+        <v>109.5</v>
+      </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>54.75</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11458,13 +15964,19 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>12</v>
+      </c>
+      <c r="L5" t="n">
+        <v>20000</v>
+      </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>10000</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11506,13 +16018,19 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>11</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-100</v>
+      </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11554,13 +16072,19 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>15</v>
+      </c>
+      <c r="L7" t="n">
+        <v>54.5</v>
+      </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>27.25</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11602,13 +16126,19 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>14</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-100</v>
+      </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11650,13 +16180,19 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>18</v>
+      </c>
+      <c r="L9" t="n">
+        <v>80</v>
+      </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11698,13 +16234,19 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>18</v>
+      </c>
+      <c r="L10" t="n">
+        <v>125</v>
+      </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>62.5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -11746,13 +16288,19 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>14</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-100</v>
+      </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -11794,13 +16342,19 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-100</v>
+      </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="N12" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -11842,13 +16396,19 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-100</v>
+      </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="N13" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -11890,13 +16450,19 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>11</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-100</v>
+      </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -11938,13 +16504,19 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>15</v>
+      </c>
+      <c r="L15" t="n">
+        <v>59.7</v>
+      </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="N15" t="n">
+        <v>29.85</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -11986,13 +16558,19 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>11</v>
+      </c>
+      <c r="L16" t="n">
+        <v>10000</v>
+      </c>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>5000</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -12034,13 +16612,19 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>15</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-100</v>
+      </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="N17" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -12082,13 +16666,19 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>21</v>
+      </c>
+      <c r="L18" t="n">
+        <v>90.91</v>
+      </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="N18" t="n">
+        <v>45.45</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -12130,13 +16720,19 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-100</v>
+      </c>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="N19" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -12178,13 +16774,19 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>16</v>
+      </c>
+      <c r="L20" t="n">
+        <v>145</v>
+      </c>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="N20" t="n">
+        <v>72.5</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -12226,13 +16828,19 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>15</v>
+      </c>
+      <c r="L21" t="n">
+        <v>57.14</v>
+      </c>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="N21" t="n">
+        <v>28.57</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -12274,13 +16882,19 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>18</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-100</v>
+      </c>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="N22" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -12322,13 +16936,19 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>12</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-100</v>
+      </c>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="N23" t="n">
+        <v>-50</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tracking/picks.xlsx
+++ b/tracking/picks.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Picks" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Season Results" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Moneyline" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totals" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hitter TB" sheetId="5" state="visible" r:id="rId5"/>
@@ -544,13 +544,21 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>7-0</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>-100</v>
+      </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -592,13 +600,19 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>7</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-100</v>
+      </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1016,13 +1030,21 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>away_1st=0 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>63.49</v>
+      </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="n">
+        <v>31.75</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1064,19 +1086,13 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>4000</v>
-      </c>
+          <t>ODDS_ERR</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="n">
-        <v>2000</v>
-      </c>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1172,19 +1188,13 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>15</v>
-      </c>
-      <c r="L14" t="n">
-        <v>10000</v>
-      </c>
+          <t>ODDS_ERR</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="n">
-        <v>5000</v>
-      </c>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1224,13 +1234,21 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>away_1st=0 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>-100</v>
+      </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="N15" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1270,13 +1288,21 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>70.67</v>
+      </c>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>35.34</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1316,13 +1342,21 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>7-11</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>82.64</v>
+      </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="N17" t="n">
+        <v>41.32</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1364,13 +1398,19 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>16</v>
+      </c>
+      <c r="L18" t="n">
+        <v>95.23999999999999</v>
+      </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="N18" t="n">
+        <v>47.62</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1412,13 +1452,19 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>18</v>
+      </c>
+      <c r="L19" t="n">
+        <v>82.64</v>
+      </c>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="N19" t="n">
+        <v>41.32</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1460,13 +1506,19 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>14</v>
+      </c>
+      <c r="L20" t="n">
+        <v>94.34</v>
+      </c>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="N20" t="n">
+        <v>47.17</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1508,13 +1560,19 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L21" t="n">
+        <v>86.95999999999999</v>
+      </c>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="N21" t="n">
+        <v>43.48</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1556,19 +1614,13 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>2</v>
-      </c>
-      <c r="L22" t="n">
-        <v>-100</v>
-      </c>
+          <t>ODDS_ERR</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="n">
-        <v>-50</v>
-      </c>
+      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2906,19 +2958,13 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K47" t="n">
-        <v>11</v>
-      </c>
-      <c r="L47" t="n">
-        <v>10000</v>
-      </c>
+          <t>ODDS_ERR</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" t="n">
-        <v>5000</v>
-      </c>
+      <c r="N47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3120,13 +3166,21 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>away_1st=2 home_1st=5</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>120</v>
+      </c>
       <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+      <c r="N51" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3166,13 +3220,21 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>away_1st=1 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>98.04000000000001</v>
+      </c>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+      <c r="N52" t="n">
+        <v>49.02</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3212,13 +3274,21 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>away_1st=0 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>-100</v>
+      </c>
       <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+      <c r="N53" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3258,13 +3328,21 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>away_1st=0 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>-100</v>
+      </c>
       <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+      <c r="N54" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3304,13 +3382,21 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>3-5</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>63.9</v>
+      </c>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+      <c r="N55" t="n">
+        <v>31.95</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3350,13 +3436,21 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>-100</v>
+      </c>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+      <c r="N56" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3396,13 +3490,21 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>8-2</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>-100</v>
+      </c>
       <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+      <c r="N57" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3444,13 +3546,19 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>3</v>
+      </c>
+      <c r="L58" t="n">
+        <v>-100</v>
+      </c>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+      <c r="N58" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3492,13 +3600,19 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>10</v>
+      </c>
+      <c r="L59" t="n">
+        <v>90.91</v>
+      </c>
       <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+      <c r="N59" t="n">
+        <v>45.45</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3540,13 +3654,19 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
+          <t>PUSH</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>8</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3588,13 +3708,19 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>3</v>
+      </c>
+      <c r="L61" t="n">
+        <v>-100</v>
+      </c>
       <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+      <c r="N61" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3636,13 +3762,19 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>3</v>
+      </c>
+      <c r="L62" t="n">
+        <v>95.23999999999999</v>
+      </c>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+      <c r="N62" t="n">
+        <v>47.62</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3684,19 +3816,13 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="n">
-        <v>-100</v>
-      </c>
+          <t>ODDS_ERR</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
-      <c r="N63" t="n">
-        <v>-50</v>
-      </c>
+      <c r="N63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3738,19 +3864,13 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K64" t="n">
-        <v>1</v>
-      </c>
-      <c r="L64" t="n">
-        <v>-100</v>
-      </c>
+          <t>ODDS_ERR</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" t="n">
-        <v>-50</v>
-      </c>
+      <c r="N64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4492,13 +4612,21 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>away_1st=0 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>-100</v>
+      </c>
       <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+      <c r="N78" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4538,13 +4666,21 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>away_1st=1 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>-100</v>
+      </c>
       <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+      <c r="N79" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4584,13 +4720,21 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>away_1st=0 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>64.52</v>
+      </c>
       <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+      <c r="N80" t="n">
+        <v>32.26</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4630,13 +4774,21 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>away_1st=4 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>118</v>
+      </c>
       <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+      <c r="N81" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4676,13 +4828,21 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>away_1st=0 home_1st=2</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>94.34</v>
+      </c>
       <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+      <c r="N82" t="n">
+        <v>47.17</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4722,13 +4882,21 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>7-9</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>107.5</v>
+      </c>
       <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+      <c r="N83" t="n">
+        <v>53.75</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4770,13 +4938,19 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>16</v>
+      </c>
+      <c r="L84" t="n">
+        <v>90.91</v>
+      </c>
       <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+      <c r="N84" t="n">
+        <v>45.45</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4818,13 +4992,19 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>16</v>
+      </c>
+      <c r="L85" t="n">
+        <v>95.23999999999999</v>
+      </c>
       <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+      <c r="N85" t="n">
+        <v>47.62</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5188,13 +5368,21 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>away_1st=0 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L92" t="n">
+        <v>-100</v>
+      </c>
       <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+      <c r="N92" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5236,13 +5424,19 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>16</v>
+      </c>
+      <c r="L93" t="n">
+        <v>90.91</v>
+      </c>
       <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+      <c r="N93" t="n">
+        <v>45.45</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5284,19 +5478,13 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K94" t="n">
-        <v>2</v>
-      </c>
-      <c r="L94" t="n">
-        <v>500</v>
-      </c>
+          <t>ODDS_ERR</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
-      <c r="N94" t="n">
-        <v>250</v>
-      </c>
+      <c r="N94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5390,13 +5578,21 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>away_1st=4 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L96" t="n">
+        <v>-100</v>
+      </c>
       <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
+      <c r="N96" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5436,13 +5632,21 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>2-8</t>
+        </is>
+      </c>
+      <c r="L97" t="n">
+        <v>-100</v>
+      </c>
       <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
+      <c r="N97" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5484,13 +5688,19 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>10</v>
+      </c>
+      <c r="L98" t="n">
+        <v>82.3</v>
+      </c>
       <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+      <c r="N98" t="n">
+        <v>41.15</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5532,13 +5742,19 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>10</v>
+      </c>
+      <c r="L99" t="n">
+        <v>-100</v>
+      </c>
       <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+      <c r="N99" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5634,19 +5850,13 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K101" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" t="n">
-        <v>200</v>
-      </c>
+          <t>ODDS_ERR</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr"/>
-      <c r="N101" t="n">
-        <v>100</v>
-      </c>
+      <c r="N101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5742,19 +5952,13 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K103" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" t="n">
-        <v>190.48</v>
-      </c>
+          <t>ODDS_ERR</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr"/>
-      <c r="N103" t="n">
-        <v>95.23999999999999</v>
-      </c>
+      <c r="N103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5796,19 +6000,13 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K104" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" t="n">
-        <v>-100</v>
-      </c>
+          <t>ODDS_ERR</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr"/>
-      <c r="N104" t="n">
-        <v>-50</v>
-      </c>
+      <c r="N104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5904,13 +6102,17 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>DNP</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
       <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6276,19 +6478,13 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K113" t="n">
-        <v>12</v>
-      </c>
-      <c r="L113" t="n">
-        <v>20000</v>
-      </c>
+          <t>ODDS_ERR</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr"/>
-      <c r="N113" t="n">
-        <v>10000</v>
-      </c>
+      <c r="N113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6384,19 +6580,13 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K115" t="n">
-        <v>18</v>
-      </c>
-      <c r="L115" t="n">
-        <v>-100</v>
-      </c>
+          <t>ODDS_ERR</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr"/>
-      <c r="N115" t="n">
-        <v>-50</v>
-      </c>
+      <c r="N115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6436,13 +6626,21 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>away_1st=2 home_1st=5</t>
+        </is>
+      </c>
+      <c r="L116" t="n">
+        <v>-100</v>
+      </c>
       <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
+      <c r="N116" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6482,13 +6680,21 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>away_1st=0 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L117" t="n">
+        <v>-100</v>
+      </c>
       <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
+      <c r="N117" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6528,13 +6734,21 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>away_1st=1 home_1st=1</t>
+        </is>
+      </c>
+      <c r="L118" t="n">
+        <v>-100</v>
+      </c>
       <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
+      <c r="N118" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6736,13 +6950,21 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>away_1st=0 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L122" t="n">
+        <v>95.23999999999999</v>
+      </c>
       <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
+      <c r="N122" t="n">
+        <v>47.62</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6755,193 +6977,104 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N81"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>pick_date</t>
+          <t>Window</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>game</t>
+          <t>W</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>subject</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>bet_type</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>Win%</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>odds</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>model_prob</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>edge</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>result</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>pnl</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>pnl_50</t>
+          <t>P&amp;L ($50 stake)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260325</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>SFG vs NYY</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Giancarlo Stanton</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>0.5</v>
       </c>
       <c r="G2" t="n">
-        <v>-159.5</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.6656</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L2" t="n">
-        <v>62.7</v>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="n">
-        <v>31.35</v>
+        <v>-37.64</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260325</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>NYY vs SFG</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Patrick Bailey</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5</v>
+        <v>0.714</v>
       </c>
       <c r="G3" t="n">
-        <v>-105</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.5429</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.06950000000000001</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>95.23999999999999</v>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="n">
-        <v>47.62</v>
+        <v>252.33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260325</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6949,377 +7082,188 @@
           <t>Hitter TB</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>NYY vs SFG</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Rafael Devers</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
+      <c r="C4" t="n">
+        <v>28</v>
+      </c>
+      <c r="D4" t="n">
+        <v>22</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>144</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.4371</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.0544</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="n">
-        <v>-50</v>
+        <v>-41.28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260325</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>SFG vs NYY</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Trent Grisham</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>0.5</v>
       </c>
       <c r="G5" t="n">
-        <v>-165</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.6313</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.0532</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L5" t="n">
-        <v>60.61</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="n">
-        <v>30.3</v>
+        <v>-39.13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260325</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>SFG vs NYY</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Ryan McMahon</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5</v>
+        <v>0.412</v>
       </c>
       <c r="G6" t="n">
-        <v>-115</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.5377</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.0426</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>86.95999999999999</v>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="n">
-        <v>43.48</v>
+        <v>-173.18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260325</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>SFG vs NYY</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Cody Bellinger</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>58</v>
+      </c>
+      <c r="D7" t="n">
+        <v>49</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5</v>
+        <v>0.542</v>
       </c>
       <c r="G7" t="n">
-        <v>135</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.4371</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="n">
-        <v>-50</v>
+        <v>-38.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260325</t>
+          <t>Last 30d</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>NYY vs SFG</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Harrison Bader</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0.5</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.4608</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>4000</v>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="n">
-        <v>2000</v>
+        <v>-37.64</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260325</t>
+          <t>Last 30d</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>NYY vs SFG</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Rafael Devers</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5</v>
+        <v>0.714</v>
       </c>
       <c r="G9" t="n">
-        <v>-161</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.6611</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.0876</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>62.11</v>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="n">
-        <v>31.06</v>
+        <v>252.33</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260325</t>
+          <t>Last 30d</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pitcher Outs</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>SFG vs NYY</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Max Fried</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>28</v>
+      </c>
+      <c r="D10" t="n">
+        <v>22</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>16.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>100</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.607</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.1454</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>19</v>
-      </c>
-      <c r="L10" t="n">
-        <v>100</v>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="n">
-        <v>50</v>
+        <v>-41.28</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260325</t>
+          <t>Last 30d</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -7327,269 +7271,134 @@
           <t>Pitcher Outs</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>NYY vs SFG</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Logan Webb</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
+      <c r="C11" t="n">
+        <v>9</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>16.5</v>
+        <v>0.5</v>
       </c>
       <c r="G11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.4107</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.394</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>15</v>
-      </c>
-      <c r="L11" t="n">
-        <v>10000</v>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="n">
-        <v>5000</v>
+        <v>-39.13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260326</t>
+          <t>Last 30d</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>NYM vs PIT</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Jared Triolo</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>7</v>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5</v>
+        <v>0.412</v>
       </c>
       <c r="G12" t="n">
-        <v>-5</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.488</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.4119</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L12" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="n">
-        <v>-50</v>
+        <v>-173.18</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260326</t>
+          <t>Last 30d</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>MIL vs CWS</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Colson Montgomery</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>58</v>
+      </c>
+      <c r="D13" t="n">
+        <v>49</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5</v>
+        <v>0.542</v>
       </c>
       <c r="G13" t="n">
-        <v>-134.5</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.6704</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.1361</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="n">
-        <v>-50</v>
+        <v>-38.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260326</t>
+          <t>Last 10d</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>TBR vs STL</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Jordan Walker</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0.5</v>
       </c>
       <c r="G14" t="n">
-        <v>128.5</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.5208</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.1146</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="n">
-        <v>-50</v>
+        <v>-37.64</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260326</t>
+          <t>Last 10d</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>PIT vs NYM</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Jorge Polanco</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>10</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5</v>
+        <v>0.714</v>
       </c>
       <c r="G15" t="n">
-        <v>-141</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.1053</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>70.92</v>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="n">
-        <v>35.46</v>
+        <v>252.33</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260326</t>
+          <t>Last 10d</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7597,3557 +7406,101 @@
           <t>Hitter TB</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>CHC vs WSN</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Jacob Young</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
+      <c r="C16" t="n">
+        <v>28</v>
+      </c>
+      <c r="D16" t="n">
+        <v>22</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>-110</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.5992</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.1134</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>4</v>
-      </c>
-      <c r="L16" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="n">
-        <v>-50</v>
+        <v>-41.28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260326</t>
+          <t>Last 10d</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>CHC vs WSN</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>James Wood</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>9</v>
+      </c>
+      <c r="D17" t="n">
+        <v>9</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
       </c>
       <c r="F17" t="n">
         <v>0.5</v>
       </c>
       <c r="G17" t="n">
-        <v>-161</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.6791</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.1056</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="n">
-        <v>-50</v>
+        <v>-39.13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260326</t>
+          <t>Last 10d</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>PIT vs NYM</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Juan Soto</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>7</v>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5</v>
+        <v>0.412</v>
       </c>
       <c r="G18" t="n">
-        <v>-153.5</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.1028</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" t="n">
-        <v>65.15000000000001</v>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="n">
-        <v>32.57</v>
+        <v>-173.18</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260326</t>
+          <t>Last 10d</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>CWS vs MIL</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>David Hamilton</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>58</v>
+      </c>
+      <c r="D19" t="n">
+        <v>49</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5</v>
+        <v>0.542</v>
       </c>
       <c r="G19" t="n">
-        <v>-118</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.6207</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.1178</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="n">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>NYM vs PIT</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Brandon Lowe</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G20" t="n">
-        <v>-150</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.6529</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>8</v>
-      </c>
-      <c r="L20" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="n">
-        <v>33.33</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>MIN vs BAL</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Tyler O'Neill</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G21" t="n">
-        <v>-175</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.6989</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.108</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>57.14</v>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="n">
-        <v>28.57</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>CHC vs WSN</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>CJ Abrams</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G22" t="n">
-        <v>-135.5</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.6195000000000001</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.0832</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>73.8</v>
-      </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="n">
-        <v>36.9</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>PIT vs NYM</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Francisco Lindor</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G23" t="n">
-        <v>-180.5</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.6811</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.0843</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="n">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>CIN vs BOS</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Ceddanne Rafaela</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G24" t="n">
-        <v>-178</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.6949</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.09719999999999999</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>2</v>
-      </c>
-      <c r="L24" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="n">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>NYM vs PIT</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Spencer Horwitz</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G25" t="n">
-        <v>-126</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.5911999999999999</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.0756</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="n">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>MIL vs CWS</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Andrew Benintendi</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G26" t="n">
-        <v>-141.5</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.6186</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.0741</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="n">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>MIL vs CWS</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Miguel Vargas</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G27" t="n">
-        <v>-145</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.6219</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.0713</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="n">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>MIN vs BAL</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Samuel Basallo</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G28" t="n">
-        <v>-185</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.6848</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.0808</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K28" t="n">
-        <v>1</v>
-      </c>
-      <c r="L28" t="n">
-        <v>54.05</v>
-      </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="n">
-        <v>27.03</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>MIN vs BAL</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Gunnar Henderson</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G29" t="n">
-        <v>-125</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.5917</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.07480000000000001</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>80</v>
-      </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>MIN vs BAL</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Adley Rutschman</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G30" t="n">
-        <v>-172</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.6712</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.0818</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K30" t="n">
-        <v>3</v>
-      </c>
-      <c r="L30" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="n">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>BAL vs MIN</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Austin Martin</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G31" t="n">
-        <v>-170</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.6679</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.08169999999999999</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K31" t="n">
-        <v>1</v>
-      </c>
-      <c r="L31" t="n">
-        <v>58.82</v>
-      </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="n">
-        <v>29.41</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>PHI vs TEX</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Wyatt Langford</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G32" t="n">
-        <v>-20</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.6369</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0.2456</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="n">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>CHC vs WSN</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Keibert Ruiz</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G33" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.5118</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.4948</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K33" t="n">
-        <v>1</v>
-      </c>
-      <c r="L33" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="n">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>BOS vs CIN</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Ke'Bryan Hayes</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G34" t="n">
-        <v>120.5</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.5485</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0.1263</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>120.5</v>
-      </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="n">
-        <v>60.25</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>CIN vs BOS</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Isiah Kiner-Falefa</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G35" t="n">
-        <v>-185</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.7533</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.1467</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>54.05</v>
-      </c>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="n">
-        <v>27.03</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>PHI vs TEX</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Sam Haggerty</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G36" t="n">
-        <v>106</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.5615</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0.1109</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>106</v>
-      </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="n">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>HOU vs LAA</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Oswald Peraza</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G37" t="n">
-        <v>-125</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.6553</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0.1406</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K37" t="n">
-        <v>1</v>
-      </c>
-      <c r="L37" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="n">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>LAA vs HOU</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Jake Meyers</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G38" t="n">
-        <v>126.5</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.5076000000000001</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0.0975</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
-        <v>126.5</v>
-      </c>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="n">
-        <v>63.25</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>HOU vs LAA</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Zach Neto</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G39" t="n">
-        <v>-183.5</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.6847</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="n">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>DET vs SDP</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Manny Machado</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G40" t="n">
-        <v>-164.5</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0.6501</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0.0707</v>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K40" t="n">
-        <v>1</v>
-      </c>
-      <c r="L40" t="n">
-        <v>60.79</v>
-      </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="n">
-        <v>30.4</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>LAA vs HOU</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Yainer Diaz</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G41" t="n">
-        <v>-182</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.6797</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="n">
-        <v>54.95</v>
-      </c>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="n">
-        <v>27.47</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>STL vs TBR</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Nick Fortes</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G42" t="n">
-        <v>119.5</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0.5552</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0.131</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K42" t="n">
-        <v>3</v>
-      </c>
-      <c r="L42" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="n">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>STL vs TBR</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Ben Williamson</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G43" t="n">
-        <v>-195.5</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0.7428</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0.1248</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K43" t="n">
-        <v>3</v>
-      </c>
-      <c r="L43" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="n">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>STL vs TBR</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Carson Williams</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G44" t="n">
-        <v>110</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0.5195</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K44" t="n">
-        <v>1</v>
-      </c>
-      <c r="L44" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="n">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>SDP vs DET</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Spencer Torkelson</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G45" t="n">
-        <v>-145</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0.6225000000000001</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0.07190000000000001</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K45" t="n">
-        <v>1</v>
-      </c>
-      <c r="L45" t="n">
-        <v>68.97</v>
-      </c>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="n">
-        <v>34.48</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>BAL vs MIN</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Matt Wallner</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G46" t="n">
-        <v>-143.5</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0.6172</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0.0706</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="n">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>TBR vs STL</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Masyn Winn</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G47" t="n">
-        <v>-20</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0.5832000000000001</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0.1919</v>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K47" t="n">
-        <v>2</v>
-      </c>
-      <c r="L47" t="n">
-        <v>500</v>
-      </c>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>MIN vs BAL</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Colton Cowser</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G48" t="n">
-        <v>250</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.5614</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0.2085</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="n">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>BAL vs MIN</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Royce Lewis</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G49" t="n">
-        <v>-50</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.4602</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0.2055</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
-        <v>200</v>
-      </c>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>CLE vs SEA</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Cal Raleigh</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G50" t="n">
-        <v>-147.5</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0.7043</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0.152</v>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="n">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>BAL vs MIN</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Josh Bell</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G51" t="n">
-        <v>-52.5</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.4279</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0.1718</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>190.48</v>
-      </c>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="n">
-        <v>95.23999999999999</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>MIN vs BAL</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Gunnar Henderson</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G52" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.4083</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0.3519</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="n">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>SEA vs CLE</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Kyle Manzardo</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G53" t="n">
-        <v>-108</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0.6057</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0.1269</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K53" t="n">
-        <v>1</v>
-      </c>
-      <c r="L53" t="n">
-        <v>92.59</v>
-      </c>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="n">
-        <v>46.3</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>CLE vs SEA</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Randy Arozarena</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G54" t="n">
-        <v>-124</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0.6155</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0.1069</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K54" t="n">
-        <v>2</v>
-      </c>
-      <c r="L54" t="n">
-        <v>80.65000000000001</v>
-      </c>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="n">
-        <v>40.32</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>SEA vs CLE</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Rhys Hoskins</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G55" t="n">
-        <v>100</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0.5556</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K55" t="n">
-        <v>4</v>
-      </c>
-      <c r="L55" t="n">
-        <v>100</v>
-      </c>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>SEA vs CLE</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Gabriel Arias</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G56" t="n">
-        <v>115</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0.5197000000000001</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K56" t="n">
-        <v>1</v>
-      </c>
-      <c r="L56" t="n">
-        <v>115</v>
-      </c>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="n">
-        <v>57.5</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>ARI vs LAD</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Miguel Rojas</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G57" t="n">
-        <v>113</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0.5123</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0.0765</v>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K57" t="n">
-        <v>1</v>
-      </c>
-      <c r="L57" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="n">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>CLE vs SEA</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Dominic Canzone</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G58" t="n">
-        <v>-118</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0.5725</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0.0725</v>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K58" t="n">
-        <v>8</v>
-      </c>
-      <c r="L58" t="n">
-        <v>84.75</v>
-      </c>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="n">
-        <v>42.37</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>LAA vs HOU</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Yordan Alvarez</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G59" t="n">
-        <v>-138</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0.6188</v>
-      </c>
-      <c r="I59" t="n">
-        <v>0.0769</v>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" t="n">
-        <v>72.45999999999999</v>
-      </c>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="n">
-        <v>36.23</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>ARI vs LAD</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Miguel Rojas</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G60" t="n">
-        <v>-260</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0.7621</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0.093</v>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K60" t="n">
-        <v>1</v>
-      </c>
-      <c r="L60" t="n">
-        <v>38.46</v>
-      </c>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="n">
-        <v>19.23</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Hitter TB</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>ARI vs LAD</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Max Muncy</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G61" t="n">
-        <v>-210</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0.7116</v>
-      </c>
-      <c r="I61" t="n">
-        <v>0.07149999999999999</v>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K61" t="n">
-        <v>1</v>
-      </c>
-      <c r="L61" t="n">
-        <v>47.62</v>
-      </c>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="n">
-        <v>23.81</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Pitcher Outs</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>CWS vs MIL</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Jacob Misiorowski</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="G62" t="n">
-        <v>-175</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0.7971</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0.2083</v>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K62" t="n">
-        <v>15</v>
-      </c>
-      <c r="L62" t="n">
-        <v>57.14</v>
-      </c>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="n">
-        <v>28.57</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Pitcher Outs</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>BAL vs MIN</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Joe Ryan</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="G63" t="n">
-        <v>145</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0.7798</v>
-      </c>
-      <c r="I63" t="n">
-        <v>0.4004</v>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K63" t="n">
-        <v>16</v>
-      </c>
-      <c r="L63" t="n">
-        <v>145</v>
-      </c>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="n">
-        <v>72.5</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Pitcher Outs</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>NYM vs PIT</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Paul Skenes</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="G64" t="n">
-        <v>-104.5</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0.7044</v>
-      </c>
-      <c r="I64" t="n">
-        <v>0.2317</v>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K64" t="n">
-        <v>2</v>
-      </c>
-      <c r="L64" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="n">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Pitcher Outs</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>MIN vs BAL</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Trevor Rogers</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="G65" t="n">
-        <v>-110</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0.7123</v>
-      </c>
-      <c r="I65" t="n">
-        <v>0.2247</v>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K65" t="n">
-        <v>21</v>
-      </c>
-      <c r="L65" t="n">
-        <v>90.91</v>
-      </c>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="n">
-        <v>45.45</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Pitcher Outs</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>PIT vs NYM</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Freddy Peralta</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F66" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="G66" t="n">
-        <v>140.5</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0.6554</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0.2699</v>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K66" t="n">
-        <v>15</v>
-      </c>
-      <c r="L66" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="n">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Pitcher Outs</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>CHC vs WSN</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Cade Cavalli</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F67" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="G67" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0.1997</v>
-      </c>
-      <c r="I67" t="n">
-        <v>0.1827</v>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K67" t="n">
-        <v>11</v>
-      </c>
-      <c r="L67" t="n">
-        <v>10000</v>
-      </c>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Pitcher Outs</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>STL vs TBR</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Drew Rasmussen</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="G68" t="n">
-        <v>-167.5</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0.7352</v>
-      </c>
-      <c r="I68" t="n">
-        <v>0.1525</v>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K68" t="n">
-        <v>15</v>
-      </c>
-      <c r="L68" t="n">
-        <v>59.7</v>
-      </c>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="n">
-        <v>29.85</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Pitcher Outs</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>WSN vs CHC</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Matthew Boyd</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="G69" t="n">
-        <v>-115</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0.6491</v>
-      </c>
-      <c r="I69" t="n">
-        <v>0.1491</v>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K69" t="n">
-        <v>11</v>
-      </c>
-      <c r="L69" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="n">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Pitcher Outs</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>MIL vs CWS</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Shane Smith</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F70" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="G70" t="n">
-        <v>-155</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0.7044</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0.1431</v>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K70" t="n">
-        <v>5</v>
-      </c>
-      <c r="L70" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="n">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Pitcher Outs</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>DET vs SDP</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Nick Pivetta</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="G71" t="n">
-        <v>-116.5</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0.8866000000000001</v>
-      </c>
-      <c r="I71" t="n">
-        <v>0.3851</v>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K71" t="n">
-        <v>9</v>
-      </c>
-      <c r="L71" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="n">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Pitcher Outs</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>PHI vs TEX</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Nathan Eovaldi</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="G72" t="n">
-        <v>-125</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0.8067</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0.2972</v>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K72" t="n">
-        <v>14</v>
-      </c>
-      <c r="L72" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="n">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Pitcher Outs</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>BOS vs CIN</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Andrew Abbott</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F73" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="G73" t="n">
-        <v>125</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0.632</v>
-      </c>
-      <c r="I73" t="n">
-        <v>0.2242</v>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K73" t="n">
-        <v>18</v>
-      </c>
-      <c r="L73" t="n">
-        <v>125</v>
-      </c>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="n">
-        <v>62.5</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Pitcher Outs</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>CIN vs BOS</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Garrett Crochet</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="G74" t="n">
-        <v>-125</v>
-      </c>
-      <c r="H74" t="n">
-        <v>0.6627999999999999</v>
-      </c>
-      <c r="I74" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K74" t="n">
-        <v>18</v>
-      </c>
-      <c r="L74" t="n">
-        <v>80</v>
-      </c>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Pitcher Outs</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>LAA vs HOU</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Hunter Brown</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F75" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="G75" t="n">
-        <v>-110.5</v>
-      </c>
-      <c r="H75" t="n">
-        <v>0.6015</v>
-      </c>
-      <c r="I75" t="n">
-        <v>0.112</v>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K75" t="n">
-        <v>14</v>
-      </c>
-      <c r="L75" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="n">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Pitcher Outs</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>TBR vs STL</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Matthew Liberatore</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F76" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="G76" t="n">
-        <v>-183.5</v>
-      </c>
-      <c r="H76" t="n">
-        <v>0.7463</v>
-      </c>
-      <c r="I76" t="n">
-        <v>0.1529</v>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K76" t="n">
-        <v>15</v>
-      </c>
-      <c r="L76" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="n">
-        <v>27.25</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Pitcher Outs</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>CHC vs WSN</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Cade Cavalli</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F77" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="G77" t="n">
-        <v>-140.5</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0.8003</v>
-      </c>
-      <c r="I77" t="n">
-        <v>0.4224</v>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K77" t="n">
-        <v>11</v>
-      </c>
-      <c r="L77" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="n">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Pitcher Outs</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>LAD vs ARI</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Zac Gallen</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F78" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="G78" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="H78" t="n">
-        <v>0.3341</v>
-      </c>
-      <c r="I78" t="n">
-        <v>0.3257</v>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K78" t="n">
-        <v>12</v>
-      </c>
-      <c r="L78" t="n">
-        <v>20000</v>
-      </c>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Pitcher Outs</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>ARI vs LAD</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Yoshinobu Yamamoto</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F79" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="G79" t="n">
-        <v>109.5</v>
-      </c>
-      <c r="H79" t="n">
-        <v>0.669</v>
-      </c>
-      <c r="I79" t="n">
-        <v>0.2304</v>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K79" t="n">
-        <v>18</v>
-      </c>
-      <c r="L79" t="n">
-        <v>109.5</v>
-      </c>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="n">
-        <v>54.75</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Pitcher Outs</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>CIN vs BOS</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Garrett Crochet</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F80" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="G80" t="n">
-        <v>-5</v>
-      </c>
-      <c r="H80" t="n">
-        <v>0.3372</v>
-      </c>
-      <c r="I80" t="n">
-        <v>0.2589</v>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K80" t="n">
-        <v>18</v>
-      </c>
-      <c r="L80" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="n">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Pitcher Outs</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>LAD vs ARI</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Zac Gallen</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F81" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="G81" t="n">
-        <v>-155</v>
-      </c>
-      <c r="H81" t="n">
-        <v>0.6659</v>
-      </c>
-      <c r="I81" t="n">
-        <v>0.0977</v>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K81" t="n">
-        <v>12</v>
-      </c>
-      <c r="L81" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="n">
-        <v>-50</v>
+        <v>-38.9</v>
       </c>
     </row>
   </sheetData>
@@ -11274,13 +7627,21 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>7-0</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>-100</v>
+      </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11320,13 +7681,21 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>70.67</v>
+      </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>35.34</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11366,13 +7735,21 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>7-11</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>82.64</v>
+      </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>41.32</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11412,13 +7789,21 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>3-5</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>63.9</v>
+      </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>31.95</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11458,13 +7843,21 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>-100</v>
+      </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11504,13 +7897,21 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>8-2</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>-100</v>
+      </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11550,13 +7951,21 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>7-9</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>107.5</v>
+      </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>53.75</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11596,13 +8005,21 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2-8</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>-100</v>
+      </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>-50</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11730,13 +8147,19 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-100</v>
+      </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11778,13 +8201,19 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>16</v>
+      </c>
+      <c r="L3" t="n">
+        <v>95.23999999999999</v>
+      </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>47.62</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11826,13 +8255,19 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>18</v>
+      </c>
+      <c r="L4" t="n">
+        <v>82.64</v>
+      </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>41.32</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11874,13 +8309,19 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>14</v>
+      </c>
+      <c r="L5" t="n">
+        <v>94.34</v>
+      </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>47.17</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11922,13 +8363,19 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>3</v>
+      </c>
+      <c r="L6" t="n">
+        <v>86.95999999999999</v>
+      </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>43.48</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11970,13 +8417,19 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-100</v>
+      </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12018,13 +8471,19 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>10</v>
+      </c>
+      <c r="L8" t="n">
+        <v>90.91</v>
+      </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>45.45</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12066,13 +8525,19 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+          <t>PUSH</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>8</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12114,13 +8579,19 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-100</v>
+      </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -12162,13 +8633,19 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>95.23999999999999</v>
+      </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="n">
+        <v>47.62</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -12210,13 +8687,19 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>16</v>
+      </c>
+      <c r="L12" t="n">
+        <v>90.91</v>
+      </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="N12" t="n">
+        <v>45.45</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -12258,13 +8741,19 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>16</v>
+      </c>
+      <c r="L13" t="n">
+        <v>95.23999999999999</v>
+      </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="N13" t="n">
+        <v>47.62</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -12306,13 +8795,19 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>16</v>
+      </c>
+      <c r="L14" t="n">
+        <v>90.91</v>
+      </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" t="n">
+        <v>45.45</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -12354,13 +8849,19 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>10</v>
+      </c>
+      <c r="L15" t="n">
+        <v>82.3</v>
+      </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="N15" t="n">
+        <v>41.15</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -12402,13 +8903,19 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>10</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-100</v>
+      </c>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>-50</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12860,19 +9367,13 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>4000</v>
-      </c>
+          <t>ODDS_ERR</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="n">
-        <v>2000</v>
-      </c>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12968,19 +9469,13 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
-      </c>
-      <c r="L10" t="n">
-        <v>500</v>
-      </c>
+          <t>ODDS_ERR</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="n">
-        <v>250</v>
-      </c>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13508,19 +10003,13 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>200</v>
-      </c>
+          <t>ODDS_ERR</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="n">
-        <v>100</v>
-      </c>
+      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -13616,19 +10105,13 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>190.48</v>
-      </c>
+          <t>ODDS_ERR</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="n">
-        <v>95.23999999999999</v>
-      </c>
+      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -13670,19 +10153,13 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>-100</v>
-      </c>
+          <t>ODDS_ERR</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" t="n">
-        <v>-50</v>
-      </c>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -13778,13 +10255,17 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>DNP</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -14258,19 +10739,13 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K34" t="n">
-        <v>1</v>
-      </c>
-      <c r="L34" t="n">
-        <v>-100</v>
-      </c>
+          <t>ODDS_ERR</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="n">
-        <v>-50</v>
-      </c>
+      <c r="N34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -14366,19 +10841,13 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K36" t="n">
-        <v>2</v>
-      </c>
-      <c r="L36" t="n">
-        <v>-100</v>
-      </c>
+          <t>ODDS_ERR</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="n">
-        <v>-50</v>
-      </c>
+      <c r="N36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -15446,19 +11915,13 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" t="n">
-        <v>-100</v>
-      </c>
+          <t>ODDS_ERR</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" t="n">
-        <v>-50</v>
-      </c>
+      <c r="N56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -15856,19 +12319,13 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>15</v>
-      </c>
-      <c r="L3" t="n">
-        <v>10000</v>
-      </c>
+          <t>ODDS_ERR</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="n">
-        <v>5000</v>
-      </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15964,19 +12421,13 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>12</v>
-      </c>
-      <c r="L5" t="n">
-        <v>20000</v>
-      </c>
+          <t>ODDS_ERR</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="n">
-        <v>10000</v>
-      </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16558,19 +13009,13 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>11</v>
-      </c>
-      <c r="L16" t="n">
-        <v>10000</v>
-      </c>
+          <t>ODDS_ERR</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="n">
-        <v>5000</v>
-      </c>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -16882,19 +13327,13 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>18</v>
-      </c>
-      <c r="L22" t="n">
-        <v>-100</v>
-      </c>
+          <t>ODDS_ERR</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="n">
-        <v>-50</v>
-      </c>
+      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -17074,13 +13513,21 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>away_1st=0 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>63.49</v>
+      </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>31.75</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17120,13 +13567,21 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>away_1st=0 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>-100</v>
+      </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -17166,13 +13621,21 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>away_1st=0 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>-100</v>
+      </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -17212,13 +13675,21 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>away_1st=2 home_1st=5</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>-100</v>
+      </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -17258,13 +13729,21 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>away_1st=4 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>-100</v>
+      </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17304,13 +13783,21 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>away_1st=0 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>-100</v>
+      </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17350,13 +13837,21 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>away_1st=0 home_1st=2</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>94.34</v>
+      </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>47.17</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -17396,13 +13891,21 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>away_1st=4 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>118</v>
+      </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -17442,13 +13945,21 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>away_1st=0 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>64.52</v>
+      </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>32.26</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -17488,13 +13999,21 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>away_1st=1 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>-100</v>
+      </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -17534,13 +14053,21 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>away_1st=0 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>-100</v>
+      </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="N12" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -17580,13 +14107,21 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>away_1st=0 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>-100</v>
+      </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="N13" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17626,13 +14161,21 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>away_1st=0 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>-100</v>
+      </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -17672,13 +14215,21 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>away_1st=1 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>98.04000000000001</v>
+      </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="N15" t="n">
+        <v>49.02</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -17718,13 +14269,21 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>away_1st=2 home_1st=5</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>120</v>
+      </c>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -17764,13 +14323,21 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>away_1st=1 home_1st=1</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>-100</v>
+      </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="N17" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -17810,13 +14377,21 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>away_1st=0 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>95.23999999999999</v>
+      </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="N18" t="n">
+        <v>47.62</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tracking/picks.xlsx
+++ b/tracking/picks.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N122"/>
+  <dimension ref="A1:N152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6965,6 +6965,1434 @@
       <c r="N122" t="n">
         <v>47.62</v>
       </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>NYY @ SFG</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>SFG</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.6142</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.1631</v>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>COL @ MIA</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="n">
+        <v>-195</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6944</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.0618</v>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>NYY @ SFG</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NYY @ SFG</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G125" t="n">
+        <v>-107</v>
+      </c>
+      <c r="H125" t="n">
+        <v>1</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.5044</v>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>OAK @ TOR</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>OAK @ TOR</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G126" t="n">
+        <v>-118</v>
+      </c>
+      <c r="H126" t="n">
+        <v>1</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.4838</v>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>COL @ MIA</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>COL @ MIA</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G127" t="n">
+        <v>-112.5</v>
+      </c>
+      <c r="H127" t="n">
+        <v>1</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.4946</v>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>KCR @ ATL</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>KCR @ ATL</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G128" t="n">
+        <v>-100</v>
+      </c>
+      <c r="H128" t="n">
+        <v>1</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.5231</v>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>MIA vs COL</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Kyle Karros</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G129" t="n">
+        <v>113</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.6227</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>COL vs MIA</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Austin Slater</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G130" t="n">
+        <v>-161</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.7345</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>COL vs MIA</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Javier Sanoja</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G131" t="n">
+        <v>-202</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.7691</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.1424</v>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>TOR vs OAK</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Nick Kurtz</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G132" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.5341</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.1023</v>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>COL vs MIA</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Xavier Edwards</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G133" t="n">
+        <v>-190</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.7413</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.1301</v>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>COL vs MIA</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Christopher Morel</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G134" t="n">
+        <v>-178</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.7256</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.1269</v>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>COL vs MIA</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Otto Lopez</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G135" t="n">
+        <v>-145</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.6723</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.1181</v>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>ATL vs KCR</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Lane Thomas</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G136" t="n">
+        <v>109</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>SFG vs NYY</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Randal Grichuk</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G137" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.5165</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.0746</v>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>ATL vs KCR</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Vinnie Pasquantino</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G138" t="n">
+        <v>-157</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.6475</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.0775</v>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>COL vs MIA</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Connor Norby</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G139" t="n">
+        <v>-168</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.6831</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>MIA vs COL</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Jake McCarthy</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G140" t="n">
+        <v>-216.5</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.7151</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.0794</v>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>SFG vs NYY</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Paul Goldschmidt</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G141" t="n">
+        <v>-136</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.6193</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.0839</v>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>OAK vs TOR</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Alejandro Kirk</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G142" t="n">
+        <v>-157</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.6521</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.07870000000000001</v>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>OAK vs TOR</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Ernie Clement</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G143" t="n">
+        <v>-193</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.0735</v>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>TOR vs OAK</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Luis Severino</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G144" t="n">
+        <v>-202.5</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0.8656</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0.2444</v>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>NYY vs SFG</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Robbie Ray</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G145" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0.738</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0.2774</v>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>SFG vs NYY</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Cam Schlittler</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G146" t="n">
+        <v>-120</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0.6915</v>
+      </c>
+      <c r="I146" t="n">
+        <v>0.1866</v>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>COL vs MIA</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Sandy Alcantara</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G147" t="n">
+        <v>135</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0.5759</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0.1795</v>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>MIA vs COL</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Kyle Freeland</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G148" t="n">
+        <v>-185</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0.0738</v>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>NYY @ SFG</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>NYY @ SFG</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>YRFI</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="n">
+        <v>-102</v>
+      </c>
+      <c r="H149" t="n">
+        <v>1</v>
+      </c>
+      <c r="I149" t="n">
+        <v>0.5239</v>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>KCR @ ATL</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>KCR @ ATL</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>YRFI</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="n">
+        <v>110</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0.5887</v>
+      </c>
+      <c r="I150" t="n">
+        <v>0.1428</v>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>COL @ MIA</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>COL @ MIA</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>NRFI</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="n">
+        <v>-128</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0.4113</v>
+      </c>
+      <c r="I151" t="n">
+        <v>-0.1152</v>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>OAK @ TOR</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>OAK @ TOR</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>NRFI</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="n">
+        <v>-109</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0.4113</v>
+      </c>
+      <c r="I152" t="n">
+        <v>-0.0756</v>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7514,7 +8942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8020,6 +9448,98 @@
       <c r="N9" t="n">
         <v>-50</v>
       </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NYY @ SFG</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>SFG</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.6142</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.1631</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>COL @ MIA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>-195</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.6944</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.0618</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8032,7 +9552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8174,45 +9694,45 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CWS @ MIL</t>
+          <t>ARI @ LAD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CWS @ MIL</t>
+          <t>ARI @ LAD</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G3" t="n">
-        <v>-105</v>
+        <v>-115</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7967</v>
+        <v>0.6322</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3076</v>
+        <v>0.1214</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="L3" t="n">
-        <v>95.23999999999999</v>
+        <v>-100</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>47.62</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="4">
@@ -8228,12 +9748,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PIT @ NYM</t>
+          <t>CLE @ SEA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PIT @ NYM</t>
+          <t>CLE @ SEA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -8242,16 +9762,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="G4" t="n">
-        <v>-121</v>
+        <v>-121.5</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7237</v>
+        <v>0.8472</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3699</v>
+        <v>0.3241</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -8259,14 +9779,14 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="L4" t="n">
-        <v>82.64</v>
+        <v>82.3</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>41.32</v>
+        <v>41.15</v>
       </c>
     </row>
     <row r="5">
@@ -8282,12 +9802,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>WSN @ CHC</t>
+          <t>TBR @ STL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>WSN @ CHC</t>
+          <t>TBR @ STL</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -8296,16 +9816,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G5" t="n">
-        <v>-106</v>
+        <v>-110</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6821</v>
+        <v>0.7002</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1918</v>
+        <v>0.1997</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -8313,14 +9833,14 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L5" t="n">
-        <v>94.34</v>
+        <v>90.91</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>47.17</v>
+        <v>45.45</v>
       </c>
     </row>
     <row r="6">
@@ -8336,30 +9856,30 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MIN @ BAL</t>
+          <t>TBR @ STL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MIN @ BAL</t>
+          <t>TBR @ STL</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>8.5</v>
+        <v>7.75</v>
       </c>
       <c r="G6" t="n">
-        <v>-115</v>
+        <v>-105</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5743</v>
+        <v>0.7002</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0634</v>
+        <v>0.2111</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -8367,14 +9887,14 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="L6" t="n">
-        <v>86.95999999999999</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>43.48</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="7">
@@ -8390,12 +9910,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LAA @ HOU</t>
+          <t>CWS @ MIL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LAA @ HOU</t>
+          <t>CWS @ MIL</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -8404,31 +9924,31 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="G7" t="n">
-        <v>-114</v>
+        <v>-110</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7235</v>
+        <v>0.7967</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2154</v>
+        <v>0.2967</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="L7" t="n">
-        <v>-100</v>
+        <v>90.91</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>-50</v>
+        <v>45.45</v>
       </c>
     </row>
     <row r="8">
@@ -8444,12 +9964,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DET @ SDP</t>
+          <t>BOS @ CIN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DET @ SDP</t>
+          <t>BOS @ CIN</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -8458,31 +9978,31 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7019</v>
+        <v>0.5835</v>
       </c>
       <c r="I8" t="n">
-        <v>0.203</v>
+        <v>0.0727</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
-        <v>90.91</v>
+        <v>-100</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>45.45</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="9">
@@ -8498,17 +10018,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TEX @ PHI</t>
+          <t>BOS @ CIN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>TEX @ PHI</t>
+          <t>BOS @ CIN</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -8518,25 +10038,25 @@
         <v>-105</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6418</v>
+        <v>0.5555</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1516</v>
+        <v>0.0663</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>PUSH</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="10">
@@ -8552,12 +10072,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BOS @ CIN</t>
+          <t>DET @ SDP</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>BOS @ CIN</t>
+          <t>DET @ SDP</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -8566,31 +10086,31 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G10" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5835</v>
+        <v>0.7019</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0727</v>
+        <v>0.203</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L10" t="n">
-        <v>-100</v>
+        <v>90.91</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>-50</v>
+        <v>45.45</v>
       </c>
     </row>
     <row r="11">
@@ -8606,45 +10126,45 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BOS @ CIN</t>
+          <t>LAA @ HOU</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>BOS @ CIN</t>
+          <t>LAA @ HOU</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>8</v>
       </c>
       <c r="G11" t="n">
-        <v>-105</v>
+        <v>-114</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5555</v>
+        <v>0.7235</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0663</v>
+        <v>0.2154</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K11" t="n">
         <v>3</v>
       </c>
       <c r="L11" t="n">
-        <v>95.23999999999999</v>
+        <v>-100</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
-        <v>47.62</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="12">
@@ -8660,30 +10180,30 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CWS @ MIL</t>
+          <t>MIN @ BAL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CWS @ MIL</t>
+          <t>MIN @ BAL</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="G12" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7967</v>
+        <v>0.5743</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2967</v>
+        <v>0.0634</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -8691,14 +10211,14 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="L12" t="n">
-        <v>90.91</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>45.45</v>
+        <v>43.48</v>
       </c>
     </row>
     <row r="13">
@@ -8714,12 +10234,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TBR @ STL</t>
+          <t>WSN @ CHC</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>TBR @ STL</t>
+          <t>WSN @ CHC</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -8728,16 +10248,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>7.75</v>
+        <v>7</v>
       </c>
       <c r="G13" t="n">
-        <v>-105</v>
+        <v>-106</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7002</v>
+        <v>0.6821</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2111</v>
+        <v>0.1918</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -8745,14 +10265,14 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L13" t="n">
-        <v>95.23999999999999</v>
+        <v>94.34</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
-        <v>47.62</v>
+        <v>47.17</v>
       </c>
     </row>
     <row r="14">
@@ -8768,12 +10288,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TBR @ STL</t>
+          <t>PIT @ NYM</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>TBR @ STL</t>
+          <t>PIT @ NYM</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -8782,16 +10302,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G14" t="n">
-        <v>-110</v>
+        <v>-121</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7002</v>
+        <v>0.7237</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1997</v>
+        <v>0.3699</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -8799,14 +10319,14 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L14" t="n">
-        <v>90.91</v>
+        <v>82.64</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
-        <v>45.45</v>
+        <v>41.32</v>
       </c>
     </row>
     <row r="15">
@@ -8822,12 +10342,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLE @ SEA</t>
+          <t>CWS @ MIL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CLE @ SEA</t>
+          <t>CWS @ MIL</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -8836,16 +10356,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="G15" t="n">
-        <v>-121.5</v>
+        <v>-105</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8472</v>
+        <v>0.7967</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3241</v>
+        <v>0.3076</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -8853,14 +10373,14 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L15" t="n">
-        <v>82.3</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
-        <v>41.15</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="16">
@@ -8876,46 +10396,238 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ARI @ LAD</t>
+          <t>TEX @ PHI</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ARI @ LAD</t>
+          <t>TEX @ PHI</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G16" t="n">
-        <v>-115</v>
+        <v>-105</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6322</v>
+        <v>0.6418</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1214</v>
+        <v>0.1516</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>PUSH</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L16" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
-        <v>-50</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>COL @ MIA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>COL @ MIA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-112.5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.4946</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NYY @ SFG</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NYY @ SFG</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-107</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.5044</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>OAK @ TOR</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>OAK @ TOR</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-118</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.4838</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>KCR @ ATL</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>KCR @ ATL</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-100</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.5231</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8928,7 +10640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N60"/>
+  <dimension ref="A1:N75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9442,12 +11154,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TBR vs STL</t>
+          <t>MIN vs BAL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Masyn Winn</t>
+          <t>Colton Cowser</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -9459,23 +11171,29 @@
         <v>0.5</v>
       </c>
       <c r="G10" t="n">
-        <v>-20</v>
+        <v>250</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.5614</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1919</v>
+        <v>0.2085</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>ODDS_ERR</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-100</v>
+      </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9490,12 +11208,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BAL vs MIN</t>
+          <t>TBR vs STL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Matt Wallner</t>
+          <t>Masyn Winn</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -9507,29 +11225,23 @@
         <v>0.5</v>
       </c>
       <c r="G11" t="n">
-        <v>-143.5</v>
+        <v>-20</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6172</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0706</v>
+        <v>0.1919</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-100</v>
-      </c>
+          <t>ODDS_ERR</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="n">
-        <v>-50</v>
-      </c>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -9544,12 +11256,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SDP vs DET</t>
+          <t>BAL vs MIN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Spencer Torkelson</t>
+          <t>Matt Wallner</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -9561,28 +11273,28 @@
         <v>0.5</v>
       </c>
       <c r="G12" t="n">
-        <v>-145</v>
+        <v>-143.5</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.6172</v>
       </c>
       <c r="I12" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0706</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>68.97</v>
+        <v>-100</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>34.48</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="13">
@@ -9598,45 +11310,45 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>STL vs TBR</t>
+          <t>SDP vs DET</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Carson Williams</t>
+          <t>Spencer Torkelson</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>0.5</v>
       </c>
       <c r="G13" t="n">
-        <v>110</v>
+        <v>-145</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5195</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>0.077</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>-100</v>
+        <v>68.97</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
-        <v>-50</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="14">
@@ -9652,30 +11364,30 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DET vs SDP</t>
+          <t>LAA vs HOU</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Manny Machado</t>
+          <t>Yainer Diaz</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G14" t="n">
-        <v>-164.5</v>
+        <v>-182</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6501</v>
+        <v>0.6797</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0707</v>
+        <v>0.077</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -9683,14 +11395,14 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>60.79</v>
+        <v>54.95</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
-        <v>30.4</v>
+        <v>27.47</v>
       </c>
     </row>
     <row r="15">
@@ -9711,7 +11423,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Ben Williamson</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -9720,16 +11432,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G15" t="n">
-        <v>119.5</v>
+        <v>-195.5</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5552</v>
+        <v>0.7428</v>
       </c>
       <c r="I15" t="n">
-        <v>0.131</v>
+        <v>0.1248</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -9760,12 +11472,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LAA vs HOU</t>
+          <t>STL vs TBR</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Yainer Diaz</t>
+          <t>Nick Fortes</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -9774,31 +11486,31 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G16" t="n">
-        <v>-182</v>
+        <v>119.5</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6797</v>
+        <v>0.5552</v>
       </c>
       <c r="I16" t="n">
-        <v>0.077</v>
+        <v>0.131</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L16" t="n">
-        <v>54.95</v>
+        <v>-100</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
-        <v>27.47</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="17">
@@ -9814,46 +11526,40 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MIN vs BAL</t>
+          <t>BAL vs MIN</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Colton Cowser</t>
+          <t>Royce Lewis</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>0.5</v>
       </c>
       <c r="G17" t="n">
-        <v>250</v>
+        <v>-50</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5614</v>
+        <v>0.4602</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2085</v>
+        <v>0.2055</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>-100</v>
-      </c>
+          <t>ODDS_ERR</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="n">
-        <v>-50</v>
-      </c>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9927,7 +11633,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Ben Williamson</t>
+          <t>Carson Williams</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9936,16 +11642,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G19" t="n">
-        <v>-195.5</v>
+        <v>110</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7428</v>
+        <v>0.5195</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1248</v>
+        <v>0.077</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -9953,7 +11659,7 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>-100</v>
@@ -9976,40 +11682,46 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BAL vs MIN</t>
+          <t>CLE vs SEA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Royce Lewis</t>
+          <t>Cal Raleigh</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>0.5</v>
       </c>
       <c r="G20" t="n">
+        <v>-147.5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.7043</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="n">
         <v>-50</v>
       </c>
-      <c r="H20" t="n">
-        <v>0.4602</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.2055</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>ODDS_ERR</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -10024,12 +11736,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SEA vs CLE</t>
+          <t>LAD vs ARI</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Kyle Manzardo</t>
+          <t>Pavin Smith</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10041,28 +11753,26 @@
         <v>0.5</v>
       </c>
       <c r="G21" t="n">
-        <v>-108</v>
+        <v>101</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6057</v>
+        <v>0.5637</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1269</v>
+        <v>0.1034</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
-        <v>92.59</v>
+        <v>0</v>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="n">
-        <v>46.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -10078,30 +11788,30 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BAL vs MIN</t>
+          <t>MIN vs BAL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Josh Bell</t>
+          <t>Gunnar Henderson</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G22" t="n">
-        <v>-52.5</v>
+        <v>-3.5</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4279</v>
+        <v>0.4083</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1718</v>
+        <v>0.3519</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -10126,12 +11836,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MIN vs BAL</t>
+          <t>SEA vs CLE</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Gunnar Henderson</t>
+          <t>Kyle Manzardo</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10140,26 +11850,32 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.5</v>
+        <v>-108</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4083</v>
+        <v>0.6057</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3519</v>
+        <v>0.1269</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>ODDS_ERR</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>92.59</v>
+      </c>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="N23" t="n">
+        <v>46.3</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -10228,12 +11944,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>LAD vs ARI</t>
+          <t>CLE vs SEA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Pavin Smith</t>
+          <t>Randy Arozarena</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -10245,26 +11961,28 @@
         <v>0.5</v>
       </c>
       <c r="G25" t="n">
-        <v>101</v>
+        <v>-124</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5637</v>
+        <v>0.6155</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1034</v>
+        <v>0.1069</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>DNP</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>2</v>
+      </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>40.32</v>
       </c>
     </row>
     <row r="26">
@@ -10280,12 +11998,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLE vs SEA</t>
+          <t>SEA vs CLE</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Randy Arozarena</t>
+          <t>Rhys Hoskins</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -10297,13 +12015,13 @@
         <v>0.5</v>
       </c>
       <c r="G26" t="n">
-        <v>-124</v>
+        <v>100</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6155</v>
+        <v>0.5556</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1069</v>
+        <v>0.094</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -10311,14 +12029,14 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L26" t="n">
-        <v>80.65000000000001</v>
+        <v>100</v>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>40.32</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27">
@@ -10339,7 +12057,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Rhys Hoskins</t>
+          <t>Gabriel Arias</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -10351,13 +12069,13 @@
         <v>0.5</v>
       </c>
       <c r="G27" t="n">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5556</v>
+        <v>0.5197000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>0.094</v>
+        <v>0.083</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -10365,14 +12083,14 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>50</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="28">
@@ -10388,45 +12106,45 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SEA vs CLE</t>
+          <t>ARI vs LAD</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Gabriel Arias</t>
+          <t>Miguel Rojas</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>0.5</v>
       </c>
       <c r="G28" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H28" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.5123</v>
       </c>
       <c r="I28" t="n">
-        <v>0.083</v>
+        <v>0.0765</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>115</v>
+        <v>-100</v>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>57.5</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="29">
@@ -10442,45 +12160,45 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ARI vs LAD</t>
+          <t>CLE vs SEA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Miguel Rojas</t>
+          <t>Dominic Canzone</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>0.5</v>
       </c>
       <c r="G29" t="n">
-        <v>113</v>
+        <v>-118</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5123</v>
+        <v>0.5725</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0765</v>
+        <v>0.0725</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L29" t="n">
-        <v>-100</v>
+        <v>84.75</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>-50</v>
+        <v>42.37</v>
       </c>
     </row>
     <row r="30">
@@ -10496,30 +12214,30 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CLE vs SEA</t>
+          <t>LAA vs HOU</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Dominic Canzone</t>
+          <t>Yordan Alvarez</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G30" t="n">
-        <v>-118</v>
+        <v>-138</v>
       </c>
       <c r="H30" t="n">
-        <v>0.5725</v>
+        <v>0.6188</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0725</v>
+        <v>0.0769</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -10527,14 +12245,14 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>84.75</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>42.37</v>
+        <v>36.23</v>
       </c>
     </row>
     <row r="31">
@@ -10550,12 +12268,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>LAA vs HOU</t>
+          <t>ARI vs LAD</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Yordan Alvarez</t>
+          <t>Miguel Rojas</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -10567,13 +12285,13 @@
         <v>1.5</v>
       </c>
       <c r="G31" t="n">
-        <v>-138</v>
+        <v>-260</v>
       </c>
       <c r="H31" t="n">
-        <v>0.6188</v>
+        <v>0.7621</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0769</v>
+        <v>0.093</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -10581,14 +12299,14 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>72.45999999999999</v>
+        <v>38.46</v>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>36.23</v>
+        <v>19.23</v>
       </c>
     </row>
     <row r="32">
@@ -10604,45 +12322,45 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CLE vs SEA</t>
+          <t>ARI vs LAD</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Cal Raleigh</t>
+          <t>Max Muncy</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G32" t="n">
-        <v>-147.5</v>
+        <v>-210</v>
       </c>
       <c r="H32" t="n">
-        <v>0.7043</v>
+        <v>0.7116</v>
       </c>
       <c r="I32" t="n">
-        <v>0.152</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>-100</v>
+        <v>47.62</v>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>-50</v>
+        <v>23.81</v>
       </c>
     </row>
     <row r="33">
@@ -10658,12 +12376,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>HOU vs LAA</t>
+          <t>BAL vs MIN</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Oswald Peraza</t>
+          <t>Josh Bell</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -10675,29 +12393,23 @@
         <v>0.5</v>
       </c>
       <c r="G33" t="n">
-        <v>-125</v>
+        <v>-52.5</v>
       </c>
       <c r="H33" t="n">
-        <v>0.6553</v>
+        <v>0.4279</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1406</v>
+        <v>0.1718</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K33" t="n">
-        <v>1</v>
-      </c>
-      <c r="L33" t="n">
-        <v>-100</v>
-      </c>
+          <t>ODDS_ERR</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" t="n">
-        <v>-50</v>
-      </c>
+      <c r="N33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -10712,12 +12424,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CHC vs WSN</t>
+          <t>HOU vs LAA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Keibert Ruiz</t>
+          <t>Oswald Peraza</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -10729,23 +12441,29 @@
         <v>0.5</v>
       </c>
       <c r="G34" t="n">
-        <v>-1</v>
+        <v>-125</v>
       </c>
       <c r="H34" t="n">
-        <v>0.5118</v>
+        <v>0.6553</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4948</v>
+        <v>0.1406</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>ODDS_ERR</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>-100</v>
+      </c>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="N34" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -10760,30 +12478,30 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CIN vs BOS</t>
+          <t>DET vs SDP</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Isiah Kiner-Falefa</t>
+          <t>Manny Machado</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G35" t="n">
-        <v>-185</v>
+        <v>-164.5</v>
       </c>
       <c r="H35" t="n">
-        <v>0.7533</v>
+        <v>0.6501</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1467</v>
+        <v>0.0707</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -10791,14 +12509,14 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>54.05</v>
+        <v>60.79</v>
       </c>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="n">
-        <v>27.03</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="36">
@@ -10814,12 +12532,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NYM vs PIT</t>
+          <t>CIN vs BOS</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Jared Triolo</t>
+          <t>Isiah Kiner-Falefa</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -10828,26 +12546,32 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G36" t="n">
-        <v>-5</v>
+        <v>-185</v>
       </c>
       <c r="H36" t="n">
-        <v>0.488</v>
+        <v>0.7533</v>
       </c>
       <c r="I36" t="n">
-        <v>0.4119</v>
+        <v>0.1467</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>ODDS_ERR</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>54.05</v>
+      </c>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="N36" t="n">
+        <v>27.03</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -10862,46 +12586,40 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MIL vs CWS</t>
+          <t>NYM vs PIT</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Colson Montgomery</t>
+          <t>Jared Triolo</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>0.5</v>
       </c>
       <c r="G37" t="n">
-        <v>-134.5</v>
+        <v>-5</v>
       </c>
       <c r="H37" t="n">
-        <v>0.6704</v>
+        <v>0.488</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1361</v>
+        <v>0.4119</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>-100</v>
-      </c>
+          <t>ODDS_ERR</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" t="n">
-        <v>-50</v>
-      </c>
+      <c r="N37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -10916,30 +12634,30 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>TBR vs STL</t>
+          <t>MIL vs CWS</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Jordan Walker</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>0.5</v>
       </c>
       <c r="G38" t="n">
-        <v>128.5</v>
+        <v>-134.5</v>
       </c>
       <c r="H38" t="n">
-        <v>0.5208</v>
+        <v>0.6704</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1146</v>
+        <v>0.1361</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -10947,7 +12665,7 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>-100</v>
@@ -10970,45 +12688,45 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PIT vs NYM</t>
+          <t>TBR vs STL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Jorge Polanco</t>
+          <t>Jordan Walker</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>0.5</v>
       </c>
       <c r="G39" t="n">
-        <v>-141</v>
+        <v>128.5</v>
       </c>
       <c r="H39" t="n">
-        <v>0.65</v>
+        <v>0.5208</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1053</v>
+        <v>0.1146</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L39" t="n">
-        <v>70.92</v>
+        <v>-100</v>
       </c>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="n">
-        <v>35.46</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="40">
@@ -11024,45 +12742,45 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CHC vs WSN</t>
+          <t>PIT vs NYM</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Jacob Young</t>
+          <t>Jorge Polanco</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>0.5</v>
       </c>
       <c r="G40" t="n">
-        <v>-110</v>
+        <v>-141</v>
       </c>
       <c r="H40" t="n">
-        <v>0.5992</v>
+        <v>0.65</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1134</v>
+        <v>0.1053</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>-100</v>
+        <v>70.92</v>
       </c>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="n">
-        <v>-50</v>
+        <v>35.46</v>
       </c>
     </row>
     <row r="41">
@@ -11083,25 +12801,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>James Wood</t>
+          <t>Jacob Young</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F41" t="n">
         <v>0.5</v>
       </c>
       <c r="G41" t="n">
-        <v>-161</v>
+        <v>-110</v>
       </c>
       <c r="H41" t="n">
-        <v>0.6791</v>
+        <v>0.5992</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1056</v>
+        <v>0.1134</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -11109,7 +12827,7 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L41" t="n">
         <v>-100</v>
@@ -11132,30 +12850,30 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PIT vs NYM</t>
+          <t>PHI vs TEX</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Juan Soto</t>
+          <t>Sam Haggerty</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>0.5</v>
       </c>
       <c r="G42" t="n">
-        <v>-153.5</v>
+        <v>106</v>
       </c>
       <c r="H42" t="n">
-        <v>0.6667</v>
+        <v>0.5615</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1028</v>
+        <v>0.1109</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -11163,14 +12881,14 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>65.15000000000001</v>
+        <v>106</v>
       </c>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="n">
-        <v>32.57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="43">
@@ -11186,45 +12904,45 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CWS vs MIL</t>
+          <t>PIT vs NYM</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Juan Soto</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F43" t="n">
         <v>0.5</v>
       </c>
       <c r="G43" t="n">
-        <v>-118</v>
+        <v>-153.5</v>
       </c>
       <c r="H43" t="n">
-        <v>0.6207</v>
+        <v>0.6667</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1178</v>
+        <v>0.1028</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L43" t="n">
-        <v>-100</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="n">
-        <v>-50</v>
+        <v>32.57</v>
       </c>
     </row>
     <row r="44">
@@ -11240,45 +12958,45 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NYM vs PIT</t>
+          <t>CWS vs MIL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Brandon Lowe</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>0.5</v>
       </c>
       <c r="G44" t="n">
-        <v>-150</v>
+        <v>-118</v>
       </c>
       <c r="H44" t="n">
-        <v>0.6529</v>
+        <v>0.6207</v>
       </c>
       <c r="I44" t="n">
-        <v>0.096</v>
+        <v>0.1178</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>66.67</v>
+        <v>-100</v>
       </c>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="n">
-        <v>33.33</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="45">
@@ -11294,30 +13012,30 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MIN vs BAL</t>
+          <t>NYM vs PIT</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Tyler O'Neill</t>
+          <t>Brandon Lowe</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G45" t="n">
-        <v>-175</v>
+        <v>-150</v>
       </c>
       <c r="H45" t="n">
-        <v>0.6989</v>
+        <v>0.6529</v>
       </c>
       <c r="I45" t="n">
-        <v>0.108</v>
+        <v>0.096</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -11325,14 +13043,14 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L45" t="n">
-        <v>57.14</v>
+        <v>66.67</v>
       </c>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="n">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="46">
@@ -11348,30 +13066,30 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CHC vs WSN</t>
+          <t>MIN vs BAL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>CJ Abrams</t>
+          <t>Tyler O'Neill</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G46" t="n">
-        <v>-135.5</v>
+        <v>-175</v>
       </c>
       <c r="H46" t="n">
-        <v>0.6195000000000001</v>
+        <v>0.6989</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0832</v>
+        <v>0.108</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -11382,11 +13100,11 @@
         <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>73.8</v>
+        <v>57.14</v>
       </c>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="n">
-        <v>36.9</v>
+        <v>28.57</v>
       </c>
     </row>
     <row r="47">
@@ -11402,12 +13120,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PIT vs NYM</t>
+          <t>CHC vs WSN</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Francisco Lindor</t>
+          <t>CJ Abrams</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -11419,28 +13137,28 @@
         <v>0.5</v>
       </c>
       <c r="G47" t="n">
-        <v>-180.5</v>
+        <v>-135.5</v>
       </c>
       <c r="H47" t="n">
-        <v>0.6811</v>
+        <v>0.6195000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>0.0843</v>
+        <v>0.0832</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>-100</v>
+        <v>73.8</v>
       </c>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="n">
-        <v>-50</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="48">
@@ -11456,30 +13174,30 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CIN vs BOS</t>
+          <t>PIT vs NYM</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Ceddanne Rafaela</t>
+          <t>Francisco Lindor</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G48" t="n">
-        <v>-178</v>
+        <v>-180.5</v>
       </c>
       <c r="H48" t="n">
-        <v>0.6949</v>
+        <v>0.6811</v>
       </c>
       <c r="I48" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.0843</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -11487,7 +13205,7 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
         <v>-100</v>
@@ -11510,12 +13228,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>NYM vs PIT</t>
+          <t>CHC vs WSN</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Spencer Horwitz</t>
+          <t>James Wood</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -11527,13 +13245,13 @@
         <v>0.5</v>
       </c>
       <c r="G49" t="n">
-        <v>-126</v>
+        <v>-161</v>
       </c>
       <c r="H49" t="n">
-        <v>0.5911999999999999</v>
+        <v>0.6791</v>
       </c>
       <c r="I49" t="n">
-        <v>0.0756</v>
+        <v>0.1056</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -11564,12 +13282,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MIL vs CWS</t>
+          <t>NYM vs PIT</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Andrew Benintendi</t>
+          <t>Spencer Horwitz</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -11581,13 +13299,13 @@
         <v>0.5</v>
       </c>
       <c r="G50" t="n">
-        <v>-141.5</v>
+        <v>-126</v>
       </c>
       <c r="H50" t="n">
-        <v>0.6186</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>0.0741</v>
+        <v>0.0756</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -11618,30 +13336,30 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MIL vs CWS</t>
+          <t>CIN vs BOS</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Miguel Vargas</t>
+          <t>Ceddanne Rafaela</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G51" t="n">
-        <v>-145</v>
+        <v>-178</v>
       </c>
       <c r="H51" t="n">
-        <v>0.6219</v>
+        <v>0.6949</v>
       </c>
       <c r="I51" t="n">
-        <v>0.0713</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -11649,7 +13367,7 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L51" t="n">
         <v>-100</v>
@@ -11672,12 +13390,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MIN vs BAL</t>
+          <t>BOS vs CIN</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Samuel Basallo</t>
+          <t>Ke'Bryan Hayes</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -11686,16 +13404,16 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G52" t="n">
-        <v>-185</v>
+        <v>120.5</v>
       </c>
       <c r="H52" t="n">
-        <v>0.6848</v>
+        <v>0.5485</v>
       </c>
       <c r="I52" t="n">
-        <v>0.0808</v>
+        <v>0.1263</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -11703,14 +13421,14 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>54.05</v>
+        <v>120.5</v>
       </c>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="n">
-        <v>27.03</v>
+        <v>60.25</v>
       </c>
     </row>
     <row r="53">
@@ -11726,46 +13444,40 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MIN vs BAL</t>
+          <t>PHI vs TEX</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Gunnar Henderson</t>
+          <t>Wyatt Langford</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G53" t="n">
-        <v>-125</v>
+        <v>-20</v>
       </c>
       <c r="H53" t="n">
-        <v>0.5917</v>
+        <v>0.6369</v>
       </c>
       <c r="I53" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.2456</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="n">
-        <v>80</v>
-      </c>
+          <t>ODDS_ERR</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
-      <c r="N53" t="n">
-        <v>40</v>
-      </c>
+      <c r="N53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -11780,12 +13492,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MIN vs BAL</t>
+          <t>BAL vs MIN</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Adley Rutschman</t>
+          <t>Austin Martin</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -11797,28 +13509,28 @@
         <v>1.5</v>
       </c>
       <c r="G54" t="n">
-        <v>-172</v>
+        <v>-170</v>
       </c>
       <c r="H54" t="n">
-        <v>0.6712</v>
+        <v>0.6679</v>
       </c>
       <c r="I54" t="n">
-        <v>0.0818</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L54" t="n">
-        <v>-100</v>
+        <v>58.82</v>
       </c>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="n">
-        <v>-50</v>
+        <v>29.41</v>
       </c>
     </row>
     <row r="55">
@@ -11834,12 +13546,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>BAL vs MIN</t>
+          <t>CHC vs WSN</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Austin Martin</t>
+          <t>Keibert Ruiz</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -11848,32 +13560,26 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G55" t="n">
-        <v>-170</v>
+        <v>-1</v>
       </c>
       <c r="H55" t="n">
-        <v>0.6679</v>
+        <v>0.5118</v>
       </c>
       <c r="I55" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.4948</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K55" t="n">
-        <v>1</v>
-      </c>
-      <c r="L55" t="n">
-        <v>58.82</v>
-      </c>
+          <t>ODDS_ERR</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" t="n">
-        <v>29.41</v>
-      </c>
+      <c r="N55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -11888,40 +13594,46 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>PHI vs TEX</t>
+          <t>MIN vs BAL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Wyatt Langford</t>
+          <t>Gunnar Henderson</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G56" t="n">
-        <v>-20</v>
+        <v>-125</v>
       </c>
       <c r="H56" t="n">
-        <v>0.6369</v>
+        <v>0.5917</v>
       </c>
       <c r="I56" t="n">
-        <v>0.2456</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>ODDS_ERR</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>80</v>
+      </c>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+      <c r="N56" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -11936,12 +13648,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ARI vs LAD</t>
+          <t>MIN vs BAL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Miguel Rojas</t>
+          <t>Samuel Basallo</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -11953,13 +13665,13 @@
         <v>1.5</v>
       </c>
       <c r="G57" t="n">
-        <v>-260</v>
+        <v>-185</v>
       </c>
       <c r="H57" t="n">
-        <v>0.7621</v>
+        <v>0.6848</v>
       </c>
       <c r="I57" t="n">
-        <v>0.093</v>
+        <v>0.0808</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -11970,11 +13682,11 @@
         <v>1</v>
       </c>
       <c r="L57" t="n">
-        <v>38.46</v>
+        <v>54.05</v>
       </c>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="n">
-        <v>19.23</v>
+        <v>27.03</v>
       </c>
     </row>
     <row r="58">
@@ -11990,45 +13702,45 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>BOS vs CIN</t>
+          <t>MIL vs CWS</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Ke'Bryan Hayes</t>
+          <t>Miguel Vargas</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F58" t="n">
         <v>0.5</v>
       </c>
       <c r="G58" t="n">
-        <v>120.5</v>
+        <v>-145</v>
       </c>
       <c r="H58" t="n">
-        <v>0.5485</v>
+        <v>0.6219</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1263</v>
+        <v>0.0713</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K58" t="n">
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>120.5</v>
+        <v>-100</v>
       </c>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="n">
-        <v>60.25</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="59">
@@ -12044,45 +13756,45 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>PHI vs TEX</t>
+          <t>MIL vs CWS</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Sam Haggerty</t>
+          <t>Andrew Benintendi</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F59" t="n">
         <v>0.5</v>
       </c>
       <c r="G59" t="n">
-        <v>106</v>
+        <v>-141.5</v>
       </c>
       <c r="H59" t="n">
-        <v>0.5615</v>
+        <v>0.6186</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1109</v>
+        <v>0.0741</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K59" t="n">
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>106</v>
+        <v>-100</v>
       </c>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="n">
-        <v>53</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="60">
@@ -12098,12 +13810,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ARI vs LAD</t>
+          <t>MIN vs BAL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Adley Rutschman</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -12115,29 +13827,749 @@
         <v>1.5</v>
       </c>
       <c r="G60" t="n">
-        <v>-210</v>
+        <v>-172</v>
       </c>
       <c r="H60" t="n">
-        <v>0.7116</v>
+        <v>0.6712</v>
       </c>
       <c r="I60" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.0818</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L60" t="n">
-        <v>47.62</v>
+        <v>-100</v>
       </c>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="n">
-        <v>23.81</v>
-      </c>
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>SFG vs NYY</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Randal Grichuk</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G61" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.5165</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.0746</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>SFG vs NYY</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Paul Goldschmidt</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-136</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.6193</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.0839</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>MIA vs COL</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Jake McCarthy</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-216.5</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.7151</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.0794</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>COL vs MIA</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Connor Norby</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-168</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.6831</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ATL vs KCR</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Vinnie Pasquantino</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G65" t="n">
+        <v>-157</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.6475</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.0775</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ATL vs KCR</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Lane Thomas</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G66" t="n">
+        <v>109</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>COL vs MIA</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Austin Slater</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G67" t="n">
+        <v>-161</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.7345</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>COL vs MIA</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Christopher Morel</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G68" t="n">
+        <v>-178</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.7256</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.1269</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>COL vs MIA</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Xavier Edwards</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G69" t="n">
+        <v>-190</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.7413</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.1301</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>TOR vs OAK</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Nick Kurtz</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G70" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.5341</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.1023</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>COL vs MIA</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Javier Sanoja</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G71" t="n">
+        <v>-202</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.7691</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.1424</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>MIA vs COL</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Kyle Karros</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G72" t="n">
+        <v>113</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.6227</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>OAK vs TOR</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Alejandro Kirk</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G73" t="n">
+        <v>-157</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.6521</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.07870000000000001</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>COL vs MIA</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Otto Lopez</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G74" t="n">
+        <v>-145</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.6723</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.1181</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>OAK vs TOR</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Ernie Clement</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-193</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.0735</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12150,7 +14582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12340,12 +14772,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ARI vs LAD</t>
+          <t>LAD vs ARI</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Zac Gallen</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -12354,31 +14786,31 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="G4" t="n">
-        <v>109.5</v>
+        <v>-155</v>
       </c>
       <c r="H4" t="n">
-        <v>0.669</v>
+        <v>0.6659</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2304</v>
+        <v>0.0977</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="L4" t="n">
-        <v>109.5</v>
+        <v>-100</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>54.75</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="5">
@@ -12394,12 +14826,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LAD vs ARI</t>
+          <t>CIN vs BOS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Zac Gallen</t>
+          <t>Garrett Crochet</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -12408,16 +14840,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5</v>
+        <v>-5</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3341</v>
+        <v>0.3372</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3257</v>
+        <v>0.2589</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -12442,12 +14874,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CHC vs WSN</t>
+          <t>ARI vs LAD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cade Cavalli</t>
+          <t>Yoshinobu Yamamoto</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -12456,31 +14888,31 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="G6" t="n">
-        <v>-140.5</v>
+        <v>109.5</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8003</v>
+        <v>0.669</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4224</v>
+        <v>0.2304</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="L6" t="n">
-        <v>-100</v>
+        <v>109.5</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>-50</v>
+        <v>54.75</v>
       </c>
     </row>
     <row r="7">
@@ -12496,46 +14928,40 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TBR vs STL</t>
+          <t>LAD vs ARI</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Matthew Liberatore</t>
+          <t>Zac Gallen</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>14.5</v>
       </c>
       <c r="G7" t="n">
-        <v>-183.5</v>
+        <v>-0.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7463</v>
+        <v>0.3341</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1529</v>
+        <v>0.3257</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>15</v>
-      </c>
-      <c r="L7" t="n">
-        <v>54.5</v>
-      </c>
+          <t>ODDS_ERR</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="n">
-        <v>27.25</v>
-      </c>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12550,12 +14976,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LAA vs HOU</t>
+          <t>CHC vs WSN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Cade Cavalli</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -12564,16 +14990,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="G8" t="n">
-        <v>-110.5</v>
+        <v>-140.5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6015</v>
+        <v>0.8003</v>
       </c>
       <c r="I8" t="n">
-        <v>0.112</v>
+        <v>0.4224</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -12581,7 +15007,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L8" t="n">
         <v>-100</v>
@@ -12604,12 +15030,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CIN vs BOS</t>
+          <t>TBR vs STL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Garrett Crochet</t>
+          <t>Matthew Liberatore</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -12618,16 +15044,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="G9" t="n">
-        <v>-125</v>
+        <v>-183.5</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6627999999999999</v>
+        <v>0.7463</v>
       </c>
       <c r="I9" t="n">
-        <v>0.147</v>
+        <v>0.1529</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -12635,14 +15061,14 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L9" t="n">
-        <v>80</v>
+        <v>54.5</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>40</v>
+        <v>27.25</v>
       </c>
     </row>
     <row r="10">
@@ -12658,12 +15084,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BOS vs CIN</t>
+          <t>LAA vs HOU</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Andrew Abbott</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -12672,31 +15098,31 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="G10" t="n">
-        <v>125</v>
+        <v>-110.5</v>
       </c>
       <c r="H10" t="n">
-        <v>0.632</v>
+        <v>0.6015</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2242</v>
+        <v>0.112</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L10" t="n">
-        <v>125</v>
+        <v>-100</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>62.5</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="11">
@@ -12712,12 +15138,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PHI vs TEX</t>
+          <t>CIN vs BOS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Nathan Eovaldi</t>
+          <t>Garrett Crochet</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -12726,31 +15152,31 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="G11" t="n">
         <v>-125</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8067</v>
+        <v>0.6627999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2972</v>
+        <v>0.147</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L11" t="n">
-        <v>-100</v>
+        <v>80</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
-        <v>-50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12">
@@ -12766,12 +15192,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DET vs SDP</t>
+          <t>PHI vs TEX</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Nick Pivetta</t>
+          <t>Nathan Eovaldi</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -12780,16 +15206,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="G12" t="n">
-        <v>-116.5</v>
+        <v>-125</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8866000000000001</v>
+        <v>0.8067</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3851</v>
+        <v>0.2972</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -12797,7 +15223,7 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="L12" t="n">
         <v>-100</v>
@@ -12820,12 +15246,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MIL vs CWS</t>
+          <t>BOS vs CIN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Shane Smith</t>
+          <t>Andrew Abbott</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -12834,31 +15260,31 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="G13" t="n">
-        <v>-155</v>
+        <v>125</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7044</v>
+        <v>0.632</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1431</v>
+        <v>0.2242</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="L13" t="n">
-        <v>-100</v>
+        <v>125</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
-        <v>-50</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="14">
@@ -12874,12 +15300,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>WSN vs CHC</t>
+          <t>MIL vs CWS</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Matthew Boyd</t>
+          <t>Shane Smith</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -12888,16 +15314,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="G14" t="n">
-        <v>-115</v>
+        <v>-155</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6491</v>
+        <v>0.7044</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1491</v>
+        <v>0.1431</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -12905,7 +15331,7 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="L14" t="n">
         <v>-100</v>
@@ -12928,12 +15354,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>STL vs TBR</t>
+          <t>WSN vs CHC</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Matthew Boyd</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -12942,31 +15368,31 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="G15" t="n">
-        <v>-167.5</v>
+        <v>-115</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7352</v>
+        <v>0.6491</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1525</v>
+        <v>0.1491</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="L15" t="n">
-        <v>59.7</v>
+        <v>-100</v>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
-        <v>29.85</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="16">
@@ -12982,40 +15408,46 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CHC vs WSN</t>
+          <t>STL vs TBR</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Cade Cavalli</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>14.5</v>
       </c>
       <c r="G16" t="n">
-        <v>-1</v>
+        <v>-167.5</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1997</v>
+        <v>0.7352</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1827</v>
+        <v>0.1525</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>ODDS_ERR</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>15</v>
+      </c>
+      <c r="L16" t="n">
+        <v>59.7</v>
+      </c>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>29.85</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -13030,46 +15462,40 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PIT vs NYM</t>
+          <t>CHC vs WSN</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Cade Cavalli</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="G17" t="n">
-        <v>140.5</v>
+        <v>-1</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6554</v>
+        <v>0.1997</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2699</v>
+        <v>0.1827</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>15</v>
-      </c>
-      <c r="L17" t="n">
-        <v>-100</v>
-      </c>
+          <t>ODDS_ERR</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="n">
-        <v>-50</v>
-      </c>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -13084,12 +15510,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MIN vs BAL</t>
+          <t>PIT vs NYM</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Trevor Rogers</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -13098,31 +15524,31 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="G18" t="n">
-        <v>-110</v>
+        <v>140.5</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7123</v>
+        <v>0.6554</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2247</v>
+        <v>0.2699</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="L18" t="n">
-        <v>90.91</v>
+        <v>-100</v>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="n">
-        <v>45.45</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="19">
@@ -13138,12 +15564,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NYM vs PIT</t>
+          <t>MIN vs BAL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Paul Skenes</t>
+          <t>Trevor Rogers</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -13152,31 +15578,31 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="G19" t="n">
-        <v>-104.5</v>
+        <v>-110</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7044</v>
+        <v>0.7123</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2317</v>
+        <v>0.2247</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="L19" t="n">
-        <v>-100</v>
+        <v>90.91</v>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
-        <v>-50</v>
+        <v>45.45</v>
       </c>
     </row>
     <row r="20">
@@ -13192,12 +15618,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BAL vs MIN</t>
+          <t>NYM vs PIT</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Joe Ryan</t>
+          <t>Paul Skenes</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -13209,28 +15635,28 @@
         <v>15.5</v>
       </c>
       <c r="G20" t="n">
-        <v>145</v>
+        <v>-104.5</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7798</v>
+        <v>0.7044</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4004</v>
+        <v>0.2317</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="L20" t="n">
-        <v>145</v>
+        <v>-100</v>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="n">
-        <v>72.5</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="21">
@@ -13246,12 +15672,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CWS vs MIL</t>
+          <t>BAL vs MIN</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Joe Ryan</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -13260,16 +15686,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="G21" t="n">
-        <v>-175</v>
+        <v>145</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7971</v>
+        <v>0.7798</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2083</v>
+        <v>0.4004</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -13277,14 +15703,14 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L21" t="n">
-        <v>57.14</v>
+        <v>145</v>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="n">
-        <v>28.57</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="22">
@@ -13300,40 +15726,46 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CIN vs BOS</t>
+          <t>CWS vs MIL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Garrett Crochet</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="G22" t="n">
-        <v>-5</v>
+        <v>-175</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3372</v>
+        <v>0.7971</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2589</v>
+        <v>0.2083</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>ODDS_ERR</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>15</v>
+      </c>
+      <c r="L22" t="n">
+        <v>57.14</v>
+      </c>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="N22" t="n">
+        <v>28.57</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -13348,12 +15780,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>LAD vs ARI</t>
+          <t>DET vs SDP</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Zac Gallen</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -13362,16 +15794,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="G23" t="n">
-        <v>-155</v>
+        <v>-116.5</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6659</v>
+        <v>0.8866000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0977</v>
+        <v>0.3851</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -13379,7 +15811,7 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L23" t="n">
         <v>-100</v>
@@ -13388,6 +15820,246 @@
       <c r="N23" t="n">
         <v>-50</v>
       </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>COL vs MIA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Sandy Alcantara</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G24" t="n">
+        <v>135</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.5759</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.1795</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>TOR vs OAK</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Luis Severino</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-202.5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.8656</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.2444</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NYY vs SFG</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Robbie Ray</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G26" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.738</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.2774</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SFG vs NYY</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Cam Schlittler</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-120</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.6915</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.1866</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>MIA vs COL</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Kyle Freeland</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-185</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.0738</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13400,7 +16072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13606,22 +16278,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>YRFI</t>
+          <t>NRFI</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>-119</v>
+        <v>-105</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4875</v>
+        <v>-0.4852</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -13630,11 +16302,11 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-100</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>-50</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="5">
@@ -13650,12 +16322,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PIT @ NYM</t>
+          <t>CLE @ SEA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PIT @ NYM</t>
+          <t>CLE @ SEA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -13665,13 +16337,13 @@
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>-162</v>
+        <v>-155</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.4113</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5818</v>
+        <v>-0.1552</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -13680,7 +16352,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>away_1st=2 home_1st=5</t>
+          <t>away_1st=1 home_1st=1</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -13704,28 +16376,28 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DET @ SDP</t>
+          <t>ARI @ LAD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DET @ SDP</t>
+          <t>ARI @ LAD</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NRFI</t>
+          <t>YRFI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>-162</v>
+        <v>-119</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4113</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1628</v>
+        <v>0.4875</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -13734,7 +16406,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>away_1st=4 home_1st=0</t>
+          <t>away_1st=0 home_1st=0</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -13758,28 +16430,28 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TBR @ STL</t>
+          <t>PIT @ NYM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>TBR @ STL</t>
+          <t>PIT @ NYM</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>YRFI</t>
+          <t>NRFI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>100</v>
+        <v>-162</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5306</v>
+        <v>-0.5818</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -13788,7 +16460,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>away_1st=0 home_1st=0</t>
+          <t>away_1st=2 home_1st=5</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -13812,45 +16484,45 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TEX @ PHI</t>
+          <t>DET @ SDP</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>TEX @ PHI</t>
+          <t>DET @ SDP</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>YRFI</t>
+          <t>NRFI</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>-106</v>
+        <v>-162</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5887</v>
+        <v>0.4113</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1079</v>
+        <v>-0.1628</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>away_1st=0 home_1st=2</t>
+          <t>away_1st=4 home_1st=0</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>94.34</v>
+        <v>-100</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>47.17</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="9">
@@ -13866,12 +16538,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DET @ SDP</t>
+          <t>TBR @ STL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>DET @ SDP</t>
+          <t>TBR @ STL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -13881,30 +16553,30 @@
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5887</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0.161</v>
+        <v>0.5306</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>away_1st=4 home_1st=0</t>
+          <t>away_1st=0 home_1st=0</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>118</v>
+        <v>-100</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>59</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="10">
@@ -13920,28 +16592,28 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BOS @ CIN</t>
+          <t>DET @ SDP</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>BOS @ CIN</t>
+          <t>DET @ SDP</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>NRFI</t>
+          <t>YRFI</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>-155</v>
+        <v>118</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3829</v>
+        <v>0.5887</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1836</v>
+        <v>0.161</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -13950,15 +16622,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>away_1st=0 home_1st=0</t>
+          <t>away_1st=4 home_1st=0</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>64.52</v>
+        <v>118</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>32.26</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11">
@@ -13974,45 +16646,45 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CWS @ MIL</t>
+          <t>TEX @ PHI</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CWS @ MIL</t>
+          <t>TEX @ PHI</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>NRFI</t>
+          <t>YRFI</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>-129</v>
+        <v>-106</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.5887</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5273</v>
+        <v>0.1079</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>away_1st=1 home_1st=0</t>
+          <t>away_1st=0 home_1st=2</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-100</v>
+        <v>94.34</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
-        <v>-50</v>
+        <v>47.17</v>
       </c>
     </row>
     <row r="12">
@@ -14028,28 +16700,28 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LAA @ HOU</t>
+          <t>CWS @ MIL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LAA @ HOU</t>
+          <t>CWS @ MIL</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>YRFI</t>
+          <t>NRFI</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>102</v>
+        <v>-129</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5347</v>
+        <v>-0.5273</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -14058,7 +16730,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>away_1st=0 home_1st=0</t>
+          <t>away_1st=1 home_1st=0</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -14082,12 +16754,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>WSN @ CHC</t>
+          <t>LAA @ HOU</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>WSN @ CHC</t>
+          <t>LAA @ HOU</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -14097,13 +16769,13 @@
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5887</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1338</v>
+        <v>0.5347</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -14136,12 +16808,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MIN @ BAL</t>
+          <t>WSN @ CHC</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MIN @ BAL</t>
+          <t>WSN @ CHC</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -14151,13 +16823,13 @@
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>-112</v>
+        <v>106</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0.5887</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5061</v>
+        <v>0.1338</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -14190,12 +16862,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CWS @ MIL</t>
+          <t>MIN @ BAL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CWS @ MIL</t>
+          <t>MIN @ BAL</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -14205,30 +16877,30 @@
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>-102</v>
+        <v>-112</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5314</v>
+        <v>0.5061</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>away_1st=1 home_1st=0</t>
+          <t>away_1st=0 home_1st=0</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>98.04000000000001</v>
+        <v>-100</v>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
-        <v>49.02</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="16">
@@ -14244,12 +16916,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PIT @ NYM</t>
+          <t>CWS @ MIL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>PIT @ NYM</t>
+          <t>CWS @ MIL</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -14259,13 +16931,13 @@
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>120</v>
+        <v>-102</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5746</v>
+        <v>0.5314</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -14274,15 +16946,15 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>away_1st=2 home_1st=5</t>
+          <t>away_1st=1 home_1st=0</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>120</v>
+        <v>98.04000000000001</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
-        <v>60</v>
+        <v>49.02</v>
       </c>
     </row>
     <row r="17">
@@ -14298,45 +16970,45 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLE @ SEA</t>
+          <t>PIT @ NYM</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CLE @ SEA</t>
+          <t>PIT @ NYM</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>NRFI</t>
+          <t>YRFI</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
-        <v>-155</v>
+        <v>120</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4113</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1552</v>
+        <v>0.5746</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>away_1st=1 home_1st=1</t>
+          <t>away_1st=2 home_1st=5</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-100</v>
+        <v>120</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="n">
-        <v>-50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18">
@@ -14352,12 +17024,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ARI @ LAD</t>
+          <t>BOS @ CIN</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ARI @ LAD</t>
+          <t>BOS @ CIN</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -14367,13 +17039,13 @@
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>-105</v>
+        <v>-155</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>0.3829</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4852</v>
+        <v>-0.1836</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -14386,12 +17058,196 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>95.23999999999999</v>
+        <v>64.52</v>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="n">
-        <v>47.62</v>
-      </c>
+        <v>32.26</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>COL @ MIA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>COL @ MIA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>NRFI</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>-128</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.4113</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-0.1152</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NYY @ SFG</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NYY @ SFG</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>YRFI</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>-102</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.5239</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>KCR @ ATL</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>KCR @ ATL</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>YRFI</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="n">
+        <v>110</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.5887</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.1428</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>OAK @ TOR</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>OAK @ TOR</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>NRFI</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>-109</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.4113</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-0.0756</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tracking/picks.xlsx
+++ b/tracking/picks.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N152"/>
+  <dimension ref="A1:N171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8393,6 +8393,912 @@
       <c r="L152" t="inlineStr"/>
       <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>LAA @ HOU</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="n">
+        <v>144.5</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0.5634</v>
+      </c>
+      <c r="I153" t="n">
+        <v>0.1691</v>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>LAA @ HOU</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>LAA @ HOU</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G154" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H154" t="n">
+        <v>1</v>
+      </c>
+      <c r="I154" t="n">
+        <v>0.4909</v>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>CLE vs SEA</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Cal Raleigh</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G155" t="n">
+        <v>-141</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0.7042</v>
+      </c>
+      <c r="I155" t="n">
+        <v>0.1595</v>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>HOU vs LAA</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Oswald Peraza</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G156" t="n">
+        <v>-125</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0.6553</v>
+      </c>
+      <c r="I156" t="n">
+        <v>0.1438</v>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>CLE vs SEA</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Randy Arozarena</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G157" t="n">
+        <v>-121</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="I157" t="n">
+        <v>0.1101</v>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>MIA vs COL</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Edouard Julien</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G158" t="n">
+        <v>100</v>
+      </c>
+      <c r="H158" t="n">
+        <v>0.5488</v>
+      </c>
+      <c r="I158" t="n">
+        <v>0.0854</v>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>NYY vs SFG</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Patrick Bailey</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G159" t="n">
+        <v>-320</v>
+      </c>
+      <c r="H159" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="I159" t="n">
+        <v>0.0726</v>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>LAA vs HOU</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Yordan Alvarez</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G160" t="n">
+        <v>-130</v>
+      </c>
+      <c r="H160" t="n">
+        <v>0.6188</v>
+      </c>
+      <c r="I160" t="n">
+        <v>0.0906</v>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>LAA vs HOU</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Yainer Diaz</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G161" t="n">
+        <v>-175</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0.6797</v>
+      </c>
+      <c r="I161" t="n">
+        <v>0.0856</v>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>ARI vs LAD</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Shohei Ohtani</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G162" t="n">
+        <v>-140</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0.6245000000000001</v>
+      </c>
+      <c r="I162" t="n">
+        <v>0.0799</v>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>OAK vs TOR</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Nathan Lukes</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G163" t="n">
+        <v>-170</v>
+      </c>
+      <c r="H163" t="n">
+        <v>0.6636</v>
+      </c>
+      <c r="I163" t="n">
+        <v>0.0742</v>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>LAD vs ARI</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Ryne Nelson</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G164" t="n">
+        <v>130</v>
+      </c>
+      <c r="H164" t="n">
+        <v>0.8461</v>
+      </c>
+      <c r="I164" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>SEA vs CLE</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Gavin Williams</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G165" t="n">
+        <v>122</v>
+      </c>
+      <c r="H165" t="n">
+        <v>0.6146</v>
+      </c>
+      <c r="I165" t="n">
+        <v>0.1957</v>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>MIA vs COL</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Kyle Freeland</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G166" t="n">
+        <v>126</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0.5602</v>
+      </c>
+      <c r="I166" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>HOU vs LAA</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Yusei Kikuchi</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G167" t="n">
+        <v>-145</v>
+      </c>
+      <c r="H167" t="n">
+        <v>0.6884</v>
+      </c>
+      <c r="I167" t="n">
+        <v>0.1403</v>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>SDP vs DET</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Framber Valdez</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G168" t="n">
+        <v>-121.5</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0.6146</v>
+      </c>
+      <c r="I168" t="n">
+        <v>0.1073</v>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>LAA vs HOU</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Mike Burrows</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G169" t="n">
+        <v>-196.5</v>
+      </c>
+      <c r="H169" t="n">
+        <v>0.7034</v>
+      </c>
+      <c r="I169" t="n">
+        <v>0.08939999999999999</v>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>LAA @ HOU</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>LAA @ HOU</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>YRFI</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="n">
+        <v>-100</v>
+      </c>
+      <c r="H170" t="n">
+        <v>1</v>
+      </c>
+      <c r="I170" t="n">
+        <v>0.5306</v>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>COL @ MIA</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>COL @ MIA</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>YRFI</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="n">
+        <v>-102</v>
+      </c>
+      <c r="H171" t="n">
+        <v>0.5887</v>
+      </c>
+      <c r="I171" t="n">
+        <v>0.1126</v>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8942,7 +9848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9540,6 +10446,52 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>LAA @ HOU</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>144.5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.5634</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.1691</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9552,7 +10504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10450,12 +11402,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>COL @ MIA</t>
+          <t>KCR @ ATL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>COL @ MIA</t>
+          <t>KCR @ ATL</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -10467,13 +11419,13 @@
         <v>7.5</v>
       </c>
       <c r="G17" t="n">
-        <v>-112.5</v>
+        <v>-100</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4946</v>
+        <v>0.5231</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -10594,12 +11546,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>KCR @ ATL</t>
+          <t>COL @ MIA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>KCR @ ATL</t>
+          <t>COL @ MIA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -10611,13 +11563,13 @@
         <v>7.5</v>
       </c>
       <c r="G20" t="n">
-        <v>-100</v>
+        <v>-112.5</v>
       </c>
       <c r="H20" t="n">
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5231</v>
+        <v>0.4946</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -10628,6 +11580,54 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>LAA @ HOU</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LAA @ HOU</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.4909</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10640,7 +11640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N75"/>
+  <dimension ref="A1:N84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11310,45 +12310,45 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SDP vs DET</t>
+          <t>STL vs TBR</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Spencer Torkelson</t>
+          <t>Carson Williams</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>0.5</v>
       </c>
       <c r="G13" t="n">
-        <v>-145</v>
+        <v>110</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.5195</v>
       </c>
       <c r="I13" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.077</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>68.97</v>
+        <v>-100</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
-        <v>34.48</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="14">
@@ -11364,30 +12364,30 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LAA vs HOU</t>
+          <t>DET vs SDP</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Yainer Diaz</t>
+          <t>Manny Machado</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G14" t="n">
-        <v>-182</v>
+        <v>-164.5</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6797</v>
+        <v>0.6501</v>
       </c>
       <c r="I14" t="n">
-        <v>0.077</v>
+        <v>0.0707</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -11395,14 +12395,14 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>54.95</v>
+        <v>60.79</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
-        <v>27.47</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="15">
@@ -11423,7 +12423,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ben Williamson</t>
+          <t>Nick Fortes</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -11432,16 +12432,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G15" t="n">
-        <v>-195.5</v>
+        <v>119.5</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7428</v>
+        <v>0.5552</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1248</v>
+        <v>0.131</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -11472,12 +12472,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>STL vs TBR</t>
+          <t>LAA vs HOU</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Yainer Diaz</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -11486,31 +12486,31 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G16" t="n">
-        <v>119.5</v>
+        <v>-182</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5552</v>
+        <v>0.6797</v>
       </c>
       <c r="I16" t="n">
-        <v>0.131</v>
+        <v>0.077</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>-100</v>
+        <v>54.95</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
-        <v>-50</v>
+        <v>27.47</v>
       </c>
     </row>
     <row r="17">
@@ -11633,7 +12633,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Carson Williams</t>
+          <t>Ben Williamson</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -11642,16 +12642,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G19" t="n">
-        <v>110</v>
+        <v>-195.5</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5195</v>
+        <v>0.7428</v>
       </c>
       <c r="I19" t="n">
-        <v>0.077</v>
+        <v>0.1248</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -11659,7 +12659,7 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L19" t="n">
         <v>-100</v>
@@ -12478,12 +13478,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>DET vs SDP</t>
+          <t>SDP vs DET</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Manny Machado</t>
+          <t>Spencer Torkelson</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -12495,13 +13495,13 @@
         <v>0.5</v>
       </c>
       <c r="G35" t="n">
-        <v>-164.5</v>
+        <v>-145</v>
       </c>
       <c r="H35" t="n">
-        <v>0.6501</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0707</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -12512,11 +13512,11 @@
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>60.79</v>
+        <v>68.97</v>
       </c>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="n">
-        <v>30.4</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="36">
@@ -12586,12 +13586,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NYM vs PIT</t>
+          <t>PHI vs TEX</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Jared Triolo</t>
+          <t>Sam Haggerty</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -12603,23 +13603,29 @@
         <v>0.5</v>
       </c>
       <c r="G37" t="n">
-        <v>-5</v>
+        <v>106</v>
       </c>
       <c r="H37" t="n">
-        <v>0.488</v>
+        <v>0.5615</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4119</v>
+        <v>0.1109</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>ODDS_ERR</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>106</v>
+      </c>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="N37" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -12850,45 +13856,45 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PHI vs TEX</t>
+          <t>CHC vs WSN</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Sam Haggerty</t>
+          <t>James Wood</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>0.5</v>
       </c>
       <c r="G42" t="n">
-        <v>106</v>
+        <v>-161</v>
       </c>
       <c r="H42" t="n">
-        <v>0.5615</v>
+        <v>0.6791</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1109</v>
+        <v>0.1056</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>106</v>
+        <v>-100</v>
       </c>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="n">
-        <v>53</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="43">
@@ -13228,46 +14234,40 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CHC vs WSN</t>
+          <t>NYM vs PIT</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>James Wood</t>
+          <t>Jared Triolo</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F49" t="n">
         <v>0.5</v>
       </c>
       <c r="G49" t="n">
-        <v>-161</v>
+        <v>-5</v>
       </c>
       <c r="H49" t="n">
-        <v>0.6791</v>
+        <v>0.488</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1056</v>
+        <v>0.4119</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
-        <v>-100</v>
-      </c>
+          <t>ODDS_ERR</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
-      <c r="N49" t="n">
-        <v>-50</v>
-      </c>
+      <c r="N49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -13390,12 +14390,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BOS vs CIN</t>
+          <t>CHC vs WSN</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Ke'Bryan Hayes</t>
+          <t>Keibert Ruiz</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -13407,29 +14407,23 @@
         <v>0.5</v>
       </c>
       <c r="G52" t="n">
-        <v>120.5</v>
+        <v>-1</v>
       </c>
       <c r="H52" t="n">
-        <v>0.5485</v>
+        <v>0.5118</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1263</v>
+        <v>0.4948</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" t="n">
-        <v>120.5</v>
-      </c>
+          <t>ODDS_ERR</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" t="n">
-        <v>60.25</v>
-      </c>
+      <c r="N52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -13546,12 +14540,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CHC vs WSN</t>
+          <t>MIN vs BAL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Keibert Ruiz</t>
+          <t>Adley Rutschman</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -13560,26 +14554,32 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G55" t="n">
-        <v>-1</v>
+        <v>-172</v>
       </c>
       <c r="H55" t="n">
-        <v>0.5118</v>
+        <v>0.6712</v>
       </c>
       <c r="I55" t="n">
-        <v>0.4948</v>
+        <v>0.0818</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>ODDS_ERR</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>3</v>
+      </c>
+      <c r="L55" t="n">
+        <v>-100</v>
+      </c>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+      <c r="N55" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -13594,12 +14594,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MIN vs BAL</t>
+          <t>BOS vs CIN</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Gunnar Henderson</t>
+          <t>Ke'Bryan Hayes</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -13608,16 +14608,16 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G56" t="n">
-        <v>-125</v>
+        <v>120.5</v>
       </c>
       <c r="H56" t="n">
-        <v>0.5917</v>
+        <v>0.5485</v>
       </c>
       <c r="I56" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.1263</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -13628,11 +14628,11 @@
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>80</v>
+        <v>120.5</v>
       </c>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="n">
-        <v>40</v>
+        <v>60.25</v>
       </c>
     </row>
     <row r="57">
@@ -13815,7 +14815,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Adley Rutschman</t>
+          <t>Gunnar Henderson</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -13827,28 +14827,28 @@
         <v>1.5</v>
       </c>
       <c r="G60" t="n">
-        <v>-172</v>
+        <v>-125</v>
       </c>
       <c r="H60" t="n">
-        <v>0.6712</v>
+        <v>0.5917</v>
       </c>
       <c r="I60" t="n">
-        <v>0.0818</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K60" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>-100</v>
+        <v>80</v>
       </c>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="n">
-        <v>-50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="61">
@@ -13864,12 +14864,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SFG vs NYY</t>
+          <t>LAA vs HOU</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Randal Grichuk</t>
+          <t>Yainer Diaz</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -13878,16 +14878,16 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G61" t="n">
-        <v>110.5</v>
+        <v>-175</v>
       </c>
       <c r="H61" t="n">
-        <v>0.5165</v>
+        <v>0.6797</v>
       </c>
       <c r="I61" t="n">
-        <v>0.0746</v>
+        <v>0.0856</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -13960,12 +14960,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MIA vs COL</t>
+          <t>LAA vs HOU</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Jake McCarthy</t>
+          <t>Yordan Alvarez</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -13977,13 +14977,13 @@
         <v>1.5</v>
       </c>
       <c r="G63" t="n">
-        <v>-216.5</v>
+        <v>-130</v>
       </c>
       <c r="H63" t="n">
-        <v>0.7151</v>
+        <v>0.6188</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0794</v>
+        <v>0.0906</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -14008,12 +15008,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>COL vs MIA</t>
+          <t>NYY vs SFG</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Connor Norby</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -14025,13 +15025,13 @@
         <v>1.5</v>
       </c>
       <c r="G64" t="n">
-        <v>-168</v>
+        <v>-320</v>
       </c>
       <c r="H64" t="n">
-        <v>0.6831</v>
+        <v>0.791</v>
       </c>
       <c r="I64" t="n">
-        <v>0.099</v>
+        <v>0.0726</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -14056,30 +15056,30 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ATL vs KCR</t>
+          <t>MIA vs COL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Vinnie Pasquantino</t>
+          <t>Edouard Julien</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F65" t="n">
         <v>0.5</v>
       </c>
       <c r="G65" t="n">
-        <v>-157</v>
+        <v>100</v>
       </c>
       <c r="H65" t="n">
-        <v>0.6475</v>
+        <v>0.5488</v>
       </c>
       <c r="I65" t="n">
-        <v>0.0775</v>
+        <v>0.0854</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -14104,30 +15104,30 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ATL vs KCR</t>
+          <t>CLE vs SEA</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Lane Thomas</t>
+          <t>Randy Arozarena</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F66" t="n">
         <v>0.5</v>
       </c>
       <c r="G66" t="n">
-        <v>109</v>
+        <v>-121</v>
       </c>
       <c r="H66" t="n">
-        <v>0.535</v>
+        <v>0.616</v>
       </c>
       <c r="I66" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.1101</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -14152,12 +15152,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>COL vs MIA</t>
+          <t>HOU vs LAA</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Austin Slater</t>
+          <t>Oswald Peraza</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -14166,16 +15166,16 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G67" t="n">
-        <v>-161</v>
+        <v>-125</v>
       </c>
       <c r="H67" t="n">
-        <v>0.7345</v>
+        <v>0.6553</v>
       </c>
       <c r="I67" t="n">
-        <v>0.156</v>
+        <v>0.1438</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -14200,30 +15200,30 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>COL vs MIA</t>
+          <t>CLE vs SEA</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Christopher Morel</t>
+          <t>Cal Raleigh</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G68" t="n">
-        <v>-178</v>
+        <v>-141</v>
       </c>
       <c r="H68" t="n">
-        <v>0.7256</v>
+        <v>0.7042</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1269</v>
+        <v>0.1595</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -14248,12 +15248,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>COL vs MIA</t>
+          <t>OAK vs TOR</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Xavier Edwards</t>
+          <t>Ernie Clement</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -14265,13 +15265,13 @@
         <v>1.5</v>
       </c>
       <c r="G69" t="n">
-        <v>-190</v>
+        <v>-193</v>
       </c>
       <c r="H69" t="n">
-        <v>0.7413</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1301</v>
+        <v>0.0735</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -14296,30 +15296,30 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>TOR vs OAK</t>
+          <t>OAK vs TOR</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Nick Kurtz</t>
+          <t>Alejandro Kirk</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F70" t="n">
         <v>1.5</v>
       </c>
       <c r="G70" t="n">
-        <v>116.5</v>
+        <v>-157</v>
       </c>
       <c r="H70" t="n">
-        <v>0.5341</v>
+        <v>0.6521</v>
       </c>
       <c r="I70" t="n">
-        <v>0.1023</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -14344,12 +15344,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>COL vs MIA</t>
+          <t>MIA vs COL</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Javier Sanoja</t>
+          <t>Jake McCarthy</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -14361,13 +15361,13 @@
         <v>1.5</v>
       </c>
       <c r="G71" t="n">
-        <v>-202</v>
+        <v>-216.5</v>
       </c>
       <c r="H71" t="n">
-        <v>0.7691</v>
+        <v>0.7151</v>
       </c>
       <c r="I71" t="n">
-        <v>0.1424</v>
+        <v>0.0794</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -14392,12 +15392,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MIA vs COL</t>
+          <t>COL vs MIA</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Kyle Karros</t>
+          <t>Otto Lopez</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -14406,16 +15406,16 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G72" t="n">
-        <v>113</v>
+        <v>-145</v>
       </c>
       <c r="H72" t="n">
-        <v>0.6227</v>
+        <v>0.6723</v>
       </c>
       <c r="I72" t="n">
-        <v>0.185</v>
+        <v>0.1181</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -14440,30 +15440,30 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>OAK vs TOR</t>
+          <t>ATL vs KCR</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Alejandro Kirk</t>
+          <t>Vinnie Pasquantino</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G73" t="n">
         <v>-157</v>
       </c>
       <c r="H73" t="n">
-        <v>0.6521</v>
+        <v>0.6475</v>
       </c>
       <c r="I73" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.0775</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -14488,12 +15488,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>COL vs MIA</t>
+          <t>SFG vs NYY</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Otto Lopez</t>
+          <t>Randal Grichuk</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -14502,16 +15502,16 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G74" t="n">
-        <v>-145</v>
+        <v>110.5</v>
       </c>
       <c r="H74" t="n">
-        <v>0.6723</v>
+        <v>0.5165</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1181</v>
+        <v>0.0746</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -14536,12 +15536,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>OAK vs TOR</t>
+          <t>ATL vs KCR</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Ernie Clement</t>
+          <t>Lane Thomas</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -14550,16 +15550,16 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G75" t="n">
-        <v>-193</v>
+        <v>109</v>
       </c>
       <c r="H75" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.535</v>
       </c>
       <c r="I75" t="n">
-        <v>0.0735</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -14570,6 +15570,438 @@
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>COL vs MIA</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Christopher Morel</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G76" t="n">
+        <v>-178</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.7256</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.1269</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>COL vs MIA</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Xavier Edwards</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G77" t="n">
+        <v>-190</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.7413</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.1301</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>TOR vs OAK</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Nick Kurtz</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G78" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.5341</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.1023</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>COL vs MIA</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Javier Sanoja</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G79" t="n">
+        <v>-202</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.7691</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.1424</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>COL vs MIA</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Austin Slater</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G80" t="n">
+        <v>-161</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.7345</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>MIA vs COL</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Kyle Karros</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G81" t="n">
+        <v>113</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.6227</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ARI vs LAD</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Shohei Ohtani</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G82" t="n">
+        <v>-140</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.6245000000000001</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0.0799</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>COL vs MIA</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Connor Norby</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G83" t="n">
+        <v>-168</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.6831</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>OAK vs TOR</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Nathan Lukes</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G84" t="n">
+        <v>-170</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0.6636</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.0742</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14582,7 +16014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N28"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15030,12 +16462,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TBR vs STL</t>
+          <t>LAA vs HOU</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Matthew Liberatore</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -15044,31 +16476,31 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="G9" t="n">
-        <v>-183.5</v>
+        <v>-110.5</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7463</v>
+        <v>0.6015</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1529</v>
+        <v>0.112</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L9" t="n">
-        <v>54.5</v>
+        <v>-100</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>27.25</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="10">
@@ -15084,12 +16516,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LAA vs HOU</t>
+          <t>CIN vs BOS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Garrett Crochet</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -15101,28 +16533,28 @@
         <v>17.5</v>
       </c>
       <c r="G10" t="n">
-        <v>-110.5</v>
+        <v>-125</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6015</v>
+        <v>0.6627999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>0.112</v>
+        <v>0.147</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L10" t="n">
-        <v>-100</v>
+        <v>80</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>-50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
@@ -15138,12 +16570,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CIN vs BOS</t>
+          <t>BOS vs CIN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Garrett Crochet</t>
+          <t>Andrew Abbott</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -15152,16 +16584,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="G11" t="n">
-        <v>-125</v>
+        <v>125</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6627999999999999</v>
+        <v>0.632</v>
       </c>
       <c r="I11" t="n">
-        <v>0.147</v>
+        <v>0.2242</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -15172,11 +16604,11 @@
         <v>18</v>
       </c>
       <c r="L11" t="n">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
-        <v>40</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="12">
@@ -15246,12 +16678,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BOS vs CIN</t>
+          <t>TBR vs STL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Andrew Abbott</t>
+          <t>Matthew Liberatore</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -15260,16 +16692,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="G13" t="n">
-        <v>125</v>
+        <v>-183.5</v>
       </c>
       <c r="H13" t="n">
-        <v>0.632</v>
+        <v>0.7463</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2242</v>
+        <v>0.1529</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -15277,14 +16709,14 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L13" t="n">
-        <v>125</v>
+        <v>54.5</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
-        <v>62.5</v>
+        <v>27.25</v>
       </c>
     </row>
     <row r="14">
@@ -15834,30 +17266,30 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>COL vs MIA</t>
+          <t>HOU vs LAA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sandy Alcantara</t>
+          <t>Yusei Kikuchi</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="G24" t="n">
-        <v>135</v>
+        <v>-145</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5759</v>
+        <v>0.6884</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1795</v>
+        <v>0.1403</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -15882,12 +17314,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TOR vs OAK</t>
+          <t>MIA vs COL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Luis Severino</t>
+          <t>Kyle Freeland</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -15896,16 +17328,16 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="G25" t="n">
-        <v>-202.5</v>
+        <v>126</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8656</v>
+        <v>0.5602</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2444</v>
+        <v>0.15</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -15930,12 +17362,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NYY vs SFG</t>
+          <t>SEA vs CLE</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Robbie Ray</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -15947,13 +17379,13 @@
         <v>15.5</v>
       </c>
       <c r="G26" t="n">
-        <v>100.5</v>
+        <v>122</v>
       </c>
       <c r="H26" t="n">
-        <v>0.738</v>
+        <v>0.6146</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2774</v>
+        <v>0.1957</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -15978,12 +17410,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SFG vs NYY</t>
+          <t>LAD vs ARI</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Cam Schlittler</t>
+          <t>Ryne Nelson</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -15992,16 +17424,16 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="G27" t="n">
-        <v>-120</v>
+        <v>130</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6915</v>
+        <v>0.8461</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1866</v>
+        <v>0.445</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -16026,12 +17458,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MIA vs COL</t>
+          <t>TOR vs OAK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Kyle Freeland</t>
+          <t>Luis Severino</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -16043,13 +17475,13 @@
         <v>14.5</v>
       </c>
       <c r="G28" t="n">
-        <v>-185</v>
+        <v>-202.5</v>
       </c>
       <c r="H28" t="n">
-        <v>0.669</v>
+        <v>0.8656</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0738</v>
+        <v>0.2444</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -16060,6 +17492,294 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>COL vs MIA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Sandy Alcantara</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>135</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.5759</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.1795</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SFG vs NYY</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Cam Schlittler</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-120</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.6915</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.1866</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NYY vs SFG</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Robbie Ray</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G31" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.738</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.2774</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SDP vs DET</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Framber Valdez</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-121.5</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.6146</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.1073</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>MIA vs COL</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Kyle Freeland</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-185</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.0738</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>LAA vs HOU</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Mike Burrows</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-196.5</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.7034</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.08939999999999999</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16072,7 +17792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16538,12 +18258,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TBR @ STL</t>
+          <t>TEX @ PHI</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>TBR @ STL</t>
+          <t>TEX @ PHI</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -16553,30 +18273,30 @@
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>100</v>
+        <v>-106</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0.5887</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5306</v>
+        <v>0.1079</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>away_1st=0 home_1st=0</t>
+          <t>away_1st=0 home_1st=2</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-100</v>
+        <v>94.34</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>-50</v>
+        <v>47.17</v>
       </c>
     </row>
     <row r="10">
@@ -16646,12 +18366,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TEX @ PHI</t>
+          <t>TBR @ STL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>TEX @ PHI</t>
+          <t>TBR @ STL</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -16661,30 +18381,30 @@
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>-106</v>
+        <v>100</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5887</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1079</v>
+        <v>0.5306</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>away_1st=0 home_1st=2</t>
+          <t>away_1st=0 home_1st=0</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>94.34</v>
+        <v>-100</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
-        <v>47.17</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="12">
@@ -17078,28 +18798,28 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>COL @ MIA</t>
+          <t>LAA @ HOU</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>COL @ MIA</t>
+          <t>LAA @ HOU</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>NRFI</t>
+          <t>YRFI</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>-128</v>
+        <v>-100</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4113</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1152</v>
+        <v>0.5306</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -17216,12 +18936,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>OAK @ TOR</t>
+          <t>COL @ MIA</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>OAK @ TOR</t>
+          <t>COL @ MIA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -17231,13 +18951,13 @@
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
-        <v>-109</v>
+        <v>-128</v>
       </c>
       <c r="H22" t="n">
         <v>0.4113</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0756</v>
+        <v>-0.1152</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -17249,6 +18969,98 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>OAK @ TOR</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>OAK @ TOR</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>NRFI</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="n">
+        <v>-109</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.4113</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-0.0756</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>COL @ MIA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>COL @ MIA</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>YRFI</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="n">
+        <v>-102</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.5887</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.1126</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tracking/picks.xlsx
+++ b/tracking/picks.xlsx
@@ -7004,13 +7004,21 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="L123" t="n">
+        <v>-100</v>
+      </c>
       <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
+      <c r="N123" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -7050,13 +7058,21 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="L124" t="n">
+        <v>51.28</v>
+      </c>
       <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
+      <c r="N124" t="n">
+        <v>25.64</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -7098,13 +7114,19 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K125" t="n">
+        <v>3</v>
+      </c>
+      <c r="L125" t="n">
+        <v>-100</v>
+      </c>
       <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
+      <c r="N125" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -7146,13 +7168,19 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K126" t="n">
+        <v>5</v>
+      </c>
+      <c r="L126" t="n">
+        <v>-100</v>
+      </c>
       <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
+      <c r="N126" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7194,13 +7222,19 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K127" t="n">
+        <v>3</v>
+      </c>
+      <c r="L127" t="n">
+        <v>-100</v>
+      </c>
       <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
+      <c r="N127" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -7242,13 +7276,19 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K128" t="n">
+        <v>6</v>
+      </c>
+      <c r="L128" t="n">
+        <v>-100</v>
+      </c>
       <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
+      <c r="N128" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -7290,13 +7330,19 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K129" t="n">
+        <v>1</v>
+      </c>
+      <c r="L129" t="n">
+        <v>-100</v>
+      </c>
       <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
+      <c r="N129" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -7338,13 +7384,19 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K130" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" t="n">
+        <v>62.11</v>
+      </c>
       <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
+      <c r="N130" t="n">
+        <v>31.06</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -7386,13 +7438,19 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K131" t="n">
+        <v>3</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-100</v>
+      </c>
       <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
+      <c r="N131" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -7434,13 +7492,19 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K132" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" t="n">
+        <v>-100</v>
+      </c>
       <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
+      <c r="N132" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -7482,13 +7546,19 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K133" t="n">
+        <v>1</v>
+      </c>
+      <c r="L133" t="n">
+        <v>52.63</v>
+      </c>
       <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
+      <c r="N133" t="n">
+        <v>26.32</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7530,13 +7600,17 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>DNP</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
+      <c r="L134" t="n">
+        <v>0</v>
+      </c>
       <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
+      <c r="N134" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7578,13 +7652,19 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K135" t="n">
+        <v>0</v>
+      </c>
+      <c r="L135" t="n">
+        <v>68.97</v>
+      </c>
       <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
+      <c r="N135" t="n">
+        <v>34.48</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -7626,13 +7706,19 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K136" t="n">
+        <v>1</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-100</v>
+      </c>
       <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
+      <c r="N136" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -7674,13 +7760,19 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K137" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" t="n">
+        <v>110.5</v>
+      </c>
       <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
+      <c r="N137" t="n">
+        <v>55.25</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -7722,13 +7814,19 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" t="n">
+        <v>-100</v>
+      </c>
       <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
+      <c r="N138" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7770,13 +7868,19 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K139" t="n">
+        <v>3</v>
+      </c>
+      <c r="L139" t="n">
+        <v>-100</v>
+      </c>
       <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
+      <c r="N139" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -7818,13 +7922,19 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K140" t="n">
+        <v>1</v>
+      </c>
+      <c r="L140" t="n">
+        <v>46.19</v>
+      </c>
       <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
+      <c r="N140" t="n">
+        <v>23.09</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -7866,13 +7976,19 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K141" t="n">
+        <v>2</v>
+      </c>
+      <c r="L141" t="n">
+        <v>-100</v>
+      </c>
       <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
+      <c r="N141" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -7914,13 +8030,19 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K142" t="n">
+        <v>0</v>
+      </c>
+      <c r="L142" t="n">
+        <v>63.69</v>
+      </c>
       <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
+      <c r="N142" t="n">
+        <v>31.85</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7962,13 +8084,19 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K143" t="n">
+        <v>4</v>
+      </c>
+      <c r="L143" t="n">
+        <v>-100</v>
+      </c>
       <c r="M143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
+      <c r="N143" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -8010,13 +8138,19 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K144" t="n">
+        <v>15</v>
+      </c>
+      <c r="L144" t="n">
+        <v>49.38</v>
+      </c>
       <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
+      <c r="N144" t="n">
+        <v>24.69</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -8058,13 +8192,19 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K145" t="n">
+        <v>16</v>
+      </c>
+      <c r="L145" t="n">
+        <v>100.5</v>
+      </c>
       <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
+      <c r="N145" t="n">
+        <v>50.25</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -8106,13 +8246,19 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K146" t="n">
+        <v>16</v>
+      </c>
+      <c r="L146" t="n">
+        <v>83.33</v>
+      </c>
       <c r="M146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
+      <c r="N146" t="n">
+        <v>41.67</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -8154,13 +8300,19 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K147" t="n">
+        <v>21</v>
+      </c>
+      <c r="L147" t="n">
+        <v>-100</v>
+      </c>
       <c r="M147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
+      <c r="N147" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -8202,13 +8354,19 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K148" t="n">
+        <v>13</v>
+      </c>
+      <c r="L148" t="n">
+        <v>-100</v>
+      </c>
       <c r="M148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
+      <c r="N148" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -8248,13 +8406,21 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>away_1st=0 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L149" t="n">
+        <v>-100</v>
+      </c>
       <c r="M149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
+      <c r="N149" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -8294,13 +8460,21 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>away_1st=0 home_1st=1</t>
+        </is>
+      </c>
+      <c r="L150" t="n">
+        <v>110</v>
+      </c>
       <c r="M150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
+      <c r="N150" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -8340,13 +8514,21 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>away_1st=0 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L151" t="n">
+        <v>78.12</v>
+      </c>
       <c r="M151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
+      <c r="N151" t="n">
+        <v>39.06</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -8386,13 +8568,21 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>away_1st=0 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L152" t="n">
+        <v>91.73999999999999</v>
+      </c>
       <c r="M152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
+      <c r="N152" t="n">
+        <v>45.87</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -8432,13 +8622,21 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>6-2</t>
+        </is>
+      </c>
+      <c r="L153" t="n">
+        <v>144.5</v>
+      </c>
       <c r="M153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
+      <c r="N153" t="n">
+        <v>72.25</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -8480,13 +8678,19 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K154" t="n">
+        <v>8</v>
+      </c>
+      <c r="L154" t="n">
+        <v>-100</v>
+      </c>
       <c r="M154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
+      <c r="N154" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -8528,13 +8732,19 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K155" t="n">
+        <v>0</v>
+      </c>
+      <c r="L155" t="n">
+        <v>-100</v>
+      </c>
       <c r="M155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
+      <c r="N155" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -8576,13 +8786,19 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K156" t="n">
+        <v>0</v>
+      </c>
+      <c r="L156" t="n">
+        <v>80</v>
+      </c>
       <c r="M156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
+      <c r="N156" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -8624,13 +8840,19 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K157" t="n">
+        <v>0</v>
+      </c>
+      <c r="L157" t="n">
+        <v>-100</v>
+      </c>
       <c r="M157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
+      <c r="N157" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -8672,13 +8894,19 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K158" t="n">
+        <v>0</v>
+      </c>
+      <c r="L158" t="n">
+        <v>100</v>
+      </c>
       <c r="M158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
+      <c r="N158" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -8720,13 +8948,19 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K159" t="n">
+        <v>0</v>
+      </c>
+      <c r="L159" t="n">
+        <v>31.25</v>
+      </c>
       <c r="M159" t="inlineStr"/>
-      <c r="N159" t="inlineStr"/>
+      <c r="N159" t="n">
+        <v>15.62</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -8768,13 +9002,19 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K160" t="n">
+        <v>4</v>
+      </c>
+      <c r="L160" t="n">
+        <v>-100</v>
+      </c>
       <c r="M160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
+      <c r="N160" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -8816,13 +9056,19 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K161" t="n">
+        <v>1</v>
+      </c>
+      <c r="L161" t="n">
+        <v>57.14</v>
+      </c>
       <c r="M161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
+      <c r="N161" t="n">
+        <v>28.57</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -8864,13 +9110,19 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K162" t="n">
+        <v>0</v>
+      </c>
+      <c r="L162" t="n">
+        <v>71.43000000000001</v>
+      </c>
       <c r="M162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
+      <c r="N162" t="n">
+        <v>35.71</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -8912,13 +9164,19 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K163" t="n">
+        <v>0</v>
+      </c>
+      <c r="L163" t="n">
+        <v>58.82</v>
+      </c>
       <c r="M163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
+      <c r="N163" t="n">
+        <v>29.41</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -8960,13 +9218,19 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K164" t="n">
+        <v>14</v>
+      </c>
+      <c r="L164" t="n">
+        <v>-100</v>
+      </c>
       <c r="M164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
+      <c r="N164" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -9008,13 +9272,19 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K165" t="n">
+        <v>15</v>
+      </c>
+      <c r="L165" t="n">
+        <v>-100</v>
+      </c>
       <c r="M165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
+      <c r="N165" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -9056,13 +9326,19 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K166" t="n">
+        <v>13</v>
+      </c>
+      <c r="L166" t="n">
+        <v>-100</v>
+      </c>
       <c r="M166" t="inlineStr"/>
-      <c r="N166" t="inlineStr"/>
+      <c r="N166" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -9104,13 +9380,19 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K167" t="n">
+        <v>13</v>
+      </c>
+      <c r="L167" t="n">
+        <v>-100</v>
+      </c>
       <c r="M167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
+      <c r="N167" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -9152,13 +9434,19 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K168" t="n">
+        <v>18</v>
+      </c>
+      <c r="L168" t="n">
+        <v>82.3</v>
+      </c>
       <c r="M168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
+      <c r="N168" t="n">
+        <v>41.15</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -9200,13 +9488,19 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K169" t="n">
+        <v>17</v>
+      </c>
+      <c r="L169" t="n">
+        <v>50.89</v>
+      </c>
       <c r="M169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
+      <c r="N169" t="n">
+        <v>25.45</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -9246,13 +9540,21 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>away_1st=1 home_1st=1</t>
+        </is>
+      </c>
+      <c r="L170" t="n">
+        <v>100</v>
+      </c>
       <c r="M170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
+      <c r="N170" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -9292,13 +9594,21 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>away_1st=0 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L171" t="n">
+        <v>-100</v>
+      </c>
       <c r="M171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
+      <c r="N171" t="n">
+        <v>-50</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9363,19 +9673,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5</v>
+        <v>0.545</v>
       </c>
       <c r="G2" t="n">
-        <v>-37.64</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="3">
@@ -9393,16 +9703,16 @@
         <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.714</v>
+        <v>0.526</v>
       </c>
       <c r="G3" t="n">
-        <v>252.33</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="4">
@@ -9417,19 +9727,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="D4" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.548</v>
       </c>
       <c r="G4" t="n">
-        <v>-41.28</v>
+        <v>-189.92</v>
       </c>
     </row>
     <row r="5">
@@ -9444,19 +9754,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5</v>
+        <v>0.483</v>
       </c>
       <c r="G5" t="n">
-        <v>-39.13</v>
+        <v>-155.92</v>
       </c>
     </row>
     <row r="6">
@@ -9471,19 +9781,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.412</v>
+        <v>0.478</v>
       </c>
       <c r="G6" t="n">
-        <v>-173.18</v>
+        <v>-83.25</v>
       </c>
     </row>
     <row r="7">
@@ -9498,19 +9808,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="D7" t="n">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0.542</v>
+        <v>0.523</v>
       </c>
       <c r="G7" t="n">
-        <v>-38.9</v>
+        <v>-416.51</v>
       </c>
     </row>
     <row r="8">
@@ -9525,19 +9835,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5</v>
+        <v>0.545</v>
       </c>
       <c r="G8" t="n">
-        <v>-37.64</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="9">
@@ -9555,16 +9865,16 @@
         <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0.714</v>
+        <v>0.526</v>
       </c>
       <c r="G9" t="n">
-        <v>252.33</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="10">
@@ -9579,19 +9889,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="D10" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.548</v>
       </c>
       <c r="G10" t="n">
-        <v>-41.28</v>
+        <v>-189.92</v>
       </c>
     </row>
     <row r="11">
@@ -9606,19 +9916,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5</v>
+        <v>0.483</v>
       </c>
       <c r="G11" t="n">
-        <v>-39.13</v>
+        <v>-155.92</v>
       </c>
     </row>
     <row r="12">
@@ -9633,19 +9943,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.412</v>
+        <v>0.478</v>
       </c>
       <c r="G12" t="n">
-        <v>-173.18</v>
+        <v>-83.25</v>
       </c>
     </row>
     <row r="13">
@@ -9660,19 +9970,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.542</v>
+        <v>0.523</v>
       </c>
       <c r="G13" t="n">
-        <v>-38.9</v>
+        <v>-416.51</v>
       </c>
     </row>
     <row r="14">
@@ -9687,19 +9997,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5</v>
+        <v>0.545</v>
       </c>
       <c r="G14" t="n">
-        <v>-37.64</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="15">
@@ -9717,16 +10027,16 @@
         <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.714</v>
+        <v>0.526</v>
       </c>
       <c r="G15" t="n">
-        <v>252.33</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="16">
@@ -9741,19 +10051,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.548</v>
       </c>
       <c r="G16" t="n">
-        <v>-41.28</v>
+        <v>-189.92</v>
       </c>
     </row>
     <row r="17">
@@ -9768,19 +10078,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5</v>
+        <v>0.483</v>
       </c>
       <c r="G17" t="n">
-        <v>-39.13</v>
+        <v>-155.92</v>
       </c>
     </row>
     <row r="18">
@@ -9795,19 +10105,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.412</v>
+        <v>0.478</v>
       </c>
       <c r="G18" t="n">
-        <v>-173.18</v>
+        <v>-83.25</v>
       </c>
     </row>
     <row r="19">
@@ -9822,19 +10132,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="D19" t="n">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>0.542</v>
+        <v>0.523</v>
       </c>
       <c r="G19" t="n">
-        <v>-38.9</v>
+        <v>-416.51</v>
       </c>
     </row>
   </sheetData>
@@ -10393,13 +10703,21 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>-100</v>
+      </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -10439,13 +10757,21 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>51.28</v>
+      </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="n">
+        <v>25.64</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -10485,13 +10811,21 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>6-2</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>144.5</v>
+      </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="N12" t="n">
+        <v>72.25</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11429,13 +11763,19 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>6</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-100</v>
+      </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="N17" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -11477,13 +11817,19 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-100</v>
+      </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="N18" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -11525,13 +11871,19 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>5</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-100</v>
+      </c>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="N19" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -11573,13 +11925,19 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>3</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-100</v>
+      </c>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="N20" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -11621,13 +11979,19 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>8</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-100</v>
+      </c>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="N21" t="n">
+        <v>-50</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14891,13 +15255,19 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>1</v>
+      </c>
+      <c r="L61" t="n">
+        <v>57.14</v>
+      </c>
       <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+      <c r="N61" t="n">
+        <v>28.57</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -14939,13 +15309,19 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>2</v>
+      </c>
+      <c r="L62" t="n">
+        <v>-100</v>
+      </c>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+      <c r="N62" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -14987,13 +15363,19 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>4</v>
+      </c>
+      <c r="L63" t="n">
+        <v>-100</v>
+      </c>
       <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+      <c r="N63" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -15035,13 +15417,19 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>31.25</v>
+      </c>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+      <c r="N64" t="n">
+        <v>15.62</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -15083,13 +15471,19 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>100</v>
+      </c>
       <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+      <c r="N65" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -15131,13 +15525,19 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>-100</v>
+      </c>
       <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+      <c r="N66" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -15179,13 +15579,19 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>80</v>
+      </c>
       <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+      <c r="N67" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -15227,13 +15633,19 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>-100</v>
+      </c>
       <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+      <c r="N68" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -15275,13 +15687,19 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>4</v>
+      </c>
+      <c r="L69" t="n">
+        <v>-100</v>
+      </c>
       <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+      <c r="N69" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -15323,13 +15741,19 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>63.69</v>
+      </c>
       <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+      <c r="N70" t="n">
+        <v>31.85</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -15371,13 +15795,19 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>1</v>
+      </c>
+      <c r="L71" t="n">
+        <v>46.19</v>
+      </c>
       <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+      <c r="N71" t="n">
+        <v>23.09</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -15419,13 +15849,19 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>68.97</v>
+      </c>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+      <c r="N72" t="n">
+        <v>34.48</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -15467,13 +15903,19 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>-100</v>
+      </c>
       <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+      <c r="N73" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -15515,13 +15957,19 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
+        <v>110.5</v>
+      </c>
       <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+      <c r="N74" t="n">
+        <v>55.25</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -15563,13 +16011,19 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>1</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-100</v>
+      </c>
       <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+      <c r="N75" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -15611,13 +16065,17 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>DNP</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
       <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -15659,13 +16117,19 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>1</v>
+      </c>
+      <c r="L77" t="n">
+        <v>52.63</v>
+      </c>
       <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+      <c r="N77" t="n">
+        <v>26.32</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -15707,13 +16171,19 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
+        <v>-100</v>
+      </c>
       <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+      <c r="N78" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -15755,13 +16225,19 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>3</v>
+      </c>
+      <c r="L79" t="n">
+        <v>-100</v>
+      </c>
       <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+      <c r="N79" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -15803,13 +16279,19 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>62.11</v>
+      </c>
       <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+      <c r="N80" t="n">
+        <v>31.06</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -15851,13 +16333,19 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L81" t="n">
+        <v>-100</v>
+      </c>
       <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+      <c r="N81" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -15899,13 +16387,19 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
+        <v>71.43000000000001</v>
+      </c>
       <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+      <c r="N82" t="n">
+        <v>35.71</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -15947,13 +16441,19 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>3</v>
+      </c>
+      <c r="L83" t="n">
+        <v>-100</v>
+      </c>
       <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+      <c r="N83" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -15995,13 +16495,19 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="n">
+        <v>58.82</v>
+      </c>
       <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+      <c r="N84" t="n">
+        <v>29.41</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17293,13 +17799,19 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>13</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-100</v>
+      </c>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="N24" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -17341,13 +17853,19 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>13</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-100</v>
+      </c>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="N25" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -17389,13 +17907,19 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>15</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-100</v>
+      </c>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="N26" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -17437,13 +17961,19 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>14</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-100</v>
+      </c>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="N27" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -17485,13 +18015,19 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>15</v>
+      </c>
+      <c r="L28" t="n">
+        <v>49.38</v>
+      </c>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="N28" t="n">
+        <v>24.69</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -17533,13 +18069,19 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>21</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-100</v>
+      </c>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="N29" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -17581,13 +18123,19 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>16</v>
+      </c>
+      <c r="L30" t="n">
+        <v>83.33</v>
+      </c>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="N30" t="n">
+        <v>41.67</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -17629,13 +18177,19 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>16</v>
+      </c>
+      <c r="L31" t="n">
+        <v>100.5</v>
+      </c>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="N31" t="n">
+        <v>50.25</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -17677,13 +18231,19 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>18</v>
+      </c>
+      <c r="L32" t="n">
+        <v>82.3</v>
+      </c>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="N32" t="n">
+        <v>41.15</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -17725,13 +18285,19 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>13</v>
+      </c>
+      <c r="L33" t="n">
+        <v>-100</v>
+      </c>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="N33" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -17773,13 +18339,19 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>17</v>
+      </c>
+      <c r="L34" t="n">
+        <v>50.89</v>
+      </c>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="N34" t="n">
+        <v>25.45</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18823,13 +19395,21 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>away_1st=1 home_1st=1</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>100</v>
+      </c>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="N19" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -18869,13 +19449,21 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>away_1st=0 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>-100</v>
+      </c>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="N20" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -18915,13 +19503,21 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>away_1st=0 home_1st=1</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>110</v>
+      </c>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="N21" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -18961,13 +19557,21 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>away_1st=0 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>78.12</v>
+      </c>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="N22" t="n">
+        <v>39.06</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -19007,13 +19611,21 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>away_1st=0 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>91.73999999999999</v>
+      </c>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="N23" t="n">
+        <v>45.87</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -19053,13 +19665,21 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>away_1st=0 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>-100</v>
+      </c>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="N24" t="n">
+        <v>-50</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tracking/picks.xlsx
+++ b/tracking/picks.xlsx
@@ -497,12 +497,12 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>pnl_50</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>pnl_50</t>
+          <t>git_commits</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,6 @@
           <t>HOME</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
         <v>100</v>
       </c>
@@ -555,8 +554,7 @@
       <c r="L2" t="n">
         <v>-100</v>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="n">
+      <c r="M2" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -609,8 +607,7 @@
       <c r="L3" t="n">
         <v>-100</v>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="n">
+      <c r="M3" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -663,8 +660,7 @@
       <c r="L4" t="n">
         <v>62.7</v>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="n">
+      <c r="M4" t="n">
         <v>31.35</v>
       </c>
     </row>
@@ -717,8 +713,7 @@
       <c r="L5" t="n">
         <v>95.23999999999999</v>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="n">
+      <c r="M5" t="n">
         <v>47.62</v>
       </c>
     </row>
@@ -771,8 +766,7 @@
       <c r="L6" t="n">
         <v>-100</v>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="n">
+      <c r="M6" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -825,8 +819,7 @@
       <c r="L7" t="n">
         <v>60.61</v>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="n">
+      <c r="M7" t="n">
         <v>30.3</v>
       </c>
     </row>
@@ -879,8 +872,7 @@
       <c r="L8" t="n">
         <v>86.95999999999999</v>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="n">
+      <c r="M8" t="n">
         <v>43.48</v>
       </c>
     </row>
@@ -933,8 +925,7 @@
       <c r="L9" t="n">
         <v>-100</v>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="n">
+      <c r="M9" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -987,8 +978,7 @@
       <c r="L10" t="n">
         <v>100</v>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="n">
+      <c r="M10" t="n">
         <v>50</v>
       </c>
     </row>
@@ -1018,7 +1008,6 @@
           <t>NRFI</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
         <v>-157.5</v>
       </c>
@@ -1041,8 +1030,7 @@
       <c r="L11" t="n">
         <v>63.49</v>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="n">
+      <c r="M11" t="n">
         <v>31.75</v>
       </c>
     </row>
@@ -1089,10 +1077,6 @@
           <t>ODDS_ERR</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1143,8 +1127,7 @@
       <c r="L13" t="n">
         <v>62.11</v>
       </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="n">
+      <c r="M13" t="n">
         <v>31.06</v>
       </c>
     </row>
@@ -1191,10 +1174,6 @@
           <t>ODDS_ERR</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1222,7 +1201,6 @@
           <t>YRFI</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
         <v>120</v>
       </c>
@@ -1245,8 +1223,7 @@
       <c r="L15" t="n">
         <v>-100</v>
       </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="n">
+      <c r="M15" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -1276,7 +1253,6 @@
           <t>HOME</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
         <v>-141.5</v>
       </c>
@@ -1299,8 +1275,7 @@
       <c r="L16" t="n">
         <v>70.67</v>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="n">
+      <c r="M16" t="n">
         <v>35.34</v>
       </c>
     </row>
@@ -1330,7 +1305,6 @@
           <t>HOME</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
         <v>-121</v>
       </c>
@@ -1353,8 +1327,7 @@
       <c r="L17" t="n">
         <v>82.64</v>
       </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="n">
+      <c r="M17" t="n">
         <v>41.32</v>
       </c>
     </row>
@@ -1407,8 +1380,7 @@
       <c r="L18" t="n">
         <v>95.23999999999999</v>
       </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="n">
+      <c r="M18" t="n">
         <v>47.62</v>
       </c>
     </row>
@@ -1461,8 +1433,7 @@
       <c r="L19" t="n">
         <v>82.64</v>
       </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="n">
+      <c r="M19" t="n">
         <v>41.32</v>
       </c>
     </row>
@@ -1515,8 +1486,7 @@
       <c r="L20" t="n">
         <v>94.34</v>
       </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="n">
+      <c r="M20" t="n">
         <v>47.17</v>
       </c>
     </row>
@@ -1569,8 +1539,7 @@
       <c r="L21" t="n">
         <v>86.95999999999999</v>
       </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="n">
+      <c r="M21" t="n">
         <v>43.48</v>
       </c>
     </row>
@@ -1617,10 +1586,6 @@
           <t>ODDS_ERR</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1671,8 +1636,7 @@
       <c r="L23" t="n">
         <v>-100</v>
       </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="n">
+      <c r="M23" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -1725,8 +1689,7 @@
       <c r="L24" t="n">
         <v>-100</v>
       </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="n">
+      <c r="M24" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -1779,8 +1742,7 @@
       <c r="L25" t="n">
         <v>70.92</v>
       </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="n">
+      <c r="M25" t="n">
         <v>35.46</v>
       </c>
     </row>
@@ -1833,8 +1795,7 @@
       <c r="L26" t="n">
         <v>-100</v>
       </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="n">
+      <c r="M26" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -1887,8 +1848,7 @@
       <c r="L27" t="n">
         <v>-100</v>
       </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="n">
+      <c r="M27" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -1941,8 +1901,7 @@
       <c r="L28" t="n">
         <v>65.15000000000001</v>
       </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="n">
+      <c r="M28" t="n">
         <v>32.57</v>
       </c>
     </row>
@@ -1995,8 +1954,7 @@
       <c r="L29" t="n">
         <v>-100</v>
       </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="n">
+      <c r="M29" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -2049,8 +2007,7 @@
       <c r="L30" t="n">
         <v>66.67</v>
       </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="n">
+      <c r="M30" t="n">
         <v>33.33</v>
       </c>
     </row>
@@ -2103,8 +2060,7 @@
       <c r="L31" t="n">
         <v>57.14</v>
       </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="n">
+      <c r="M31" t="n">
         <v>28.57</v>
       </c>
     </row>
@@ -2157,8 +2113,7 @@
       <c r="L32" t="n">
         <v>73.8</v>
       </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="n">
+      <c r="M32" t="n">
         <v>36.9</v>
       </c>
     </row>
@@ -2211,8 +2166,7 @@
       <c r="L33" t="n">
         <v>-100</v>
       </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="n">
+      <c r="M33" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -2265,8 +2219,7 @@
       <c r="L34" t="n">
         <v>-100</v>
       </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="n">
+      <c r="M34" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -2319,8 +2272,7 @@
       <c r="L35" t="n">
         <v>-100</v>
       </c>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="n">
+      <c r="M35" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -2373,8 +2325,7 @@
       <c r="L36" t="n">
         <v>-100</v>
       </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="n">
+      <c r="M36" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -2427,8 +2378,7 @@
       <c r="L37" t="n">
         <v>-100</v>
       </c>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="n">
+      <c r="M37" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -2481,8 +2431,7 @@
       <c r="L38" t="n">
         <v>54.05</v>
       </c>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="n">
+      <c r="M38" t="n">
         <v>27.03</v>
       </c>
     </row>
@@ -2535,8 +2484,7 @@
       <c r="L39" t="n">
         <v>80</v>
       </c>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="n">
+      <c r="M39" t="n">
         <v>40</v>
       </c>
     </row>
@@ -2589,8 +2537,7 @@
       <c r="L40" t="n">
         <v>-100</v>
       </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="n">
+      <c r="M40" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -2643,8 +2590,7 @@
       <c r="L41" t="n">
         <v>58.82</v>
       </c>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="n">
+      <c r="M41" t="n">
         <v>29.41</v>
       </c>
     </row>
@@ -2697,8 +2643,7 @@
       <c r="L42" t="n">
         <v>57.14</v>
       </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="n">
+      <c r="M42" t="n">
         <v>28.57</v>
       </c>
     </row>
@@ -2751,8 +2696,7 @@
       <c r="L43" t="n">
         <v>145</v>
       </c>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="n">
+      <c r="M43" t="n">
         <v>72.5</v>
       </c>
     </row>
@@ -2805,8 +2749,7 @@
       <c r="L44" t="n">
         <v>-100</v>
       </c>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="n">
+      <c r="M44" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -2859,8 +2802,7 @@
       <c r="L45" t="n">
         <v>90.91</v>
       </c>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="n">
+      <c r="M45" t="n">
         <v>45.45</v>
       </c>
     </row>
@@ -2913,8 +2855,7 @@
       <c r="L46" t="n">
         <v>-100</v>
       </c>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="n">
+      <c r="M46" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -2961,10 +2902,6 @@
           <t>ODDS_ERR</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3015,8 +2952,7 @@
       <c r="L48" t="n">
         <v>59.7</v>
       </c>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="n">
+      <c r="M48" t="n">
         <v>29.85</v>
       </c>
     </row>
@@ -3069,8 +3005,7 @@
       <c r="L49" t="n">
         <v>-100</v>
       </c>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="n">
+      <c r="M49" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -3123,8 +3058,7 @@
       <c r="L50" t="n">
         <v>-100</v>
       </c>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="n">
+      <c r="M50" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -3154,7 +3088,6 @@
           <t>YRFI</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
         <v>120</v>
       </c>
@@ -3177,8 +3110,7 @@
       <c r="L51" t="n">
         <v>120</v>
       </c>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="n">
+      <c r="M51" t="n">
         <v>60</v>
       </c>
     </row>
@@ -3208,7 +3140,6 @@
           <t>YRFI</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
         <v>-102</v>
       </c>
@@ -3231,8 +3162,7 @@
       <c r="L52" t="n">
         <v>98.04000000000001</v>
       </c>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="n">
+      <c r="M52" t="n">
         <v>49.02</v>
       </c>
     </row>
@@ -3262,7 +3192,6 @@
           <t>YRFI</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
         <v>-112</v>
       </c>
@@ -3285,8 +3214,7 @@
       <c r="L53" t="n">
         <v>-100</v>
       </c>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="n">
+      <c r="M53" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -3316,7 +3244,6 @@
           <t>YRFI</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
         <v>106</v>
       </c>
@@ -3339,8 +3266,7 @@
       <c r="L54" t="n">
         <v>-100</v>
       </c>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="n">
+      <c r="M54" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -3370,7 +3296,6 @@
           <t>HOME</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
       <c r="G55" t="n">
         <v>-156.5</v>
       </c>
@@ -3393,8 +3318,7 @@
       <c r="L55" t="n">
         <v>63.9</v>
       </c>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="n">
+      <c r="M55" t="n">
         <v>31.95</v>
       </c>
     </row>
@@ -3424,7 +3348,6 @@
           <t>HOME</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
       <c r="G56" t="n">
         <v>135</v>
       </c>
@@ -3447,8 +3370,7 @@
       <c r="L56" t="n">
         <v>-100</v>
       </c>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="n">
+      <c r="M56" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -3478,7 +3400,6 @@
           <t>HOME</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
       <c r="G57" t="n">
         <v>107</v>
       </c>
@@ -3501,8 +3422,7 @@
       <c r="L57" t="n">
         <v>-100</v>
       </c>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="n">
+      <c r="M57" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -3555,8 +3475,7 @@
       <c r="L58" t="n">
         <v>-100</v>
       </c>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="n">
+      <c r="M58" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -3609,8 +3528,7 @@
       <c r="L59" t="n">
         <v>90.91</v>
       </c>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="n">
+      <c r="M59" t="n">
         <v>45.45</v>
       </c>
     </row>
@@ -3663,8 +3581,7 @@
       <c r="L60" t="n">
         <v>0</v>
       </c>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="n">
+      <c r="M60" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3717,8 +3634,7 @@
       <c r="L61" t="n">
         <v>-100</v>
       </c>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="n">
+      <c r="M61" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -3771,8 +3687,7 @@
       <c r="L62" t="n">
         <v>95.23999999999999</v>
       </c>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="n">
+      <c r="M62" t="n">
         <v>47.62</v>
       </c>
     </row>
@@ -3819,10 +3734,6 @@
           <t>ODDS_ERR</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3867,10 +3778,6 @@
           <t>ODDS_ERR</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3921,8 +3828,7 @@
       <c r="L65" t="n">
         <v>120.5</v>
       </c>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="n">
+      <c r="M65" t="n">
         <v>60.25</v>
       </c>
     </row>
@@ -3975,8 +3881,7 @@
       <c r="L66" t="n">
         <v>54.05</v>
       </c>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="n">
+      <c r="M66" t="n">
         <v>27.03</v>
       </c>
     </row>
@@ -4029,8 +3934,7 @@
       <c r="L67" t="n">
         <v>106</v>
       </c>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="n">
+      <c r="M67" t="n">
         <v>53</v>
       </c>
     </row>
@@ -4083,8 +3987,7 @@
       <c r="L68" t="n">
         <v>-100</v>
       </c>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="n">
+      <c r="M68" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -4137,8 +4040,7 @@
       <c r="L69" t="n">
         <v>126.5</v>
       </c>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="n">
+      <c r="M69" t="n">
         <v>63.25</v>
       </c>
     </row>
@@ -4191,8 +4093,7 @@
       <c r="L70" t="n">
         <v>-100</v>
       </c>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="n">
+      <c r="M70" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -4245,8 +4146,7 @@
       <c r="L71" t="n">
         <v>60.79</v>
       </c>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="n">
+      <c r="M71" t="n">
         <v>30.4</v>
       </c>
     </row>
@@ -4299,8 +4199,7 @@
       <c r="L72" t="n">
         <v>54.95</v>
       </c>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="n">
+      <c r="M72" t="n">
         <v>27.47</v>
       </c>
     </row>
@@ -4353,8 +4252,7 @@
       <c r="L73" t="n">
         <v>-100</v>
       </c>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="n">
+      <c r="M73" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -4407,8 +4305,7 @@
       <c r="L74" t="n">
         <v>-100</v>
       </c>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="n">
+      <c r="M74" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -4461,8 +4358,7 @@
       <c r="L75" t="n">
         <v>125</v>
       </c>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="n">
+      <c r="M75" t="n">
         <v>62.5</v>
       </c>
     </row>
@@ -4515,8 +4411,7 @@
       <c r="L76" t="n">
         <v>80</v>
       </c>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="n">
+      <c r="M76" t="n">
         <v>40</v>
       </c>
     </row>
@@ -4569,8 +4464,7 @@
       <c r="L77" t="n">
         <v>-100</v>
       </c>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="n">
+      <c r="M77" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -4600,7 +4494,6 @@
           <t>YRFI</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
         <v>102</v>
       </c>
@@ -4623,8 +4516,7 @@
       <c r="L78" t="n">
         <v>-100</v>
       </c>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="n">
+      <c r="M78" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -4654,7 +4546,6 @@
           <t>NRFI</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
         <v>-129</v>
       </c>
@@ -4677,8 +4568,7 @@
       <c r="L79" t="n">
         <v>-100</v>
       </c>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="n">
+      <c r="M79" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -4708,7 +4598,6 @@
           <t>NRFI</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
         <v>-155</v>
       </c>
@@ -4731,8 +4620,7 @@
       <c r="L80" t="n">
         <v>64.52</v>
       </c>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="n">
+      <c r="M80" t="n">
         <v>32.26</v>
       </c>
     </row>
@@ -4762,7 +4650,6 @@
           <t>YRFI</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
         <v>118</v>
       </c>
@@ -4785,8 +4672,7 @@
       <c r="L81" t="n">
         <v>118</v>
       </c>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="n">
+      <c r="M81" t="n">
         <v>59</v>
       </c>
     </row>
@@ -4816,7 +4702,6 @@
           <t>YRFI</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
         <v>-106</v>
       </c>
@@ -4839,8 +4724,7 @@
       <c r="L82" t="n">
         <v>94.34</v>
       </c>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="n">
+      <c r="M82" t="n">
         <v>47.17</v>
       </c>
     </row>
@@ -4870,7 +4754,6 @@
           <t>HOME</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
       <c r="G83" t="n">
         <v>107.5</v>
       </c>
@@ -4893,8 +4776,7 @@
       <c r="L83" t="n">
         <v>107.5</v>
       </c>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="n">
+      <c r="M83" t="n">
         <v>53.75</v>
       </c>
     </row>
@@ -4947,8 +4829,7 @@
       <c r="L84" t="n">
         <v>90.91</v>
       </c>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="n">
+      <c r="M84" t="n">
         <v>45.45</v>
       </c>
     </row>
@@ -5001,8 +4882,7 @@
       <c r="L85" t="n">
         <v>95.23999999999999</v>
       </c>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="n">
+      <c r="M85" t="n">
         <v>47.62</v>
       </c>
     </row>
@@ -5055,8 +4935,7 @@
       <c r="L86" t="n">
         <v>-100</v>
       </c>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="n">
+      <c r="M86" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -5109,8 +4988,7 @@
       <c r="L87" t="n">
         <v>-100</v>
       </c>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="n">
+      <c r="M87" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -5163,8 +5041,7 @@
       <c r="L88" t="n">
         <v>-100</v>
       </c>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="n">
+      <c r="M88" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -5217,8 +5094,7 @@
       <c r="L89" t="n">
         <v>68.97</v>
       </c>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="n">
+      <c r="M89" t="n">
         <v>34.48</v>
       </c>
     </row>
@@ -5271,8 +5147,7 @@
       <c r="L90" t="n">
         <v>-100</v>
       </c>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="n">
+      <c r="M90" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -5325,8 +5200,7 @@
       <c r="L91" t="n">
         <v>54.5</v>
       </c>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="n">
+      <c r="M91" t="n">
         <v>27.25</v>
       </c>
     </row>
@@ -5356,7 +5230,6 @@
           <t>YRFI</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr"/>
       <c r="G92" t="n">
         <v>100</v>
       </c>
@@ -5379,8 +5252,7 @@
       <c r="L92" t="n">
         <v>-100</v>
       </c>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="n">
+      <c r="M92" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -5433,8 +5305,7 @@
       <c r="L93" t="n">
         <v>90.91</v>
       </c>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="n">
+      <c r="M93" t="n">
         <v>45.45</v>
       </c>
     </row>
@@ -5481,10 +5352,6 @@
           <t>ODDS_ERR</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5535,8 +5402,7 @@
       <c r="L95" t="n">
         <v>-100</v>
       </c>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="n">
+      <c r="M95" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -5566,7 +5432,6 @@
           <t>NRFI</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr"/>
       <c r="G96" t="n">
         <v>-162</v>
       </c>
@@ -5589,8 +5454,7 @@
       <c r="L96" t="n">
         <v>-100</v>
       </c>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="n">
+      <c r="M96" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -5620,7 +5484,6 @@
           <t>AWAY</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr"/>
       <c r="G97" t="n">
         <v>217.5</v>
       </c>
@@ -5643,8 +5506,7 @@
       <c r="L97" t="n">
         <v>-100</v>
       </c>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="n">
+      <c r="M97" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -5697,8 +5559,7 @@
       <c r="L98" t="n">
         <v>82.3</v>
       </c>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="n">
+      <c r="M98" t="n">
         <v>41.15</v>
       </c>
     </row>
@@ -5751,8 +5612,7 @@
       <c r="L99" t="n">
         <v>-100</v>
       </c>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="n">
+      <c r="M99" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -5805,8 +5665,7 @@
       <c r="L100" t="n">
         <v>-100</v>
       </c>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="n">
+      <c r="M100" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -5853,10 +5712,6 @@
           <t>ODDS_ERR</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5907,8 +5762,7 @@
       <c r="L102" t="n">
         <v>-100</v>
       </c>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="n">
+      <c r="M102" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -5955,10 +5809,6 @@
           <t>ODDS_ERR</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6003,10 +5853,6 @@
           <t>ODDS_ERR</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6057,8 +5903,7 @@
       <c r="L105" t="n">
         <v>92.59</v>
       </c>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="n">
+      <c r="M105" t="n">
         <v>46.3</v>
       </c>
     </row>
@@ -6105,12 +5950,10 @@
           <t>DNP</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
       <c r="L106" t="n">
         <v>0</v>
       </c>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="n">
+      <c r="M106" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6163,8 +6006,7 @@
       <c r="L107" t="n">
         <v>80.65000000000001</v>
       </c>
-      <c r="M107" t="inlineStr"/>
-      <c r="N107" t="n">
+      <c r="M107" t="n">
         <v>40.32</v>
       </c>
     </row>
@@ -6217,8 +6059,7 @@
       <c r="L108" t="n">
         <v>100</v>
       </c>
-      <c r="M108" t="inlineStr"/>
-      <c r="N108" t="n">
+      <c r="M108" t="n">
         <v>50</v>
       </c>
     </row>
@@ -6271,8 +6112,7 @@
       <c r="L109" t="n">
         <v>115</v>
       </c>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="n">
+      <c r="M109" t="n">
         <v>57.5</v>
       </c>
     </row>
@@ -6325,8 +6165,7 @@
       <c r="L110" t="n">
         <v>-100</v>
       </c>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="n">
+      <c r="M110" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -6379,8 +6218,7 @@
       <c r="L111" t="n">
         <v>84.75</v>
       </c>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="n">
+      <c r="M111" t="n">
         <v>42.37</v>
       </c>
     </row>
@@ -6433,8 +6271,7 @@
       <c r="L112" t="n">
         <v>72.45999999999999</v>
       </c>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="n">
+      <c r="M112" t="n">
         <v>36.23</v>
       </c>
     </row>
@@ -6481,10 +6318,6 @@
           <t>ODDS_ERR</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6535,8 +6368,7 @@
       <c r="L114" t="n">
         <v>109.5</v>
       </c>
-      <c r="M114" t="inlineStr"/>
-      <c r="N114" t="n">
+      <c r="M114" t="n">
         <v>54.75</v>
       </c>
     </row>
@@ -6583,10 +6415,6 @@
           <t>ODDS_ERR</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6614,7 +6442,6 @@
           <t>NRFI</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr"/>
       <c r="G116" t="n">
         <v>-162</v>
       </c>
@@ -6637,8 +6464,7 @@
       <c r="L116" t="n">
         <v>-100</v>
       </c>
-      <c r="M116" t="inlineStr"/>
-      <c r="N116" t="n">
+      <c r="M116" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -6668,7 +6494,6 @@
           <t>YRFI</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr"/>
       <c r="G117" t="n">
         <v>-119</v>
       </c>
@@ -6691,8 +6516,7 @@
       <c r="L117" t="n">
         <v>-100</v>
       </c>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="n">
+      <c r="M117" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -6722,7 +6546,6 @@
           <t>NRFI</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr"/>
       <c r="G118" t="n">
         <v>-155</v>
       </c>
@@ -6745,8 +6568,7 @@
       <c r="L118" t="n">
         <v>-100</v>
       </c>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="n">
+      <c r="M118" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -6799,8 +6621,7 @@
       <c r="L119" t="n">
         <v>38.46</v>
       </c>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="n">
+      <c r="M119" t="n">
         <v>19.23</v>
       </c>
     </row>
@@ -6853,8 +6674,7 @@
       <c r="L120" t="n">
         <v>47.62</v>
       </c>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="n">
+      <c r="M120" t="n">
         <v>23.81</v>
       </c>
     </row>
@@ -6907,8 +6727,7 @@
       <c r="L121" t="n">
         <v>-100</v>
       </c>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="n">
+      <c r="M121" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -6938,7 +6757,6 @@
           <t>NRFI</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr"/>
       <c r="G122" t="n">
         <v>-105</v>
       </c>
@@ -6961,8 +6779,7 @@
       <c r="L122" t="n">
         <v>95.23999999999999</v>
       </c>
-      <c r="M122" t="inlineStr"/>
-      <c r="N122" t="n">
+      <c r="M122" t="n">
         <v>47.62</v>
       </c>
     </row>
@@ -6992,7 +6809,6 @@
           <t>HOME</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr"/>
       <c r="G123" t="n">
         <v>112.5</v>
       </c>
@@ -7015,8 +6831,7 @@
       <c r="L123" t="n">
         <v>-100</v>
       </c>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="n">
+      <c r="M123" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -7046,7 +6861,6 @@
           <t>HOME</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr"/>
       <c r="G124" t="n">
         <v>-195</v>
       </c>
@@ -7069,8 +6883,7 @@
       <c r="L124" t="n">
         <v>51.28</v>
       </c>
-      <c r="M124" t="inlineStr"/>
-      <c r="N124" t="n">
+      <c r="M124" t="n">
         <v>25.64</v>
       </c>
     </row>
@@ -7123,8 +6936,7 @@
       <c r="L125" t="n">
         <v>-100</v>
       </c>
-      <c r="M125" t="inlineStr"/>
-      <c r="N125" t="n">
+      <c r="M125" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -7177,8 +6989,7 @@
       <c r="L126" t="n">
         <v>-100</v>
       </c>
-      <c r="M126" t="inlineStr"/>
-      <c r="N126" t="n">
+      <c r="M126" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -7231,8 +7042,7 @@
       <c r="L127" t="n">
         <v>-100</v>
       </c>
-      <c r="M127" t="inlineStr"/>
-      <c r="N127" t="n">
+      <c r="M127" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -7285,8 +7095,7 @@
       <c r="L128" t="n">
         <v>-100</v>
       </c>
-      <c r="M128" t="inlineStr"/>
-      <c r="N128" t="n">
+      <c r="M128" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -7339,8 +7148,7 @@
       <c r="L129" t="n">
         <v>-100</v>
       </c>
-      <c r="M129" t="inlineStr"/>
-      <c r="N129" t="n">
+      <c r="M129" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -7393,8 +7201,7 @@
       <c r="L130" t="n">
         <v>62.11</v>
       </c>
-      <c r="M130" t="inlineStr"/>
-      <c r="N130" t="n">
+      <c r="M130" t="n">
         <v>31.06</v>
       </c>
     </row>
@@ -7447,8 +7254,7 @@
       <c r="L131" t="n">
         <v>-100</v>
       </c>
-      <c r="M131" t="inlineStr"/>
-      <c r="N131" t="n">
+      <c r="M131" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -7501,8 +7307,7 @@
       <c r="L132" t="n">
         <v>-100</v>
       </c>
-      <c r="M132" t="inlineStr"/>
-      <c r="N132" t="n">
+      <c r="M132" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -7555,8 +7360,7 @@
       <c r="L133" t="n">
         <v>52.63</v>
       </c>
-      <c r="M133" t="inlineStr"/>
-      <c r="N133" t="n">
+      <c r="M133" t="n">
         <v>26.32</v>
       </c>
     </row>
@@ -7603,12 +7407,10 @@
           <t>DNP</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
       <c r="L134" t="n">
         <v>0</v>
       </c>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="n">
+      <c r="M134" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7661,8 +7463,7 @@
       <c r="L135" t="n">
         <v>68.97</v>
       </c>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="n">
+      <c r="M135" t="n">
         <v>34.48</v>
       </c>
     </row>
@@ -7715,8 +7516,7 @@
       <c r="L136" t="n">
         <v>-100</v>
       </c>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="n">
+      <c r="M136" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -7769,8 +7569,7 @@
       <c r="L137" t="n">
         <v>110.5</v>
       </c>
-      <c r="M137" t="inlineStr"/>
-      <c r="N137" t="n">
+      <c r="M137" t="n">
         <v>55.25</v>
       </c>
     </row>
@@ -7823,8 +7622,7 @@
       <c r="L138" t="n">
         <v>-100</v>
       </c>
-      <c r="M138" t="inlineStr"/>
-      <c r="N138" t="n">
+      <c r="M138" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -7877,8 +7675,7 @@
       <c r="L139" t="n">
         <v>-100</v>
       </c>
-      <c r="M139" t="inlineStr"/>
-      <c r="N139" t="n">
+      <c r="M139" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -7931,8 +7728,7 @@
       <c r="L140" t="n">
         <v>46.19</v>
       </c>
-      <c r="M140" t="inlineStr"/>
-      <c r="N140" t="n">
+      <c r="M140" t="n">
         <v>23.09</v>
       </c>
     </row>
@@ -7985,8 +7781,7 @@
       <c r="L141" t="n">
         <v>-100</v>
       </c>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="n">
+      <c r="M141" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -8039,8 +7834,7 @@
       <c r="L142" t="n">
         <v>63.69</v>
       </c>
-      <c r="M142" t="inlineStr"/>
-      <c r="N142" t="n">
+      <c r="M142" t="n">
         <v>31.85</v>
       </c>
     </row>
@@ -8093,8 +7887,7 @@
       <c r="L143" t="n">
         <v>-100</v>
       </c>
-      <c r="M143" t="inlineStr"/>
-      <c r="N143" t="n">
+      <c r="M143" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -8147,8 +7940,7 @@
       <c r="L144" t="n">
         <v>49.38</v>
       </c>
-      <c r="M144" t="inlineStr"/>
-      <c r="N144" t="n">
+      <c r="M144" t="n">
         <v>24.69</v>
       </c>
     </row>
@@ -8201,8 +7993,7 @@
       <c r="L145" t="n">
         <v>100.5</v>
       </c>
-      <c r="M145" t="inlineStr"/>
-      <c r="N145" t="n">
+      <c r="M145" t="n">
         <v>50.25</v>
       </c>
     </row>
@@ -8255,8 +8046,7 @@
       <c r="L146" t="n">
         <v>83.33</v>
       </c>
-      <c r="M146" t="inlineStr"/>
-      <c r="N146" t="n">
+      <c r="M146" t="n">
         <v>41.67</v>
       </c>
     </row>
@@ -8309,8 +8099,7 @@
       <c r="L147" t="n">
         <v>-100</v>
       </c>
-      <c r="M147" t="inlineStr"/>
-      <c r="N147" t="n">
+      <c r="M147" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -8363,8 +8152,7 @@
       <c r="L148" t="n">
         <v>-100</v>
       </c>
-      <c r="M148" t="inlineStr"/>
-      <c r="N148" t="n">
+      <c r="M148" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -8394,7 +8182,6 @@
           <t>YRFI</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr"/>
       <c r="G149" t="n">
         <v>-102</v>
       </c>
@@ -8417,8 +8204,7 @@
       <c r="L149" t="n">
         <v>-100</v>
       </c>
-      <c r="M149" t="inlineStr"/>
-      <c r="N149" t="n">
+      <c r="M149" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -8448,7 +8234,6 @@
           <t>YRFI</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr"/>
       <c r="G150" t="n">
         <v>110</v>
       </c>
@@ -8471,8 +8256,7 @@
       <c r="L150" t="n">
         <v>110</v>
       </c>
-      <c r="M150" t="inlineStr"/>
-      <c r="N150" t="n">
+      <c r="M150" t="n">
         <v>55</v>
       </c>
     </row>
@@ -8502,7 +8286,6 @@
           <t>NRFI</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr"/>
       <c r="G151" t="n">
         <v>-128</v>
       </c>
@@ -8525,8 +8308,7 @@
       <c r="L151" t="n">
         <v>78.12</v>
       </c>
-      <c r="M151" t="inlineStr"/>
-      <c r="N151" t="n">
+      <c r="M151" t="n">
         <v>39.06</v>
       </c>
     </row>
@@ -8556,7 +8338,6 @@
           <t>NRFI</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr"/>
       <c r="G152" t="n">
         <v>-109</v>
       </c>
@@ -8579,8 +8360,7 @@
       <c r="L152" t="n">
         <v>91.73999999999999</v>
       </c>
-      <c r="M152" t="inlineStr"/>
-      <c r="N152" t="n">
+      <c r="M152" t="n">
         <v>45.87</v>
       </c>
     </row>
@@ -8610,7 +8390,6 @@
           <t>AWAY</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr"/>
       <c r="G153" t="n">
         <v>144.5</v>
       </c>
@@ -8633,8 +8412,7 @@
       <c r="L153" t="n">
         <v>144.5</v>
       </c>
-      <c r="M153" t="inlineStr"/>
-      <c r="N153" t="n">
+      <c r="M153" t="n">
         <v>72.25</v>
       </c>
     </row>
@@ -8687,8 +8465,7 @@
       <c r="L154" t="n">
         <v>-100</v>
       </c>
-      <c r="M154" t="inlineStr"/>
-      <c r="N154" t="n">
+      <c r="M154" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -8741,8 +8518,7 @@
       <c r="L155" t="n">
         <v>-100</v>
       </c>
-      <c r="M155" t="inlineStr"/>
-      <c r="N155" t="n">
+      <c r="M155" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -8795,8 +8571,7 @@
       <c r="L156" t="n">
         <v>80</v>
       </c>
-      <c r="M156" t="inlineStr"/>
-      <c r="N156" t="n">
+      <c r="M156" t="n">
         <v>40</v>
       </c>
     </row>
@@ -8849,8 +8624,7 @@
       <c r="L157" t="n">
         <v>-100</v>
       </c>
-      <c r="M157" t="inlineStr"/>
-      <c r="N157" t="n">
+      <c r="M157" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -8903,8 +8677,7 @@
       <c r="L158" t="n">
         <v>100</v>
       </c>
-      <c r="M158" t="inlineStr"/>
-      <c r="N158" t="n">
+      <c r="M158" t="n">
         <v>50</v>
       </c>
     </row>
@@ -8957,8 +8730,7 @@
       <c r="L159" t="n">
         <v>31.25</v>
       </c>
-      <c r="M159" t="inlineStr"/>
-      <c r="N159" t="n">
+      <c r="M159" t="n">
         <v>15.62</v>
       </c>
     </row>
@@ -9011,8 +8783,7 @@
       <c r="L160" t="n">
         <v>-100</v>
       </c>
-      <c r="M160" t="inlineStr"/>
-      <c r="N160" t="n">
+      <c r="M160" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -9065,8 +8836,7 @@
       <c r="L161" t="n">
         <v>57.14</v>
       </c>
-      <c r="M161" t="inlineStr"/>
-      <c r="N161" t="n">
+      <c r="M161" t="n">
         <v>28.57</v>
       </c>
     </row>
@@ -9119,8 +8889,7 @@
       <c r="L162" t="n">
         <v>71.43000000000001</v>
       </c>
-      <c r="M162" t="inlineStr"/>
-      <c r="N162" t="n">
+      <c r="M162" t="n">
         <v>35.71</v>
       </c>
     </row>
@@ -9173,8 +8942,7 @@
       <c r="L163" t="n">
         <v>58.82</v>
       </c>
-      <c r="M163" t="inlineStr"/>
-      <c r="N163" t="n">
+      <c r="M163" t="n">
         <v>29.41</v>
       </c>
     </row>
@@ -9227,8 +8995,7 @@
       <c r="L164" t="n">
         <v>-100</v>
       </c>
-      <c r="M164" t="inlineStr"/>
-      <c r="N164" t="n">
+      <c r="M164" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -9281,8 +9048,7 @@
       <c r="L165" t="n">
         <v>-100</v>
       </c>
-      <c r="M165" t="inlineStr"/>
-      <c r="N165" t="n">
+      <c r="M165" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -9335,8 +9101,7 @@
       <c r="L166" t="n">
         <v>-100</v>
       </c>
-      <c r="M166" t="inlineStr"/>
-      <c r="N166" t="n">
+      <c r="M166" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -9389,8 +9154,7 @@
       <c r="L167" t="n">
         <v>-100</v>
       </c>
-      <c r="M167" t="inlineStr"/>
-      <c r="N167" t="n">
+      <c r="M167" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -9443,8 +9207,7 @@
       <c r="L168" t="n">
         <v>82.3</v>
       </c>
-      <c r="M168" t="inlineStr"/>
-      <c r="N168" t="n">
+      <c r="M168" t="n">
         <v>41.15</v>
       </c>
     </row>
@@ -9497,8 +9260,7 @@
       <c r="L169" t="n">
         <v>50.89</v>
       </c>
-      <c r="M169" t="inlineStr"/>
-      <c r="N169" t="n">
+      <c r="M169" t="n">
         <v>25.45</v>
       </c>
     </row>
@@ -9528,7 +9290,6 @@
           <t>YRFI</t>
         </is>
       </c>
-      <c r="F170" t="inlineStr"/>
       <c r="G170" t="n">
         <v>-100</v>
       </c>
@@ -9551,8 +9312,7 @@
       <c r="L170" t="n">
         <v>100</v>
       </c>
-      <c r="M170" t="inlineStr"/>
-      <c r="N170" t="n">
+      <c r="M170" t="n">
         <v>50</v>
       </c>
     </row>
@@ -9582,7 +9342,6 @@
           <t>YRFI</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr"/>
       <c r="G171" t="n">
         <v>-102</v>
       </c>
@@ -9605,8 +9364,7 @@
       <c r="L171" t="n">
         <v>-100</v>
       </c>
-      <c r="M171" t="inlineStr"/>
-      <c r="N171" t="n">
+      <c r="M171" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -10224,12 +9982,12 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>pnl_50</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>pnl_50</t>
+          <t>git_commits</t>
         </is>
       </c>
     </row>
@@ -10259,7 +10017,6 @@
           <t>HOME</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
         <v>100</v>
       </c>
@@ -10282,8 +10039,7 @@
       <c r="L2" t="n">
         <v>-100</v>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="n">
+      <c r="M2" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -10313,7 +10069,6 @@
           <t>HOME</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
         <v>-141.5</v>
       </c>
@@ -10336,8 +10091,7 @@
       <c r="L3" t="n">
         <v>70.67</v>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="n">
+      <c r="M3" t="n">
         <v>35.34</v>
       </c>
     </row>
@@ -10367,7 +10121,6 @@
           <t>HOME</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
         <v>-121</v>
       </c>
@@ -10390,8 +10143,7 @@
       <c r="L4" t="n">
         <v>82.64</v>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="n">
+      <c r="M4" t="n">
         <v>41.32</v>
       </c>
     </row>
@@ -10421,7 +10173,6 @@
           <t>HOME</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
         <v>-156.5</v>
       </c>
@@ -10444,8 +10195,7 @@
       <c r="L5" t="n">
         <v>63.9</v>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="n">
+      <c r="M5" t="n">
         <v>31.95</v>
       </c>
     </row>
@@ -10475,7 +10225,6 @@
           <t>HOME</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
         <v>135</v>
       </c>
@@ -10498,8 +10247,7 @@
       <c r="L6" t="n">
         <v>-100</v>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="n">
+      <c r="M6" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -10529,7 +10277,6 @@
           <t>HOME</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
         <v>107</v>
       </c>
@@ -10552,8 +10299,7 @@
       <c r="L7" t="n">
         <v>-100</v>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="n">
+      <c r="M7" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -10583,7 +10329,6 @@
           <t>HOME</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
         <v>107.5</v>
       </c>
@@ -10606,8 +10351,7 @@
       <c r="L8" t="n">
         <v>107.5</v>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="n">
+      <c r="M8" t="n">
         <v>53.75</v>
       </c>
     </row>
@@ -10637,7 +10381,6 @@
           <t>AWAY</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
         <v>217.5</v>
       </c>
@@ -10660,8 +10403,7 @@
       <c r="L9" t="n">
         <v>-100</v>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="n">
+      <c r="M9" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -10691,7 +10433,6 @@
           <t>HOME</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
         <v>112.5</v>
       </c>
@@ -10714,8 +10455,7 @@
       <c r="L10" t="n">
         <v>-100</v>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="n">
+      <c r="M10" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -10745,7 +10485,6 @@
           <t>HOME</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
         <v>-195</v>
       </c>
@@ -10768,8 +10507,7 @@
       <c r="L11" t="n">
         <v>51.28</v>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="n">
+      <c r="M11" t="n">
         <v>25.64</v>
       </c>
     </row>
@@ -10799,7 +10537,6 @@
           <t>AWAY</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
         <v>144.5</v>
       </c>
@@ -10822,8 +10559,7 @@
       <c r="L12" t="n">
         <v>144.5</v>
       </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="n">
+      <c r="M12" t="n">
         <v>72.25</v>
       </c>
     </row>
@@ -10904,12 +10640,12 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>pnl_50</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>pnl_50</t>
+          <t>git_commits</t>
         </is>
       </c>
     </row>
@@ -10962,8 +10698,7 @@
       <c r="L2" t="n">
         <v>-100</v>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="n">
+      <c r="M2" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -11016,8 +10751,7 @@
       <c r="L3" t="n">
         <v>-100</v>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="n">
+      <c r="M3" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -11070,8 +10804,7 @@
       <c r="L4" t="n">
         <v>82.3</v>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="n">
+      <c r="M4" t="n">
         <v>41.15</v>
       </c>
     </row>
@@ -11124,8 +10857,7 @@
       <c r="L5" t="n">
         <v>90.91</v>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="n">
+      <c r="M5" t="n">
         <v>45.45</v>
       </c>
     </row>
@@ -11178,8 +10910,7 @@
       <c r="L6" t="n">
         <v>95.23999999999999</v>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="n">
+      <c r="M6" t="n">
         <v>47.62</v>
       </c>
     </row>
@@ -11232,8 +10963,7 @@
       <c r="L7" t="n">
         <v>90.91</v>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="n">
+      <c r="M7" t="n">
         <v>45.45</v>
       </c>
     </row>
@@ -11286,8 +11016,7 @@
       <c r="L8" t="n">
         <v>-100</v>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="n">
+      <c r="M8" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -11340,8 +11069,7 @@
       <c r="L9" t="n">
         <v>95.23999999999999</v>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="n">
+      <c r="M9" t="n">
         <v>47.62</v>
       </c>
     </row>
@@ -11394,8 +11122,7 @@
       <c r="L10" t="n">
         <v>90.91</v>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="n">
+      <c r="M10" t="n">
         <v>45.45</v>
       </c>
     </row>
@@ -11448,8 +11175,7 @@
       <c r="L11" t="n">
         <v>-100</v>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="n">
+      <c r="M11" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -11502,8 +11228,7 @@
       <c r="L12" t="n">
         <v>86.95999999999999</v>
       </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="n">
+      <c r="M12" t="n">
         <v>43.48</v>
       </c>
     </row>
@@ -11556,8 +11281,7 @@
       <c r="L13" t="n">
         <v>94.34</v>
       </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="n">
+      <c r="M13" t="n">
         <v>47.17</v>
       </c>
     </row>
@@ -11610,8 +11334,7 @@
       <c r="L14" t="n">
         <v>82.64</v>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="n">
+      <c r="M14" t="n">
         <v>41.32</v>
       </c>
     </row>
@@ -11664,8 +11387,7 @@
       <c r="L15" t="n">
         <v>95.23999999999999</v>
       </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="n">
+      <c r="M15" t="n">
         <v>47.62</v>
       </c>
     </row>
@@ -11718,8 +11440,7 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="n">
+      <c r="M16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11772,8 +11493,7 @@
       <c r="L17" t="n">
         <v>-100</v>
       </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="n">
+      <c r="M17" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -11826,8 +11546,7 @@
       <c r="L18" t="n">
         <v>-100</v>
       </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="n">
+      <c r="M18" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -11880,8 +11599,7 @@
       <c r="L19" t="n">
         <v>-100</v>
       </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="n">
+      <c r="M19" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -11934,8 +11652,7 @@
       <c r="L20" t="n">
         <v>-100</v>
       </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="n">
+      <c r="M20" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -11988,8 +11705,7 @@
       <c r="L21" t="n">
         <v>-100</v>
       </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="n">
+      <c r="M21" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -12070,12 +11786,12 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>pnl_50</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>pnl_50</t>
+          <t>git_commits</t>
         </is>
       </c>
     </row>
@@ -12128,8 +11844,7 @@
       <c r="L2" t="n">
         <v>62.7</v>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="n">
+      <c r="M2" t="n">
         <v>31.35</v>
       </c>
     </row>
@@ -12182,8 +11897,7 @@
       <c r="L3" t="n">
         <v>95.23999999999999</v>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="n">
+      <c r="M3" t="n">
         <v>47.62</v>
       </c>
     </row>
@@ -12236,8 +11950,7 @@
       <c r="L4" t="n">
         <v>-100</v>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="n">
+      <c r="M4" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -12290,8 +12003,7 @@
       <c r="L5" t="n">
         <v>60.61</v>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="n">
+      <c r="M5" t="n">
         <v>30.3</v>
       </c>
     </row>
@@ -12344,8 +12056,7 @@
       <c r="L6" t="n">
         <v>86.95999999999999</v>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="n">
+      <c r="M6" t="n">
         <v>43.48</v>
       </c>
     </row>
@@ -12398,8 +12109,7 @@
       <c r="L7" t="n">
         <v>-100</v>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="n">
+      <c r="M7" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -12446,10 +12156,6 @@
           <t>ODDS_ERR</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12500,8 +12206,7 @@
       <c r="L9" t="n">
         <v>62.11</v>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="n">
+      <c r="M9" t="n">
         <v>31.06</v>
       </c>
     </row>
@@ -12554,8 +12259,7 @@
       <c r="L10" t="n">
         <v>-100</v>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="n">
+      <c r="M10" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -12602,10 +12306,6 @@
           <t>ODDS_ERR</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -12656,8 +12356,7 @@
       <c r="L12" t="n">
         <v>-100</v>
       </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="n">
+      <c r="M12" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -12710,8 +12409,7 @@
       <c r="L13" t="n">
         <v>-100</v>
       </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="n">
+      <c r="M13" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -12764,8 +12462,7 @@
       <c r="L14" t="n">
         <v>60.79</v>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="n">
+      <c r="M14" t="n">
         <v>30.4</v>
       </c>
     </row>
@@ -12818,8 +12515,7 @@
       <c r="L15" t="n">
         <v>-100</v>
       </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="n">
+      <c r="M15" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -12872,8 +12568,7 @@
       <c r="L16" t="n">
         <v>54.95</v>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="n">
+      <c r="M16" t="n">
         <v>27.47</v>
       </c>
     </row>
@@ -12920,10 +12615,6 @@
           <t>ODDS_ERR</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -12974,8 +12665,7 @@
       <c r="L18" t="n">
         <v>-100</v>
       </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="n">
+      <c r="M18" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -13028,8 +12718,7 @@
       <c r="L19" t="n">
         <v>-100</v>
       </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="n">
+      <c r="M19" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -13082,8 +12771,7 @@
       <c r="L20" t="n">
         <v>-100</v>
       </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="n">
+      <c r="M20" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -13130,12 +12818,10 @@
           <t>DNP</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
         <v>0</v>
       </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="n">
+      <c r="M21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13182,10 +12868,6 @@
           <t>ODDS_ERR</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -13236,8 +12918,7 @@
       <c r="L23" t="n">
         <v>92.59</v>
       </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="n">
+      <c r="M23" t="n">
         <v>46.3</v>
       </c>
     </row>
@@ -13290,8 +12971,7 @@
       <c r="L24" t="n">
         <v>126.5</v>
       </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="n">
+      <c r="M24" t="n">
         <v>63.25</v>
       </c>
     </row>
@@ -13344,8 +13024,7 @@
       <c r="L25" t="n">
         <v>80.65000000000001</v>
       </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="n">
+      <c r="M25" t="n">
         <v>40.32</v>
       </c>
     </row>
@@ -13398,8 +13077,7 @@
       <c r="L26" t="n">
         <v>100</v>
       </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="n">
+      <c r="M26" t="n">
         <v>50</v>
       </c>
     </row>
@@ -13452,8 +13130,7 @@
       <c r="L27" t="n">
         <v>115</v>
       </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="n">
+      <c r="M27" t="n">
         <v>57.5</v>
       </c>
     </row>
@@ -13506,8 +13183,7 @@
       <c r="L28" t="n">
         <v>-100</v>
       </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="n">
+      <c r="M28" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -13560,8 +13236,7 @@
       <c r="L29" t="n">
         <v>84.75</v>
       </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="n">
+      <c r="M29" t="n">
         <v>42.37</v>
       </c>
     </row>
@@ -13614,8 +13289,7 @@
       <c r="L30" t="n">
         <v>72.45999999999999</v>
       </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="n">
+      <c r="M30" t="n">
         <v>36.23</v>
       </c>
     </row>
@@ -13668,8 +13342,7 @@
       <c r="L31" t="n">
         <v>38.46</v>
       </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="n">
+      <c r="M31" t="n">
         <v>19.23</v>
       </c>
     </row>
@@ -13722,8 +13395,7 @@
       <c r="L32" t="n">
         <v>47.62</v>
       </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="n">
+      <c r="M32" t="n">
         <v>23.81</v>
       </c>
     </row>
@@ -13770,10 +13442,6 @@
           <t>ODDS_ERR</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -13824,8 +13492,7 @@
       <c r="L34" t="n">
         <v>-100</v>
       </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="n">
+      <c r="M34" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -13878,8 +13545,7 @@
       <c r="L35" t="n">
         <v>68.97</v>
       </c>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="n">
+      <c r="M35" t="n">
         <v>34.48</v>
       </c>
     </row>
@@ -13932,8 +13598,7 @@
       <c r="L36" t="n">
         <v>54.05</v>
       </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="n">
+      <c r="M36" t="n">
         <v>27.03</v>
       </c>
     </row>
@@ -13986,8 +13651,7 @@
       <c r="L37" t="n">
         <v>106</v>
       </c>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="n">
+      <c r="M37" t="n">
         <v>53</v>
       </c>
     </row>
@@ -14040,8 +13704,7 @@
       <c r="L38" t="n">
         <v>-100</v>
       </c>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="n">
+      <c r="M38" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -14094,8 +13757,7 @@
       <c r="L39" t="n">
         <v>-100</v>
       </c>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="n">
+      <c r="M39" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -14148,8 +13810,7 @@
       <c r="L40" t="n">
         <v>70.92</v>
       </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="n">
+      <c r="M40" t="n">
         <v>35.46</v>
       </c>
     </row>
@@ -14202,8 +13863,7 @@
       <c r="L41" t="n">
         <v>-100</v>
       </c>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="n">
+      <c r="M41" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -14256,8 +13916,7 @@
       <c r="L42" t="n">
         <v>-100</v>
       </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="n">
+      <c r="M42" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -14310,8 +13969,7 @@
       <c r="L43" t="n">
         <v>65.15000000000001</v>
       </c>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="n">
+      <c r="M43" t="n">
         <v>32.57</v>
       </c>
     </row>
@@ -14364,8 +14022,7 @@
       <c r="L44" t="n">
         <v>-100</v>
       </c>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="n">
+      <c r="M44" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -14418,8 +14075,7 @@
       <c r="L45" t="n">
         <v>66.67</v>
       </c>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="n">
+      <c r="M45" t="n">
         <v>33.33</v>
       </c>
     </row>
@@ -14472,8 +14128,7 @@
       <c r="L46" t="n">
         <v>57.14</v>
       </c>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="n">
+      <c r="M46" t="n">
         <v>28.57</v>
       </c>
     </row>
@@ -14526,8 +14181,7 @@
       <c r="L47" t="n">
         <v>73.8</v>
       </c>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="n">
+      <c r="M47" t="n">
         <v>36.9</v>
       </c>
     </row>
@@ -14580,8 +14234,7 @@
       <c r="L48" t="n">
         <v>-100</v>
       </c>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="n">
+      <c r="M48" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -14628,10 +14281,6 @@
           <t>ODDS_ERR</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -14682,8 +14331,7 @@
       <c r="L50" t="n">
         <v>-100</v>
       </c>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="n">
+      <c r="M50" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -14736,8 +14384,7 @@
       <c r="L51" t="n">
         <v>-100</v>
       </c>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="n">
+      <c r="M51" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -14784,10 +14431,6 @@
           <t>ODDS_ERR</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -14832,10 +14475,6 @@
           <t>ODDS_ERR</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -14886,8 +14525,7 @@
       <c r="L54" t="n">
         <v>58.82</v>
       </c>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="n">
+      <c r="M54" t="n">
         <v>29.41</v>
       </c>
     </row>
@@ -14940,8 +14578,7 @@
       <c r="L55" t="n">
         <v>-100</v>
       </c>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="n">
+      <c r="M55" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -14994,8 +14631,7 @@
       <c r="L56" t="n">
         <v>120.5</v>
       </c>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="n">
+      <c r="M56" t="n">
         <v>60.25</v>
       </c>
     </row>
@@ -15048,8 +14684,7 @@
       <c r="L57" t="n">
         <v>54.05</v>
       </c>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="n">
+      <c r="M57" t="n">
         <v>27.03</v>
       </c>
     </row>
@@ -15102,8 +14737,7 @@
       <c r="L58" t="n">
         <v>-100</v>
       </c>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="n">
+      <c r="M58" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -15156,8 +14790,7 @@
       <c r="L59" t="n">
         <v>-100</v>
       </c>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="n">
+      <c r="M59" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -15210,8 +14843,7 @@
       <c r="L60" t="n">
         <v>80</v>
       </c>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="n">
+      <c r="M60" t="n">
         <v>40</v>
       </c>
     </row>
@@ -15264,8 +14896,7 @@
       <c r="L61" t="n">
         <v>57.14</v>
       </c>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="n">
+      <c r="M61" t="n">
         <v>28.57</v>
       </c>
     </row>
@@ -15318,8 +14949,7 @@
       <c r="L62" t="n">
         <v>-100</v>
       </c>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="n">
+      <c r="M62" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -15372,8 +15002,7 @@
       <c r="L63" t="n">
         <v>-100</v>
       </c>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="n">
+      <c r="M63" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -15426,8 +15055,7 @@
       <c r="L64" t="n">
         <v>31.25</v>
       </c>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="n">
+      <c r="M64" t="n">
         <v>15.62</v>
       </c>
     </row>
@@ -15480,8 +15108,7 @@
       <c r="L65" t="n">
         <v>100</v>
       </c>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="n">
+      <c r="M65" t="n">
         <v>50</v>
       </c>
     </row>
@@ -15534,8 +15161,7 @@
       <c r="L66" t="n">
         <v>-100</v>
       </c>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="n">
+      <c r="M66" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -15588,8 +15214,7 @@
       <c r="L67" t="n">
         <v>80</v>
       </c>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="n">
+      <c r="M67" t="n">
         <v>40</v>
       </c>
     </row>
@@ -15642,8 +15267,7 @@
       <c r="L68" t="n">
         <v>-100</v>
       </c>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="n">
+      <c r="M68" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -15696,8 +15320,7 @@
       <c r="L69" t="n">
         <v>-100</v>
       </c>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="n">
+      <c r="M69" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -15750,8 +15373,7 @@
       <c r="L70" t="n">
         <v>63.69</v>
       </c>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="n">
+      <c r="M70" t="n">
         <v>31.85</v>
       </c>
     </row>
@@ -15804,8 +15426,7 @@
       <c r="L71" t="n">
         <v>46.19</v>
       </c>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="n">
+      <c r="M71" t="n">
         <v>23.09</v>
       </c>
     </row>
@@ -15858,8 +15479,7 @@
       <c r="L72" t="n">
         <v>68.97</v>
       </c>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="n">
+      <c r="M72" t="n">
         <v>34.48</v>
       </c>
     </row>
@@ -15912,8 +15532,7 @@
       <c r="L73" t="n">
         <v>-100</v>
       </c>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="n">
+      <c r="M73" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -15966,8 +15585,7 @@
       <c r="L74" t="n">
         <v>110.5</v>
       </c>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="n">
+      <c r="M74" t="n">
         <v>55.25</v>
       </c>
     </row>
@@ -16020,8 +15638,7 @@
       <c r="L75" t="n">
         <v>-100</v>
       </c>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="n">
+      <c r="M75" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -16068,12 +15685,10 @@
           <t>DNP</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
       <c r="L76" t="n">
         <v>0</v>
       </c>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="n">
+      <c r="M76" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16126,8 +15741,7 @@
       <c r="L77" t="n">
         <v>52.63</v>
       </c>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="n">
+      <c r="M77" t="n">
         <v>26.32</v>
       </c>
     </row>
@@ -16180,8 +15794,7 @@
       <c r="L78" t="n">
         <v>-100</v>
       </c>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="n">
+      <c r="M78" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -16234,8 +15847,7 @@
       <c r="L79" t="n">
         <v>-100</v>
       </c>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="n">
+      <c r="M79" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -16288,8 +15900,7 @@
       <c r="L80" t="n">
         <v>62.11</v>
       </c>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="n">
+      <c r="M80" t="n">
         <v>31.06</v>
       </c>
     </row>
@@ -16342,8 +15953,7 @@
       <c r="L81" t="n">
         <v>-100</v>
       </c>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="n">
+      <c r="M81" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -16396,8 +16006,7 @@
       <c r="L82" t="n">
         <v>71.43000000000001</v>
       </c>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="n">
+      <c r="M82" t="n">
         <v>35.71</v>
       </c>
     </row>
@@ -16450,8 +16059,7 @@
       <c r="L83" t="n">
         <v>-100</v>
       </c>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="n">
+      <c r="M83" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -16504,8 +16112,7 @@
       <c r="L84" t="n">
         <v>58.82</v>
       </c>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="n">
+      <c r="M84" t="n">
         <v>29.41</v>
       </c>
     </row>
@@ -16586,12 +16193,12 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>pnl_50</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>pnl_50</t>
+          <t>git_commits</t>
         </is>
       </c>
     </row>
@@ -16644,8 +16251,7 @@
       <c r="L2" t="n">
         <v>100</v>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="n">
+      <c r="M2" t="n">
         <v>50</v>
       </c>
     </row>
@@ -16692,10 +16298,6 @@
           <t>ODDS_ERR</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -16746,8 +16348,7 @@
       <c r="L4" t="n">
         <v>-100</v>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="n">
+      <c r="M4" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -16794,10 +16395,6 @@
           <t>ODDS_ERR</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16848,8 +16445,7 @@
       <c r="L6" t="n">
         <v>109.5</v>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="n">
+      <c r="M6" t="n">
         <v>54.75</v>
       </c>
     </row>
@@ -16896,10 +16492,6 @@
           <t>ODDS_ERR</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16950,8 +16542,7 @@
       <c r="L8" t="n">
         <v>-100</v>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="n">
+      <c r="M8" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -17004,8 +16595,7 @@
       <c r="L9" t="n">
         <v>-100</v>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="n">
+      <c r="M9" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -17058,8 +16648,7 @@
       <c r="L10" t="n">
         <v>80</v>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="n">
+      <c r="M10" t="n">
         <v>40</v>
       </c>
     </row>
@@ -17112,8 +16701,7 @@
       <c r="L11" t="n">
         <v>125</v>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="n">
+      <c r="M11" t="n">
         <v>62.5</v>
       </c>
     </row>
@@ -17166,8 +16754,7 @@
       <c r="L12" t="n">
         <v>-100</v>
       </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="n">
+      <c r="M12" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -17220,8 +16807,7 @@
       <c r="L13" t="n">
         <v>54.5</v>
       </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="n">
+      <c r="M13" t="n">
         <v>27.25</v>
       </c>
     </row>
@@ -17274,8 +16860,7 @@
       <c r="L14" t="n">
         <v>-100</v>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="n">
+      <c r="M14" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -17328,8 +16913,7 @@
       <c r="L15" t="n">
         <v>-100</v>
       </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="n">
+      <c r="M15" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -17382,8 +16966,7 @@
       <c r="L16" t="n">
         <v>59.7</v>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="n">
+      <c r="M16" t="n">
         <v>29.85</v>
       </c>
     </row>
@@ -17430,10 +17013,6 @@
           <t>ODDS_ERR</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -17484,8 +17063,7 @@
       <c r="L18" t="n">
         <v>-100</v>
       </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="n">
+      <c r="M18" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -17538,8 +17116,7 @@
       <c r="L19" t="n">
         <v>90.91</v>
       </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="n">
+      <c r="M19" t="n">
         <v>45.45</v>
       </c>
     </row>
@@ -17592,8 +17169,7 @@
       <c r="L20" t="n">
         <v>-100</v>
       </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="n">
+      <c r="M20" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -17646,8 +17222,7 @@
       <c r="L21" t="n">
         <v>145</v>
       </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="n">
+      <c r="M21" t="n">
         <v>72.5</v>
       </c>
     </row>
@@ -17700,8 +17275,7 @@
       <c r="L22" t="n">
         <v>57.14</v>
       </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="n">
+      <c r="M22" t="n">
         <v>28.57</v>
       </c>
     </row>
@@ -17754,8 +17328,7 @@
       <c r="L23" t="n">
         <v>-100</v>
       </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="n">
+      <c r="M23" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -17808,8 +17381,7 @@
       <c r="L24" t="n">
         <v>-100</v>
       </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="n">
+      <c r="M24" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -17862,8 +17434,7 @@
       <c r="L25" t="n">
         <v>-100</v>
       </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="n">
+      <c r="M25" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -17916,8 +17487,7 @@
       <c r="L26" t="n">
         <v>-100</v>
       </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="n">
+      <c r="M26" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -17970,8 +17540,7 @@
       <c r="L27" t="n">
         <v>-100</v>
       </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="n">
+      <c r="M27" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -18024,8 +17593,7 @@
       <c r="L28" t="n">
         <v>49.38</v>
       </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="n">
+      <c r="M28" t="n">
         <v>24.69</v>
       </c>
     </row>
@@ -18078,8 +17646,7 @@
       <c r="L29" t="n">
         <v>-100</v>
       </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="n">
+      <c r="M29" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -18132,8 +17699,7 @@
       <c r="L30" t="n">
         <v>83.33</v>
       </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="n">
+      <c r="M30" t="n">
         <v>41.67</v>
       </c>
     </row>
@@ -18186,8 +17752,7 @@
       <c r="L31" t="n">
         <v>100.5</v>
       </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="n">
+      <c r="M31" t="n">
         <v>50.25</v>
       </c>
     </row>
@@ -18240,8 +17805,7 @@
       <c r="L32" t="n">
         <v>82.3</v>
       </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="n">
+      <c r="M32" t="n">
         <v>41.15</v>
       </c>
     </row>
@@ -18294,8 +17858,7 @@
       <c r="L33" t="n">
         <v>-100</v>
       </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="n">
+      <c r="M33" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -18348,8 +17911,7 @@
       <c r="L34" t="n">
         <v>50.89</v>
       </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="n">
+      <c r="M34" t="n">
         <v>25.45</v>
       </c>
     </row>
@@ -18430,12 +17992,12 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>pnl_50</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>pnl_50</t>
+          <t>git_commits</t>
         </is>
       </c>
     </row>
@@ -18465,7 +18027,6 @@
           <t>NRFI</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
         <v>-157.5</v>
       </c>
@@ -18488,8 +18049,7 @@
       <c r="L2" t="n">
         <v>63.49</v>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="n">
+      <c r="M2" t="n">
         <v>31.75</v>
       </c>
     </row>
@@ -18519,7 +18079,6 @@
           <t>YRFI</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
         <v>120</v>
       </c>
@@ -18542,8 +18101,7 @@
       <c r="L3" t="n">
         <v>-100</v>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="n">
+      <c r="M3" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -18573,7 +18131,6 @@
           <t>NRFI</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
         <v>-105</v>
       </c>
@@ -18596,8 +18153,7 @@
       <c r="L4" t="n">
         <v>95.23999999999999</v>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="n">
+      <c r="M4" t="n">
         <v>47.62</v>
       </c>
     </row>
@@ -18627,7 +18183,6 @@
           <t>NRFI</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
         <v>-155</v>
       </c>
@@ -18650,8 +18205,7 @@
       <c r="L5" t="n">
         <v>-100</v>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="n">
+      <c r="M5" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -18681,7 +18235,6 @@
           <t>YRFI</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
         <v>-119</v>
       </c>
@@ -18704,8 +18257,7 @@
       <c r="L6" t="n">
         <v>-100</v>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="n">
+      <c r="M6" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -18735,7 +18287,6 @@
           <t>NRFI</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
         <v>-162</v>
       </c>
@@ -18758,8 +18309,7 @@
       <c r="L7" t="n">
         <v>-100</v>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="n">
+      <c r="M7" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -18789,7 +18339,6 @@
           <t>NRFI</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
         <v>-162</v>
       </c>
@@ -18812,8 +18361,7 @@
       <c r="L8" t="n">
         <v>-100</v>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="n">
+      <c r="M8" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -18843,7 +18391,6 @@
           <t>YRFI</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
         <v>-106</v>
       </c>
@@ -18866,8 +18413,7 @@
       <c r="L9" t="n">
         <v>94.34</v>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="n">
+      <c r="M9" t="n">
         <v>47.17</v>
       </c>
     </row>
@@ -18897,7 +18443,6 @@
           <t>YRFI</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
         <v>118</v>
       </c>
@@ -18920,8 +18465,7 @@
       <c r="L10" t="n">
         <v>118</v>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="n">
+      <c r="M10" t="n">
         <v>59</v>
       </c>
     </row>
@@ -18951,7 +18495,6 @@
           <t>YRFI</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
         <v>100</v>
       </c>
@@ -18974,8 +18517,7 @@
       <c r="L11" t="n">
         <v>-100</v>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="n">
+      <c r="M11" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -19005,7 +18547,6 @@
           <t>NRFI</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
         <v>-129</v>
       </c>
@@ -19028,8 +18569,7 @@
       <c r="L12" t="n">
         <v>-100</v>
       </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="n">
+      <c r="M12" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -19059,7 +18599,6 @@
           <t>YRFI</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
         <v>102</v>
       </c>
@@ -19082,8 +18621,7 @@
       <c r="L13" t="n">
         <v>-100</v>
       </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="n">
+      <c r="M13" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -19113,7 +18651,6 @@
           <t>YRFI</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
         <v>106</v>
       </c>
@@ -19136,8 +18673,7 @@
       <c r="L14" t="n">
         <v>-100</v>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="n">
+      <c r="M14" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -19167,7 +18703,6 @@
           <t>YRFI</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
         <v>-112</v>
       </c>
@@ -19190,8 +18725,7 @@
       <c r="L15" t="n">
         <v>-100</v>
       </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="n">
+      <c r="M15" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -19221,7 +18755,6 @@
           <t>YRFI</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
         <v>-102</v>
       </c>
@@ -19244,8 +18777,7 @@
       <c r="L16" t="n">
         <v>98.04000000000001</v>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="n">
+      <c r="M16" t="n">
         <v>49.02</v>
       </c>
     </row>
@@ -19275,7 +18807,6 @@
           <t>YRFI</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
         <v>120</v>
       </c>
@@ -19298,8 +18829,7 @@
       <c r="L17" t="n">
         <v>120</v>
       </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="n">
+      <c r="M17" t="n">
         <v>60</v>
       </c>
     </row>
@@ -19329,7 +18859,6 @@
           <t>NRFI</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
         <v>-155</v>
       </c>
@@ -19352,8 +18881,7 @@
       <c r="L18" t="n">
         <v>64.52</v>
       </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="n">
+      <c r="M18" t="n">
         <v>32.26</v>
       </c>
     </row>
@@ -19383,7 +18911,6 @@
           <t>YRFI</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
         <v>-100</v>
       </c>
@@ -19406,8 +18933,7 @@
       <c r="L19" t="n">
         <v>100</v>
       </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="n">
+      <c r="M19" t="n">
         <v>50</v>
       </c>
     </row>
@@ -19437,7 +18963,6 @@
           <t>YRFI</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
         <v>-102</v>
       </c>
@@ -19460,8 +18985,7 @@
       <c r="L20" t="n">
         <v>-100</v>
       </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="n">
+      <c r="M20" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -19491,7 +19015,6 @@
           <t>YRFI</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
         <v>110</v>
       </c>
@@ -19514,8 +19037,7 @@
       <c r="L21" t="n">
         <v>110</v>
       </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="n">
+      <c r="M21" t="n">
         <v>55</v>
       </c>
     </row>
@@ -19545,7 +19067,6 @@
           <t>NRFI</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
         <v>-128</v>
       </c>
@@ -19568,8 +19089,7 @@
       <c r="L22" t="n">
         <v>78.12</v>
       </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="n">
+      <c r="M22" t="n">
         <v>39.06</v>
       </c>
     </row>
@@ -19599,7 +19119,6 @@
           <t>NRFI</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
         <v>-109</v>
       </c>
@@ -19622,8 +19141,7 @@
       <c r="L23" t="n">
         <v>91.73999999999999</v>
       </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="n">
+      <c r="M23" t="n">
         <v>45.87</v>
       </c>
     </row>
@@ -19653,7 +19171,6 @@
           <t>YRFI</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
         <v>-102</v>
       </c>
@@ -19676,8 +19193,7 @@
       <c r="L24" t="n">
         <v>-100</v>
       </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="n">
+      <c r="M24" t="n">
         <v>-50</v>
       </c>
     </row>

--- a/tracking/picks.xlsx
+++ b/tracking/picks.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N229"/>
+  <dimension ref="A1:N248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12595,6 +12595,984 @@
       <c r="L229" t="inlineStr"/>
       <c r="M229" t="inlineStr"/>
       <c r="N229" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix NRFI scoreboard period param and Discord embed truncation; Fix NRFI odds: parse from scoreboard markets instead of props endpoint; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Gate NRFI scoring on confirmed lineups, consistent with other models; Fix 04_export_nrfi.py DataFrame iteration and lineup format bugs; Fix API crash guards and FanGraphs splits method errors; Add NRFI/YRFI fifth model and rebuild all four existing models; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>TBR @ STL</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>TBR @ STL</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F230" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G230" t="n">
+        <v>-100</v>
+      </c>
+      <c r="H230" t="n">
+        <v>0.7544999999999999</v>
+      </c>
+      <c r="I230" t="n">
+        <v>0.2771</v>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr"/>
+      <c r="M230" t="inlineStr"/>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>TEX @ PHI</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>TEX @ PHI</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F231" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G231" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H231" t="n">
+        <v>0.8219</v>
+      </c>
+      <c r="I231" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr"/>
+      <c r="M231" t="inlineStr"/>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>PIT @ NYM</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>PIT @ NYM</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F232" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G232" t="n">
+        <v>-105</v>
+      </c>
+      <c r="H232" t="n">
+        <v>0.8766</v>
+      </c>
+      <c r="I232" t="n">
+        <v>0.3875</v>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr"/>
+      <c r="M232" t="inlineStr"/>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>MIN @ BAL</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>MIN @ BAL</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F233" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G233" t="n">
+        <v>-118</v>
+      </c>
+      <c r="H233" t="n">
+        <v>0.8299</v>
+      </c>
+      <c r="I233" t="n">
+        <v>0.3161</v>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr"/>
+      <c r="M233" t="inlineStr"/>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>OAK @ TOR</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>OAK @ TOR</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F234" t="n">
+        <v>8</v>
+      </c>
+      <c r="G234" t="n">
+        <v>-116</v>
+      </c>
+      <c r="H234" t="n">
+        <v>0.7155</v>
+      </c>
+      <c r="I234" t="n">
+        <v>0.2025</v>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr"/>
+      <c r="L234" t="inlineStr"/>
+      <c r="M234" t="inlineStr"/>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>BOS @ CIN</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>BOS @ CIN</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F235" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G235" t="n">
+        <v>-105</v>
+      </c>
+      <c r="H235" t="n">
+        <v>0.6288</v>
+      </c>
+      <c r="I235" t="n">
+        <v>0.1396</v>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr"/>
+      <c r="M235" t="inlineStr"/>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>COL @ MIA</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>COL @ MIA</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F236" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G236" t="n">
+        <v>-104</v>
+      </c>
+      <c r="H236" t="n">
+        <v>0.5831</v>
+      </c>
+      <c r="I236" t="n">
+        <v>0.09810000000000001</v>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr"/>
+      <c r="M236" t="inlineStr"/>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>NYY @ SFG</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>NYY @ SFG</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F237" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G237" t="n">
+        <v>-108</v>
+      </c>
+      <c r="H237" t="n">
+        <v>0.5569</v>
+      </c>
+      <c r="I237" t="n">
+        <v>0.0613</v>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr"/>
+      <c r="M237" t="inlineStr"/>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>NYY @ SFG</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>SFG</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr"/>
+      <c r="G238" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="H238" t="n">
+        <v>0.5914</v>
+      </c>
+      <c r="I238" t="n">
+        <v>0.1307</v>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr"/>
+      <c r="M238" t="inlineStr"/>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>CWS @ MIL</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="n">
+        <v>-199</v>
+      </c>
+      <c r="H239" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="I239" t="n">
+        <v>0.0862</v>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr"/>
+      <c r="L239" t="inlineStr"/>
+      <c r="M239" t="inlineStr"/>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>CWS @ MIL</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>CWS @ MIL</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F240" t="n">
+        <v>8</v>
+      </c>
+      <c r="G240" t="n">
+        <v>-105</v>
+      </c>
+      <c r="H240" t="n">
+        <v>0.5642</v>
+      </c>
+      <c r="I240" t="n">
+        <v>0.0751</v>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr"/>
+      <c r="M240" t="inlineStr"/>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>CWS @ MIL</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>CWS @ MIL</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F241" t="n">
+        <v>8</v>
+      </c>
+      <c r="G241" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H241" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="I241" t="n">
+        <v>0.06419999999999999</v>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr"/>
+      <c r="M241" t="inlineStr"/>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>CWS vs MIL</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Brandon Lockridge</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F242" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G242" t="n">
+        <v>-106</v>
+      </c>
+      <c r="H242" t="n">
+        <v>0.6246</v>
+      </c>
+      <c r="I242" t="n">
+        <v>0.1446</v>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr"/>
+      <c r="L242" t="inlineStr"/>
+      <c r="M242" t="inlineStr"/>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>CWS vs MIL</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>David Hamilton</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F243" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G243" t="n">
+        <v>-125</v>
+      </c>
+      <c r="H243" t="n">
+        <v>0.6313</v>
+      </c>
+      <c r="I243" t="n">
+        <v>0.1166</v>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr"/>
+      <c r="L243" t="inlineStr"/>
+      <c r="M243" t="inlineStr"/>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>MIL vs CWS</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Sean Burke</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F244" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G244" t="n">
+        <v>-106</v>
+      </c>
+      <c r="H244" t="n">
+        <v>0.8197</v>
+      </c>
+      <c r="I244" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr"/>
+      <c r="L244" t="inlineStr"/>
+      <c r="M244" t="inlineStr"/>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Add opp_bb_pct to pitcher outs, bullpen features to totals, bullpen availability utility; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Use confirmed SP from lineup card, fall back to probable pitcher; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Cap pitcher outs to 1 pick per game (not per pitcher); Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Gate all 5 models on confirmed starting pitchers; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>NYY vs SFG</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Tyler Mahle</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F245" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G245" t="n">
+        <v>-165.5</v>
+      </c>
+      <c r="H245" t="n">
+        <v>0.7963</v>
+      </c>
+      <c r="I245" t="n">
+        <v>0.2191</v>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr"/>
+      <c r="L245" t="inlineStr"/>
+      <c r="M245" t="inlineStr"/>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Add opp_bb_pct to pitcher outs, bullpen features to totals, bullpen availability utility; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Use confirmed SP from lineup card, fall back to probable pitcher; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Cap pitcher outs to 1 pick per game (not per pitcher); Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Gate all 5 models on confirmed starting pitchers; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>NYY @ SFG</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>NYY @ SFG</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>YRFI</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="n">
+        <v>-107</v>
+      </c>
+      <c r="H246" t="n">
+        <v>1</v>
+      </c>
+      <c r="I246" t="n">
+        <v>0.5158</v>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr"/>
+      <c r="L246" t="inlineStr"/>
+      <c r="M246" t="inlineStr"/>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix NRFI scoreboard period param and Discord embed truncation; Fix NRFI odds: parse from scoreboard markets instead of props endpoint; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Gate NRFI scoring on confirmed lineups, consistent with other models; Fix 04_export_nrfi.py DataFrame iteration and lineup format bugs; Fix API crash guards and FanGraphs splits method errors; Add NRFI/YRFI fifth model and rebuild all four existing models; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>CWS @ MIL</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>CWS @ MIL</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>YRFI</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr"/>
+      <c r="G247" t="n">
+        <v>-107</v>
+      </c>
+      <c r="H247" t="n">
+        <v>0.5887</v>
+      </c>
+      <c r="I247" t="n">
+        <v>0.1026</v>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr"/>
+      <c r="L247" t="inlineStr"/>
+      <c r="M247" t="inlineStr"/>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix NRFI scoreboard period param and Discord embed truncation; Fix NRFI odds: parse from scoreboard markets instead of props endpoint; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Gate NRFI scoring on confirmed lineups, consistent with other models; Fix 04_export_nrfi.py DataFrame iteration and lineup format bugs; Fix API crash guards and FanGraphs splits method errors; Add NRFI/YRFI fifth model and rebuild all four existing models; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>DET @ SDP</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>DET @ SDP</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>YRFI</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr"/>
+      <c r="G248" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H248" t="n">
+        <v>0.5887</v>
+      </c>
+      <c r="I248" t="n">
+        <v>0.0872</v>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr"/>
+      <c r="L248" t="inlineStr"/>
+      <c r="M248" t="inlineStr"/>
+      <c r="N248" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix NRFI scoreboard period param and Discord embed truncation; Fix NRFI odds: parse from scoreboard markets instead of props endpoint; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Gate NRFI scoring on confirmed lineups, consistent with other models; Fix 04_export_nrfi.py DataFrame iteration and lineup format bugs; Fix API crash guards and FanGraphs splits method errors; Add NRFI/YRFI fifth model and rebuild all four existing models; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
         </is>
@@ -13148,7 +14126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13962,6 +14940,106 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
+        <is>
+          <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NYY @ SFG</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>SFG</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.5914</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.1307</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CWS @ MIL</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>-199</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.0862</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
         <is>
           <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
         </is>
@@ -13978,7 +15056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14120,44 +15198,44 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ARI @ LAD</t>
+          <t>CLE @ SEA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ARI @ LAD</t>
+          <t>CLE @ SEA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="G3" t="n">
-        <v>-115</v>
+        <v>-121.5</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6322</v>
+        <v>0.8472</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1214</v>
+        <v>0.3241</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K3" t="n">
         <v>10</v>
       </c>
       <c r="L3" t="n">
-        <v>-100</v>
+        <v>82.3</v>
       </c>
       <c r="M3" t="n">
-        <v>-50</v>
+        <v>41.15</v>
       </c>
       <c r="N3" t="inlineStr"/>
     </row>
@@ -14174,12 +15252,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLE @ SEA</t>
+          <t>TBR @ STL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CLE @ SEA</t>
+          <t>TBR @ STL</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -14188,16 +15266,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="G4" t="n">
-        <v>-121.5</v>
+        <v>-110</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8472</v>
+        <v>0.7002</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3241</v>
+        <v>0.1997</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -14205,13 +15283,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L4" t="n">
-        <v>82.3</v>
+        <v>90.91</v>
       </c>
       <c r="M4" t="n">
-        <v>41.15</v>
+        <v>45.45</v>
       </c>
       <c r="N4" t="inlineStr"/>
     </row>
@@ -14242,16 +15320,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>7.75</v>
       </c>
       <c r="G5" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="H5" t="n">
         <v>0.7002</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1997</v>
+        <v>0.2111</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -14262,10 +15340,10 @@
         <v>16</v>
       </c>
       <c r="L5" t="n">
-        <v>90.91</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>45.45</v>
+        <v>47.62</v>
       </c>
       <c r="N5" t="inlineStr"/>
     </row>
@@ -14282,12 +15360,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TBR @ STL</t>
+          <t>CWS @ MIL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>TBR @ STL</t>
+          <t>CWS @ MIL</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -14296,16 +15374,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>7.75</v>
+        <v>7.5</v>
       </c>
       <c r="G6" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7002</v>
+        <v>0.7967</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2111</v>
+        <v>0.2967</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -14316,10 +15394,10 @@
         <v>16</v>
       </c>
       <c r="L6" t="n">
-        <v>95.23999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="M6" t="n">
-        <v>47.62</v>
+        <v>45.45</v>
       </c>
       <c r="N6" t="inlineStr"/>
     </row>
@@ -14336,30 +15414,30 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CWS @ MIL</t>
+          <t>BOS @ CIN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CWS @ MIL</t>
+          <t>BOS @ CIN</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7967</v>
+        <v>0.5555</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2967</v>
+        <v>0.0663</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -14367,13 +15445,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
-        <v>90.91</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>45.45</v>
+        <v>47.62</v>
       </c>
       <c r="N7" t="inlineStr"/>
     </row>
@@ -14444,12 +15522,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BOS @ CIN</t>
+          <t>ARI @ LAD</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>BOS @ CIN</t>
+          <t>ARI @ LAD</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -14458,30 +15536,30 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G9" t="n">
-        <v>-105</v>
+        <v>-115</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5555</v>
+        <v>0.6322</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0663</v>
+        <v>0.1214</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L9" t="n">
-        <v>95.23999999999999</v>
+        <v>-100</v>
       </c>
       <c r="M9" t="n">
-        <v>47.62</v>
+        <v>-50</v>
       </c>
       <c r="N9" t="inlineStr"/>
     </row>
@@ -14876,12 +15954,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>KCR @ ATL</t>
+          <t>LAA @ HOU</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>KCR @ ATL</t>
+          <t>LAA @ HOU</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -14890,16 +15968,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="G17" t="n">
-        <v>-100</v>
+        <v>-115</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5231</v>
+        <v>0.4909</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -14907,7 +15985,7 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L17" t="n">
         <v>-100</v>
@@ -14930,12 +16008,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NYY @ SFG</t>
+          <t>COL @ MIA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NYY @ SFG</t>
+          <t>COL @ MIA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -14944,16 +16022,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="G18" t="n">
-        <v>-107</v>
+        <v>-112.5</v>
       </c>
       <c r="H18" t="n">
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5044</v>
+        <v>0.4946</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -14984,12 +16062,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>OAK @ TOR</t>
+          <t>KCR @ ATL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>OAK @ TOR</t>
+          <t>KCR @ ATL</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -14998,16 +16076,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="G19" t="n">
-        <v>-118</v>
+        <v>-100</v>
       </c>
       <c r="H19" t="n">
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4838</v>
+        <v>0.5231</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -15015,7 +16093,7 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L19" t="n">
         <v>-100</v>
@@ -15038,12 +16116,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>COL @ MIA</t>
+          <t>NYY @ SFG</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>COL @ MIA</t>
+          <t>NYY @ SFG</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -15052,16 +16130,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="G20" t="n">
-        <v>-112.5</v>
+        <v>-107</v>
       </c>
       <c r="H20" t="n">
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4946</v>
+        <v>0.5044</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -15092,12 +16170,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>LAA @ HOU</t>
+          <t>OAK @ TOR</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LAA @ HOU</t>
+          <t>OAK @ TOR</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -15109,13 +16187,13 @@
         <v>8.5</v>
       </c>
       <c r="G21" t="n">
-        <v>-115</v>
+        <v>-118</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4909</v>
+        <v>0.4838</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -15123,7 +16201,7 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L21" t="n">
         <v>-100</v>
@@ -15132,6 +16210,526 @@
         <v>-50</v>
       </c>
       <c r="N21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CWS @ MIL</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CWS @ MIL</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>8</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-105</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.5642</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.0751</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>TBR @ STL</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TBR @ STL</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-100</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.7544999999999999</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.2771</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>TEX @ PHI</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TEX @ PHI</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.8219</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>PIT @ NYM</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>PIT @ NYM</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-105</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.8766</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.3875</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>MIN @ BAL</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>MIN @ BAL</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-118</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.8299</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.3161</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>OAK @ TOR</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>OAK @ TOR</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>8</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-116</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.7155</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.2025</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>BOS @ CIN</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>BOS @ CIN</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-105</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.6288</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.1396</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>COL @ MIA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>COL @ MIA</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-104</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.5831</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.09810000000000001</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NYY @ SFG</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NYY @ SFG</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-108</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.5569</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.0613</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CWS @ MIL</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CWS @ MIL</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>8</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.06419999999999999</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15144,7 +16742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N117"/>
+  <dimension ref="A1:N119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16825,7 +18423,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Miguel Rojas</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -16837,13 +18435,13 @@
         <v>1.5</v>
       </c>
       <c r="G32" t="n">
-        <v>-210</v>
+        <v>-260</v>
       </c>
       <c r="H32" t="n">
-        <v>0.7116</v>
+        <v>0.7621</v>
       </c>
       <c r="I32" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.093</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -16854,10 +18452,10 @@
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>47.62</v>
+        <v>38.46</v>
       </c>
       <c r="M32" t="n">
-        <v>23.81</v>
+        <v>19.23</v>
       </c>
       <c r="N32" t="inlineStr"/>
     </row>
@@ -16987,7 +18585,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Miguel Rojas</t>
+          <t>Max Muncy</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -16999,13 +18597,13 @@
         <v>1.5</v>
       </c>
       <c r="G35" t="n">
-        <v>-260</v>
+        <v>-210</v>
       </c>
       <c r="H35" t="n">
-        <v>0.7621</v>
+        <v>0.7116</v>
       </c>
       <c r="I35" t="n">
-        <v>0.093</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -17016,10 +18614,10 @@
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>38.46</v>
+        <v>47.62</v>
       </c>
       <c r="M35" t="n">
-        <v>19.23</v>
+        <v>23.81</v>
       </c>
       <c r="N35" t="inlineStr"/>
     </row>
@@ -17786,44 +19384,44 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BOS vs CIN</t>
+          <t>NYM vs PIT</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Ke'Bryan Hayes</t>
+          <t>Spencer Horwitz</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F50" t="n">
         <v>0.5</v>
       </c>
       <c r="G50" t="n">
-        <v>120.5</v>
+        <v>-126</v>
       </c>
       <c r="H50" t="n">
-        <v>0.5485</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1263</v>
+        <v>0.0756</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>120.5</v>
+        <v>-100</v>
       </c>
       <c r="M50" t="n">
-        <v>60.25</v>
+        <v>-50</v>
       </c>
       <c r="N50" t="inlineStr"/>
     </row>
@@ -17840,12 +19438,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>PIT vs NYM</t>
+          <t>MIL vs CWS</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Francisco Lindor</t>
+          <t>Andrew Benintendi</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -17857,13 +19455,13 @@
         <v>0.5</v>
       </c>
       <c r="G51" t="n">
-        <v>-180.5</v>
+        <v>-141.5</v>
       </c>
       <c r="H51" t="n">
-        <v>0.6811</v>
+        <v>0.6186</v>
       </c>
       <c r="I51" t="n">
-        <v>0.0843</v>
+        <v>0.0741</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -17894,12 +19492,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>PHI vs TEX</t>
+          <t>MIL vs CWS</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Wyatt Langford</t>
+          <t>Miguel Vargas</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -17911,22 +19509,28 @@
         <v>0.5</v>
       </c>
       <c r="G52" t="n">
-        <v>-20</v>
+        <v>-145</v>
       </c>
       <c r="H52" t="n">
-        <v>0.6369</v>
+        <v>0.6219</v>
       </c>
       <c r="I52" t="n">
-        <v>0.2456</v>
+        <v>0.0713</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>ODDS_ERR</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M52" t="n">
+        <v>-50</v>
+      </c>
       <c r="N52" t="inlineStr"/>
     </row>
     <row r="53">
@@ -17942,12 +19546,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BAL vs MIN</t>
+          <t>MIN vs BAL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Austin Martin</t>
+          <t>Samuel Basallo</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -17959,13 +19563,13 @@
         <v>1.5</v>
       </c>
       <c r="G53" t="n">
-        <v>-170</v>
+        <v>-185</v>
       </c>
       <c r="H53" t="n">
-        <v>0.6679</v>
+        <v>0.6848</v>
       </c>
       <c r="I53" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.0808</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -17976,10 +19580,10 @@
         <v>1</v>
       </c>
       <c r="L53" t="n">
-        <v>58.82</v>
+        <v>54.05</v>
       </c>
       <c r="M53" t="n">
-        <v>29.41</v>
+        <v>27.03</v>
       </c>
       <c r="N53" t="inlineStr"/>
     </row>
@@ -18001,7 +19605,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Adley Rutschman</t>
+          <t>Gunnar Henderson</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -18013,27 +19617,27 @@
         <v>1.5</v>
       </c>
       <c r="G54" t="n">
-        <v>-172</v>
+        <v>-125</v>
       </c>
       <c r="H54" t="n">
-        <v>0.6712</v>
+        <v>0.5917</v>
       </c>
       <c r="I54" t="n">
-        <v>0.0818</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>-100</v>
+        <v>80</v>
       </c>
       <c r="M54" t="n">
-        <v>-50</v>
+        <v>40</v>
       </c>
       <c r="N54" t="inlineStr"/>
     </row>
@@ -18050,12 +19654,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CHC vs WSN</t>
+          <t>MIN vs BAL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Keibert Ruiz</t>
+          <t>Adley Rutschman</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -18064,25 +19668,31 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G55" t="n">
-        <v>-1</v>
+        <v>-172</v>
       </c>
       <c r="H55" t="n">
-        <v>0.5118</v>
+        <v>0.6712</v>
       </c>
       <c r="I55" t="n">
-        <v>0.4948</v>
+        <v>0.0818</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>ODDS_ERR</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>3</v>
+      </c>
+      <c r="L55" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M55" t="n">
+        <v>-50</v>
+      </c>
       <c r="N55" t="inlineStr"/>
     </row>
     <row r="56">
@@ -18098,12 +19708,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MIN vs BAL</t>
+          <t>BAL vs MIN</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Samuel Basallo</t>
+          <t>Austin Martin</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -18115,13 +19725,13 @@
         <v>1.5</v>
       </c>
       <c r="G56" t="n">
-        <v>-185</v>
+        <v>-170</v>
       </c>
       <c r="H56" t="n">
-        <v>0.6848</v>
+        <v>0.6679</v>
       </c>
       <c r="I56" t="n">
-        <v>0.0808</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -18132,10 +19742,10 @@
         <v>1</v>
       </c>
       <c r="L56" t="n">
-        <v>54.05</v>
+        <v>58.82</v>
       </c>
       <c r="M56" t="n">
-        <v>27.03</v>
+        <v>29.41</v>
       </c>
       <c r="N56" t="inlineStr"/>
     </row>
@@ -18152,12 +19762,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MIL vs CWS</t>
+          <t>PHI vs TEX</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Miguel Vargas</t>
+          <t>Wyatt Langford</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -18169,28 +19779,22 @@
         <v>0.5</v>
       </c>
       <c r="G57" t="n">
-        <v>-145</v>
+        <v>-20</v>
       </c>
       <c r="H57" t="n">
-        <v>0.6219</v>
+        <v>0.6369</v>
       </c>
       <c r="I57" t="n">
-        <v>0.0713</v>
+        <v>0.2456</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M57" t="n">
-        <v>-50</v>
-      </c>
+          <t>ODDS_ERR</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
     </row>
     <row r="58">
@@ -18206,45 +19810,39 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MIL vs CWS</t>
+          <t>CHC vs WSN</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Andrew Benintendi</t>
+          <t>Keibert Ruiz</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F58" t="n">
         <v>0.5</v>
       </c>
       <c r="G58" t="n">
-        <v>-141.5</v>
+        <v>-1</v>
       </c>
       <c r="H58" t="n">
-        <v>0.6186</v>
+        <v>0.5118</v>
       </c>
       <c r="I58" t="n">
-        <v>0.0741</v>
+        <v>0.4948</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M58" t="n">
-        <v>-50</v>
-      </c>
+          <t>ODDS_ERR</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
     </row>
     <row r="59">
@@ -18260,12 +19858,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>NYM vs PIT</t>
+          <t>PIT vs NYM</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Spencer Horwitz</t>
+          <t>Francisco Lindor</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -18277,13 +19875,13 @@
         <v>0.5</v>
       </c>
       <c r="G59" t="n">
-        <v>-126</v>
+        <v>-180.5</v>
       </c>
       <c r="H59" t="n">
-        <v>0.5911999999999999</v>
+        <v>0.6811</v>
       </c>
       <c r="I59" t="n">
-        <v>0.0756</v>
+        <v>0.0843</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -18314,12 +19912,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MIN vs BAL</t>
+          <t>BOS vs CIN</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Gunnar Henderson</t>
+          <t>Ke'Bryan Hayes</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -18328,16 +19926,16 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G60" t="n">
-        <v>-125</v>
+        <v>120.5</v>
       </c>
       <c r="H60" t="n">
-        <v>0.5917</v>
+        <v>0.5485</v>
       </c>
       <c r="I60" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.1263</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -18348,10 +19946,10 @@
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>80</v>
+        <v>120.5</v>
       </c>
       <c r="M60" t="n">
-        <v>40</v>
+        <v>60.25</v>
       </c>
       <c r="N60" t="inlineStr"/>
     </row>
@@ -18373,7 +19971,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Alejandro Kirk</t>
+          <t>Ernie Clement</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -18385,27 +19983,27 @@
         <v>1.5</v>
       </c>
       <c r="G61" t="n">
-        <v>-157</v>
+        <v>-193</v>
       </c>
       <c r="H61" t="n">
-        <v>0.6521</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.0735</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L61" t="n">
-        <v>63.69</v>
+        <v>-100</v>
       </c>
       <c r="M61" t="n">
-        <v>31.85</v>
+        <v>-50</v>
       </c>
       <c r="N61" t="inlineStr"/>
     </row>
@@ -18422,44 +20020,44 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>OAK vs TOR</t>
+          <t>CLE vs SEA</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Nathan Lukes</t>
+          <t>Cal Raleigh</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G62" t="n">
-        <v>-170</v>
+        <v>-141</v>
       </c>
       <c r="H62" t="n">
-        <v>0.6636</v>
+        <v>0.7042</v>
       </c>
       <c r="I62" t="n">
-        <v>0.0742</v>
+        <v>0.1595</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K62" t="n">
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>58.82</v>
+        <v>-100</v>
       </c>
       <c r="M62" t="n">
-        <v>29.41</v>
+        <v>-50</v>
       </c>
       <c r="N62" t="inlineStr"/>
     </row>
@@ -18476,44 +20074,44 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ARI vs LAD</t>
+          <t>CLE vs SEA</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Shohei Ohtani</t>
+          <t>Randy Arozarena</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="G63" t="n">
-        <v>-140</v>
+        <v>-121</v>
       </c>
       <c r="H63" t="n">
-        <v>0.6245000000000001</v>
+        <v>0.616</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0799</v>
+        <v>0.1101</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K63" t="n">
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>71.43000000000001</v>
+        <v>-100</v>
       </c>
       <c r="M63" t="n">
-        <v>35.71</v>
+        <v>-50</v>
       </c>
       <c r="N63" t="inlineStr"/>
     </row>
@@ -18530,12 +20128,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>LAA vs HOU</t>
+          <t>MIA vs COL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Yainer Diaz</t>
+          <t>Edouard Julien</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -18544,16 +20142,16 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G64" t="n">
-        <v>-175</v>
+        <v>100</v>
       </c>
       <c r="H64" t="n">
-        <v>0.6797</v>
+        <v>0.5488</v>
       </c>
       <c r="I64" t="n">
-        <v>0.0856</v>
+        <v>0.0854</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -18561,13 +20159,13 @@
         </is>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>57.14</v>
+        <v>100</v>
       </c>
       <c r="M64" t="n">
-        <v>28.57</v>
+        <v>50</v>
       </c>
       <c r="N64" t="inlineStr"/>
     </row>
@@ -18584,12 +20182,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>LAA vs HOU</t>
+          <t>OAK vs TOR</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Yordan Alvarez</t>
+          <t>Nathan Lukes</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -18601,27 +20199,27 @@
         <v>1.5</v>
       </c>
       <c r="G65" t="n">
-        <v>-130</v>
+        <v>-170</v>
       </c>
       <c r="H65" t="n">
-        <v>0.6188</v>
+        <v>0.6636</v>
       </c>
       <c r="I65" t="n">
-        <v>0.0906</v>
+        <v>0.0742</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K65" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>-100</v>
+        <v>58.82</v>
       </c>
       <c r="M65" t="n">
-        <v>-50</v>
+        <v>29.41</v>
       </c>
       <c r="N65" t="inlineStr"/>
     </row>
@@ -18638,12 +20236,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NYY vs SFG</t>
+          <t>LAA vs HOU</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Yordan Alvarez</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -18655,27 +20253,27 @@
         <v>1.5</v>
       </c>
       <c r="G66" t="n">
-        <v>-320</v>
+        <v>-130</v>
       </c>
       <c r="H66" t="n">
-        <v>0.791</v>
+        <v>0.6188</v>
       </c>
       <c r="I66" t="n">
-        <v>0.0726</v>
+        <v>0.0906</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L66" t="n">
-        <v>31.25</v>
+        <v>-100</v>
       </c>
       <c r="M66" t="n">
-        <v>15.62</v>
+        <v>-50</v>
       </c>
       <c r="N66" t="inlineStr"/>
     </row>
@@ -18692,12 +20290,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MIA vs COL</t>
+          <t>LAA vs HOU</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Edouard Julien</t>
+          <t>Yainer Diaz</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -18706,16 +20304,16 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G67" t="n">
-        <v>100</v>
+        <v>-175</v>
       </c>
       <c r="H67" t="n">
-        <v>0.5488</v>
+        <v>0.6797</v>
       </c>
       <c r="I67" t="n">
-        <v>0.0854</v>
+        <v>0.0856</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -18723,13 +20321,13 @@
         </is>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" t="n">
-        <v>100</v>
+        <v>57.14</v>
       </c>
       <c r="M67" t="n">
-        <v>50</v>
+        <v>28.57</v>
       </c>
       <c r="N67" t="inlineStr"/>
     </row>
@@ -18746,44 +20344,44 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CLE vs SEA</t>
+          <t>ARI vs LAD</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Randy Arozarena</t>
+          <t>Shohei Ohtani</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="G68" t="n">
-        <v>-121</v>
+        <v>-140</v>
       </c>
       <c r="H68" t="n">
-        <v>0.616</v>
+        <v>0.6245000000000001</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1101</v>
+        <v>0.0799</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K68" t="n">
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>-100</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="M68" t="n">
-        <v>-50</v>
+        <v>35.71</v>
       </c>
       <c r="N68" t="inlineStr"/>
     </row>
@@ -18800,12 +20398,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>HOU vs LAA</t>
+          <t>OAK vs TOR</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Oswald Peraza</t>
+          <t>Alejandro Kirk</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -18814,16 +20412,16 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G69" t="n">
-        <v>-125</v>
+        <v>-157</v>
       </c>
       <c r="H69" t="n">
-        <v>0.6553</v>
+        <v>0.6521</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1438</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -18834,10 +20432,10 @@
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>80</v>
+        <v>63.69</v>
       </c>
       <c r="M69" t="n">
-        <v>40</v>
+        <v>31.85</v>
       </c>
       <c r="N69" t="inlineStr"/>
     </row>
@@ -18854,12 +20452,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>OAK vs TOR</t>
+          <t>NYY vs SFG</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Ernie Clement</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -18871,27 +20469,27 @@
         <v>1.5</v>
       </c>
       <c r="G70" t="n">
-        <v>-193</v>
+        <v>-320</v>
       </c>
       <c r="H70" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.791</v>
       </c>
       <c r="I70" t="n">
-        <v>0.0735</v>
+        <v>0.0726</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K70" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>-100</v>
+        <v>31.25</v>
       </c>
       <c r="M70" t="n">
-        <v>-50</v>
+        <v>15.62</v>
       </c>
       <c r="N70" t="inlineStr"/>
     </row>
@@ -18962,44 +20560,44 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CLE vs SEA</t>
+          <t>HOU vs LAA</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Cal Raleigh</t>
+          <t>Oswald Peraza</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F72" t="n">
         <v>0.5</v>
       </c>
       <c r="G72" t="n">
-        <v>-141</v>
+        <v>-125</v>
       </c>
       <c r="H72" t="n">
-        <v>0.7042</v>
+        <v>0.6553</v>
       </c>
       <c r="I72" t="n">
-        <v>0.1595</v>
+        <v>0.1438</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K72" t="n">
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>-100</v>
+        <v>80</v>
       </c>
       <c r="M72" t="n">
-        <v>-50</v>
+        <v>40</v>
       </c>
       <c r="N72" t="inlineStr"/>
     </row>
@@ -19662,12 +21260,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MIL vs CWS</t>
+          <t>MIN vs BAL</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Colson Montgomery</t>
+          <t>Pete Alonso</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -19676,16 +21274,16 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G85" t="n">
-        <v>-170</v>
+        <v>135</v>
       </c>
       <c r="H85" t="n">
-        <v>0.6704</v>
+        <v>0.47</v>
       </c>
       <c r="I85" t="n">
-        <v>0.0842</v>
+        <v>0.0717</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -19714,12 +21312,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>OAK vs TOR</t>
+          <t>NYY vs SFG</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Myles Straw</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -19728,16 +21326,16 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G86" t="n">
-        <v>-355</v>
+        <v>102</v>
       </c>
       <c r="H86" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.5429</v>
       </c>
       <c r="I86" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.0808</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -19766,30 +21364,30 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NYY vs SFG</t>
+          <t>TOR vs OAK</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Shea Langeliers</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G87" t="n">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="H87" t="n">
-        <v>0.5429</v>
+        <v>0.4855</v>
       </c>
       <c r="I87" t="n">
-        <v>0.0808</v>
+        <v>0.076</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -19818,12 +21416,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>TOR vs OAK</t>
+          <t>BAL vs MIN</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Shea Langeliers</t>
+          <t>Byron Buxton</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -19835,13 +21433,13 @@
         <v>1.5</v>
       </c>
       <c r="G88" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H88" t="n">
-        <v>0.4855</v>
+        <v>0.4823</v>
       </c>
       <c r="I88" t="n">
-        <v>0.076</v>
+        <v>0.0746</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -19870,12 +21468,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>BAL vs MIN</t>
+          <t>MIL vs CWS</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Byron Buxton</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -19884,16 +21482,16 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G89" t="n">
-        <v>129</v>
+        <v>-170</v>
       </c>
       <c r="H89" t="n">
-        <v>0.4823</v>
+        <v>0.6704</v>
       </c>
       <c r="I89" t="n">
-        <v>0.0746</v>
+        <v>0.0842</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -19922,12 +21520,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MIN vs BAL</t>
+          <t>NYM vs PIT</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Pete Alonso</t>
+          <t>Ryan O'Hearn</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -19939,13 +21537,13 @@
         <v>1.5</v>
       </c>
       <c r="G90" t="n">
-        <v>135</v>
+        <v>205</v>
       </c>
       <c r="H90" t="n">
-        <v>0.47</v>
+        <v>0.3854</v>
       </c>
       <c r="I90" t="n">
-        <v>0.0717</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -19974,12 +21572,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>OAK vs TOR</t>
+          <t>WSN vs CHC</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Ernie Clement</t>
+          <t>Dansby Swanson</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -19991,13 +21589,13 @@
         <v>1.5</v>
       </c>
       <c r="G91" t="n">
-        <v>-168</v>
+        <v>-162.5</v>
       </c>
       <c r="H91" t="n">
-        <v>0.6761</v>
+        <v>0.6579</v>
       </c>
       <c r="I91" t="n">
-        <v>0.0888</v>
+        <v>0.078</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -20026,30 +21624,30 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>BAL vs MIN</t>
+          <t>STL vs TBR</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Trevor Larnach</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G92" t="n">
-        <v>-115</v>
+        <v>-209</v>
       </c>
       <c r="H92" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.7207</v>
       </c>
       <c r="I92" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.0877</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -20078,12 +21676,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>STL vs TBR</t>
+          <t>COL vs MIA</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Connor Norby</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -20095,13 +21693,13 @@
         <v>1.5</v>
       </c>
       <c r="G93" t="n">
-        <v>-209</v>
+        <v>-196.5</v>
       </c>
       <c r="H93" t="n">
-        <v>0.7207</v>
+        <v>0.7072000000000001</v>
       </c>
       <c r="I93" t="n">
-        <v>0.0877</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -20130,12 +21728,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>COL vs MIA</t>
+          <t>OAK vs TOR</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Connor Norby</t>
+          <t>Ernie Clement</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -20147,13 +21745,13 @@
         <v>1.5</v>
       </c>
       <c r="G94" t="n">
-        <v>-196.5</v>
+        <v>-168</v>
       </c>
       <c r="H94" t="n">
-        <v>0.7072000000000001</v>
+        <v>0.6761</v>
       </c>
       <c r="I94" t="n">
-        <v>0.09030000000000001</v>
+        <v>0.0888</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -20182,30 +21780,30 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MIN vs BAL</t>
+          <t>COL vs MIA</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Taylor Ward</t>
+          <t>Xavier Edwards</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G95" t="n">
-        <v>-165</v>
+        <v>-170</v>
       </c>
       <c r="H95" t="n">
-        <v>0.6717</v>
+        <v>0.6768999999999999</v>
       </c>
       <c r="I95" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.0907</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -20234,12 +21832,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>COL vs MIA</t>
+          <t>OAK vs TOR</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Xavier Edwards</t>
+          <t>Myles Straw</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -20251,13 +21849,13 @@
         <v>1.5</v>
       </c>
       <c r="G96" t="n">
-        <v>-170</v>
+        <v>-355</v>
       </c>
       <c r="H96" t="n">
-        <v>0.6768999999999999</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="I96" t="n">
-        <v>0.0907</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -20291,7 +21889,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Dansby Swanson</t>
+          <t>Ian Happ</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -20303,13 +21901,13 @@
         <v>1.5</v>
       </c>
       <c r="G97" t="n">
-        <v>-162.5</v>
+        <v>-133</v>
       </c>
       <c r="H97" t="n">
-        <v>0.6579</v>
+        <v>0.6044</v>
       </c>
       <c r="I97" t="n">
-        <v>0.078</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -20338,30 +21936,30 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>NYM vs PIT</t>
+          <t>WSN vs CHC</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Ryan O'Hearn</t>
+          <t>Nico Hoerner</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F98" t="n">
         <v>1.5</v>
       </c>
       <c r="G98" t="n">
-        <v>205</v>
+        <v>-153</v>
       </c>
       <c r="H98" t="n">
-        <v>0.3854</v>
+        <v>0.6441</v>
       </c>
       <c r="I98" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.0794</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -20390,12 +21988,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>TOR vs OAK</t>
+          <t>BAL vs MIN</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Brent Rooker</t>
+          <t>Trevor Larnach</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -20404,16 +22002,16 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G99" t="n">
-        <v>166</v>
+        <v>-115</v>
       </c>
       <c r="H99" t="n">
-        <v>0.4369</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="I99" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -20442,30 +22040,30 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>NYM vs PIT</t>
+          <t>MIN vs BAL</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Jake Mangum</t>
+          <t>Taylor Ward</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F100" t="n">
         <v>0.5</v>
       </c>
       <c r="G100" t="n">
-        <v>130</v>
+        <v>-165</v>
       </c>
       <c r="H100" t="n">
-        <v>0.4946</v>
+        <v>0.6717</v>
       </c>
       <c r="I100" t="n">
-        <v>0.0934</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -20494,12 +22092,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>BOS vs CIN</t>
+          <t>NYY vs SFG</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Ke'Bryan Hayes</t>
+          <t>Casey Schmitt</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -20508,16 +22106,16 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G101" t="n">
-        <v>102</v>
+        <v>-186</v>
       </c>
       <c r="H101" t="n">
-        <v>0.5485</v>
+        <v>0.724</v>
       </c>
       <c r="I101" t="n">
-        <v>0.0895</v>
+        <v>0.1165</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -20546,12 +22144,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>WSN vs CHC</t>
+          <t>TBR vs STL</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Ian Happ</t>
+          <t>Jordan Walker</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -20563,13 +22161,13 @@
         <v>1.5</v>
       </c>
       <c r="G102" t="n">
-        <v>-133</v>
+        <v>-290</v>
       </c>
       <c r="H102" t="n">
-        <v>0.6044</v>
+        <v>0.7907999999999999</v>
       </c>
       <c r="I102" t="n">
-        <v>0.07439999999999999</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -20598,12 +22196,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>WSN vs CHC</t>
+          <t>CWS vs MIL</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Michael Busch</t>
+          <t>Brandon Lockridge</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -20612,16 +22210,16 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G103" t="n">
-        <v>-2</v>
+        <v>-106</v>
       </c>
       <c r="H103" t="n">
-        <v>0.5424</v>
+        <v>0.6246</v>
       </c>
       <c r="I103" t="n">
-        <v>0.5093</v>
+        <v>0.1446</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -20655,25 +22253,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Alex Bregman</t>
+          <t>Michael Busch</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F104" t="n">
         <v>1.5</v>
       </c>
       <c r="G104" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H104" t="n">
-        <v>0.4486</v>
+        <v>0.5424</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4313</v>
+        <v>0.5093</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -20702,12 +22300,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>TOR vs OAK</t>
+          <t>WSN vs CHC</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Nick Kurtz</t>
+          <t>Alex Bregman</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -20719,13 +22317,13 @@
         <v>1.5</v>
       </c>
       <c r="G105" t="n">
-        <v>141</v>
+        <v>-1</v>
       </c>
       <c r="H105" t="n">
-        <v>0.5341</v>
+        <v>0.4486</v>
       </c>
       <c r="I105" t="n">
-        <v>0.1437</v>
+        <v>0.4313</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -20754,30 +22352,30 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>COL vs MIA</t>
+          <t>TOR vs OAK</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Nick Kurtz</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G106" t="n">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="H106" t="n">
-        <v>0.4978</v>
+        <v>0.5341</v>
       </c>
       <c r="I106" t="n">
-        <v>0.1293</v>
+        <v>0.1437</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -20806,30 +22404,30 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>TEX vs PHI</t>
+          <t>COL vs MIA</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Kyle Schwarber</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F107" t="n">
         <v>0.5</v>
       </c>
       <c r="G107" t="n">
-        <v>-160</v>
+        <v>153</v>
       </c>
       <c r="H107" t="n">
-        <v>0.6923</v>
+        <v>0.4978</v>
       </c>
       <c r="I107" t="n">
-        <v>0.1205</v>
+        <v>0.1293</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -20858,30 +22456,30 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>TBR vs STL</t>
+          <t>TEX vs PHI</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Jordan Walker</t>
+          <t>Kyle Schwarber</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G108" t="n">
-        <v>-290</v>
+        <v>-160</v>
       </c>
       <c r="H108" t="n">
-        <v>0.7907999999999999</v>
+        <v>0.6923</v>
       </c>
       <c r="I108" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.1205</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -20967,25 +22565,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>James Wood</t>
+          <t>Jacob Young</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G110" t="n">
-        <v>158.5</v>
+        <v>-106.5</v>
       </c>
       <c r="H110" t="n">
-        <v>0.4611</v>
+        <v>0.5992</v>
       </c>
       <c r="I110" t="n">
-        <v>0.0968</v>
+        <v>0.1177</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -21014,12 +22612,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>BAL vs MIN</t>
+          <t>CHC vs WSN</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Matt Wallner</t>
+          <t>James Wood</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -21028,16 +22626,16 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G111" t="n">
-        <v>-125</v>
+        <v>158.5</v>
       </c>
       <c r="H111" t="n">
-        <v>0.6262</v>
+        <v>0.4611</v>
       </c>
       <c r="I111" t="n">
-        <v>0.1115</v>
+        <v>0.0968</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -21066,12 +22664,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>NYM vs PIT</t>
+          <t>BAL vs MIN</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Brandon Lowe</t>
+          <t>Matt Wallner</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -21086,10 +22684,10 @@
         <v>-125</v>
       </c>
       <c r="H112" t="n">
-        <v>0.6173999999999999</v>
+        <v>0.6262</v>
       </c>
       <c r="I112" t="n">
-        <v>0.1027</v>
+        <v>0.1115</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -21118,30 +22716,30 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>NYY vs SFG</t>
+          <t>NYM vs PIT</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Casey Schmitt</t>
+          <t>Brandon Lowe</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G113" t="n">
-        <v>-186</v>
+        <v>-125</v>
       </c>
       <c r="H113" t="n">
-        <v>0.724</v>
+        <v>0.6173999999999999</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1165</v>
+        <v>0.1027</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -21170,12 +22768,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>STL vs TBR</t>
+          <t>NYM vs PIT</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Jake Mangum</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -21184,16 +22782,16 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G114" t="n">
-        <v>-350</v>
+        <v>130</v>
       </c>
       <c r="H114" t="n">
-        <v>0.827</v>
+        <v>0.4946</v>
       </c>
       <c r="I114" t="n">
-        <v>0.0929</v>
+        <v>0.0934</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -21222,12 +22820,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>COL vs MIA</t>
+          <t>STL vs TBR</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Otto Lopez</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -21239,13 +22837,13 @@
         <v>1.5</v>
       </c>
       <c r="G115" t="n">
-        <v>-155</v>
+        <v>-350</v>
       </c>
       <c r="H115" t="n">
-        <v>0.6829</v>
+        <v>0.827</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1141</v>
+        <v>0.0929</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -21274,12 +22872,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>CHC vs WSN</t>
+          <t>COL vs MIA</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Jacob Young</t>
+          <t>Otto Lopez</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -21288,16 +22886,16 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G116" t="n">
-        <v>-106.5</v>
+        <v>-155</v>
       </c>
       <c r="H116" t="n">
-        <v>0.5992</v>
+        <v>0.6829</v>
       </c>
       <c r="I116" t="n">
-        <v>0.1177</v>
+        <v>0.1141</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -21326,12 +22924,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>WSN vs CHC</t>
+          <t>BOS vs CIN</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Nico Hoerner</t>
+          <t>Ke'Bryan Hayes</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -21340,16 +22938,16 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G117" t="n">
-        <v>-153</v>
+        <v>102</v>
       </c>
       <c r="H117" t="n">
-        <v>0.6441</v>
+        <v>0.5485</v>
       </c>
       <c r="I117" t="n">
-        <v>0.0794</v>
+        <v>0.0895</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -21360,6 +22958,110 @@
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>TOR vs OAK</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Brent Rooker</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G118" t="n">
+        <v>166</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.4369</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>CWS vs MIL</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>David Hamilton</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G119" t="n">
+        <v>-125</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.6313</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.1166</v>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
         </is>
@@ -21376,7 +23078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N46"/>
+  <dimension ref="A1:N48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22898,12 +24600,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>TOR vs OAK</t>
+          <t>NYY vs SFG</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Luis Severino</t>
+          <t>Robbie Ray</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -22912,16 +24614,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="G29" t="n">
-        <v>-202.5</v>
+        <v>100.5</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8656</v>
+        <v>0.738</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2444</v>
+        <v>0.2774</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -22929,13 +24631,13 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L29" t="n">
-        <v>49.38</v>
+        <v>100.5</v>
       </c>
       <c r="M29" t="n">
-        <v>24.69</v>
+        <v>50.25</v>
       </c>
       <c r="N29" t="inlineStr"/>
     </row>
@@ -23114,12 +24816,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NYY vs SFG</t>
+          <t>TOR vs OAK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Robbie Ray</t>
+          <t>Luis Severino</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -23128,16 +24830,16 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="G33" t="n">
-        <v>100.5</v>
+        <v>-202.5</v>
       </c>
       <c r="H33" t="n">
-        <v>0.738</v>
+        <v>0.8656</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2774</v>
+        <v>0.2444</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -23145,13 +24847,13 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L33" t="n">
-        <v>100.5</v>
+        <v>49.38</v>
       </c>
       <c r="M33" t="n">
-        <v>50.25</v>
+        <v>24.69</v>
       </c>
       <c r="N33" t="inlineStr"/>
     </row>
@@ -23222,12 +24924,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MIA vs COL</t>
+          <t>BAL vs MIN</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Michael Lorenzen</t>
+          <t>Taj Bradley</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -23236,16 +24938,16 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="G35" t="n">
-        <v>108</v>
+        <v>-154</v>
       </c>
       <c r="H35" t="n">
-        <v>0.6125</v>
+        <v>0.6834</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1676</v>
+        <v>0.1233</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -23274,12 +24976,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>TEX vs PHI</t>
+          <t>ATL vs KCR</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -23291,13 +24993,13 @@
         <v>15.5</v>
       </c>
       <c r="G36" t="n">
-        <v>-105</v>
+        <v>-121</v>
       </c>
       <c r="H36" t="n">
-        <v>0.6395</v>
+        <v>0.6596</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1662</v>
+        <v>0.1486</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -23326,12 +25028,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MIN vs BAL</t>
+          <t>MIA vs COL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Kyle Bradish</t>
+          <t>Michael Lorenzen</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -23343,13 +25045,13 @@
         <v>15.5</v>
       </c>
       <c r="G37" t="n">
-        <v>123.5</v>
+        <v>108</v>
       </c>
       <c r="H37" t="n">
-        <v>0.6048</v>
+        <v>0.6125</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1899</v>
+        <v>0.1676</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -23378,12 +25080,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BOS vs CIN</t>
+          <t>TEX vs PHI</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Brady Singer</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -23395,13 +25097,13 @@
         <v>15.5</v>
       </c>
       <c r="G38" t="n">
-        <v>106</v>
+        <v>-105</v>
       </c>
       <c r="H38" t="n">
-        <v>0.6352</v>
+        <v>0.6395</v>
       </c>
       <c r="I38" t="n">
-        <v>0.188</v>
+        <v>0.1662</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -23430,12 +25132,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>WSN vs CHC</t>
+          <t>MIN vs BAL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Cade Horton</t>
+          <t>Kyle Bradish</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -23447,13 +25149,13 @@
         <v>15.5</v>
       </c>
       <c r="G39" t="n">
-        <v>141.5</v>
+        <v>123.5</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6026</v>
+        <v>0.6048</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2149</v>
+        <v>0.1899</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -23482,12 +25184,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NYM vs PIT</t>
+          <t>BOS vs CIN</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Mitch Keller</t>
+          <t>Brady Singer</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -23499,13 +25201,13 @@
         <v>15.5</v>
       </c>
       <c r="G40" t="n">
-        <v>120.5</v>
+        <v>106</v>
       </c>
       <c r="H40" t="n">
-        <v>0.6752</v>
+        <v>0.6352</v>
       </c>
       <c r="I40" t="n">
-        <v>0.2583</v>
+        <v>0.188</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -23534,12 +25236,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>HOU vs LAA</t>
+          <t>PIT vs NYM</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Reid Detmers</t>
+          <t>David Peterson</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -23548,16 +25250,16 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="G41" t="n">
-        <v>-147.5</v>
+        <v>110</v>
       </c>
       <c r="H41" t="n">
-        <v>0.7408</v>
+        <v>0.6647999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1903</v>
+        <v>0.2286</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -23586,12 +25288,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>STL vs TBR</t>
+          <t>NYM vs PIT</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Joe Boyle</t>
+          <t>Mitch Keller</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -23600,16 +25302,16 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="G42" t="n">
-        <v>-128.5</v>
+        <v>120.5</v>
       </c>
       <c r="H42" t="n">
-        <v>0.789</v>
+        <v>0.6752</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2662</v>
+        <v>0.2583</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -23638,12 +25340,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>TOR vs OAK</t>
+          <t>HOU vs LAA</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Jeffrey Springs</t>
+          <t>Reid Detmers</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -23655,13 +25357,13 @@
         <v>14.5</v>
       </c>
       <c r="G43" t="n">
-        <v>-165</v>
+        <v>-147.5</v>
       </c>
       <c r="H43" t="n">
-        <v>0.7914</v>
+        <v>0.7408</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2107</v>
+        <v>0.1903</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -23690,12 +25392,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ATL vs KCR</t>
+          <t>STL vs TBR</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>Joe Boyle</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -23704,16 +25406,16 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="G44" t="n">
-        <v>-121</v>
+        <v>-128.5</v>
       </c>
       <c r="H44" t="n">
-        <v>0.6596</v>
+        <v>0.789</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1486</v>
+        <v>0.2662</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -23742,12 +25444,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PIT vs NYM</t>
+          <t>TOR vs OAK</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>David Peterson</t>
+          <t>Jeffrey Springs</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -23756,16 +25458,16 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="G45" t="n">
-        <v>110</v>
+        <v>-165</v>
       </c>
       <c r="H45" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.7914</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2286</v>
+        <v>0.2107</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -23794,12 +25496,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BAL vs MIN</t>
+          <t>MIL vs CWS</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Taj Bradley</t>
+          <t>Sean Burke</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -23811,13 +25513,13 @@
         <v>14.5</v>
       </c>
       <c r="G46" t="n">
-        <v>-154</v>
+        <v>-106</v>
       </c>
       <c r="H46" t="n">
-        <v>0.6834</v>
+        <v>0.8197</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1233</v>
+        <v>0.3432</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -23828,6 +25530,110 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Add opp_bb_pct to pitcher outs, bullpen features to totals, bullpen availability utility; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Use confirmed SP from lineup card, fall back to probable pitcher; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Cap pitcher outs to 1 pick per game (not per pitcher); Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Gate all 5 models on confirmed starting pitchers; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>WSN vs CHC</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Cade Horton</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G47" t="n">
+        <v>141.5</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.6026</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.2149</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Add opp_bb_pct to pitcher outs, bullpen features to totals, bullpen availability utility; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Use confirmed SP from lineup card, fall back to probable pitcher; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Cap pitcher outs to 1 pick per game (not per pitcher); Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Gate all 5 models on confirmed starting pitchers; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>NYY vs SFG</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Tyler Mahle</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-165.5</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.7963</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.2191</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Add opp_bb_pct to pitcher outs, bullpen features to totals, bullpen availability utility; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Use confirmed SP from lineup card, fall back to probable pitcher; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Cap pitcher outs to 1 pick per game (not per pitcher); Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Gate all 5 models on confirmed starting pitchers; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
         </is>
@@ -23844,7 +25650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24040,12 +25846,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLE @ SEA</t>
+          <t>ARI @ LAD</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CLE @ SEA</t>
+          <t>ARI @ LAD</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -24055,29 +25861,29 @@
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>-155</v>
+        <v>-105</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4113</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1552</v>
+        <v>-0.4852</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>away_1st=1 home_1st=1</t>
+          <t>away_1st=0 home_1st=0</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-100</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-50</v>
+        <v>47.62</v>
       </c>
       <c r="N4" t="inlineStr"/>
     </row>
@@ -24094,28 +25900,28 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARI @ LAD</t>
+          <t>CLE @ SEA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ARI @ LAD</t>
+          <t>CLE @ SEA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>YRFI</t>
+          <t>NRFI</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>-119</v>
+        <v>-155</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0.4113</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4875</v>
+        <v>-0.1552</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -24124,7 +25930,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>away_1st=0 home_1st=0</t>
+          <t>away_1st=1 home_1st=1</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -24148,28 +25954,28 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PIT @ NYM</t>
+          <t>ARI @ LAD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PIT @ NYM</t>
+          <t>ARI @ LAD</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NRFI</t>
+          <t>YRFI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>-162</v>
+        <v>-119</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5818</v>
+        <v>0.4875</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -24178,7 +25984,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>away_1st=2 home_1st=5</t>
+          <t>away_1st=0 home_1st=0</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -24202,12 +26008,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DET @ SDP</t>
+          <t>PIT @ NYM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>DET @ SDP</t>
+          <t>PIT @ NYM</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -24220,10 +26026,10 @@
         <v>-162</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4113</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1628</v>
+        <v>-0.5818</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -24232,7 +26038,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>away_1st=4 home_1st=0</t>
+          <t>away_1st=2 home_1st=5</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -24256,28 +26062,28 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TBR @ STL</t>
+          <t>DET @ SDP</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>TBR @ STL</t>
+          <t>DET @ SDP</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>YRFI</t>
+          <t>NRFI</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>100</v>
+        <v>-162</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0.4113</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5306</v>
+        <v>-0.1628</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -24286,7 +26092,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>away_1st=0 home_1st=0</t>
+          <t>away_1st=4 home_1st=0</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -24310,12 +26116,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TEX @ PHI</t>
+          <t>TBR @ STL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>TEX @ PHI</t>
+          <t>TBR @ STL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -24325,29 +26131,29 @@
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>-106</v>
+        <v>100</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5887</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1079</v>
+        <v>0.5306</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>away_1st=0 home_1st=2</t>
+          <t>away_1st=0 home_1st=0</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>94.34</v>
+        <v>-100</v>
       </c>
       <c r="M9" t="n">
-        <v>47.17</v>
+        <v>-50</v>
       </c>
       <c r="N9" t="inlineStr"/>
     </row>
@@ -24364,12 +26170,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DET @ SDP</t>
+          <t>TEX @ PHI</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DET @ SDP</t>
+          <t>TEX @ PHI</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -24379,13 +26185,13 @@
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>118</v>
+        <v>-106</v>
       </c>
       <c r="H10" t="n">
         <v>0.5887</v>
       </c>
       <c r="I10" t="n">
-        <v>0.161</v>
+        <v>0.1079</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -24394,14 +26200,14 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>away_1st=4 home_1st=0</t>
+          <t>away_1st=0 home_1st=2</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>118</v>
+        <v>94.34</v>
       </c>
       <c r="M10" t="n">
-        <v>59</v>
+        <v>47.17</v>
       </c>
       <c r="N10" t="inlineStr"/>
     </row>
@@ -24418,28 +26224,28 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ARI @ LAD</t>
+          <t>DET @ SDP</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ARI @ LAD</t>
+          <t>DET @ SDP</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>NRFI</t>
+          <t>YRFI</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>-105</v>
+        <v>118</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.5887</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4852</v>
+        <v>0.161</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -24448,14 +26254,14 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>away_1st=0 home_1st=0</t>
+          <t>away_1st=4 home_1st=0</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>95.23999999999999</v>
+        <v>118</v>
       </c>
       <c r="M11" t="n">
-        <v>47.62</v>
+        <v>59</v>
       </c>
       <c r="N11" t="inlineStr"/>
     </row>
@@ -24472,12 +26278,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CWS @ MIL</t>
+          <t>BOS @ CIN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CWS @ MIL</t>
+          <t>BOS @ CIN</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -24487,29 +26293,29 @@
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>-129</v>
+        <v>-155</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>0.3829</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5273</v>
+        <v>-0.1836</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>away_1st=1 home_1st=0</t>
+          <t>away_1st=0 home_1st=0</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-100</v>
+        <v>64.52</v>
       </c>
       <c r="M12" t="n">
-        <v>-50</v>
+        <v>32.26</v>
       </c>
       <c r="N12" t="inlineStr"/>
     </row>
@@ -24526,28 +26332,28 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LAA @ HOU</t>
+          <t>CWS @ MIL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LAA @ HOU</t>
+          <t>CWS @ MIL</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>YRFI</t>
+          <t>NRFI</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>102</v>
+        <v>-129</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5347</v>
+        <v>-0.5273</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -24556,7 +26362,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>away_1st=0 home_1st=0</t>
+          <t>away_1st=1 home_1st=0</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -24580,12 +26386,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>WSN @ CHC</t>
+          <t>LAA @ HOU</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>WSN @ CHC</t>
+          <t>LAA @ HOU</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -24595,13 +26401,13 @@
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5887</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1338</v>
+        <v>0.5347</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -24634,12 +26440,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MIN @ BAL</t>
+          <t>WSN @ CHC</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MIN @ BAL</t>
+          <t>WSN @ CHC</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -24649,13 +26455,13 @@
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>-112</v>
+        <v>106</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0.5887</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5061</v>
+        <v>0.1338</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -24688,12 +26494,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CWS @ MIL</t>
+          <t>MIN @ BAL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CWS @ MIL</t>
+          <t>MIN @ BAL</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -24703,29 +26509,29 @@
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>-102</v>
+        <v>-112</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5314</v>
+        <v>0.5061</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>away_1st=1 home_1st=0</t>
+          <t>away_1st=0 home_1st=0</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>98.04000000000001</v>
+        <v>-100</v>
       </c>
       <c r="M16" t="n">
-        <v>49.02</v>
+        <v>-50</v>
       </c>
       <c r="N16" t="inlineStr"/>
     </row>
@@ -24742,12 +26548,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PIT @ NYM</t>
+          <t>CWS @ MIL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>PIT @ NYM</t>
+          <t>CWS @ MIL</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -24757,13 +26563,13 @@
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
-        <v>120</v>
+        <v>-102</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5746</v>
+        <v>0.5314</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -24772,14 +26578,14 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>away_1st=2 home_1st=5</t>
+          <t>away_1st=1 home_1st=0</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>120</v>
+        <v>98.04000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>60</v>
+        <v>49.02</v>
       </c>
       <c r="N17" t="inlineStr"/>
     </row>
@@ -24796,28 +26602,28 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BOS @ CIN</t>
+          <t>PIT @ NYM</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>BOS @ CIN</t>
+          <t>PIT @ NYM</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>NRFI</t>
+          <t>YRFI</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>-155</v>
+        <v>120</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3829</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1836</v>
+        <v>0.5746</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -24826,14 +26632,14 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>away_1st=0 home_1st=0</t>
+          <t>away_1st=2 home_1st=5</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>64.52</v>
+        <v>120</v>
       </c>
       <c r="M18" t="n">
-        <v>32.26</v>
+        <v>60</v>
       </c>
       <c r="N18" t="inlineStr"/>
     </row>
@@ -24904,28 +26710,28 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>OAK @ TOR</t>
+          <t>LAA @ HOU</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>OAK @ TOR</t>
+          <t>LAA @ HOU</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>NRFI</t>
+          <t>YRFI</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
-        <v>-109</v>
+        <v>-100</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4113</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0756</v>
+        <v>0.5306</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -24934,14 +26740,14 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>away_1st=0 home_1st=0</t>
+          <t>away_1st=1 home_1st=1</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>91.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="M20" t="n">
-        <v>45.87</v>
+        <v>50</v>
       </c>
       <c r="N20" t="inlineStr"/>
     </row>
@@ -24958,28 +26764,28 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>LAA @ HOU</t>
+          <t>OAK @ TOR</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LAA @ HOU</t>
+          <t>OAK @ TOR</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>YRFI</t>
+          <t>NRFI</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
-        <v>-100</v>
+        <v>-109</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0.4113</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5306</v>
+        <v>-0.0756</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -24988,14 +26794,14 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>away_1st=1 home_1st=1</t>
+          <t>away_1st=0 home_1st=0</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>100</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>50</v>
+        <v>45.87</v>
       </c>
       <c r="N21" t="inlineStr"/>
     </row>
@@ -25012,12 +26818,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>KCR @ ATL</t>
+          <t>NYY @ SFG</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>KCR @ ATL</t>
+          <t>NYY @ SFG</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -25027,29 +26833,29 @@
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
-        <v>110</v>
+        <v>-102</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5887</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1428</v>
+        <v>0.5239</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>away_1st=0 home_1st=1</t>
+          <t>away_1st=0 home_1st=0</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>110</v>
+        <v>-100</v>
       </c>
       <c r="M22" t="n">
-        <v>55</v>
+        <v>-50</v>
       </c>
       <c r="N22" t="inlineStr"/>
     </row>
@@ -25066,12 +26872,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NYY @ SFG</t>
+          <t>KCR @ ATL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NYY @ SFG</t>
+          <t>KCR @ ATL</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -25081,29 +26887,29 @@
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
-        <v>-102</v>
+        <v>110</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0.5887</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5239</v>
+        <v>0.1428</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>away_1st=0 home_1st=0</t>
+          <t>away_1st=0 home_1st=1</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>-100</v>
+        <v>110</v>
       </c>
       <c r="M23" t="n">
-        <v>-50</v>
+        <v>55</v>
       </c>
       <c r="N23" t="inlineStr"/>
     </row>
@@ -25174,12 +26980,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TEX @ PHI</t>
+          <t>CWS @ MIL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>TEX @ PHI</t>
+          <t>CWS @ MIL</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -25189,13 +26995,13 @@
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
-        <v>-106</v>
+        <v>-107</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5704</v>
+        <v>0.5887</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0887</v>
+        <v>0.1026</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -25624,12 +27430,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>OAK @ TOR</t>
+          <t>TEX @ PHI</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>OAK @ TOR</t>
+          <t>TEX @ PHI</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -25639,13 +27445,13 @@
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
-        <v>-121.5</v>
+        <v>-106</v>
       </c>
       <c r="H34" t="n">
-        <v>0.5887</v>
+        <v>0.5704</v>
       </c>
       <c r="I34" t="n">
-        <v>0.075</v>
+        <v>0.0887</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -25661,6 +27467,156 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>OAK @ TOR</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>OAK @ TOR</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>YRFI</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="n">
+        <v>-121.5</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.5887</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix NRFI scoreboard period param and Discord embed truncation; Fix NRFI odds: parse from scoreboard markets instead of props endpoint; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Gate NRFI scoring on confirmed lineups, consistent with other models; Fix 04_export_nrfi.py DataFrame iteration and lineup format bugs; Fix API crash guards and FanGraphs splits method errors; Add NRFI/YRFI fifth model and rebuild all four existing models; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>NYY @ SFG</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NYY @ SFG</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>YRFI</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="n">
+        <v>-107</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.5158</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix NRFI scoreboard period param and Discord embed truncation; Fix NRFI odds: parse from scoreboard markets instead of props endpoint; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Gate NRFI scoring on confirmed lineups, consistent with other models; Fix 04_export_nrfi.py DataFrame iteration and lineup format bugs; Fix API crash guards and FanGraphs splits method errors; Add NRFI/YRFI fifth model and rebuild all four existing models; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>DET @ SDP</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>DET @ SDP</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>YRFI</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.5887</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.0872</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix NRFI scoreboard period param and Discord embed truncation; Fix NRFI odds: parse from scoreboard markets instead of props endpoint; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Gate NRFI scoring on confirmed lineups, consistent with other models; Fix 04_export_nrfi.py DataFrame iteration and lineup format bugs; Fix API crash guards and FanGraphs splits method errors; Add NRFI/YRFI fifth model and rebuild all four existing models; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tracking/picks.xlsx
+++ b/tracking/picks.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N248"/>
+  <dimension ref="A1:N259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13575,6 +13575,578 @@
       <c r="N248" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix NRFI scoreboard period param and Discord embed truncation; Fix NRFI odds: parse from scoreboard markets instead of props endpoint; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Gate NRFI scoring on confirmed lineups, consistent with other models; Fix 04_export_nrfi.py DataFrame iteration and lineup format bugs; Fix API crash guards and FanGraphs splits method errors; Add NRFI/YRFI fifth model and rebuild all four existing models; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>ARI @ LAD</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>ARI @ LAD</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F249" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G249" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H249" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="I249" t="n">
+        <v>0.3687</v>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr"/>
+      <c r="M249" t="inlineStr"/>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>DET @ SDP</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>DET @ SDP</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F250" t="n">
+        <v>8</v>
+      </c>
+      <c r="G250" t="n">
+        <v>-108</v>
+      </c>
+      <c r="H250" t="n">
+        <v>0.744</v>
+      </c>
+      <c r="I250" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr"/>
+      <c r="L250" t="inlineStr"/>
+      <c r="M250" t="inlineStr"/>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>SDP vs DET</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Matt Vierling</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F251" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G251" t="n">
+        <v>125</v>
+      </c>
+      <c r="H251" t="n">
+        <v>0.5705</v>
+      </c>
+      <c r="I251" t="n">
+        <v>0.1567</v>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr"/>
+      <c r="L251" t="inlineStr"/>
+      <c r="M251" t="inlineStr"/>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>ARI vs LAD</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Santiago Espinal</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F252" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G252" t="n">
+        <v>116</v>
+      </c>
+      <c r="H252" t="n">
+        <v>0.6064000000000001</v>
+      </c>
+      <c r="I252" t="n">
+        <v>0.1771</v>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr"/>
+      <c r="L252" t="inlineStr"/>
+      <c r="M252" t="inlineStr"/>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>SDP vs DET</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Jake Rogers</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F253" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G253" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H253" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="I253" t="n">
+        <v>0.1168</v>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr"/>
+      <c r="L253" t="inlineStr"/>
+      <c r="M253" t="inlineStr"/>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>LAD vs ARI</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Ketel Marte</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F254" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G254" t="n">
+        <v>137</v>
+      </c>
+      <c r="H254" t="n">
+        <v>0.4777</v>
+      </c>
+      <c r="I254" t="n">
+        <v>0.0814</v>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr"/>
+      <c r="L254" t="inlineStr"/>
+      <c r="M254" t="inlineStr"/>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>ARI vs LAD</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Miguel Rojas</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F255" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G255" t="n">
+        <v>116</v>
+      </c>
+      <c r="H255" t="n">
+        <v>0.5123</v>
+      </c>
+      <c r="I255" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr"/>
+      <c r="L255" t="inlineStr"/>
+      <c r="M255" t="inlineStr"/>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>LAD vs ARI</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Geraldo Perdomo</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F256" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G256" t="n">
+        <v>-155</v>
+      </c>
+      <c r="H256" t="n">
+        <v>0.6403</v>
+      </c>
+      <c r="I256" t="n">
+        <v>0.0761</v>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr"/>
+      <c r="L256" t="inlineStr"/>
+      <c r="M256" t="inlineStr"/>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>DET vs SDP</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Freddy Fermin</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F257" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G257" t="n">
+        <v>-105</v>
+      </c>
+      <c r="H257" t="n">
+        <v>0.5414</v>
+      </c>
+      <c r="I257" t="n">
+        <v>0.0701</v>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr"/>
+      <c r="L257" t="inlineStr"/>
+      <c r="M257" t="inlineStr"/>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>LAD vs ARI</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Pavin Smith</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F258" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G258" t="n">
+        <v>-124</v>
+      </c>
+      <c r="H258" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="I258" t="n">
+        <v>0.07389999999999999</v>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr"/>
+      <c r="L258" t="inlineStr"/>
+      <c r="M258" t="inlineStr"/>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>ARI vs LAD</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Mookie Betts</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F259" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G259" t="n">
+        <v>-134</v>
+      </c>
+      <c r="H259" t="n">
+        <v>0.6084000000000001</v>
+      </c>
+      <c r="I259" t="n">
+        <v>0.0746</v>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr"/>
+      <c r="L259" t="inlineStr"/>
+      <c r="M259" t="inlineStr"/>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
         </is>
       </c>
     </row>
@@ -15056,7 +15628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:N33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15198,44 +15770,44 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLE @ SEA</t>
+          <t>ARI @ LAD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CLE @ SEA</t>
+          <t>ARI @ LAD</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="G3" t="n">
-        <v>-121.5</v>
+        <v>-115</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8472</v>
+        <v>0.6322</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3241</v>
+        <v>0.1214</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K3" t="n">
         <v>10</v>
       </c>
       <c r="L3" t="n">
-        <v>82.3</v>
+        <v>-100</v>
       </c>
       <c r="M3" t="n">
-        <v>41.15</v>
+        <v>-50</v>
       </c>
       <c r="N3" t="inlineStr"/>
     </row>
@@ -15252,12 +15824,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TBR @ STL</t>
+          <t>CLE @ SEA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>TBR @ STL</t>
+          <t>CLE @ SEA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -15266,16 +15838,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="G4" t="n">
-        <v>-110</v>
+        <v>-121.5</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7002</v>
+        <v>0.8472</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1997</v>
+        <v>0.3241</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -15283,13 +15855,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="L4" t="n">
-        <v>90.91</v>
+        <v>82.3</v>
       </c>
       <c r="M4" t="n">
-        <v>45.45</v>
+        <v>41.15</v>
       </c>
       <c r="N4" t="inlineStr"/>
     </row>
@@ -15320,16 +15892,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="G5" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="H5" t="n">
         <v>0.7002</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2111</v>
+        <v>0.1997</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -15340,10 +15912,10 @@
         <v>16</v>
       </c>
       <c r="L5" t="n">
-        <v>95.23999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="M5" t="n">
-        <v>47.62</v>
+        <v>45.45</v>
       </c>
       <c r="N5" t="inlineStr"/>
     </row>
@@ -15360,12 +15932,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CWS @ MIL</t>
+          <t>TBR @ STL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CWS @ MIL</t>
+          <t>TBR @ STL</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -15374,16 +15946,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
       <c r="G6" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7967</v>
+        <v>0.7002</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2967</v>
+        <v>0.2111</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -15394,10 +15966,10 @@
         <v>16</v>
       </c>
       <c r="L6" t="n">
-        <v>90.91</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>45.45</v>
+        <v>47.62</v>
       </c>
       <c r="N6" t="inlineStr"/>
     </row>
@@ -15414,30 +15986,30 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BOS @ CIN</t>
+          <t>CWS @ MIL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BOS @ CIN</t>
+          <t>CWS @ MIL</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="G7" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5555</v>
+        <v>0.7967</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0663</v>
+        <v>0.2967</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -15445,13 +16017,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="L7" t="n">
-        <v>95.23999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="M7" t="n">
-        <v>47.62</v>
+        <v>45.45</v>
       </c>
       <c r="N7" t="inlineStr"/>
     </row>
@@ -15478,34 +16050,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>-115</v>
+        <v>-105</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5835</v>
+        <v>0.5555</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0727</v>
+        <v>0.0663</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K8" t="n">
         <v>3</v>
       </c>
       <c r="L8" t="n">
-        <v>-100</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-50</v>
+        <v>47.62</v>
       </c>
       <c r="N8" t="inlineStr"/>
     </row>
@@ -15522,30 +16094,30 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ARI @ LAD</t>
+          <t>BOS @ CIN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ARI @ LAD</t>
+          <t>BOS @ CIN</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G9" t="n">
         <v>-115</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6322</v>
+        <v>0.5835</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1214</v>
+        <v>0.0727</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -15553,7 +16125,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
         <v>-100</v>
@@ -16008,12 +16580,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>COL @ MIA</t>
+          <t>KCR @ ATL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>COL @ MIA</t>
+          <t>KCR @ ATL</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -16025,13 +16597,13 @@
         <v>7.5</v>
       </c>
       <c r="G18" t="n">
-        <v>-112.5</v>
+        <v>-100</v>
       </c>
       <c r="H18" t="n">
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4946</v>
+        <v>0.5231</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -16039,7 +16611,7 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L18" t="n">
         <v>-100</v>
@@ -16062,12 +16634,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>KCR @ ATL</t>
+          <t>NYY @ SFG</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>KCR @ ATL</t>
+          <t>NYY @ SFG</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -16076,16 +16648,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="G19" t="n">
-        <v>-100</v>
+        <v>-107</v>
       </c>
       <c r="H19" t="n">
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5231</v>
+        <v>0.5044</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -16093,7 +16665,7 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L19" t="n">
         <v>-100</v>
@@ -16116,12 +16688,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NYY @ SFG</t>
+          <t>OAK @ TOR</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NYY @ SFG</t>
+          <t>OAK @ TOR</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -16133,13 +16705,13 @@
         <v>8.5</v>
       </c>
       <c r="G20" t="n">
-        <v>-107</v>
+        <v>-118</v>
       </c>
       <c r="H20" t="n">
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5044</v>
+        <v>0.4838</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -16147,7 +16719,7 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L20" t="n">
         <v>-100</v>
@@ -16170,12 +16742,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>OAK @ TOR</t>
+          <t>COL @ MIA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>OAK @ TOR</t>
+          <t>COL @ MIA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -16184,16 +16756,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="G21" t="n">
-        <v>-118</v>
+        <v>-112.5</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4838</v>
+        <v>0.4946</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -16201,7 +16773,7 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L21" t="n">
         <v>-100</v>
@@ -16224,30 +16796,30 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CWS @ MIL</t>
+          <t>ARI @ LAD</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CWS @ MIL</t>
+          <t>ARI @ LAD</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="G22" t="n">
-        <v>-105</v>
+        <v>-115</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5642</v>
+        <v>0.875</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0751</v>
+        <v>0.3687</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -16702,20 +17274,20 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>8</v>
       </c>
       <c r="G31" t="n">
-        <v>-115</v>
+        <v>-105</v>
       </c>
       <c r="H31" t="n">
-        <v>0.575</v>
+        <v>0.5642</v>
       </c>
       <c r="I31" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.0751</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -16726,6 +17298,110 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
+        <is>
+          <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CWS @ MIL</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CWS @ MIL</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>8</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.06419999999999999</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>DET @ SDP</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>DET @ SDP</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>8</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-108</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.744</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
         <is>
           <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
         </is>
@@ -16742,7 +17418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N119"/>
+  <dimension ref="A1:N128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17256,12 +17932,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TBR vs STL</t>
+          <t>MIN vs BAL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Masyn Winn</t>
+          <t>Colton Cowser</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -17273,22 +17949,28 @@
         <v>0.5</v>
       </c>
       <c r="G10" t="n">
-        <v>-20</v>
+        <v>250</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.5614</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1919</v>
+        <v>0.2085</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>ODDS_ERR</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-50</v>
+      </c>
       <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -17304,12 +17986,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BAL vs MIN</t>
+          <t>TBR vs STL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Matt Wallner</t>
+          <t>Masyn Winn</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -17321,28 +18003,22 @@
         <v>0.5</v>
       </c>
       <c r="G11" t="n">
-        <v>-143.5</v>
+        <v>-20</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6172</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0706</v>
+        <v>0.1919</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M11" t="n">
-        <v>-50</v>
-      </c>
+          <t>ODDS_ERR</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -17358,12 +18034,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SDP vs DET</t>
+          <t>BAL vs MIN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Spencer Torkelson</t>
+          <t>Matt Wallner</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -17375,27 +18051,27 @@
         <v>0.5</v>
       </c>
       <c r="G12" t="n">
-        <v>-145</v>
+        <v>-143.5</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.6172</v>
       </c>
       <c r="I12" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0706</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>68.97</v>
+        <v>-100</v>
       </c>
       <c r="M12" t="n">
-        <v>34.48</v>
+        <v>-50</v>
       </c>
       <c r="N12" t="inlineStr"/>
     </row>
@@ -17412,44 +18088,44 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>STL vs TBR</t>
+          <t>SDP vs DET</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Carson Williams</t>
+          <t>Spencer Torkelson</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>0.5</v>
       </c>
       <c r="G13" t="n">
-        <v>110</v>
+        <v>-145</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5195</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>0.077</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>-100</v>
+        <v>68.97</v>
       </c>
       <c r="M13" t="n">
-        <v>-50</v>
+        <v>34.48</v>
       </c>
       <c r="N13" t="inlineStr"/>
     </row>
@@ -17466,30 +18142,30 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DET vs SDP</t>
+          <t>LAA vs HOU</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Manny Machado</t>
+          <t>Yainer Diaz</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G14" t="n">
-        <v>-164.5</v>
+        <v>-182</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6501</v>
+        <v>0.6797</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0707</v>
+        <v>0.077</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -17497,13 +18173,13 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>60.79</v>
+        <v>54.95</v>
       </c>
       <c r="M14" t="n">
-        <v>30.4</v>
+        <v>27.47</v>
       </c>
       <c r="N14" t="inlineStr"/>
     </row>
@@ -17525,7 +18201,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Ben Williamson</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -17534,16 +18210,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G15" t="n">
-        <v>119.5</v>
+        <v>-195.5</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5552</v>
+        <v>0.7428</v>
       </c>
       <c r="I15" t="n">
-        <v>0.131</v>
+        <v>0.1248</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -17574,12 +18250,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LAA vs HOU</t>
+          <t>STL vs TBR</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Yainer Diaz</t>
+          <t>Nick Fortes</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -17588,30 +18264,30 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G16" t="n">
-        <v>-182</v>
+        <v>119.5</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6797</v>
+        <v>0.5552</v>
       </c>
       <c r="I16" t="n">
-        <v>0.077</v>
+        <v>0.131</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L16" t="n">
-        <v>54.95</v>
+        <v>-100</v>
       </c>
       <c r="M16" t="n">
-        <v>27.47</v>
+        <v>-50</v>
       </c>
       <c r="N16" t="inlineStr"/>
     </row>
@@ -17628,45 +18304,39 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MIN vs BAL</t>
+          <t>BAL vs MIN</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Colton Cowser</t>
+          <t>Royce Lewis</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>0.5</v>
       </c>
       <c r="G17" t="n">
-        <v>250</v>
+        <v>-50</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5614</v>
+        <v>0.4602</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2085</v>
+        <v>0.2055</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M17" t="n">
-        <v>-50</v>
-      </c>
+          <t>ODDS_ERR</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -17682,12 +18352,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>HOU vs LAA</t>
+          <t>DET vs SDP</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Zach Neto</t>
+          <t>Manny Machado</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -17699,27 +18369,27 @@
         <v>0.5</v>
       </c>
       <c r="G18" t="n">
-        <v>-183.5</v>
+        <v>-164.5</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6847</v>
+        <v>0.6501</v>
       </c>
       <c r="I18" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.0707</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>-100</v>
+        <v>60.79</v>
       </c>
       <c r="M18" t="n">
-        <v>-50</v>
+        <v>30.4</v>
       </c>
       <c r="N18" t="inlineStr"/>
     </row>
@@ -17741,7 +18411,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Ben Williamson</t>
+          <t>Carson Williams</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -17750,16 +18420,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G19" t="n">
-        <v>-195.5</v>
+        <v>110</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7428</v>
+        <v>0.5195</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1248</v>
+        <v>0.077</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -17767,7 +18437,7 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>-100</v>
@@ -17790,39 +18460,45 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BAL vs MIN</t>
+          <t>CLE vs SEA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Royce Lewis</t>
+          <t>Cal Raleigh</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>0.5</v>
       </c>
       <c r="G20" t="n">
+        <v>-147.5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.7043</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M20" t="n">
         <v>-50</v>
       </c>
-      <c r="H20" t="n">
-        <v>0.4602</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.2055</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>ODDS_ERR</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -17838,12 +18514,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SEA vs CLE</t>
+          <t>LAD vs ARI</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Kyle Manzardo</t>
+          <t>Pavin Smith</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -17855,27 +18531,25 @@
         <v>0.5</v>
       </c>
       <c r="G21" t="n">
-        <v>-108</v>
+        <v>101</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6057</v>
+        <v>0.5637</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1269</v>
+        <v>0.1034</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
-        <v>92.59</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>46.3</v>
+        <v>0</v>
       </c>
       <c r="N21" t="inlineStr"/>
     </row>
@@ -17892,30 +18566,30 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BAL vs MIN</t>
+          <t>MIN vs BAL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Josh Bell</t>
+          <t>Gunnar Henderson</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G22" t="n">
-        <v>-52.5</v>
+        <v>-3.5</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4279</v>
+        <v>0.4083</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1718</v>
+        <v>0.3519</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -17940,12 +18614,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MIN vs BAL</t>
+          <t>SEA vs CLE</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Gunnar Henderson</t>
+          <t>Kyle Manzardo</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -17954,25 +18628,31 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.5</v>
+        <v>-108</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4083</v>
+        <v>0.6057</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3519</v>
+        <v>0.1269</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>ODDS_ERR</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>92.59</v>
+      </c>
+      <c r="M23" t="n">
+        <v>46.3</v>
+      </c>
       <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -18042,12 +18722,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>LAD vs ARI</t>
+          <t>CLE vs SEA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Pavin Smith</t>
+          <t>Randy Arozarena</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -18059,25 +18739,27 @@
         <v>0.5</v>
       </c>
       <c r="G25" t="n">
-        <v>101</v>
+        <v>-124</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5637</v>
+        <v>0.6155</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1034</v>
+        <v>0.1069</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>DNP</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>2</v>
+      </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>40.32</v>
       </c>
       <c r="N25" t="inlineStr"/>
     </row>
@@ -18094,12 +18776,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLE vs SEA</t>
+          <t>SEA vs CLE</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Randy Arozarena</t>
+          <t>Rhys Hoskins</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -18111,13 +18793,13 @@
         <v>0.5</v>
       </c>
       <c r="G26" t="n">
-        <v>-124</v>
+        <v>100</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6155</v>
+        <v>0.5556</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1069</v>
+        <v>0.094</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -18125,13 +18807,13 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L26" t="n">
-        <v>80.65000000000001</v>
+        <v>100</v>
       </c>
       <c r="M26" t="n">
-        <v>40.32</v>
+        <v>50</v>
       </c>
       <c r="N26" t="inlineStr"/>
     </row>
@@ -18153,7 +18835,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Rhys Hoskins</t>
+          <t>Gabriel Arias</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -18165,13 +18847,13 @@
         <v>0.5</v>
       </c>
       <c r="G27" t="n">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5556</v>
+        <v>0.5197000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>0.094</v>
+        <v>0.083</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -18179,13 +18861,13 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="M27" t="n">
-        <v>50</v>
+        <v>57.5</v>
       </c>
       <c r="N27" t="inlineStr"/>
     </row>
@@ -18202,44 +18884,44 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SEA vs CLE</t>
+          <t>ARI vs LAD</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Gabriel Arias</t>
+          <t>Miguel Rojas</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>0.5</v>
       </c>
       <c r="G28" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H28" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.5123</v>
       </c>
       <c r="I28" t="n">
-        <v>0.083</v>
+        <v>0.0765</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>115</v>
+        <v>-100</v>
       </c>
       <c r="M28" t="n">
-        <v>57.5</v>
+        <v>-50</v>
       </c>
       <c r="N28" t="inlineStr"/>
     </row>
@@ -18256,44 +18938,44 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ARI vs LAD</t>
+          <t>CLE vs SEA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Miguel Rojas</t>
+          <t>Dominic Canzone</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>0.5</v>
       </c>
       <c r="G29" t="n">
-        <v>113</v>
+        <v>-118</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5123</v>
+        <v>0.5725</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0765</v>
+        <v>0.0725</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L29" t="n">
-        <v>-100</v>
+        <v>84.75</v>
       </c>
       <c r="M29" t="n">
-        <v>-50</v>
+        <v>42.37</v>
       </c>
       <c r="N29" t="inlineStr"/>
     </row>
@@ -18310,30 +18992,30 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CLE vs SEA</t>
+          <t>LAA vs HOU</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Dominic Canzone</t>
+          <t>Yordan Alvarez</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G30" t="n">
-        <v>-118</v>
+        <v>-138</v>
       </c>
       <c r="H30" t="n">
-        <v>0.5725</v>
+        <v>0.6188</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0725</v>
+        <v>0.0769</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -18341,13 +19023,13 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>84.75</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="M30" t="n">
-        <v>42.37</v>
+        <v>36.23</v>
       </c>
       <c r="N30" t="inlineStr"/>
     </row>
@@ -18364,12 +19046,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>LAA vs HOU</t>
+          <t>ARI vs LAD</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Yordan Alvarez</t>
+          <t>Miguel Rojas</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -18381,13 +19063,13 @@
         <v>1.5</v>
       </c>
       <c r="G31" t="n">
-        <v>-138</v>
+        <v>-260</v>
       </c>
       <c r="H31" t="n">
-        <v>0.6188</v>
+        <v>0.7621</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0769</v>
+        <v>0.093</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -18395,13 +19077,13 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>72.45999999999999</v>
+        <v>38.46</v>
       </c>
       <c r="M31" t="n">
-        <v>36.23</v>
+        <v>19.23</v>
       </c>
       <c r="N31" t="inlineStr"/>
     </row>
@@ -18423,7 +19105,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Miguel Rojas</t>
+          <t>Max Muncy</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -18435,13 +19117,13 @@
         <v>1.5</v>
       </c>
       <c r="G32" t="n">
-        <v>-260</v>
+        <v>-210</v>
       </c>
       <c r="H32" t="n">
-        <v>0.7621</v>
+        <v>0.7116</v>
       </c>
       <c r="I32" t="n">
-        <v>0.093</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -18452,10 +19134,10 @@
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>38.46</v>
+        <v>47.62</v>
       </c>
       <c r="M32" t="n">
-        <v>19.23</v>
+        <v>23.81</v>
       </c>
       <c r="N32" t="inlineStr"/>
     </row>
@@ -18472,45 +19154,39 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CLE vs SEA</t>
+          <t>BAL vs MIN</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Cal Raleigh</t>
+          <t>Josh Bell</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>0.5</v>
       </c>
       <c r="G33" t="n">
-        <v>-147.5</v>
+        <v>-52.5</v>
       </c>
       <c r="H33" t="n">
-        <v>0.7043</v>
+        <v>0.4279</v>
       </c>
       <c r="I33" t="n">
-        <v>0.152</v>
+        <v>0.1718</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M33" t="n">
-        <v>-50</v>
-      </c>
+          <t>ODDS_ERR</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
     </row>
     <row r="34">
@@ -18580,44 +19256,44 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ARI vs LAD</t>
+          <t>HOU vs LAA</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Zach Neto</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G35" t="n">
-        <v>-210</v>
+        <v>-183.5</v>
       </c>
       <c r="H35" t="n">
-        <v>0.7116</v>
+        <v>0.6847</v>
       </c>
       <c r="I35" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>47.62</v>
+        <v>-100</v>
       </c>
       <c r="M35" t="n">
-        <v>23.81</v>
+        <v>-50</v>
       </c>
       <c r="N35" t="inlineStr"/>
     </row>
@@ -18688,12 +19364,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PHI vs TEX</t>
+          <t>NYM vs PIT</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Sam Haggerty</t>
+          <t>Jared Triolo</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -18705,28 +19381,22 @@
         <v>0.5</v>
       </c>
       <c r="G37" t="n">
-        <v>106</v>
+        <v>-5</v>
       </c>
       <c r="H37" t="n">
-        <v>0.5615</v>
+        <v>0.488</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1109</v>
+        <v>0.4119</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>106</v>
-      </c>
-      <c r="M37" t="n">
-        <v>53</v>
-      </c>
+          <t>ODDS_ERR</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
     </row>
     <row r="38">
@@ -18742,39 +19412,45 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NYM vs PIT</t>
+          <t>MIL vs CWS</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Jared Triolo</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>0.5</v>
       </c>
       <c r="G38" t="n">
-        <v>-5</v>
+        <v>-134.5</v>
       </c>
       <c r="H38" t="n">
-        <v>0.488</v>
+        <v>0.6704</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4119</v>
+        <v>0.1361</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>ODDS_ERR</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M38" t="n">
+        <v>-50</v>
+      </c>
       <c r="N38" t="inlineStr"/>
     </row>
     <row r="39">
@@ -18790,30 +19466,30 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MIL vs CWS</t>
+          <t>TBR vs STL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Colson Montgomery</t>
+          <t>Jordan Walker</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>0.5</v>
       </c>
       <c r="G39" t="n">
-        <v>-134.5</v>
+        <v>128.5</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6704</v>
+        <v>0.5208</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1361</v>
+        <v>0.1146</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -18821,7 +19497,7 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L39" t="n">
         <v>-100</v>
@@ -18844,44 +19520,44 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>TBR vs STL</t>
+          <t>PIT vs NYM</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Jordan Walker</t>
+          <t>Jorge Polanco</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>0.5</v>
       </c>
       <c r="G40" t="n">
-        <v>128.5</v>
+        <v>-141</v>
       </c>
       <c r="H40" t="n">
-        <v>0.5208</v>
+        <v>0.65</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1146</v>
+        <v>0.1053</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>-100</v>
+        <v>70.92</v>
       </c>
       <c r="M40" t="n">
-        <v>-50</v>
+        <v>35.46</v>
       </c>
       <c r="N40" t="inlineStr"/>
     </row>
@@ -18898,44 +19574,44 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PIT vs NYM</t>
+          <t>CHC vs WSN</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Jorge Polanco</t>
+          <t>Jacob Young</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F41" t="n">
         <v>0.5</v>
       </c>
       <c r="G41" t="n">
-        <v>-141</v>
+        <v>-110</v>
       </c>
       <c r="H41" t="n">
-        <v>0.65</v>
+        <v>0.5992</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1053</v>
+        <v>0.1134</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L41" t="n">
-        <v>70.92</v>
+        <v>-100</v>
       </c>
       <c r="M41" t="n">
-        <v>35.46</v>
+        <v>-50</v>
       </c>
       <c r="N41" t="inlineStr"/>
     </row>
@@ -18957,25 +19633,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Jacob Young</t>
+          <t>James Wood</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>0.5</v>
       </c>
       <c r="G42" t="n">
-        <v>-110</v>
+        <v>-161</v>
       </c>
       <c r="H42" t="n">
-        <v>0.5992</v>
+        <v>0.6791</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1134</v>
+        <v>0.1056</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -18983,7 +19659,7 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>-100</v>
@@ -19006,44 +19682,44 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CHC vs WSN</t>
+          <t>PHI vs TEX</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>James Wood</t>
+          <t>Sam Haggerty</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F43" t="n">
         <v>0.5</v>
       </c>
       <c r="G43" t="n">
-        <v>-161</v>
+        <v>106</v>
       </c>
       <c r="H43" t="n">
-        <v>0.6791</v>
+        <v>0.5615</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1056</v>
+        <v>0.1109</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>-100</v>
+        <v>106</v>
       </c>
       <c r="M43" t="n">
-        <v>-50</v>
+        <v>53</v>
       </c>
       <c r="N43" t="inlineStr"/>
     </row>
@@ -19281,7 +19957,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Juan Soto</t>
+          <t>Francisco Lindor</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -19293,27 +19969,27 @@
         <v>0.5</v>
       </c>
       <c r="G48" t="n">
-        <v>-153.5</v>
+        <v>-180.5</v>
       </c>
       <c r="H48" t="n">
-        <v>0.6667</v>
+        <v>0.6811</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1028</v>
+        <v>0.0843</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>65.15000000000001</v>
+        <v>-100</v>
       </c>
       <c r="M48" t="n">
-        <v>32.57</v>
+        <v>-50</v>
       </c>
       <c r="N48" t="inlineStr"/>
     </row>
@@ -19330,44 +20006,44 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CIN vs BOS</t>
+          <t>PIT vs NYM</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Ceddanne Rafaela</t>
+          <t>Juan Soto</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G49" t="n">
-        <v>-178</v>
+        <v>-153.5</v>
       </c>
       <c r="H49" t="n">
-        <v>0.6949</v>
+        <v>0.6667</v>
       </c>
       <c r="I49" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.1028</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K49" t="n">
         <v>2</v>
       </c>
       <c r="L49" t="n">
-        <v>-100</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="M49" t="n">
-        <v>-50</v>
+        <v>32.57</v>
       </c>
       <c r="N49" t="inlineStr"/>
     </row>
@@ -19858,44 +20534,44 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>PIT vs NYM</t>
+          <t>BOS vs CIN</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Francisco Lindor</t>
+          <t>Ke'Bryan Hayes</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F59" t="n">
         <v>0.5</v>
       </c>
       <c r="G59" t="n">
-        <v>-180.5</v>
+        <v>120.5</v>
       </c>
       <c r="H59" t="n">
-        <v>0.6811</v>
+        <v>0.5485</v>
       </c>
       <c r="I59" t="n">
-        <v>0.0843</v>
+        <v>0.1263</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K59" t="n">
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>-100</v>
+        <v>120.5</v>
       </c>
       <c r="M59" t="n">
-        <v>-50</v>
+        <v>60.25</v>
       </c>
       <c r="N59" t="inlineStr"/>
     </row>
@@ -19912,12 +20588,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>BOS vs CIN</t>
+          <t>CIN vs BOS</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Ke'Bryan Hayes</t>
+          <t>Ceddanne Rafaela</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -19926,30 +20602,30 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G60" t="n">
-        <v>120.5</v>
+        <v>-178</v>
       </c>
       <c r="H60" t="n">
-        <v>0.5485</v>
+        <v>0.6949</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1263</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L60" t="n">
-        <v>120.5</v>
+        <v>-100</v>
       </c>
       <c r="M60" t="n">
-        <v>60.25</v>
+        <v>-50</v>
       </c>
       <c r="N60" t="inlineStr"/>
     </row>
@@ -20074,44 +20750,44 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CLE vs SEA</t>
+          <t>HOU vs LAA</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Randy Arozarena</t>
+          <t>Oswald Peraza</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F63" t="n">
         <v>0.5</v>
       </c>
       <c r="G63" t="n">
-        <v>-121</v>
+        <v>-125</v>
       </c>
       <c r="H63" t="n">
-        <v>0.616</v>
+        <v>0.6553</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1101</v>
+        <v>0.1438</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K63" t="n">
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>-100</v>
+        <v>80</v>
       </c>
       <c r="M63" t="n">
-        <v>-50</v>
+        <v>40</v>
       </c>
       <c r="N63" t="inlineStr"/>
     </row>
@@ -20128,44 +20804,44 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MIA vs COL</t>
+          <t>CLE vs SEA</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Edouard Julien</t>
+          <t>Randy Arozarena</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F64" t="n">
         <v>0.5</v>
       </c>
       <c r="G64" t="n">
-        <v>100</v>
+        <v>-121</v>
       </c>
       <c r="H64" t="n">
-        <v>0.5488</v>
+        <v>0.616</v>
       </c>
       <c r="I64" t="n">
-        <v>0.0854</v>
+        <v>0.1101</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K64" t="n">
         <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="M64" t="n">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="N64" t="inlineStr"/>
     </row>
@@ -20182,12 +20858,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>OAK vs TOR</t>
+          <t>MIA vs COL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Nathan Lukes</t>
+          <t>Edouard Julien</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -20196,16 +20872,16 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G65" t="n">
-        <v>-170</v>
+        <v>100</v>
       </c>
       <c r="H65" t="n">
-        <v>0.6636</v>
+        <v>0.5488</v>
       </c>
       <c r="I65" t="n">
-        <v>0.0742</v>
+        <v>0.0854</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -20216,10 +20892,10 @@
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>58.82</v>
+        <v>100</v>
       </c>
       <c r="M65" t="n">
-        <v>29.41</v>
+        <v>50</v>
       </c>
       <c r="N65" t="inlineStr"/>
     </row>
@@ -20236,12 +20912,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>LAA vs HOU</t>
+          <t>OAK vs TOR</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Yordan Alvarez</t>
+          <t>Nathan Lukes</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -20253,27 +20929,27 @@
         <v>1.5</v>
       </c>
       <c r="G66" t="n">
-        <v>-130</v>
+        <v>-170</v>
       </c>
       <c r="H66" t="n">
-        <v>0.6188</v>
+        <v>0.6636</v>
       </c>
       <c r="I66" t="n">
-        <v>0.0906</v>
+        <v>0.0742</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K66" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>-100</v>
+        <v>58.82</v>
       </c>
       <c r="M66" t="n">
-        <v>-50</v>
+        <v>29.41</v>
       </c>
       <c r="N66" t="inlineStr"/>
     </row>
@@ -20295,7 +20971,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Yainer Diaz</t>
+          <t>Yordan Alvarez</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -20307,27 +20983,27 @@
         <v>1.5</v>
       </c>
       <c r="G67" t="n">
-        <v>-175</v>
+        <v>-130</v>
       </c>
       <c r="H67" t="n">
-        <v>0.6797</v>
+        <v>0.6188</v>
       </c>
       <c r="I67" t="n">
-        <v>0.0856</v>
+        <v>0.0906</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K67" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L67" t="n">
-        <v>57.14</v>
+        <v>-100</v>
       </c>
       <c r="M67" t="n">
-        <v>28.57</v>
+        <v>-50</v>
       </c>
       <c r="N67" t="inlineStr"/>
     </row>
@@ -20344,12 +21020,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ARI vs LAD</t>
+          <t>LAA vs HOU</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Shohei Ohtani</t>
+          <t>Yainer Diaz</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -20358,16 +21034,16 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="G68" t="n">
-        <v>-140</v>
+        <v>-175</v>
       </c>
       <c r="H68" t="n">
-        <v>0.6245000000000001</v>
+        <v>0.6797</v>
       </c>
       <c r="I68" t="n">
-        <v>0.0799</v>
+        <v>0.0856</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -20375,13 +21051,13 @@
         </is>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" t="n">
-        <v>71.43000000000001</v>
+        <v>57.14</v>
       </c>
       <c r="M68" t="n">
-        <v>35.71</v>
+        <v>28.57</v>
       </c>
       <c r="N68" t="inlineStr"/>
     </row>
@@ -20398,12 +21074,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>OAK vs TOR</t>
+          <t>ARI vs LAD</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Alejandro Kirk</t>
+          <t>Shohei Ohtani</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -20412,16 +21088,16 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="G69" t="n">
-        <v>-157</v>
+        <v>-140</v>
       </c>
       <c r="H69" t="n">
-        <v>0.6521</v>
+        <v>0.6245000000000001</v>
       </c>
       <c r="I69" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.0799</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -20432,10 +21108,10 @@
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>63.69</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="M69" t="n">
-        <v>31.85</v>
+        <v>35.71</v>
       </c>
       <c r="N69" t="inlineStr"/>
     </row>
@@ -20452,12 +21128,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>NYY vs SFG</t>
+          <t>OAK vs TOR</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Alejandro Kirk</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -20469,13 +21145,13 @@
         <v>1.5</v>
       </c>
       <c r="G70" t="n">
-        <v>-320</v>
+        <v>-157</v>
       </c>
       <c r="H70" t="n">
-        <v>0.791</v>
+        <v>0.6521</v>
       </c>
       <c r="I70" t="n">
-        <v>0.0726</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -20486,10 +21162,10 @@
         <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>31.25</v>
+        <v>63.69</v>
       </c>
       <c r="M70" t="n">
-        <v>15.62</v>
+        <v>31.85</v>
       </c>
       <c r="N70" t="inlineStr"/>
     </row>
@@ -20506,12 +21182,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SFG vs NYY</t>
+          <t>NYY vs SFG</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Paul Goldschmidt</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -20523,27 +21199,27 @@
         <v>1.5</v>
       </c>
       <c r="G71" t="n">
-        <v>-136</v>
+        <v>-320</v>
       </c>
       <c r="H71" t="n">
-        <v>0.6193</v>
+        <v>0.791</v>
       </c>
       <c r="I71" t="n">
-        <v>0.0839</v>
+        <v>0.0726</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>-100</v>
+        <v>31.25</v>
       </c>
       <c r="M71" t="n">
-        <v>-50</v>
+        <v>15.62</v>
       </c>
       <c r="N71" t="inlineStr"/>
     </row>
@@ -20560,12 +21236,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>HOU vs LAA</t>
+          <t>SFG vs NYY</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Oswald Peraza</t>
+          <t>Paul Goldschmidt</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -20574,30 +21250,30 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G72" t="n">
-        <v>-125</v>
+        <v>-136</v>
       </c>
       <c r="H72" t="n">
-        <v>0.6553</v>
+        <v>0.6193</v>
       </c>
       <c r="I72" t="n">
-        <v>0.1438</v>
+        <v>0.0839</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L72" t="n">
-        <v>80</v>
+        <v>-100</v>
       </c>
       <c r="M72" t="n">
-        <v>40</v>
+        <v>-50</v>
       </c>
       <c r="N72" t="inlineStr"/>
     </row>
@@ -20619,7 +21295,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Connor Norby</t>
+          <t>Xavier Edwards</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -20631,27 +21307,27 @@
         <v>1.5</v>
       </c>
       <c r="G73" t="n">
-        <v>-168</v>
+        <v>-190</v>
       </c>
       <c r="H73" t="n">
-        <v>0.6831</v>
+        <v>0.7413</v>
       </c>
       <c r="I73" t="n">
-        <v>0.099</v>
+        <v>0.1301</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L73" t="n">
-        <v>-100</v>
+        <v>52.63</v>
       </c>
       <c r="M73" t="n">
-        <v>-50</v>
+        <v>26.32</v>
       </c>
       <c r="N73" t="inlineStr"/>
     </row>
@@ -20668,12 +21344,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MIA vs COL</t>
+          <t>COL vs MIA</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Jake McCarthy</t>
+          <t>Connor Norby</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -20685,27 +21361,27 @@
         <v>1.5</v>
       </c>
       <c r="G74" t="n">
-        <v>-216.5</v>
+        <v>-168</v>
       </c>
       <c r="H74" t="n">
-        <v>0.7151</v>
+        <v>0.6831</v>
       </c>
       <c r="I74" t="n">
-        <v>0.0794</v>
+        <v>0.099</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L74" t="n">
-        <v>46.19</v>
+        <v>-100</v>
       </c>
       <c r="M74" t="n">
-        <v>23.09</v>
+        <v>-50</v>
       </c>
       <c r="N74" t="inlineStr"/>
     </row>
@@ -20727,7 +21403,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Kyle Karros</t>
+          <t>Jake McCarthy</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -20736,30 +21412,30 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G75" t="n">
-        <v>113</v>
+        <v>-216.5</v>
       </c>
       <c r="H75" t="n">
-        <v>0.6227</v>
+        <v>0.7151</v>
       </c>
       <c r="I75" t="n">
-        <v>0.185</v>
+        <v>0.0794</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K75" t="n">
         <v>1</v>
       </c>
       <c r="L75" t="n">
-        <v>-100</v>
+        <v>46.19</v>
       </c>
       <c r="M75" t="n">
-        <v>-50</v>
+        <v>23.09</v>
       </c>
       <c r="N75" t="inlineStr"/>
     </row>
@@ -20776,12 +21452,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>COL vs MIA</t>
+          <t>MIA vs COL</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Austin Slater</t>
+          <t>Kyle Karros</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -20790,30 +21466,30 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G76" t="n">
-        <v>-161</v>
+        <v>113</v>
       </c>
       <c r="H76" t="n">
-        <v>0.7345</v>
+        <v>0.6227</v>
       </c>
       <c r="I76" t="n">
-        <v>0.156</v>
+        <v>0.185</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" t="n">
-        <v>62.11</v>
+        <v>-100</v>
       </c>
       <c r="M76" t="n">
-        <v>31.06</v>
+        <v>-50</v>
       </c>
       <c r="N76" t="inlineStr"/>
     </row>
@@ -20830,30 +21506,30 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>TOR vs OAK</t>
+          <t>COL vs MIA</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Nick Kurtz</t>
+          <t>Javier Sanoja</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F77" t="n">
         <v>1.5</v>
       </c>
       <c r="G77" t="n">
-        <v>116.5</v>
+        <v>-202</v>
       </c>
       <c r="H77" t="n">
-        <v>0.5341</v>
+        <v>0.7691</v>
       </c>
       <c r="I77" t="n">
-        <v>0.1023</v>
+        <v>0.1424</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -20861,7 +21537,7 @@
         </is>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L77" t="n">
         <v>-100</v>
@@ -20884,44 +21560,44 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>COL vs MIA</t>
+          <t>TOR vs OAK</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Xavier Edwards</t>
+          <t>Nick Kurtz</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F78" t="n">
         <v>1.5</v>
       </c>
       <c r="G78" t="n">
-        <v>-190</v>
+        <v>116.5</v>
       </c>
       <c r="H78" t="n">
-        <v>0.7413</v>
+        <v>0.5341</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1301</v>
+        <v>0.1023</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>52.63</v>
+        <v>-100</v>
       </c>
       <c r="M78" t="n">
-        <v>26.32</v>
+        <v>-50</v>
       </c>
       <c r="N78" t="inlineStr"/>
     </row>
@@ -20943,7 +21619,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Javier Sanoja</t>
+          <t>Austin Slater</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -20955,27 +21631,27 @@
         <v>1.5</v>
       </c>
       <c r="G79" t="n">
-        <v>-202</v>
+        <v>-161</v>
       </c>
       <c r="H79" t="n">
-        <v>0.7691</v>
+        <v>0.7345</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1424</v>
+        <v>0.156</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K79" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>-100</v>
+        <v>62.11</v>
       </c>
       <c r="M79" t="n">
-        <v>-50</v>
+        <v>31.06</v>
       </c>
       <c r="N79" t="inlineStr"/>
     </row>
@@ -21312,12 +21988,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>NYY vs SFG</t>
+          <t>WSN vs CHC</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Dansby Swanson</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -21326,16 +22002,16 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G86" t="n">
-        <v>102</v>
+        <v>-162.5</v>
       </c>
       <c r="H86" t="n">
-        <v>0.5429</v>
+        <v>0.6579</v>
       </c>
       <c r="I86" t="n">
-        <v>0.0808</v>
+        <v>0.078</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -21364,12 +22040,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>TOR vs OAK</t>
+          <t>NYM vs PIT</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Shea Langeliers</t>
+          <t>Ryan O'Hearn</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -21381,13 +22057,13 @@
         <v>1.5</v>
       </c>
       <c r="G87" t="n">
-        <v>128</v>
+        <v>205</v>
       </c>
       <c r="H87" t="n">
-        <v>0.4855</v>
+        <v>0.3854</v>
       </c>
       <c r="I87" t="n">
-        <v>0.076</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -21421,7 +22097,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Byron Buxton</t>
+          <t>Trevor Larnach</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -21430,16 +22106,16 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G88" t="n">
-        <v>129</v>
+        <v>-115</v>
       </c>
       <c r="H88" t="n">
-        <v>0.4823</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="I88" t="n">
-        <v>0.0746</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -21468,30 +22144,30 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MIL vs CWS</t>
+          <t>STL vs TBR</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Colson Montgomery</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G89" t="n">
-        <v>-170</v>
+        <v>-209</v>
       </c>
       <c r="H89" t="n">
-        <v>0.6704</v>
+        <v>0.7207</v>
       </c>
       <c r="I89" t="n">
-        <v>0.0842</v>
+        <v>0.0877</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -21520,30 +22196,30 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>NYM vs PIT</t>
+          <t>COL vs MIA</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Ryan O'Hearn</t>
+          <t>Connor Norby</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F90" t="n">
         <v>1.5</v>
       </c>
       <c r="G90" t="n">
-        <v>205</v>
+        <v>-196.5</v>
       </c>
       <c r="H90" t="n">
-        <v>0.3854</v>
+        <v>0.7072000000000001</v>
       </c>
       <c r="I90" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -21572,12 +22248,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>WSN vs CHC</t>
+          <t>OAK vs TOR</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Dansby Swanson</t>
+          <t>Ernie Clement</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -21589,13 +22265,13 @@
         <v>1.5</v>
       </c>
       <c r="G91" t="n">
-        <v>-162.5</v>
+        <v>-168</v>
       </c>
       <c r="H91" t="n">
-        <v>0.6579</v>
+        <v>0.6761</v>
       </c>
       <c r="I91" t="n">
-        <v>0.078</v>
+        <v>0.0888</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -21624,12 +22300,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>STL vs TBR</t>
+          <t>COL vs MIA</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Xavier Edwards</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -21641,13 +22317,13 @@
         <v>1.5</v>
       </c>
       <c r="G92" t="n">
-        <v>-209</v>
+        <v>-170</v>
       </c>
       <c r="H92" t="n">
-        <v>0.7207</v>
+        <v>0.6768999999999999</v>
       </c>
       <c r="I92" t="n">
-        <v>0.0877</v>
+        <v>0.0907</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -21676,12 +22352,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>COL vs MIA</t>
+          <t>WSN vs CHC</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Connor Norby</t>
+          <t>Ian Happ</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -21693,13 +22369,13 @@
         <v>1.5</v>
       </c>
       <c r="G93" t="n">
-        <v>-196.5</v>
+        <v>-133</v>
       </c>
       <c r="H93" t="n">
-        <v>0.7072000000000001</v>
+        <v>0.6044</v>
       </c>
       <c r="I93" t="n">
-        <v>0.09030000000000001</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -21728,12 +22404,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>OAK vs TOR</t>
+          <t>ARI vs LAD</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Ernie Clement</t>
+          <t>Santiago Espinal</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -21742,16 +22418,16 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G94" t="n">
-        <v>-168</v>
+        <v>116</v>
       </c>
       <c r="H94" t="n">
-        <v>0.6761</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="I94" t="n">
-        <v>0.0888</v>
+        <v>0.1771</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -21780,12 +22456,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>COL vs MIA</t>
+          <t>CWS vs MIL</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Xavier Edwards</t>
+          <t>Brandon Lockridge</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -21794,16 +22470,16 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G95" t="n">
-        <v>-170</v>
+        <v>-106</v>
       </c>
       <c r="H95" t="n">
-        <v>0.6768999999999999</v>
+        <v>0.6246</v>
       </c>
       <c r="I95" t="n">
-        <v>0.0907</v>
+        <v>0.1446</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -21832,12 +22508,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>OAK vs TOR</t>
+          <t>CWS vs MIL</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Myles Straw</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -21846,16 +22522,16 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G96" t="n">
-        <v>-355</v>
+        <v>-125</v>
       </c>
       <c r="H96" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.6313</v>
       </c>
       <c r="I96" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.1166</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -21884,12 +22560,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>WSN vs CHC</t>
+          <t>SDP vs DET</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Ian Happ</t>
+          <t>Matt Vierling</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -21898,16 +22574,16 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G97" t="n">
-        <v>-133</v>
+        <v>125</v>
       </c>
       <c r="H97" t="n">
-        <v>0.6044</v>
+        <v>0.5705</v>
       </c>
       <c r="I97" t="n">
-        <v>0.07439999999999999</v>
+        <v>0.1567</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -21936,30 +22612,30 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>WSN vs CHC</t>
+          <t>MIL vs CWS</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Nico Hoerner</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G98" t="n">
-        <v>-153</v>
+        <v>-170</v>
       </c>
       <c r="H98" t="n">
-        <v>0.6441</v>
+        <v>0.6704</v>
       </c>
       <c r="I98" t="n">
-        <v>0.0794</v>
+        <v>0.0842</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -21988,30 +22664,30 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>BAL vs MIN</t>
+          <t>SDP vs DET</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Trevor Larnach</t>
+          <t>Jake Rogers</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F99" t="n">
         <v>0.5</v>
       </c>
       <c r="G99" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="H99" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.602</v>
       </c>
       <c r="I99" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.1168</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -22040,12 +22716,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MIN vs BAL</t>
+          <t>LAD vs ARI</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Taylor Ward</t>
+          <t>Ketel Marte</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -22054,16 +22730,16 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G100" t="n">
-        <v>-165</v>
+        <v>137</v>
       </c>
       <c r="H100" t="n">
-        <v>0.6717</v>
+        <v>0.4777</v>
       </c>
       <c r="I100" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.0814</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -22092,12 +22768,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>NYY vs SFG</t>
+          <t>ARI vs LAD</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Casey Schmitt</t>
+          <t>Miguel Rojas</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -22106,16 +22782,16 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G101" t="n">
-        <v>-186</v>
+        <v>116</v>
       </c>
       <c r="H101" t="n">
-        <v>0.724</v>
+        <v>0.5123</v>
       </c>
       <c r="I101" t="n">
-        <v>0.1165</v>
+        <v>0.083</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -22144,30 +22820,30 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>TBR vs STL</t>
+          <t>LAD vs ARI</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Jordan Walker</t>
+          <t>Geraldo Perdomo</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G102" t="n">
-        <v>-290</v>
+        <v>-155</v>
       </c>
       <c r="H102" t="n">
-        <v>0.7907999999999999</v>
+        <v>0.6403</v>
       </c>
       <c r="I102" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.0761</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -22196,12 +22872,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>CWS vs MIL</t>
+          <t>DET vs SDP</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Brandon Lockridge</t>
+          <t>Freddy Fermin</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -22213,13 +22889,13 @@
         <v>0.5</v>
       </c>
       <c r="G103" t="n">
-        <v>-106</v>
+        <v>-105</v>
       </c>
       <c r="H103" t="n">
-        <v>0.6246</v>
+        <v>0.5414</v>
       </c>
       <c r="I103" t="n">
-        <v>0.1446</v>
+        <v>0.0701</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -22253,7 +22929,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Michael Busch</t>
+          <t>Nico Hoerner</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -22265,13 +22941,13 @@
         <v>1.5</v>
       </c>
       <c r="G104" t="n">
-        <v>-2</v>
+        <v>-153</v>
       </c>
       <c r="H104" t="n">
-        <v>0.5424</v>
+        <v>0.6441</v>
       </c>
       <c r="I104" t="n">
-        <v>0.5093</v>
+        <v>0.0794</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -22300,12 +22976,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>WSN vs CHC</t>
+          <t>BAL vs MIN</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Alex Bregman</t>
+          <t>Byron Buxton</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -22317,13 +22993,13 @@
         <v>1.5</v>
       </c>
       <c r="G105" t="n">
-        <v>-1</v>
+        <v>129</v>
       </c>
       <c r="H105" t="n">
-        <v>0.4486</v>
+        <v>0.4823</v>
       </c>
       <c r="I105" t="n">
-        <v>0.4313</v>
+        <v>0.0746</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -22357,7 +23033,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Nick Kurtz</t>
+          <t>Brent Rooker</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -22369,13 +23045,13 @@
         <v>1.5</v>
       </c>
       <c r="G106" t="n">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="H106" t="n">
-        <v>0.5341</v>
+        <v>0.4369</v>
       </c>
       <c r="I106" t="n">
-        <v>0.1437</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -22404,12 +23080,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>COL vs MIA</t>
+          <t>NYY vs SFG</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -22421,13 +23097,13 @@
         <v>0.5</v>
       </c>
       <c r="G107" t="n">
-        <v>153</v>
+        <v>102</v>
       </c>
       <c r="H107" t="n">
-        <v>0.4978</v>
+        <v>0.5429</v>
       </c>
       <c r="I107" t="n">
-        <v>0.1293</v>
+        <v>0.0808</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -22456,12 +23132,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>TEX vs PHI</t>
+          <t>LAD vs ARI</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Kyle Schwarber</t>
+          <t>Pavin Smith</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -22473,13 +23149,13 @@
         <v>0.5</v>
       </c>
       <c r="G108" t="n">
-        <v>-160</v>
+        <v>-124</v>
       </c>
       <c r="H108" t="n">
-        <v>0.6923</v>
+        <v>0.573</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1205</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -22508,12 +23184,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>MIA vs COL</t>
+          <t>WSN vs CHC</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Kyle Karros</t>
+          <t>Michael Busch</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -22522,16 +23198,16 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G109" t="n">
-        <v>-108</v>
+        <v>-2</v>
       </c>
       <c r="H109" t="n">
-        <v>0.6086</v>
+        <v>0.5424</v>
       </c>
       <c r="I109" t="n">
-        <v>0.1339</v>
+        <v>0.5093</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -22560,30 +23236,30 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>CHC vs WSN</t>
+          <t>WSN vs CHC</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Jacob Young</t>
+          <t>Alex Bregman</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G110" t="n">
-        <v>-106.5</v>
+        <v>-1</v>
       </c>
       <c r="H110" t="n">
-        <v>0.5992</v>
+        <v>0.4486</v>
       </c>
       <c r="I110" t="n">
-        <v>0.1177</v>
+        <v>0.4313</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -22612,12 +23288,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>CHC vs WSN</t>
+          <t>TOR vs OAK</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>James Wood</t>
+          <t>Nick Kurtz</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -22629,13 +23305,13 @@
         <v>1.5</v>
       </c>
       <c r="G111" t="n">
-        <v>158.5</v>
+        <v>141</v>
       </c>
       <c r="H111" t="n">
-        <v>0.4611</v>
+        <v>0.5341</v>
       </c>
       <c r="I111" t="n">
-        <v>0.0968</v>
+        <v>0.1437</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -22664,30 +23340,30 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>BAL vs MIN</t>
+          <t>COL vs MIA</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Matt Wallner</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F112" t="n">
         <v>0.5</v>
       </c>
       <c r="G112" t="n">
-        <v>-125</v>
+        <v>153</v>
       </c>
       <c r="H112" t="n">
-        <v>0.6262</v>
+        <v>0.4978</v>
       </c>
       <c r="I112" t="n">
-        <v>0.1115</v>
+        <v>0.1293</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -22716,12 +23392,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>NYM vs PIT</t>
+          <t>TEX vs PHI</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Brandon Lowe</t>
+          <t>Kyle Schwarber</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -22733,13 +23409,13 @@
         <v>0.5</v>
       </c>
       <c r="G113" t="n">
-        <v>-125</v>
+        <v>-160</v>
       </c>
       <c r="H113" t="n">
-        <v>0.6173999999999999</v>
+        <v>0.6923</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1027</v>
+        <v>0.1205</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -22768,12 +23444,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>NYM vs PIT</t>
+          <t>MIA vs COL</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Jake Mangum</t>
+          <t>Kyle Karros</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -22785,13 +23461,13 @@
         <v>0.5</v>
       </c>
       <c r="G114" t="n">
-        <v>130</v>
+        <v>-108</v>
       </c>
       <c r="H114" t="n">
-        <v>0.4946</v>
+        <v>0.6086</v>
       </c>
       <c r="I114" t="n">
-        <v>0.0934</v>
+        <v>0.1339</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -22820,12 +23496,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>STL vs TBR</t>
+          <t>CHC vs WSN</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Jacob Young</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -22834,16 +23510,16 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G115" t="n">
-        <v>-350</v>
+        <v>-106.5</v>
       </c>
       <c r="H115" t="n">
-        <v>0.827</v>
+        <v>0.5992</v>
       </c>
       <c r="I115" t="n">
-        <v>0.0929</v>
+        <v>0.1177</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -22872,30 +23548,30 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>COL vs MIA</t>
+          <t>CHC vs WSN</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Otto Lopez</t>
+          <t>James Wood</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F116" t="n">
         <v>1.5</v>
       </c>
       <c r="G116" t="n">
-        <v>-155</v>
+        <v>158.5</v>
       </c>
       <c r="H116" t="n">
-        <v>0.6829</v>
+        <v>0.4611</v>
       </c>
       <c r="I116" t="n">
-        <v>0.1141</v>
+        <v>0.0968</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -22924,30 +23600,30 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>BOS vs CIN</t>
+          <t>BAL vs MIN</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Ke'Bryan Hayes</t>
+          <t>Matt Wallner</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F117" t="n">
         <v>0.5</v>
       </c>
       <c r="G117" t="n">
-        <v>102</v>
+        <v>-125</v>
       </c>
       <c r="H117" t="n">
-        <v>0.5485</v>
+        <v>0.6262</v>
       </c>
       <c r="I117" t="n">
-        <v>0.0895</v>
+        <v>0.1115</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -22976,12 +23652,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>TOR vs OAK</t>
+          <t>NYM vs PIT</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Brent Rooker</t>
+          <t>Brandon Lowe</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -22990,16 +23666,16 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G118" t="n">
-        <v>166</v>
+        <v>-125</v>
       </c>
       <c r="H118" t="n">
-        <v>0.4369</v>
+        <v>0.6173999999999999</v>
       </c>
       <c r="I118" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.1027</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -23028,12 +23704,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>CWS vs MIL</t>
+          <t>NYM vs PIT</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Jake Mangum</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -23045,13 +23721,13 @@
         <v>0.5</v>
       </c>
       <c r="G119" t="n">
-        <v>-125</v>
+        <v>130</v>
       </c>
       <c r="H119" t="n">
-        <v>0.6313</v>
+        <v>0.4946</v>
       </c>
       <c r="I119" t="n">
-        <v>0.1166</v>
+        <v>0.0934</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -23062,6 +23738,474 @@
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>NYY vs SFG</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Casey Schmitt</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G120" t="n">
+        <v>-186</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.1165</v>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>STL vs TBR</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Richie Palacios</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G121" t="n">
+        <v>-350</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.0929</v>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>COL vs MIA</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Otto Lopez</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G122" t="n">
+        <v>-155</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.6829</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.1141</v>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>BOS vs CIN</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Ke'Bryan Hayes</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G123" t="n">
+        <v>102</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.5485</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.0895</v>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>TBR vs STL</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Jordan Walker</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G124" t="n">
+        <v>-290</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.7907999999999999</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.09329999999999999</v>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>MIN vs BAL</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Taylor Ward</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G125" t="n">
+        <v>-165</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.6717</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.09370000000000001</v>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>OAK vs TOR</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Myles Straw</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G126" t="n">
+        <v>-355</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>TOR vs OAK</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Shea Langeliers</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G127" t="n">
+        <v>128</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.4855</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>ARI vs LAD</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Mookie Betts</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G128" t="n">
+        <v>-134</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.6084000000000001</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.0746</v>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
         </is>

--- a/tracking/picks.xlsx
+++ b/tracking/picks.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N259"/>
+  <dimension ref="A1:N268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14147,6 +14147,468 @@
       <c r="N259" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>CLE @ SEA</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr"/>
+      <c r="G260" t="n">
+        <v>-180.5</v>
+      </c>
+      <c r="H260" t="n">
+        <v>0.6882</v>
+      </c>
+      <c r="I260" t="n">
+        <v>0.07149999999999999</v>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr"/>
+      <c r="L260" t="inlineStr"/>
+      <c r="M260" t="inlineStr"/>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>CLE @ SEA</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>CLE @ SEA</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F261" t="n">
+        <v>7</v>
+      </c>
+      <c r="G261" t="n">
+        <v>-102</v>
+      </c>
+      <c r="H261" t="n">
+        <v>0.7501</v>
+      </c>
+      <c r="I261" t="n">
+        <v>0.2693</v>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr"/>
+      <c r="L261" t="inlineStr"/>
+      <c r="M261" t="inlineStr"/>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>CLE vs SEA</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Cal Raleigh</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F262" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G262" t="n">
+        <v>-165</v>
+      </c>
+      <c r="H262" t="n">
+        <v>0.7042</v>
+      </c>
+      <c r="I262" t="n">
+        <v>0.1262</v>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr"/>
+      <c r="L262" t="inlineStr"/>
+      <c r="M262" t="inlineStr"/>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>SEA vs CLE</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Kyle Manzardo</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F263" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G263" t="n">
+        <v>-120</v>
+      </c>
+      <c r="H263" t="n">
+        <v>0.6057</v>
+      </c>
+      <c r="I263" t="n">
+        <v>0.1038</v>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr"/>
+      <c r="L263" t="inlineStr"/>
+      <c r="M263" t="inlineStr"/>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>SEA vs CLE</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>CJ Kayfus</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F264" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G264" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="H264" t="n">
+        <v>0.5321</v>
+      </c>
+      <c r="I264" t="n">
+        <v>0.0713</v>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr"/>
+      <c r="L264" t="inlineStr"/>
+      <c r="M264" t="inlineStr"/>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>SEA vs CLE</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Joey Cantillo</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F265" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G265" t="n">
+        <v>-151.5</v>
+      </c>
+      <c r="H265" t="n">
+        <v>0.9568</v>
+      </c>
+      <c r="I265" t="n">
+        <v>0.3983</v>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr"/>
+      <c r="L265" t="inlineStr"/>
+      <c r="M265" t="inlineStr"/>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Add opp_bb_pct to pitcher outs, bullpen features to totals, bullpen availability utility; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Use confirmed SP from lineup card, fall back to probable pitcher; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Cap pitcher outs to 1 pick per game (not per pitcher); Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Gate all 5 models on confirmed starting pitchers; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>LAD vs ARI</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Eduardo Rodriguez</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F266" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G266" t="n">
+        <v>-117</v>
+      </c>
+      <c r="H266" t="n">
+        <v>0.6627999999999999</v>
+      </c>
+      <c r="I266" t="n">
+        <v>0.1628</v>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr"/>
+      <c r="L266" t="inlineStr"/>
+      <c r="M266" t="inlineStr"/>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Add opp_bb_pct to pitcher outs, bullpen features to totals, bullpen availability utility; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Use confirmed SP from lineup card, fall back to probable pitcher; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Cap pitcher outs to 1 pick per game (not per pitcher); Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Gate all 5 models on confirmed starting pitchers; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>ARI @ LAD</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>ARI @ LAD</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>YRFI</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr"/>
+      <c r="G267" t="n">
+        <v>-124.5</v>
+      </c>
+      <c r="H267" t="n">
+        <v>1</v>
+      </c>
+      <c r="I267" t="n">
+        <v>0.479</v>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr"/>
+      <c r="L267" t="inlineStr"/>
+      <c r="M267" t="inlineStr"/>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix NRFI scoreboard period param and Discord embed truncation; Fix NRFI odds: parse from scoreboard markets instead of props endpoint; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Gate NRFI scoring on confirmed lineups, consistent with other models; Fix 04_export_nrfi.py DataFrame iteration and lineup format bugs; Fix API crash guards and FanGraphs splits method errors; Add NRFI/YRFI fifth model and rebuild all four existing models; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>CLE @ SEA</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>CLE @ SEA</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>YRFI</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr"/>
+      <c r="G268" t="n">
+        <v>109</v>
+      </c>
+      <c r="H268" t="n">
+        <v>0.5887</v>
+      </c>
+      <c r="I268" t="n">
+        <v>0.1388</v>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr"/>
+      <c r="L268" t="inlineStr"/>
+      <c r="M268" t="inlineStr"/>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix NRFI scoreboard period param and Discord embed truncation; Fix NRFI odds: parse from scoreboard markets instead of props endpoint; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Gate NRFI scoring on confirmed lineups, consistent with other models; Fix 04_export_nrfi.py DataFrame iteration and lineup format bugs; Fix API crash guards and FanGraphs splits method errors; Add NRFI/YRFI fifth model and rebuild all four existing models; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
         </is>
       </c>
     </row>
@@ -14698,7 +15160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15218,44 +15680,44 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NYY @ SFG</t>
+          <t>LAA @ HOU</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SFG</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>112.5</v>
+        <v>144.5</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6142</v>
+        <v>0.5634</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1631</v>
+        <v>0.1691</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>6-2</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-100</v>
+        <v>144.5</v>
       </c>
       <c r="M10" t="n">
-        <v>-50</v>
+        <v>72.25</v>
       </c>
       <c r="N10" t="inlineStr"/>
     </row>
@@ -15272,12 +15734,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>COL @ MIA</t>
+          <t>NYY @ SFG</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SFG</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -15287,29 +15749,29 @@
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>-195</v>
+        <v>112.5</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6944</v>
+        <v>0.6142</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0618</v>
+        <v>0.1631</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>51.28</v>
+        <v>-100</v>
       </c>
       <c r="M11" t="n">
-        <v>25.64</v>
+        <v>-50</v>
       </c>
       <c r="N11" t="inlineStr"/>
     </row>
@@ -15326,28 +15788,28 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LAA @ HOU</t>
+          <t>COL @ MIA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>144.5</v>
+        <v>-195</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5634</v>
+        <v>0.6944</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1691</v>
+        <v>0.0618</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -15356,14 +15818,14 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>6-2</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>144.5</v>
+        <v>51.28</v>
       </c>
       <c r="M12" t="n">
-        <v>72.25</v>
+        <v>25.64</v>
       </c>
       <c r="N12" t="inlineStr"/>
     </row>
@@ -15380,28 +15842,28 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>OAK @ TOR</t>
+          <t>CWS @ MIL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>OAK</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>162.5</v>
+        <v>-199</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5144</v>
+        <v>0.7235</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1504</v>
+        <v>0.0862</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -15430,28 +15892,28 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BOS @ CIN</t>
+          <t>OAK @ TOR</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>OAK</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>115</v>
+        <v>162.5</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5144</v>
       </c>
       <c r="I14" t="n">
-        <v>0.11</v>
+        <v>0.1504</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -15480,12 +15942,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TBR @ STL</t>
+          <t>BOS @ CIN</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -15495,13 +15957,13 @@
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>-105</v>
+        <v>115</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5876</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1004</v>
+        <v>0.11</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -15530,12 +15992,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NYY @ SFG</t>
+          <t>TBR @ STL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SFG</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -15545,13 +16007,13 @@
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>108.5</v>
+        <v>-105</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5914</v>
+        <v>0.5876</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1307</v>
+        <v>0.1004</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -15580,12 +16042,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CWS @ MIL</t>
+          <t>NYY @ SFG</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>SFG</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -15595,13 +16057,13 @@
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
-        <v>-199</v>
+        <v>108.5</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7235</v>
+        <v>0.5914</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0862</v>
+        <v>0.1307</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -15612,6 +16074,56 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
+        <is>
+          <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLE @ SEA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="n">
+        <v>-180.5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.6882</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.07149999999999999</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
         <is>
           <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
         </is>
@@ -15628,7 +16140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16634,12 +17146,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NYY @ SFG</t>
+          <t>OAK @ TOR</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NYY @ SFG</t>
+          <t>OAK @ TOR</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -16651,13 +17163,13 @@
         <v>8.5</v>
       </c>
       <c r="G19" t="n">
-        <v>-107</v>
+        <v>-118</v>
       </c>
       <c r="H19" t="n">
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5044</v>
+        <v>0.4838</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -16665,7 +17177,7 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L19" t="n">
         <v>-100</v>
@@ -16688,12 +17200,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>OAK @ TOR</t>
+          <t>NYY @ SFG</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>OAK @ TOR</t>
+          <t>NYY @ SFG</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -16705,13 +17217,13 @@
         <v>8.5</v>
       </c>
       <c r="G20" t="n">
-        <v>-118</v>
+        <v>-107</v>
       </c>
       <c r="H20" t="n">
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4838</v>
+        <v>0.5044</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -16719,7 +17231,7 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L20" t="n">
         <v>-100</v>
@@ -16796,30 +17308,30 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ARI @ LAD</t>
+          <t>DET @ SDP</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ARI @ LAD</t>
+          <t>DET @ SDP</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="G22" t="n">
-        <v>-115</v>
+        <v>-108</v>
       </c>
       <c r="H22" t="n">
-        <v>0.875</v>
+        <v>0.744</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3687</v>
+        <v>0.2514</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -17368,30 +17880,30 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DET @ SDP</t>
+          <t>ARI @ LAD</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DET @ SDP</t>
+          <t>ARI @ LAD</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="G33" t="n">
-        <v>-108</v>
+        <v>-115</v>
       </c>
       <c r="H33" t="n">
-        <v>0.744</v>
+        <v>0.875</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2514</v>
+        <v>0.3687</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -17402,6 +17914,58 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
+        <is>
+          <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CLE @ SEA</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>CLE @ SEA</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>7</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-102</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.7501</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.2693</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
         <is>
           <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
         </is>
@@ -17418,7 +17982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N128"/>
+  <dimension ref="A1:N131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21295,7 +21859,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Xavier Edwards</t>
+          <t>Christopher Morel</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -21307,27 +21871,25 @@
         <v>1.5</v>
       </c>
       <c r="G73" t="n">
-        <v>-190</v>
+        <v>-178</v>
       </c>
       <c r="H73" t="n">
-        <v>0.7413</v>
+        <v>0.7256</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1301</v>
+        <v>0.1269</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="K73" t="n">
-        <v>1</v>
-      </c>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
       <c r="L73" t="n">
-        <v>52.63</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>26.32</v>
+        <v>0</v>
       </c>
       <c r="N73" t="inlineStr"/>
     </row>
@@ -21619,7 +22181,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Austin Slater</t>
+          <t>Xavier Edwards</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -21631,13 +22193,13 @@
         <v>1.5</v>
       </c>
       <c r="G79" t="n">
-        <v>-161</v>
+        <v>-190</v>
       </c>
       <c r="H79" t="n">
-        <v>0.7345</v>
+        <v>0.7413</v>
       </c>
       <c r="I79" t="n">
-        <v>0.156</v>
+        <v>0.1301</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -21645,13 +22207,13 @@
         </is>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" t="n">
-        <v>62.11</v>
+        <v>52.63</v>
       </c>
       <c r="M79" t="n">
-        <v>31.06</v>
+        <v>26.32</v>
       </c>
       <c r="N79" t="inlineStr"/>
     </row>
@@ -21673,7 +22235,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Otto Lopez</t>
+          <t>Austin Slater</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -21685,13 +22247,13 @@
         <v>1.5</v>
       </c>
       <c r="G80" t="n">
-        <v>-145</v>
+        <v>-161</v>
       </c>
       <c r="H80" t="n">
-        <v>0.6723</v>
+        <v>0.7345</v>
       </c>
       <c r="I80" t="n">
-        <v>0.1181</v>
+        <v>0.156</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -21702,10 +22264,10 @@
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>68.97</v>
+        <v>62.11</v>
       </c>
       <c r="M80" t="n">
-        <v>34.48</v>
+        <v>31.06</v>
       </c>
       <c r="N80" t="inlineStr"/>
     </row>
@@ -21722,12 +22284,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ATL vs KCR</t>
+          <t>COL vs MIA</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Lane Thomas</t>
+          <t>Otto Lopez</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -21736,30 +22298,30 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G81" t="n">
-        <v>109</v>
+        <v>-145</v>
       </c>
       <c r="H81" t="n">
-        <v>0.535</v>
+        <v>0.6723</v>
       </c>
       <c r="I81" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.1181</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>-100</v>
+        <v>68.97</v>
       </c>
       <c r="M81" t="n">
-        <v>-50</v>
+        <v>34.48</v>
       </c>
       <c r="N81" t="inlineStr"/>
     </row>
@@ -21776,12 +22338,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SFG vs NYY</t>
+          <t>ATL vs KCR</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Randal Grichuk</t>
+          <t>Lane Thomas</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -21793,27 +22355,27 @@
         <v>0.5</v>
       </c>
       <c r="G82" t="n">
-        <v>110.5</v>
+        <v>109</v>
       </c>
       <c r="H82" t="n">
-        <v>0.5165</v>
+        <v>0.535</v>
       </c>
       <c r="I82" t="n">
-        <v>0.0746</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" t="n">
-        <v>110.5</v>
+        <v>-100</v>
       </c>
       <c r="M82" t="n">
-        <v>55.25</v>
+        <v>-50</v>
       </c>
       <c r="N82" t="inlineStr"/>
     </row>
@@ -21830,44 +22392,44 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ATL vs KCR</t>
+          <t>SFG vs NYY</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Vinnie Pasquantino</t>
+          <t>Randal Grichuk</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F83" t="n">
         <v>0.5</v>
       </c>
       <c r="G83" t="n">
-        <v>-157</v>
+        <v>110.5</v>
       </c>
       <c r="H83" t="n">
-        <v>0.6475</v>
+        <v>0.5165</v>
       </c>
       <c r="I83" t="n">
-        <v>0.0775</v>
+        <v>0.0746</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K83" t="n">
         <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>-100</v>
+        <v>110.5</v>
       </c>
       <c r="M83" t="n">
-        <v>-50</v>
+        <v>55.25</v>
       </c>
       <c r="N83" t="inlineStr"/>
     </row>
@@ -21884,42 +22446,44 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>COL vs MIA</t>
+          <t>ATL vs KCR</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Christopher Morel</t>
+          <t>Vinnie Pasquantino</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G84" t="n">
-        <v>-178</v>
+        <v>-157</v>
       </c>
       <c r="H84" t="n">
-        <v>0.7256</v>
+        <v>0.6475</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1269</v>
+        <v>0.0775</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>DNP</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="N84" t="inlineStr"/>
     </row>
@@ -21936,30 +22500,30 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MIN vs BAL</t>
+          <t>WSN vs CHC</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Pete Alonso</t>
+          <t>Nico Hoerner</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F85" t="n">
         <v>1.5</v>
       </c>
       <c r="G85" t="n">
-        <v>135</v>
+        <v>-153</v>
       </c>
       <c r="H85" t="n">
-        <v>0.47</v>
+        <v>0.6441</v>
       </c>
       <c r="I85" t="n">
-        <v>0.0717</v>
+        <v>0.0794</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -21988,12 +22552,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>WSN vs CHC</t>
+          <t>STL vs TBR</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Dansby Swanson</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -22005,13 +22569,13 @@
         <v>1.5</v>
       </c>
       <c r="G86" t="n">
-        <v>-162.5</v>
+        <v>-209</v>
       </c>
       <c r="H86" t="n">
-        <v>0.6579</v>
+        <v>0.7207</v>
       </c>
       <c r="I86" t="n">
-        <v>0.078</v>
+        <v>0.0877</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -22040,30 +22604,30 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NYM vs PIT</t>
+          <t>COL vs MIA</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Ryan O'Hearn</t>
+          <t>Connor Norby</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F87" t="n">
         <v>1.5</v>
       </c>
       <c r="G87" t="n">
-        <v>205</v>
+        <v>-196.5</v>
       </c>
       <c r="H87" t="n">
-        <v>0.3854</v>
+        <v>0.7072000000000001</v>
       </c>
       <c r="I87" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -22092,30 +22656,30 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>BAL vs MIN</t>
+          <t>OAK vs TOR</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Trevor Larnach</t>
+          <t>Ernie Clement</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G88" t="n">
-        <v>-115</v>
+        <v>-168</v>
       </c>
       <c r="H88" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.6761</v>
       </c>
       <c r="I88" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.0888</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -22144,12 +22708,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>STL vs TBR</t>
+          <t>COL vs MIA</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Xavier Edwards</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -22161,13 +22725,13 @@
         <v>1.5</v>
       </c>
       <c r="G89" t="n">
-        <v>-209</v>
+        <v>-170</v>
       </c>
       <c r="H89" t="n">
-        <v>0.7207</v>
+        <v>0.6768999999999999</v>
       </c>
       <c r="I89" t="n">
-        <v>0.0877</v>
+        <v>0.0907</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -22196,12 +22760,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>COL vs MIA</t>
+          <t>WSN vs CHC</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Connor Norby</t>
+          <t>Dansby Swanson</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -22213,13 +22777,13 @@
         <v>1.5</v>
       </c>
       <c r="G90" t="n">
-        <v>-196.5</v>
+        <v>-162.5</v>
       </c>
       <c r="H90" t="n">
-        <v>0.7072000000000001</v>
+        <v>0.6579</v>
       </c>
       <c r="I90" t="n">
-        <v>0.09030000000000001</v>
+        <v>0.078</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -22248,12 +22812,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>OAK vs TOR</t>
+          <t>WSN vs CHC</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Ernie Clement</t>
+          <t>Ian Happ</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -22265,13 +22829,13 @@
         <v>1.5</v>
       </c>
       <c r="G91" t="n">
-        <v>-168</v>
+        <v>-133</v>
       </c>
       <c r="H91" t="n">
-        <v>0.6761</v>
+        <v>0.6044</v>
       </c>
       <c r="I91" t="n">
-        <v>0.0888</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -22300,30 +22864,30 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>COL vs MIA</t>
+          <t>BAL vs MIN</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Xavier Edwards</t>
+          <t>Trevor Larnach</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G92" t="n">
-        <v>-170</v>
+        <v>-115</v>
       </c>
       <c r="H92" t="n">
-        <v>0.6768999999999999</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="I92" t="n">
-        <v>0.0907</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -22352,12 +22916,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>WSN vs CHC</t>
+          <t>CWS vs MIL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Ian Happ</t>
+          <t>Brandon Lockridge</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -22366,16 +22930,16 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G93" t="n">
-        <v>-133</v>
+        <v>-106</v>
       </c>
       <c r="H93" t="n">
-        <v>0.6044</v>
+        <v>0.6246</v>
       </c>
       <c r="I93" t="n">
-        <v>0.07439999999999999</v>
+        <v>0.1446</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -22404,30 +22968,30 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ARI vs LAD</t>
+          <t>LAD vs ARI</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Santiago Espinal</t>
+          <t>Ketel Marte</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G94" t="n">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="H94" t="n">
-        <v>0.6064000000000001</v>
+        <v>0.4777</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1771</v>
+        <v>0.0814</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -22456,12 +23020,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>CWS vs MIL</t>
+          <t>SDP vs DET</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Brandon Lockridge</t>
+          <t>Matt Vierling</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -22473,13 +23037,13 @@
         <v>0.5</v>
       </c>
       <c r="G95" t="n">
-        <v>-106</v>
+        <v>125</v>
       </c>
       <c r="H95" t="n">
-        <v>0.6246</v>
+        <v>0.5705</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1446</v>
+        <v>0.1567</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -22508,12 +23072,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CWS vs MIL</t>
+          <t>ARI vs LAD</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Santiago Espinal</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -22525,13 +23089,13 @@
         <v>0.5</v>
       </c>
       <c r="G96" t="n">
-        <v>-125</v>
+        <v>116</v>
       </c>
       <c r="H96" t="n">
-        <v>0.6313</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="I96" t="n">
-        <v>0.1166</v>
+        <v>0.1771</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -22565,7 +23129,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Matt Vierling</t>
+          <t>Jake Rogers</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -22577,13 +23141,13 @@
         <v>0.5</v>
       </c>
       <c r="G97" t="n">
-        <v>125</v>
+        <v>-110</v>
       </c>
       <c r="H97" t="n">
-        <v>0.5705</v>
+        <v>0.602</v>
       </c>
       <c r="I97" t="n">
-        <v>0.1567</v>
+        <v>0.1168</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -22612,12 +23176,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MIL vs CWS</t>
+          <t>NYM vs PIT</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Colson Montgomery</t>
+          <t>Ryan O'Hearn</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -22626,16 +23190,16 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G98" t="n">
-        <v>-170</v>
+        <v>205</v>
       </c>
       <c r="H98" t="n">
-        <v>0.6704</v>
+        <v>0.3854</v>
       </c>
       <c r="I98" t="n">
-        <v>0.0842</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -22664,12 +23228,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SDP vs DET</t>
+          <t>ARI vs LAD</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Jake Rogers</t>
+          <t>Miguel Rojas</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -22681,13 +23245,13 @@
         <v>0.5</v>
       </c>
       <c r="G99" t="n">
-        <v>-110</v>
+        <v>116</v>
       </c>
       <c r="H99" t="n">
-        <v>0.602</v>
+        <v>0.5123</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1168</v>
+        <v>0.083</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -22721,7 +23285,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Ketel Marte</t>
+          <t>Geraldo Perdomo</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -22730,16 +23294,16 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G100" t="n">
-        <v>137</v>
+        <v>-155</v>
       </c>
       <c r="H100" t="n">
-        <v>0.4777</v>
+        <v>0.6403</v>
       </c>
       <c r="I100" t="n">
-        <v>0.0814</v>
+        <v>0.0761</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -22768,12 +23332,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ARI vs LAD</t>
+          <t>DET vs SDP</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Miguel Rojas</t>
+          <t>Freddy Fermin</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -22785,13 +23349,13 @@
         <v>0.5</v>
       </c>
       <c r="G101" t="n">
-        <v>116</v>
+        <v>-105</v>
       </c>
       <c r="H101" t="n">
-        <v>0.5123</v>
+        <v>0.5414</v>
       </c>
       <c r="I101" t="n">
-        <v>0.083</v>
+        <v>0.0701</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -22825,7 +23389,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Geraldo Perdomo</t>
+          <t>Pavin Smith</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -22837,13 +23401,13 @@
         <v>0.5</v>
       </c>
       <c r="G102" t="n">
-        <v>-155</v>
+        <v>-124</v>
       </c>
       <c r="H102" t="n">
-        <v>0.6403</v>
+        <v>0.573</v>
       </c>
       <c r="I102" t="n">
-        <v>0.0761</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -22872,12 +23436,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>DET vs SDP</t>
+          <t>ARI vs LAD</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Freddy Fermin</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -22886,16 +23450,16 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G103" t="n">
-        <v>-105</v>
+        <v>-134</v>
       </c>
       <c r="H103" t="n">
-        <v>0.5414</v>
+        <v>0.6084000000000001</v>
       </c>
       <c r="I103" t="n">
-        <v>0.0701</v>
+        <v>0.0746</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -22924,30 +23488,30 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>WSN vs CHC</t>
+          <t>CLE vs SEA</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Nico Hoerner</t>
+          <t>Cal Raleigh</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G104" t="n">
-        <v>-153</v>
+        <v>-165</v>
       </c>
       <c r="H104" t="n">
-        <v>0.6441</v>
+        <v>0.7042</v>
       </c>
       <c r="I104" t="n">
-        <v>0.0794</v>
+        <v>0.1262</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -22976,30 +23540,30 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>BAL vs MIN</t>
+          <t>CWS vs MIL</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Byron Buxton</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G105" t="n">
-        <v>129</v>
+        <v>-125</v>
       </c>
       <c r="H105" t="n">
-        <v>0.4823</v>
+        <v>0.6313</v>
       </c>
       <c r="I105" t="n">
-        <v>0.0746</v>
+        <v>0.1166</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -23028,12 +23592,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>TOR vs OAK</t>
+          <t>MIN vs BAL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Brent Rooker</t>
+          <t>Pete Alonso</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -23045,13 +23609,13 @@
         <v>1.5</v>
       </c>
       <c r="G106" t="n">
-        <v>166</v>
+        <v>135</v>
       </c>
       <c r="H106" t="n">
-        <v>0.4369</v>
+        <v>0.47</v>
       </c>
       <c r="I106" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.0717</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -23080,30 +23644,30 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>NYY vs SFG</t>
+          <t>MIN vs BAL</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Taylor Ward</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F107" t="n">
         <v>0.5</v>
       </c>
       <c r="G107" t="n">
-        <v>102</v>
+        <v>-165</v>
       </c>
       <c r="H107" t="n">
-        <v>0.5429</v>
+        <v>0.6717</v>
       </c>
       <c r="I107" t="n">
-        <v>0.0808</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -23132,12 +23696,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>LAD vs ARI</t>
+          <t>BAL vs MIN</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Pavin Smith</t>
+          <t>Byron Buxton</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -23146,16 +23710,16 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G108" t="n">
-        <v>-124</v>
+        <v>129</v>
       </c>
       <c r="H108" t="n">
-        <v>0.573</v>
+        <v>0.4823</v>
       </c>
       <c r="I108" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.0746</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -23184,30 +23748,30 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>WSN vs CHC</t>
+          <t>SEA vs CLE</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Michael Busch</t>
+          <t>Kyle Manzardo</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G109" t="n">
-        <v>-2</v>
+        <v>-120</v>
       </c>
       <c r="H109" t="n">
-        <v>0.5424</v>
+        <v>0.6057</v>
       </c>
       <c r="I109" t="n">
-        <v>0.5093</v>
+        <v>0.1038</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -23241,25 +23805,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Alex Bregman</t>
+          <t>Michael Busch</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F110" t="n">
         <v>1.5</v>
       </c>
       <c r="G110" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H110" t="n">
-        <v>0.4486</v>
+        <v>0.5424</v>
       </c>
       <c r="I110" t="n">
-        <v>0.4313</v>
+        <v>0.5093</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -23288,12 +23852,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>TOR vs OAK</t>
+          <t>WSN vs CHC</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Nick Kurtz</t>
+          <t>Alex Bregman</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -23305,13 +23869,13 @@
         <v>1.5</v>
       </c>
       <c r="G111" t="n">
-        <v>141</v>
+        <v>-1</v>
       </c>
       <c r="H111" t="n">
-        <v>0.5341</v>
+        <v>0.4486</v>
       </c>
       <c r="I111" t="n">
-        <v>0.1437</v>
+        <v>0.4313</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -23340,30 +23904,30 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>COL vs MIA</t>
+          <t>TOR vs OAK</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Nick Kurtz</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G112" t="n">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="H112" t="n">
-        <v>0.4978</v>
+        <v>0.5341</v>
       </c>
       <c r="I112" t="n">
-        <v>0.1293</v>
+        <v>0.1437</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -23392,30 +23956,30 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>TEX vs PHI</t>
+          <t>COL vs MIA</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Kyle Schwarber</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F113" t="n">
         <v>0.5</v>
       </c>
       <c r="G113" t="n">
-        <v>-160</v>
+        <v>153</v>
       </c>
       <c r="H113" t="n">
-        <v>0.6923</v>
+        <v>0.4978</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1205</v>
+        <v>0.1293</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -23444,30 +24008,30 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>MIA vs COL</t>
+          <t>TEX vs PHI</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Kyle Karros</t>
+          <t>Kyle Schwarber</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F114" t="n">
         <v>0.5</v>
       </c>
       <c r="G114" t="n">
-        <v>-108</v>
+        <v>-160</v>
       </c>
       <c r="H114" t="n">
-        <v>0.6086</v>
+        <v>0.6923</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1339</v>
+        <v>0.1205</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -23496,12 +24060,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>CHC vs WSN</t>
+          <t>MIA vs COL</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Jacob Young</t>
+          <t>Kyle Karros</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -23513,13 +24077,13 @@
         <v>0.5</v>
       </c>
       <c r="G115" t="n">
-        <v>-106.5</v>
+        <v>-108</v>
       </c>
       <c r="H115" t="n">
-        <v>0.5992</v>
+        <v>0.6086</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1177</v>
+        <v>0.1339</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -23553,25 +24117,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>James Wood</t>
+          <t>Jacob Young</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G116" t="n">
-        <v>158.5</v>
+        <v>-106.5</v>
       </c>
       <c r="H116" t="n">
-        <v>0.4611</v>
+        <v>0.5992</v>
       </c>
       <c r="I116" t="n">
-        <v>0.0968</v>
+        <v>0.1177</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -23600,12 +24164,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>BAL vs MIN</t>
+          <t>CHC vs WSN</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Matt Wallner</t>
+          <t>James Wood</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -23614,16 +24178,16 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G117" t="n">
-        <v>-125</v>
+        <v>158.5</v>
       </c>
       <c r="H117" t="n">
-        <v>0.6262</v>
+        <v>0.4611</v>
       </c>
       <c r="I117" t="n">
-        <v>0.1115</v>
+        <v>0.0968</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -23652,12 +24216,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>NYM vs PIT</t>
+          <t>BAL vs MIN</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Brandon Lowe</t>
+          <t>Matt Wallner</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -23672,10 +24236,10 @@
         <v>-125</v>
       </c>
       <c r="H118" t="n">
-        <v>0.6173999999999999</v>
+        <v>0.6262</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1027</v>
+        <v>0.1115</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -23709,25 +24273,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Jake Mangum</t>
+          <t>Brandon Lowe</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F119" t="n">
         <v>0.5</v>
       </c>
       <c r="G119" t="n">
-        <v>130</v>
+        <v>-125</v>
       </c>
       <c r="H119" t="n">
-        <v>0.4946</v>
+        <v>0.6173999999999999</v>
       </c>
       <c r="I119" t="n">
-        <v>0.0934</v>
+        <v>0.1027</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -23756,12 +24320,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>NYY vs SFG</t>
+          <t>NYM vs PIT</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Casey Schmitt</t>
+          <t>Jake Mangum</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -23770,16 +24334,16 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G120" t="n">
-        <v>-186</v>
+        <v>130</v>
       </c>
       <c r="H120" t="n">
-        <v>0.724</v>
+        <v>0.4946</v>
       </c>
       <c r="I120" t="n">
-        <v>0.1165</v>
+        <v>0.0934</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -23808,12 +24372,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>STL vs TBR</t>
+          <t>NYY vs SFG</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Casey Schmitt</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -23825,13 +24389,13 @@
         <v>1.5</v>
       </c>
       <c r="G121" t="n">
-        <v>-350</v>
+        <v>-186</v>
       </c>
       <c r="H121" t="n">
-        <v>0.827</v>
+        <v>0.724</v>
       </c>
       <c r="I121" t="n">
-        <v>0.0929</v>
+        <v>0.1165</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -23860,12 +24424,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>COL vs MIA</t>
+          <t>STL vs TBR</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Otto Lopez</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -23877,13 +24441,13 @@
         <v>1.5</v>
       </c>
       <c r="G122" t="n">
-        <v>-155</v>
+        <v>-350</v>
       </c>
       <c r="H122" t="n">
-        <v>0.6829</v>
+        <v>0.827</v>
       </c>
       <c r="I122" t="n">
-        <v>0.1141</v>
+        <v>0.0929</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
@@ -23912,12 +24476,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>BOS vs CIN</t>
+          <t>COL vs MIA</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Ke'Bryan Hayes</t>
+          <t>Otto Lopez</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -23926,16 +24490,16 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G123" t="n">
-        <v>102</v>
+        <v>-155</v>
       </c>
       <c r="H123" t="n">
-        <v>0.5485</v>
+        <v>0.6829</v>
       </c>
       <c r="I123" t="n">
-        <v>0.0895</v>
+        <v>0.1141</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -23964,12 +24528,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>TBR vs STL</t>
+          <t>BOS vs CIN</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Jordan Walker</t>
+          <t>Ke'Bryan Hayes</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -23978,16 +24542,16 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G124" t="n">
-        <v>-290</v>
+        <v>102</v>
       </c>
       <c r="H124" t="n">
-        <v>0.7907999999999999</v>
+        <v>0.5485</v>
       </c>
       <c r="I124" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.0895</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -24016,30 +24580,30 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>MIN vs BAL</t>
+          <t>TBR vs STL</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Taylor Ward</t>
+          <t>Jordan Walker</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G125" t="n">
-        <v>-165</v>
+        <v>-290</v>
       </c>
       <c r="H125" t="n">
-        <v>0.6717</v>
+        <v>0.7907999999999999</v>
       </c>
       <c r="I125" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -24068,30 +24632,30 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>OAK vs TOR</t>
+          <t>TOR vs OAK</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Myles Straw</t>
+          <t>Brent Rooker</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F126" t="n">
         <v>1.5</v>
       </c>
       <c r="G126" t="n">
-        <v>-355</v>
+        <v>166</v>
       </c>
       <c r="H126" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.4369</v>
       </c>
       <c r="I126" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -24120,30 +24684,30 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>TOR vs OAK</t>
+          <t>OAK vs TOR</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Shea Langeliers</t>
+          <t>Myles Straw</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F127" t="n">
         <v>1.5</v>
       </c>
       <c r="G127" t="n">
-        <v>128</v>
+        <v>-355</v>
       </c>
       <c r="H127" t="n">
-        <v>0.4855</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="I127" t="n">
-        <v>0.076</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -24172,12 +24736,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>ARI vs LAD</t>
+          <t>NYY vs SFG</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -24186,16 +24750,16 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G128" t="n">
-        <v>-134</v>
+        <v>102</v>
       </c>
       <c r="H128" t="n">
-        <v>0.6084000000000001</v>
+        <v>0.5429</v>
       </c>
       <c r="I128" t="n">
-        <v>0.0746</v>
+        <v>0.0808</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -24206,6 +24770,162 @@
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>TOR vs OAK</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Shea Langeliers</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G129" t="n">
+        <v>128</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.4855</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>MIL vs CWS</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Colson Montgomery</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G130" t="n">
+        <v>-170</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.6704</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.0842</v>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Hitter TB</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>SEA vs CLE</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>CJ Kayfus</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G131" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.5321</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.0713</v>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
         </is>
@@ -24222,7 +24942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N48"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25744,12 +26464,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NYY vs SFG</t>
+          <t>SFG vs NYY</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Robbie Ray</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -25758,16 +26478,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="G29" t="n">
-        <v>100.5</v>
+        <v>-120</v>
       </c>
       <c r="H29" t="n">
-        <v>0.738</v>
+        <v>0.6915</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2774</v>
+        <v>0.1866</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -25778,10 +26498,10 @@
         <v>16</v>
       </c>
       <c r="L29" t="n">
-        <v>100.5</v>
+        <v>83.33</v>
       </c>
       <c r="M29" t="n">
-        <v>50.25</v>
+        <v>41.67</v>
       </c>
       <c r="N29" t="inlineStr"/>
     </row>
@@ -25906,12 +26626,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SFG vs NYY</t>
+          <t>NYY vs SFG</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Cam Schlittler</t>
+          <t>Robbie Ray</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -25920,16 +26640,16 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="G32" t="n">
-        <v>-120</v>
+        <v>100.5</v>
       </c>
       <c r="H32" t="n">
-        <v>0.6915</v>
+        <v>0.738</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1866</v>
+        <v>0.2774</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -25940,10 +26660,10 @@
         <v>16</v>
       </c>
       <c r="L32" t="n">
-        <v>83.33</v>
+        <v>100.5</v>
       </c>
       <c r="M32" t="n">
-        <v>41.67</v>
+        <v>50.25</v>
       </c>
       <c r="N32" t="inlineStr"/>
     </row>
@@ -26068,12 +26788,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BAL vs MIN</t>
+          <t>NYY vs SFG</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Taj Bradley</t>
+          <t>Tyler Mahle</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -26085,13 +26805,13 @@
         <v>14.5</v>
       </c>
       <c r="G35" t="n">
-        <v>-154</v>
+        <v>-165.5</v>
       </c>
       <c r="H35" t="n">
-        <v>0.6834</v>
+        <v>0.7963</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1233</v>
+        <v>0.2191</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -26120,12 +26840,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ATL vs KCR</t>
+          <t>MIL vs CWS</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>Sean Burke</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -26134,16 +26854,16 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="G36" t="n">
-        <v>-121</v>
+        <v>-106</v>
       </c>
       <c r="H36" t="n">
-        <v>0.6596</v>
+        <v>0.8197</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1486</v>
+        <v>0.3432</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -26172,12 +26892,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MIA vs COL</t>
+          <t>BAL vs MIN</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Michael Lorenzen</t>
+          <t>Taj Bradley</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -26186,16 +26906,16 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="G37" t="n">
-        <v>108</v>
+        <v>-154</v>
       </c>
       <c r="H37" t="n">
-        <v>0.6125</v>
+        <v>0.6834</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1676</v>
+        <v>0.1233</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -26224,12 +26944,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>TEX vs PHI</t>
+          <t>ATL vs KCR</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -26241,13 +26961,13 @@
         <v>15.5</v>
       </c>
       <c r="G38" t="n">
-        <v>-105</v>
+        <v>-121</v>
       </c>
       <c r="H38" t="n">
-        <v>0.6395</v>
+        <v>0.6596</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1662</v>
+        <v>0.1486</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -26276,12 +26996,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MIN vs BAL</t>
+          <t>MIA vs COL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Kyle Bradish</t>
+          <t>Michael Lorenzen</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -26293,13 +27013,13 @@
         <v>15.5</v>
       </c>
       <c r="G39" t="n">
-        <v>123.5</v>
+        <v>108</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6048</v>
+        <v>0.6125</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1899</v>
+        <v>0.1676</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -26328,12 +27048,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BOS vs CIN</t>
+          <t>TEX vs PHI</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Brady Singer</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -26345,13 +27065,13 @@
         <v>15.5</v>
       </c>
       <c r="G40" t="n">
-        <v>106</v>
+        <v>-105</v>
       </c>
       <c r="H40" t="n">
-        <v>0.6352</v>
+        <v>0.6395</v>
       </c>
       <c r="I40" t="n">
-        <v>0.188</v>
+        <v>0.1662</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -26380,12 +27100,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PIT vs NYM</t>
+          <t>MIN vs BAL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>David Peterson</t>
+          <t>Kyle Bradish</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -26397,13 +27117,13 @@
         <v>15.5</v>
       </c>
       <c r="G41" t="n">
-        <v>110</v>
+        <v>123.5</v>
       </c>
       <c r="H41" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.6048</v>
       </c>
       <c r="I41" t="n">
-        <v>0.2286</v>
+        <v>0.1899</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -26432,12 +27152,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NYM vs PIT</t>
+          <t>WSN vs CHC</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Mitch Keller</t>
+          <t>Cade Horton</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -26449,13 +27169,13 @@
         <v>15.5</v>
       </c>
       <c r="G42" t="n">
-        <v>120.5</v>
+        <v>141.5</v>
       </c>
       <c r="H42" t="n">
-        <v>0.6752</v>
+        <v>0.6026</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2583</v>
+        <v>0.2149</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -26484,12 +27204,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>HOU vs LAA</t>
+          <t>PIT vs NYM</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Reid Detmers</t>
+          <t>David Peterson</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -26498,16 +27218,16 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="G43" t="n">
-        <v>-147.5</v>
+        <v>110</v>
       </c>
       <c r="H43" t="n">
-        <v>0.7408</v>
+        <v>0.6647999999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1903</v>
+        <v>0.2286</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -26536,12 +27256,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>STL vs TBR</t>
+          <t>NYM vs PIT</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Joe Boyle</t>
+          <t>Mitch Keller</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -26550,16 +27270,16 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="G44" t="n">
-        <v>-128.5</v>
+        <v>120.5</v>
       </c>
       <c r="H44" t="n">
-        <v>0.789</v>
+        <v>0.6752</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2662</v>
+        <v>0.2583</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -26588,12 +27308,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>TOR vs OAK</t>
+          <t>HOU vs LAA</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Jeffrey Springs</t>
+          <t>Reid Detmers</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -26605,13 +27325,13 @@
         <v>14.5</v>
       </c>
       <c r="G45" t="n">
-        <v>-165</v>
+        <v>-147.5</v>
       </c>
       <c r="H45" t="n">
-        <v>0.7914</v>
+        <v>0.7408</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2107</v>
+        <v>0.1903</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -26640,12 +27360,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MIL vs CWS</t>
+          <t>STL vs TBR</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Sean Burke</t>
+          <t>Joe Boyle</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -26657,13 +27377,13 @@
         <v>14.5</v>
       </c>
       <c r="G46" t="n">
-        <v>-106</v>
+        <v>-128.5</v>
       </c>
       <c r="H46" t="n">
-        <v>0.8197</v>
+        <v>0.789</v>
       </c>
       <c r="I46" t="n">
-        <v>0.3432</v>
+        <v>0.2662</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -26692,12 +27412,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>WSN vs CHC</t>
+          <t>TOR vs OAK</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Cade Horton</t>
+          <t>Jeffrey Springs</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -26706,16 +27426,16 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="G47" t="n">
-        <v>141.5</v>
+        <v>-165</v>
       </c>
       <c r="H47" t="n">
-        <v>0.6026</v>
+        <v>0.7914</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2149</v>
+        <v>0.2107</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -26744,12 +27464,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NYY vs SFG</t>
+          <t>SEA vs CLE</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Tyler Mahle</t>
+          <t>Joey Cantillo</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -26761,13 +27481,13 @@
         <v>14.5</v>
       </c>
       <c r="G48" t="n">
-        <v>-165.5</v>
+        <v>-151.5</v>
       </c>
       <c r="H48" t="n">
-        <v>0.7963</v>
+        <v>0.9568</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2191</v>
+        <v>0.3983</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -26778,6 +27498,110 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Add opp_bb_pct to pitcher outs, bullpen features to totals, bullpen availability utility; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Use confirmed SP from lineup card, fall back to probable pitcher; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Cap pitcher outs to 1 pick per game (not per pitcher); Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Gate all 5 models on confirmed starting pitchers; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>BOS vs CIN</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Brady Singer</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G49" t="n">
+        <v>106</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.6352</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Add opp_bb_pct to pitcher outs, bullpen features to totals, bullpen availability utility; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Use confirmed SP from lineup card, fall back to probable pitcher; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Cap pitcher outs to 1 pick per game (not per pitcher); Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Gate all 5 models on confirmed starting pitchers; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Pitcher Outs</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>LAD vs ARI</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Eduardo Rodriguez</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-117</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.6627999999999999</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.1628</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Add opp_bb_pct to pitcher outs, bullpen features to totals, bullpen availability utility; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Use confirmed SP from lineup card, fall back to probable pitcher; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Cap pitcher outs to 1 pick per game (not per pitcher); Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Gate all 5 models on confirmed starting pitchers; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
         </is>
@@ -26794,7 +27618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27962,12 +28786,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NYY @ SFG</t>
+          <t>KCR @ ATL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NYY @ SFG</t>
+          <t>KCR @ ATL</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -27977,29 +28801,29 @@
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
-        <v>-102</v>
+        <v>110</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0.5887</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5239</v>
+        <v>0.1428</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>away_1st=0 home_1st=0</t>
+          <t>away_1st=0 home_1st=1</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>-100</v>
+        <v>110</v>
       </c>
       <c r="M22" t="n">
-        <v>-50</v>
+        <v>55</v>
       </c>
       <c r="N22" t="inlineStr"/>
     </row>
@@ -28016,12 +28840,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>KCR @ ATL</t>
+          <t>NYY @ SFG</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>KCR @ ATL</t>
+          <t>NYY @ SFG</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -28031,29 +28855,29 @@
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
-        <v>110</v>
+        <v>-102</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5887</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1428</v>
+        <v>0.5239</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>away_1st=0 home_1st=1</t>
+          <t>away_1st=0 home_1st=0</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>110</v>
+        <v>-100</v>
       </c>
       <c r="M23" t="n">
-        <v>55</v>
+        <v>-50</v>
       </c>
       <c r="N23" t="inlineStr"/>
     </row>
@@ -28124,12 +28948,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CWS @ MIL</t>
+          <t>ARI @ LAD</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CWS @ MIL</t>
+          <t>ARI @ LAD</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -28139,13 +28963,13 @@
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
-        <v>-107</v>
+        <v>-124.5</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5887</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1026</v>
+        <v>0.479</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -28174,12 +28998,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MIN @ BAL</t>
+          <t>DET @ SDP</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MIN @ BAL</t>
+          <t>DET @ SDP</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -28189,13 +29013,13 @@
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
-        <v>-0.5</v>
+        <v>-115</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0.5887</v>
       </c>
       <c r="I26" t="n">
-        <v>0.9913</v>
+        <v>0.0872</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -28224,12 +29048,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>WSN @ CHC</t>
+          <t>CWS @ MIL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>WSN @ CHC</t>
+          <t>CWS @ MIL</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -28239,13 +29063,13 @@
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
-        <v>-132.5</v>
+        <v>-107</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0.5887</v>
       </c>
       <c r="I27" t="n">
-        <v>0.637</v>
+        <v>0.1026</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -28274,12 +29098,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>TBR @ STL</t>
+          <t>NYY @ SFG</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>TBR @ STL</t>
+          <t>NYY @ SFG</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -28289,13 +29113,13 @@
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
-        <v>114</v>
+        <v>-107</v>
       </c>
       <c r="H28" t="n">
         <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5615</v>
+        <v>0.5158</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -28324,12 +29148,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PIT @ NYM</t>
+          <t>OAK @ TOR</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>PIT @ NYM</t>
+          <t>OAK @ TOR</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -28339,13 +29163,13 @@
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
-        <v>107</v>
+        <v>-121.5</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0.5887</v>
       </c>
       <c r="I29" t="n">
-        <v>0.547</v>
+        <v>0.075</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -28374,12 +29198,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>LAA @ HOU</t>
+          <t>TEX @ PHI</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LAA @ HOU</t>
+          <t>TEX @ PHI</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -28389,13 +29213,13 @@
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
-        <v>-119.5</v>
+        <v>-106</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0.5704</v>
       </c>
       <c r="I30" t="n">
-        <v>0.4893</v>
+        <v>0.0887</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -28424,12 +29248,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>KCR @ ATL</t>
+          <t>COL @ MIA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>KCR @ ATL</t>
+          <t>COL @ MIA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -28439,13 +29263,13 @@
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
-        <v>-122.5</v>
+        <v>107.5</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0.5887</v>
       </c>
       <c r="I31" t="n">
-        <v>0.4842</v>
+        <v>0.1359</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -28524,12 +29348,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>COL @ MIA</t>
+          <t>LAA @ HOU</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>COL @ MIA</t>
+          <t>LAA @ HOU</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -28539,13 +29363,13 @@
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
-        <v>107.5</v>
+        <v>-119.5</v>
       </c>
       <c r="H33" t="n">
-        <v>0.5887</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1359</v>
+        <v>0.4893</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -28574,12 +29398,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>TEX @ PHI</t>
+          <t>PIT @ NYM</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>TEX @ PHI</t>
+          <t>PIT @ NYM</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -28589,13 +29413,13 @@
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
-        <v>-106</v>
+        <v>107</v>
       </c>
       <c r="H34" t="n">
-        <v>0.5704</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0887</v>
+        <v>0.547</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -28624,12 +29448,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>OAK @ TOR</t>
+          <t>TBR @ STL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>OAK @ TOR</t>
+          <t>TBR @ STL</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -28639,13 +29463,13 @@
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>-121.5</v>
+        <v>114</v>
       </c>
       <c r="H35" t="n">
-        <v>0.5887</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>0.075</v>
+        <v>0.5615</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -28674,12 +29498,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NYY @ SFG</t>
+          <t>WSN @ CHC</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NYY @ SFG</t>
+          <t>WSN @ CHC</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -28689,13 +29513,13 @@
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>-107</v>
+        <v>-132.5</v>
       </c>
       <c r="H36" t="n">
         <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>0.5158</v>
+        <v>0.637</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -28724,12 +29548,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DET @ SDP</t>
+          <t>MIN @ BAL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>DET @ SDP</t>
+          <t>MIN @ BAL</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -28739,13 +29563,13 @@
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
-        <v>-115</v>
+        <v>-0.5</v>
       </c>
       <c r="H37" t="n">
-        <v>0.5887</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>0.0872</v>
+        <v>0.9913</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -28761,6 +29585,106 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>KCR @ ATL</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>KCR @ ATL</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>YRFI</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="n">
+        <v>-122.5</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.4842</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix NRFI scoreboard period param and Discord embed truncation; Fix NRFI odds: parse from scoreboard markets instead of props endpoint; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Gate NRFI scoring on confirmed lineups, consistent with other models; Fix 04_export_nrfi.py DataFrame iteration and lineup format bugs; Fix API crash guards and FanGraphs splits method errors; Add NRFI/YRFI fifth model and rebuild all four existing models; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>NRFI/YRFI</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CLE @ SEA</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>CLE @ SEA</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>YRFI</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="n">
+        <v>109</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.5887</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.1388</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix NRFI scoreboard period param and Discord embed truncation; Fix NRFI odds: parse from scoreboard markets instead of props endpoint; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Gate NRFI scoring on confirmed lineups, consistent with other models; Fix 04_export_nrfi.py DataFrame iteration and lineup format bugs; Fix API crash guards and FanGraphs splits method errors; Add NRFI/YRFI fifth model and rebuild all four existing models; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tracking/picks.xlsx
+++ b/tracking/picks.xlsx
@@ -9648,12 +9648,20 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K172" t="inlineStr"/>
-      <c r="L172" t="inlineStr"/>
-      <c r="M172" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>7-8</t>
+        </is>
+      </c>
+      <c r="L172" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M172" t="n">
+        <v>-50</v>
+      </c>
       <c r="N172" t="inlineStr">
         <is>
           <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -9698,12 +9706,20 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr"/>
-      <c r="M173" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>5-6</t>
+        </is>
+      </c>
+      <c r="L173" t="n">
+        <v>115</v>
+      </c>
+      <c r="M173" t="n">
+        <v>57.5</v>
+      </c>
       <c r="N173" t="inlineStr">
         <is>
           <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -9748,12 +9764,20 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K174" t="inlineStr"/>
-      <c r="L174" t="inlineStr"/>
-      <c r="M174" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>5-6</t>
+        </is>
+      </c>
+      <c r="L174" t="n">
+        <v>95.23999999999999</v>
+      </c>
+      <c r="M174" t="n">
+        <v>47.62</v>
+      </c>
       <c r="N174" t="inlineStr">
         <is>
           <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -9800,7 +9824,7 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>ODDS_ERR</t>
         </is>
       </c>
       <c r="K175" t="inlineStr"/>
@@ -9852,7 +9876,7 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>ODDS_ERR</t>
         </is>
       </c>
       <c r="K176" t="inlineStr"/>
@@ -9904,12 +9928,18 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr"/>
-      <c r="L177" t="inlineStr"/>
-      <c r="M177" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K177" t="n">
+        <v>0</v>
+      </c>
+      <c r="L177" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M177" t="n">
+        <v>-50</v>
+      </c>
       <c r="N177" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -9956,12 +9986,18 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr"/>
-      <c r="L178" t="inlineStr"/>
-      <c r="M178" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K178" t="n">
+        <v>4</v>
+      </c>
+      <c r="L178" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M178" t="n">
+        <v>-50</v>
+      </c>
       <c r="N178" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -10008,12 +10044,18 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K179" t="inlineStr"/>
-      <c r="L179" t="inlineStr"/>
-      <c r="M179" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K179" t="n">
+        <v>0</v>
+      </c>
+      <c r="L179" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M179" t="n">
+        <v>-50</v>
+      </c>
       <c r="N179" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -10060,12 +10102,18 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K180" t="inlineStr"/>
-      <c r="L180" t="inlineStr"/>
-      <c r="M180" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L180" t="n">
+        <v>92.59</v>
+      </c>
+      <c r="M180" t="n">
+        <v>46.3</v>
+      </c>
       <c r="N180" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -10112,12 +10160,18 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K181" t="inlineStr"/>
-      <c r="L181" t="inlineStr"/>
-      <c r="M181" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K181" t="n">
+        <v>0</v>
+      </c>
+      <c r="L181" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="M181" t="n">
+        <v>46.95</v>
+      </c>
       <c r="N181" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -10164,12 +10218,18 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K182" t="inlineStr"/>
-      <c r="L182" t="inlineStr"/>
-      <c r="M182" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K182" t="n">
+        <v>4</v>
+      </c>
+      <c r="L182" t="n">
+        <v>158.5</v>
+      </c>
+      <c r="M182" t="n">
+        <v>79.25</v>
+      </c>
       <c r="N182" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -10216,12 +10276,18 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K183" t="inlineStr"/>
-      <c r="L183" t="inlineStr"/>
-      <c r="M183" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K183" t="n">
+        <v>0</v>
+      </c>
+      <c r="L183" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M183" t="n">
+        <v>-50</v>
+      </c>
       <c r="N183" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -10268,12 +10334,18 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K184" t="inlineStr"/>
-      <c r="L184" t="inlineStr"/>
-      <c r="M184" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K184" t="n">
+        <v>1</v>
+      </c>
+      <c r="L184" t="n">
+        <v>80</v>
+      </c>
+      <c r="M184" t="n">
+        <v>40</v>
+      </c>
       <c r="N184" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -10320,12 +10392,18 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
-      <c r="M185" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K185" t="n">
+        <v>3</v>
+      </c>
+      <c r="L185" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M185" t="n">
+        <v>-50</v>
+      </c>
       <c r="N185" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -10372,12 +10450,18 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr"/>
-      <c r="M186" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K186" t="n">
+        <v>0</v>
+      </c>
+      <c r="L186" t="n">
+        <v>53.76</v>
+      </c>
+      <c r="M186" t="n">
+        <v>26.88</v>
+      </c>
       <c r="N186" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -10424,12 +10508,18 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr"/>
-      <c r="M187" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K187" t="n">
+        <v>0</v>
+      </c>
+      <c r="L187" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="M187" t="n">
+        <v>14.29</v>
+      </c>
       <c r="N187" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -10476,12 +10566,18 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr"/>
-      <c r="M188" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K188" t="n">
+        <v>1</v>
+      </c>
+      <c r="L188" t="n">
+        <v>64.52</v>
+      </c>
+      <c r="M188" t="n">
+        <v>32.26</v>
+      </c>
       <c r="N188" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -10528,12 +10624,18 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr"/>
-      <c r="M189" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K189" t="n">
+        <v>0</v>
+      </c>
+      <c r="L189" t="n">
+        <v>102</v>
+      </c>
+      <c r="M189" t="n">
+        <v>51</v>
+      </c>
       <c r="N189" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -10580,12 +10682,18 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K190" t="inlineStr"/>
-      <c r="L190" t="inlineStr"/>
-      <c r="M190" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K190" t="n">
+        <v>0</v>
+      </c>
+      <c r="L190" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="M190" t="n">
+        <v>17.24</v>
+      </c>
       <c r="N190" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -10632,12 +10740,18 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr"/>
-      <c r="L191" t="inlineStr"/>
-      <c r="M191" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K191" t="n">
+        <v>1</v>
+      </c>
+      <c r="L191" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M191" t="n">
+        <v>-50</v>
+      </c>
       <c r="N191" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -10684,12 +10798,18 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr"/>
-      <c r="M192" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K192" t="n">
+        <v>0</v>
+      </c>
+      <c r="L192" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M192" t="n">
+        <v>-50</v>
+      </c>
       <c r="N192" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -10736,12 +10856,18 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K193" t="inlineStr"/>
-      <c r="L193" t="inlineStr"/>
-      <c r="M193" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K193" t="n">
+        <v>1</v>
+      </c>
+      <c r="L193" t="n">
+        <v>28.17</v>
+      </c>
+      <c r="M193" t="n">
+        <v>14.08</v>
+      </c>
       <c r="N193" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -10788,12 +10914,18 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K194" t="inlineStr"/>
-      <c r="L194" t="inlineStr"/>
-      <c r="M194" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K194" t="n">
+        <v>0</v>
+      </c>
+      <c r="L194" t="n">
+        <v>102</v>
+      </c>
+      <c r="M194" t="n">
+        <v>51</v>
+      </c>
       <c r="N194" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -10840,12 +10972,18 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K195" t="inlineStr"/>
-      <c r="L195" t="inlineStr"/>
-      <c r="M195" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K195" t="n">
+        <v>5</v>
+      </c>
+      <c r="L195" t="n">
+        <v>128</v>
+      </c>
+      <c r="M195" t="n">
+        <v>64</v>
+      </c>
       <c r="N195" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -10892,12 +11030,18 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K196" t="inlineStr"/>
-      <c r="L196" t="inlineStr"/>
-      <c r="M196" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K196" t="n">
+        <v>2</v>
+      </c>
+      <c r="L196" t="n">
+        <v>129</v>
+      </c>
+      <c r="M196" t="n">
+        <v>64.5</v>
+      </c>
       <c r="N196" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -10944,12 +11088,18 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K197" t="inlineStr"/>
-      <c r="L197" t="inlineStr"/>
-      <c r="M197" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K197" t="n">
+        <v>1</v>
+      </c>
+      <c r="L197" t="n">
+        <v>58.82</v>
+      </c>
+      <c r="M197" t="n">
+        <v>29.41</v>
+      </c>
       <c r="N197" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -10996,12 +11146,18 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K198" t="inlineStr"/>
-      <c r="L198" t="inlineStr"/>
-      <c r="M198" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K198" t="n">
+        <v>1</v>
+      </c>
+      <c r="L198" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M198" t="n">
+        <v>-50</v>
+      </c>
       <c r="N198" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -11048,12 +11204,18 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K199" t="inlineStr"/>
-      <c r="L199" t="inlineStr"/>
-      <c r="M199" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K199" t="n">
+        <v>1</v>
+      </c>
+      <c r="L199" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M199" t="n">
+        <v>-50</v>
+      </c>
       <c r="N199" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -11100,12 +11262,18 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K200" t="inlineStr"/>
-      <c r="L200" t="inlineStr"/>
-      <c r="M200" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K200" t="n">
+        <v>0</v>
+      </c>
+      <c r="L200" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M200" t="n">
+        <v>-50</v>
+      </c>
       <c r="N200" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -11152,12 +11320,18 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr"/>
-      <c r="L201" t="inlineStr"/>
-      <c r="M201" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K201" t="n">
+        <v>2</v>
+      </c>
+      <c r="L201" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M201" t="n">
+        <v>-50</v>
+      </c>
       <c r="N201" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -11204,12 +11378,18 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K202" t="inlineStr"/>
-      <c r="L202" t="inlineStr"/>
-      <c r="M202" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K202" t="n">
+        <v>0</v>
+      </c>
+      <c r="L202" t="n">
+        <v>50.89</v>
+      </c>
+      <c r="M202" t="n">
+        <v>25.45</v>
+      </c>
       <c r="N202" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -11256,12 +11436,18 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K203" t="inlineStr"/>
-      <c r="L203" t="inlineStr"/>
-      <c r="M203" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K203" t="n">
+        <v>2</v>
+      </c>
+      <c r="L203" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M203" t="n">
+        <v>-50</v>
+      </c>
       <c r="N203" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -11308,12 +11494,18 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K204" t="inlineStr"/>
-      <c r="L204" t="inlineStr"/>
-      <c r="M204" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K204" t="n">
+        <v>1</v>
+      </c>
+      <c r="L204" t="n">
+        <v>58.82</v>
+      </c>
+      <c r="M204" t="n">
+        <v>29.41</v>
+      </c>
       <c r="N204" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -11360,12 +11552,18 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K205" t="inlineStr"/>
-      <c r="L205" t="inlineStr"/>
-      <c r="M205" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K205" t="n">
+        <v>0</v>
+      </c>
+      <c r="L205" t="n">
+        <v>61.54</v>
+      </c>
+      <c r="M205" t="n">
+        <v>30.77</v>
+      </c>
       <c r="N205" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -11412,12 +11610,18 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K206" t="inlineStr"/>
-      <c r="L206" t="inlineStr"/>
-      <c r="M206" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K206" t="n">
+        <v>4</v>
+      </c>
+      <c r="L206" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M206" t="n">
+        <v>-50</v>
+      </c>
       <c r="N206" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -11464,12 +11668,18 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K207" t="inlineStr"/>
-      <c r="L207" t="inlineStr"/>
-      <c r="M207" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K207" t="n">
+        <v>2</v>
+      </c>
+      <c r="L207" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M207" t="n">
+        <v>-50</v>
+      </c>
       <c r="N207" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -11516,12 +11726,18 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K208" t="inlineStr"/>
-      <c r="L208" t="inlineStr"/>
-      <c r="M208" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K208" t="n">
+        <v>16</v>
+      </c>
+      <c r="L208" t="n">
+        <v>60.61</v>
+      </c>
+      <c r="M208" t="n">
+        <v>30.3</v>
+      </c>
       <c r="N208" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Add opp_bb_pct to pitcher outs, bullpen features to totals, bullpen availability utility; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Use confirmed SP from lineup card, fall back to probable pitcher; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Cap pitcher outs to 1 pick per game (not per pitcher); Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Gate all 5 models on confirmed starting pitchers; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -11568,12 +11784,18 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K209" t="inlineStr"/>
-      <c r="L209" t="inlineStr"/>
-      <c r="M209" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K209" t="n">
+        <v>18</v>
+      </c>
+      <c r="L209" t="n">
+        <v>77.81999999999999</v>
+      </c>
+      <c r="M209" t="n">
+        <v>38.91</v>
+      </c>
       <c r="N209" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Add opp_bb_pct to pitcher outs, bullpen features to totals, bullpen availability utility; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Use confirmed SP from lineup card, fall back to probable pitcher; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Cap pitcher outs to 1 pick per game (not per pitcher); Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Gate all 5 models on confirmed starting pitchers; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -11620,12 +11842,18 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K210" t="inlineStr"/>
-      <c r="L210" t="inlineStr"/>
-      <c r="M210" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K210" t="n">
+        <v>14</v>
+      </c>
+      <c r="L210" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M210" t="n">
+        <v>-50</v>
+      </c>
       <c r="N210" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Add opp_bb_pct to pitcher outs, bullpen features to totals, bullpen availability utility; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Use confirmed SP from lineup card, fall back to probable pitcher; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Cap pitcher outs to 1 pick per game (not per pitcher); Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Gate all 5 models on confirmed starting pitchers; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -11672,12 +11900,18 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K211" t="inlineStr"/>
-      <c r="L211" t="inlineStr"/>
-      <c r="M211" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K211" t="n">
+        <v>18</v>
+      </c>
+      <c r="L211" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="M211" t="n">
+        <v>60.25</v>
+      </c>
       <c r="N211" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Add opp_bb_pct to pitcher outs, bullpen features to totals, bullpen availability utility; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Use confirmed SP from lineup card, fall back to probable pitcher; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Cap pitcher outs to 1 pick per game (not per pitcher); Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Gate all 5 models on confirmed starting pitchers; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -11724,12 +11958,18 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K212" t="inlineStr"/>
-      <c r="L212" t="inlineStr"/>
-      <c r="M212" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K212" t="n">
+        <v>16</v>
+      </c>
+      <c r="L212" t="n">
+        <v>110</v>
+      </c>
+      <c r="M212" t="n">
+        <v>55</v>
+      </c>
       <c r="N212" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Add opp_bb_pct to pitcher outs, bullpen features to totals, bullpen availability utility; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Use confirmed SP from lineup card, fall back to probable pitcher; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Cap pitcher outs to 1 pick per game (not per pitcher); Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Gate all 5 models on confirmed starting pitchers; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -11776,12 +12016,18 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K213" t="inlineStr"/>
-      <c r="L213" t="inlineStr"/>
-      <c r="M213" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K213" t="n">
+        <v>19</v>
+      </c>
+      <c r="L213" t="n">
+        <v>141.5</v>
+      </c>
+      <c r="M213" t="n">
+        <v>70.75</v>
+      </c>
       <c r="N213" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Add opp_bb_pct to pitcher outs, bullpen features to totals, bullpen availability utility; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Use confirmed SP from lineup card, fall back to probable pitcher; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Cap pitcher outs to 1 pick per game (not per pitcher); Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Gate all 5 models on confirmed starting pitchers; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -11828,12 +12074,18 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K214" t="inlineStr"/>
-      <c r="L214" t="inlineStr"/>
-      <c r="M214" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K214" t="n">
+        <v>12</v>
+      </c>
+      <c r="L214" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M214" t="n">
+        <v>-50</v>
+      </c>
       <c r="N214" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Add opp_bb_pct to pitcher outs, bullpen features to totals, bullpen availability utility; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Use confirmed SP from lineup card, fall back to probable pitcher; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Cap pitcher outs to 1 pick per game (not per pitcher); Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Gate all 5 models on confirmed starting pitchers; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -11880,12 +12132,18 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K215" t="inlineStr"/>
-      <c r="L215" t="inlineStr"/>
-      <c r="M215" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K215" t="n">
+        <v>14</v>
+      </c>
+      <c r="L215" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M215" t="n">
+        <v>-50</v>
+      </c>
       <c r="N215" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Add opp_bb_pct to pitcher outs, bullpen features to totals, bullpen availability utility; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Use confirmed SP from lineup card, fall back to probable pitcher; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Cap pitcher outs to 1 pick per game (not per pitcher); Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Gate all 5 models on confirmed starting pitchers; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -11932,12 +12190,18 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K216" t="inlineStr"/>
-      <c r="L216" t="inlineStr"/>
-      <c r="M216" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K216" t="n">
+        <v>15</v>
+      </c>
+      <c r="L216" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M216" t="n">
+        <v>-50</v>
+      </c>
       <c r="N216" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Add opp_bb_pct to pitcher outs, bullpen features to totals, bullpen availability utility; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Use confirmed SP from lineup card, fall back to probable pitcher; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Cap pitcher outs to 1 pick per game (not per pitcher); Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Gate all 5 models on confirmed starting pitchers; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -11984,12 +12248,18 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K217" t="inlineStr"/>
-      <c r="L217" t="inlineStr"/>
-      <c r="M217" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K217" t="n">
+        <v>13</v>
+      </c>
+      <c r="L217" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M217" t="n">
+        <v>-50</v>
+      </c>
       <c r="N217" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Add opp_bb_pct to pitcher outs, bullpen features to totals, bullpen availability utility; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Use confirmed SP from lineup card, fall back to probable pitcher; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Cap pitcher outs to 1 pick per game (not per pitcher); Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Gate all 5 models on confirmed starting pitchers; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -12036,12 +12306,18 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K218" t="inlineStr"/>
-      <c r="L218" t="inlineStr"/>
-      <c r="M218" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K218" t="n">
+        <v>18</v>
+      </c>
+      <c r="L218" t="n">
+        <v>82.64</v>
+      </c>
+      <c r="M218" t="n">
+        <v>41.32</v>
+      </c>
       <c r="N218" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Add opp_bb_pct to pitcher outs, bullpen features to totals, bullpen availability utility; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Use confirmed SP from lineup card, fall back to probable pitcher; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Cap pitcher outs to 1 pick per game (not per pitcher); Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Gate all 5 models on confirmed starting pitchers; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -12088,12 +12364,18 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K219" t="inlineStr"/>
-      <c r="L219" t="inlineStr"/>
-      <c r="M219" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K219" t="n">
+        <v>13</v>
+      </c>
+      <c r="L219" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M219" t="n">
+        <v>-50</v>
+      </c>
       <c r="N219" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Add opp_bb_pct to pitcher outs, bullpen features to totals, bullpen availability utility; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Use confirmed SP from lineup card, fall back to probable pitcher; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Cap pitcher outs to 1 pick per game (not per pitcher); Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Gate all 5 models on confirmed starting pitchers; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -12138,7 +12420,7 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>ODDS_ERR</t>
         </is>
       </c>
       <c r="K220" t="inlineStr"/>
@@ -12188,12 +12470,20 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K221" t="inlineStr"/>
-      <c r="L221" t="inlineStr"/>
-      <c r="M221" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>away_1st=0 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L221" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M221" t="n">
+        <v>-50</v>
+      </c>
       <c r="N221" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix NRFI scoreboard period param and Discord embed truncation; Fix NRFI odds: parse from scoreboard markets instead of props endpoint; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Gate NRFI scoring on confirmed lineups, consistent with other models; Fix 04_export_nrfi.py DataFrame iteration and lineup format bugs; Fix API crash guards and FanGraphs splits method errors; Add NRFI/YRFI fifth model and rebuild all four existing models; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -12238,12 +12528,20 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K222" t="inlineStr"/>
-      <c r="L222" t="inlineStr"/>
-      <c r="M222" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>away_1st=0 home_1st=2</t>
+        </is>
+      </c>
+      <c r="L222" t="n">
+        <v>114</v>
+      </c>
+      <c r="M222" t="n">
+        <v>57</v>
+      </c>
       <c r="N222" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix NRFI scoreboard period param and Discord embed truncation; Fix NRFI odds: parse from scoreboard markets instead of props endpoint; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Gate NRFI scoring on confirmed lineups, consistent with other models; Fix 04_export_nrfi.py DataFrame iteration and lineup format bugs; Fix API crash guards and FanGraphs splits method errors; Add NRFI/YRFI fifth model and rebuild all four existing models; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -12288,12 +12586,20 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K223" t="inlineStr"/>
-      <c r="L223" t="inlineStr"/>
-      <c r="M223" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>away_1st=0 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L223" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M223" t="n">
+        <v>-50</v>
+      </c>
       <c r="N223" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix NRFI scoreboard period param and Discord embed truncation; Fix NRFI odds: parse from scoreboard markets instead of props endpoint; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Gate NRFI scoring on confirmed lineups, consistent with other models; Fix 04_export_nrfi.py DataFrame iteration and lineup format bugs; Fix API crash guards and FanGraphs splits method errors; Add NRFI/YRFI fifth model and rebuild all four existing models; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -12338,12 +12644,20 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K224" t="inlineStr"/>
-      <c r="L224" t="inlineStr"/>
-      <c r="M224" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>away_1st=0 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L224" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M224" t="n">
+        <v>-50</v>
+      </c>
       <c r="N224" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix NRFI scoreboard period param and Discord embed truncation; Fix NRFI odds: parse from scoreboard markets instead of props endpoint; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Gate NRFI scoring on confirmed lineups, consistent with other models; Fix 04_export_nrfi.py DataFrame iteration and lineup format bugs; Fix API crash guards and FanGraphs splits method errors; Add NRFI/YRFI fifth model and rebuild all four existing models; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -12388,12 +12702,20 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K225" t="inlineStr"/>
-      <c r="L225" t="inlineStr"/>
-      <c r="M225" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>away_1st=0 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L225" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M225" t="n">
+        <v>-50</v>
+      </c>
       <c r="N225" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix NRFI scoreboard period param and Discord embed truncation; Fix NRFI odds: parse from scoreboard markets instead of props endpoint; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Gate NRFI scoring on confirmed lineups, consistent with other models; Fix 04_export_nrfi.py DataFrame iteration and lineup format bugs; Fix API crash guards and FanGraphs splits method errors; Add NRFI/YRFI fifth model and rebuild all four existing models; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -12438,12 +12760,20 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K226" t="inlineStr"/>
-      <c r="L226" t="inlineStr"/>
-      <c r="M226" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>away_1st=0 home_1st=2</t>
+        </is>
+      </c>
+      <c r="L226" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="M226" t="n">
+        <v>56.75</v>
+      </c>
       <c r="N226" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix NRFI scoreboard period param and Discord embed truncation; Fix NRFI odds: parse from scoreboard markets instead of props endpoint; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Gate NRFI scoring on confirmed lineups, consistent with other models; Fix 04_export_nrfi.py DataFrame iteration and lineup format bugs; Fix API crash guards and FanGraphs splits method errors; Add NRFI/YRFI fifth model and rebuild all four existing models; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -12488,12 +12818,20 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K227" t="inlineStr"/>
-      <c r="L227" t="inlineStr"/>
-      <c r="M227" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>away_1st=0 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L227" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M227" t="n">
+        <v>-50</v>
+      </c>
       <c r="N227" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix NRFI scoreboard period param and Discord embed truncation; Fix NRFI odds: parse from scoreboard markets instead of props endpoint; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Gate NRFI scoring on confirmed lineups, consistent with other models; Fix 04_export_nrfi.py DataFrame iteration and lineup format bugs; Fix API crash guards and FanGraphs splits method errors; Add NRFI/YRFI fifth model and rebuild all four existing models; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -12538,12 +12876,20 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K228" t="inlineStr"/>
-      <c r="L228" t="inlineStr"/>
-      <c r="M228" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>away_1st=1 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L228" t="n">
+        <v>94.34</v>
+      </c>
+      <c r="M228" t="n">
+        <v>47.17</v>
+      </c>
       <c r="N228" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix NRFI scoreboard period param and Discord embed truncation; Fix NRFI odds: parse from scoreboard markets instead of props endpoint; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Gate NRFI scoring on confirmed lineups, consistent with other models; Fix 04_export_nrfi.py DataFrame iteration and lineup format bugs; Fix API crash guards and FanGraphs splits method errors; Add NRFI/YRFI fifth model and rebuild all four existing models; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -12588,12 +12934,20 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K229" t="inlineStr"/>
-      <c r="L229" t="inlineStr"/>
-      <c r="M229" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>away_1st=0 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L229" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M229" t="n">
+        <v>-50</v>
+      </c>
       <c r="N229" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix NRFI scoreboard period param and Discord embed truncation; Fix NRFI odds: parse from scoreboard markets instead of props endpoint; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Gate NRFI scoring on confirmed lineups, consistent with other models; Fix 04_export_nrfi.py DataFrame iteration and lineup format bugs; Fix API crash guards and FanGraphs splits method errors; Add NRFI/YRFI fifth model and rebuild all four existing models; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -12640,12 +12994,18 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K230" t="inlineStr"/>
-      <c r="L230" t="inlineStr"/>
-      <c r="M230" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K230" t="n">
+        <v>11</v>
+      </c>
+      <c r="L230" t="n">
+        <v>100</v>
+      </c>
+      <c r="M230" t="n">
+        <v>50</v>
+      </c>
       <c r="N230" t="inlineStr">
         <is>
           <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -12692,12 +13052,18 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K231" t="inlineStr"/>
-      <c r="L231" t="inlineStr"/>
-      <c r="M231" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K231" t="n">
+        <v>9</v>
+      </c>
+      <c r="L231" t="n">
+        <v>90.91</v>
+      </c>
+      <c r="M231" t="n">
+        <v>45.45</v>
+      </c>
       <c r="N231" t="inlineStr">
         <is>
           <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -12744,12 +13110,18 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K232" t="inlineStr"/>
-      <c r="L232" t="inlineStr"/>
-      <c r="M232" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K232" t="n">
+        <v>6</v>
+      </c>
+      <c r="L232" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M232" t="n">
+        <v>-50</v>
+      </c>
       <c r="N232" t="inlineStr">
         <is>
           <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -12796,12 +13168,18 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K233" t="inlineStr"/>
-      <c r="L233" t="inlineStr"/>
-      <c r="M233" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K233" t="n">
+        <v>5</v>
+      </c>
+      <c r="L233" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M233" t="n">
+        <v>-50</v>
+      </c>
       <c r="N233" t="inlineStr">
         <is>
           <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -12848,12 +13226,18 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K234" t="inlineStr"/>
-      <c r="L234" t="inlineStr"/>
-      <c r="M234" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K234" t="n">
+        <v>15</v>
+      </c>
+      <c r="L234" t="n">
+        <v>86.20999999999999</v>
+      </c>
+      <c r="M234" t="n">
+        <v>43.1</v>
+      </c>
       <c r="N234" t="inlineStr">
         <is>
           <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -12900,12 +13284,18 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K235" t="inlineStr"/>
-      <c r="L235" t="inlineStr"/>
-      <c r="M235" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K235" t="n">
+        <v>11</v>
+      </c>
+      <c r="L235" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M235" t="n">
+        <v>-50</v>
+      </c>
       <c r="N235" t="inlineStr">
         <is>
           <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -12952,12 +13342,18 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K236" t="inlineStr"/>
-      <c r="L236" t="inlineStr"/>
-      <c r="M236" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K236" t="n">
+        <v>7</v>
+      </c>
+      <c r="L236" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M236" t="n">
+        <v>-50</v>
+      </c>
       <c r="N236" t="inlineStr">
         <is>
           <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -13004,12 +13400,18 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K237" t="inlineStr"/>
-      <c r="L237" t="inlineStr"/>
-      <c r="M237" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K237" t="n">
+        <v>4</v>
+      </c>
+      <c r="L237" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M237" t="n">
+        <v>-50</v>
+      </c>
       <c r="N237" t="inlineStr">
         <is>
           <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -13054,12 +13456,20 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K238" t="inlineStr"/>
-      <c r="L238" t="inlineStr"/>
-      <c r="M238" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="L238" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M238" t="n">
+        <v>-50</v>
+      </c>
       <c r="N238" t="inlineStr">
         <is>
           <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -13104,12 +13514,20 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K239" t="inlineStr"/>
-      <c r="L239" t="inlineStr"/>
-      <c r="M239" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>1-6</t>
+        </is>
+      </c>
+      <c r="L239" t="n">
+        <v>50.25</v>
+      </c>
+      <c r="M239" t="n">
+        <v>25.13</v>
+      </c>
       <c r="N239" t="inlineStr">
         <is>
           <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -13156,12 +13574,18 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K240" t="inlineStr"/>
-      <c r="L240" t="inlineStr"/>
-      <c r="M240" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K240" t="n">
+        <v>7</v>
+      </c>
+      <c r="L240" t="n">
+        <v>95.23999999999999</v>
+      </c>
+      <c r="M240" t="n">
+        <v>47.62</v>
+      </c>
       <c r="N240" t="inlineStr">
         <is>
           <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -13208,12 +13632,18 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K241" t="inlineStr"/>
-      <c r="L241" t="inlineStr"/>
-      <c r="M241" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K241" t="n">
+        <v>7</v>
+      </c>
+      <c r="L241" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M241" t="n">
+        <v>-50</v>
+      </c>
       <c r="N241" t="inlineStr">
         <is>
           <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -13260,12 +13690,18 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K242" t="inlineStr"/>
-      <c r="L242" t="inlineStr"/>
-      <c r="M242" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K242" t="n">
+        <v>1</v>
+      </c>
+      <c r="L242" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M242" t="n">
+        <v>-50</v>
+      </c>
       <c r="N242" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -13312,12 +13748,18 @@
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K243" t="inlineStr"/>
-      <c r="L243" t="inlineStr"/>
-      <c r="M243" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K243" t="n">
+        <v>0</v>
+      </c>
+      <c r="L243" t="n">
+        <v>80</v>
+      </c>
+      <c r="M243" t="n">
+        <v>40</v>
+      </c>
       <c r="N243" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -13364,12 +13806,18 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K244" t="inlineStr"/>
-      <c r="L244" t="inlineStr"/>
-      <c r="M244" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K244" t="n">
+        <v>12</v>
+      </c>
+      <c r="L244" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M244" t="n">
+        <v>-50</v>
+      </c>
       <c r="N244" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Add opp_bb_pct to pitcher outs, bullpen features to totals, bullpen availability utility; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Use confirmed SP from lineup card, fall back to probable pitcher; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Cap pitcher outs to 1 pick per game (not per pitcher); Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Gate all 5 models on confirmed starting pitchers; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -13416,12 +13864,18 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K245" t="inlineStr"/>
-      <c r="L245" t="inlineStr"/>
-      <c r="M245" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K245" t="n">
+        <v>12</v>
+      </c>
+      <c r="L245" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M245" t="n">
+        <v>-50</v>
+      </c>
       <c r="N245" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Add opp_bb_pct to pitcher outs, bullpen features to totals, bullpen availability utility; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Use confirmed SP from lineup card, fall back to probable pitcher; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Cap pitcher outs to 1 pick per game (not per pitcher); Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Gate all 5 models on confirmed starting pitchers; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -13466,12 +13920,20 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K246" t="inlineStr"/>
-      <c r="L246" t="inlineStr"/>
-      <c r="M246" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>away_1st=0 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L246" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M246" t="n">
+        <v>-50</v>
+      </c>
       <c r="N246" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix NRFI scoreboard period param and Discord embed truncation; Fix NRFI odds: parse from scoreboard markets instead of props endpoint; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Gate NRFI scoring on confirmed lineups, consistent with other models; Fix 04_export_nrfi.py DataFrame iteration and lineup format bugs; Fix API crash guards and FanGraphs splits method errors; Add NRFI/YRFI fifth model and rebuild all four existing models; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -13516,12 +13978,20 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K247" t="inlineStr"/>
-      <c r="L247" t="inlineStr"/>
-      <c r="M247" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>away_1st=0 home_1st=3</t>
+        </is>
+      </c>
+      <c r="L247" t="n">
+        <v>93.45999999999999</v>
+      </c>
+      <c r="M247" t="n">
+        <v>46.73</v>
+      </c>
       <c r="N247" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix NRFI scoreboard period param and Discord embed truncation; Fix NRFI odds: parse from scoreboard markets instead of props endpoint; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Gate NRFI scoring on confirmed lineups, consistent with other models; Fix 04_export_nrfi.py DataFrame iteration and lineup format bugs; Fix API crash guards and FanGraphs splits method errors; Add NRFI/YRFI fifth model and rebuild all four existing models; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -13566,12 +14036,20 @@
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K248" t="inlineStr"/>
-      <c r="L248" t="inlineStr"/>
-      <c r="M248" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>away_1st=0 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L248" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M248" t="n">
+        <v>-50</v>
+      </c>
       <c r="N248" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix NRFI scoreboard period param and Discord embed truncation; Fix NRFI odds: parse from scoreboard markets instead of props endpoint; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Gate NRFI scoring on confirmed lineups, consistent with other models; Fix 04_export_nrfi.py DataFrame iteration and lineup format bugs; Fix API crash guards and FanGraphs splits method errors; Add NRFI/YRFI fifth model and rebuild all four existing models; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -13618,12 +14096,18 @@
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K249" t="inlineStr"/>
-      <c r="L249" t="inlineStr"/>
-      <c r="M249" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K249" t="n">
+        <v>5</v>
+      </c>
+      <c r="L249" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M249" t="n">
+        <v>-50</v>
+      </c>
       <c r="N249" t="inlineStr">
         <is>
           <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -13670,12 +14154,18 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K250" t="inlineStr"/>
-      <c r="L250" t="inlineStr"/>
-      <c r="M250" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K250" t="n">
+        <v>3</v>
+      </c>
+      <c r="L250" t="n">
+        <v>92.59</v>
+      </c>
+      <c r="M250" t="n">
+        <v>46.3</v>
+      </c>
       <c r="N250" t="inlineStr">
         <is>
           <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -13722,12 +14212,18 @@
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K251" t="inlineStr"/>
-      <c r="L251" t="inlineStr"/>
-      <c r="M251" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K251" t="n">
+        <v>0</v>
+      </c>
+      <c r="L251" t="n">
+        <v>125</v>
+      </c>
+      <c r="M251" t="n">
+        <v>62.5</v>
+      </c>
       <c r="N251" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -13774,12 +14270,18 @@
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K252" t="inlineStr"/>
-      <c r="L252" t="inlineStr"/>
-      <c r="M252" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K252" t="n">
+        <v>0</v>
+      </c>
+      <c r="L252" t="n">
+        <v>116</v>
+      </c>
+      <c r="M252" t="n">
+        <v>58</v>
+      </c>
       <c r="N252" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -13826,12 +14328,18 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K253" t="inlineStr"/>
-      <c r="L253" t="inlineStr"/>
-      <c r="M253" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K253" t="n">
+        <v>0</v>
+      </c>
+      <c r="L253" t="n">
+        <v>90.91</v>
+      </c>
+      <c r="M253" t="n">
+        <v>45.45</v>
+      </c>
       <c r="N253" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -13878,12 +14386,18 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K254" t="inlineStr"/>
-      <c r="L254" t="inlineStr"/>
-      <c r="M254" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K254" t="n">
+        <v>1</v>
+      </c>
+      <c r="L254" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M254" t="n">
+        <v>-50</v>
+      </c>
       <c r="N254" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -13930,12 +14444,18 @@
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K255" t="inlineStr"/>
-      <c r="L255" t="inlineStr"/>
-      <c r="M255" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K255" t="n">
+        <v>2</v>
+      </c>
+      <c r="L255" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M255" t="n">
+        <v>-50</v>
+      </c>
       <c r="N255" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -13982,12 +14502,18 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K256" t="inlineStr"/>
-      <c r="L256" t="inlineStr"/>
-      <c r="M256" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K256" t="n">
+        <v>1</v>
+      </c>
+      <c r="L256" t="n">
+        <v>64.52</v>
+      </c>
+      <c r="M256" t="n">
+        <v>32.26</v>
+      </c>
       <c r="N256" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -14034,12 +14560,18 @@
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K257" t="inlineStr"/>
-      <c r="L257" t="inlineStr"/>
-      <c r="M257" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K257" t="n">
+        <v>1</v>
+      </c>
+      <c r="L257" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M257" t="n">
+        <v>-50</v>
+      </c>
       <c r="N257" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -14086,12 +14618,18 @@
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K258" t="inlineStr"/>
-      <c r="L258" t="inlineStr"/>
-      <c r="M258" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K258" t="n">
+        <v>1</v>
+      </c>
+      <c r="L258" t="n">
+        <v>80.65000000000001</v>
+      </c>
+      <c r="M258" t="n">
+        <v>40.32</v>
+      </c>
       <c r="N258" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -14138,12 +14676,18 @@
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K259" t="inlineStr"/>
-      <c r="L259" t="inlineStr"/>
-      <c r="M259" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K259" t="n">
+        <v>0</v>
+      </c>
+      <c r="L259" t="n">
+        <v>74.63</v>
+      </c>
+      <c r="M259" t="n">
+        <v>37.31</v>
+      </c>
       <c r="N259" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -14188,12 +14732,20 @@
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K260" t="inlineStr"/>
-      <c r="L260" t="inlineStr"/>
-      <c r="M260" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>6-5</t>
+        </is>
+      </c>
+      <c r="L260" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M260" t="n">
+        <v>-50</v>
+      </c>
       <c r="N260" t="inlineStr">
         <is>
           <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -14240,12 +14792,18 @@
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K261" t="inlineStr"/>
-      <c r="L261" t="inlineStr"/>
-      <c r="M261" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K261" t="n">
+        <v>11</v>
+      </c>
+      <c r="L261" t="n">
+        <v>98.04000000000001</v>
+      </c>
+      <c r="M261" t="n">
+        <v>49.02</v>
+      </c>
       <c r="N261" t="inlineStr">
         <is>
           <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -14292,12 +14850,18 @@
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K262" t="inlineStr"/>
-      <c r="L262" t="inlineStr"/>
-      <c r="M262" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K262" t="n">
+        <v>1</v>
+      </c>
+      <c r="L262" t="n">
+        <v>60.61</v>
+      </c>
+      <c r="M262" t="n">
+        <v>30.3</v>
+      </c>
       <c r="N262" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -14344,12 +14908,18 @@
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K263" t="inlineStr"/>
-      <c r="L263" t="inlineStr"/>
-      <c r="M263" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K263" t="n">
+        <v>1</v>
+      </c>
+      <c r="L263" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="M263" t="n">
+        <v>41.67</v>
+      </c>
       <c r="N263" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -14396,12 +14966,18 @@
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K264" t="inlineStr"/>
-      <c r="L264" t="inlineStr"/>
-      <c r="M264" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K264" t="n">
+        <v>0</v>
+      </c>
+      <c r="L264" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M264" t="n">
+        <v>-50</v>
+      </c>
       <c r="N264" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix hitter TB model: consensus line selection and geometric distribution; Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -14448,12 +15024,18 @@
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K265" t="inlineStr"/>
-      <c r="L265" t="inlineStr"/>
-      <c r="M265" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K265" t="n">
+        <v>11</v>
+      </c>
+      <c r="L265" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M265" t="n">
+        <v>-50</v>
+      </c>
       <c r="N265" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Add opp_bb_pct to pitcher outs, bullpen features to totals, bullpen availability utility; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Use confirmed SP from lineup card, fall back to probable pitcher; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Cap pitcher outs to 1 pick per game (not per pitcher); Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Gate all 5 models on confirmed starting pitchers; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -14500,12 +15082,18 @@
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K266" t="inlineStr"/>
-      <c r="L266" t="inlineStr"/>
-      <c r="M266" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K266" t="n">
+        <v>15</v>
+      </c>
+      <c r="L266" t="n">
+        <v>85.47</v>
+      </c>
+      <c r="M266" t="n">
+        <v>42.74</v>
+      </c>
       <c r="N266" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Add opp_bb_pct to pitcher outs, bullpen features to totals, bullpen availability utility; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Use confirmed SP from lineup card, fall back to probable pitcher; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Cap pitcher outs to 1 pick per game (not per pitcher); Cap hitter TB and pitcher outs to one best pick per player; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Gate all 5 models on confirmed starting pitchers; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -14550,12 +15138,20 @@
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K267" t="inlineStr"/>
-      <c r="L267" t="inlineStr"/>
-      <c r="M267" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>away_1st=1 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L267" t="n">
+        <v>80.31999999999999</v>
+      </c>
+      <c r="M267" t="n">
+        <v>40.16</v>
+      </c>
       <c r="N267" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix NRFI scoreboard period param and Discord embed truncation; Fix NRFI odds: parse from scoreboard markets instead of props endpoint; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Gate NRFI scoring on confirmed lineups, consistent with other models; Fix 04_export_nrfi.py DataFrame iteration and lineup format bugs; Fix API crash guards and FanGraphs splits method errors; Add NRFI/YRFI fifth model and rebuild all four existing models; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -14600,12 +15196,20 @@
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K268" t="inlineStr"/>
-      <c r="L268" t="inlineStr"/>
-      <c r="M268" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>away_1st=0 home_1st=0</t>
+        </is>
+      </c>
+      <c r="L268" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M268" t="n">
+        <v>-50</v>
+      </c>
       <c r="N268" t="inlineStr">
         <is>
           <t>Fix four model bugs: totals inf lambda, NRFI neg-edge, pitcher dupe picks, hitter TB leakage checks; Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Fix NRFI scoreboard period param and Discord embed truncation; Fix NRFI odds: parse from scoreboard markets instead of props endpoint; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Gate NRFI scoring on confirmed lineups, consistent with other models; Fix 04_export_nrfi.py DataFrame iteration and lineup format bugs; Fix API crash guards and FanGraphs splits method errors; Add NRFI/YRFI fifth model and rebuild all four existing models; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -14675,19 +15279,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.545</v>
+        <v>0.529</v>
       </c>
       <c r="G2" t="n">
-        <v>10.25</v>
+        <v>-9.5</v>
       </c>
     </row>
     <row r="3">
@@ -14702,19 +15306,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.526</v>
+        <v>0.5</v>
       </c>
       <c r="G3" t="n">
-        <v>2.33</v>
+        <v>-66.18000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -14729,19 +15333,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="D4" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.548</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>-189.92</v>
+        <v>-89.31999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -14756,19 +15360,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.483</v>
+        <v>0.467</v>
       </c>
       <c r="G5" t="n">
-        <v>-155.92</v>
+        <v>-266.65</v>
       </c>
     </row>
     <row r="6">
@@ -14783,19 +15387,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.478</v>
+        <v>0.432</v>
       </c>
       <c r="G6" t="n">
-        <v>-83.25</v>
+        <v>-285.44</v>
       </c>
     </row>
     <row r="7">
@@ -14810,19 +15414,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>81</v>
+        <v>128</v>
       </c>
       <c r="D7" t="n">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0.523</v>
+        <v>0.514</v>
       </c>
       <c r="G7" t="n">
-        <v>-416.51</v>
+        <v>-717.09</v>
       </c>
     </row>
     <row r="8">
@@ -14837,19 +15441,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.545</v>
+        <v>0.529</v>
       </c>
       <c r="G8" t="n">
-        <v>10.25</v>
+        <v>-9.5</v>
       </c>
     </row>
     <row r="9">
@@ -14864,19 +15468,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0.526</v>
+        <v>0.5</v>
       </c>
       <c r="G9" t="n">
-        <v>2.33</v>
+        <v>-66.18000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -14891,19 +15495,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="D10" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.548</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-189.92</v>
+        <v>-89.31999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -14918,19 +15522,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D11" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.483</v>
+        <v>0.467</v>
       </c>
       <c r="G11" t="n">
-        <v>-155.92</v>
+        <v>-266.65</v>
       </c>
     </row>
     <row r="12">
@@ -14945,19 +15549,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.478</v>
+        <v>0.432</v>
       </c>
       <c r="G12" t="n">
-        <v>-83.25</v>
+        <v>-285.44</v>
       </c>
     </row>
     <row r="13">
@@ -14972,19 +15576,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.523</v>
+        <v>0.514</v>
       </c>
       <c r="G13" t="n">
-        <v>-416.51</v>
+        <v>-717.09</v>
       </c>
     </row>
     <row r="14">
@@ -14999,19 +15603,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.545</v>
+        <v>0.529</v>
       </c>
       <c r="G14" t="n">
-        <v>10.25</v>
+        <v>-9.5</v>
       </c>
     </row>
     <row r="15">
@@ -15026,19 +15630,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.526</v>
+        <v>0.5</v>
       </c>
       <c r="G15" t="n">
-        <v>2.33</v>
+        <v>-66.18000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -15053,19 +15657,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.548</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>-189.92</v>
+        <v>-89.31999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -15080,19 +15684,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D17" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.483</v>
+        <v>0.467</v>
       </c>
       <c r="G17" t="n">
-        <v>-155.92</v>
+        <v>-266.65</v>
       </c>
     </row>
     <row r="18">
@@ -15107,19 +15711,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D18" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.478</v>
+        <v>0.432</v>
       </c>
       <c r="G18" t="n">
-        <v>-83.25</v>
+        <v>-285.44</v>
       </c>
     </row>
     <row r="19">
@@ -15134,19 +15738,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>81</v>
+        <v>128</v>
       </c>
       <c r="D19" t="n">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>0.523</v>
+        <v>0.514</v>
       </c>
       <c r="G19" t="n">
-        <v>-416.51</v>
+        <v>-717.09</v>
       </c>
     </row>
   </sheetData>
@@ -15867,12 +16471,20 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>1-6</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>50.25</v>
+      </c>
+      <c r="M13" t="n">
+        <v>25.13</v>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -15917,12 +16529,20 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>7-8</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-50</v>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
           <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -15967,12 +16587,20 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>5-6</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>115</v>
+      </c>
+      <c r="M15" t="n">
+        <v>57.5</v>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
           <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -16017,12 +16645,20 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>5-6</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>95.23999999999999</v>
+      </c>
+      <c r="M16" t="n">
+        <v>47.62</v>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -16067,12 +16703,20 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-50</v>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -16117,12 +16761,20 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>6-5</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-50</v>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -17335,12 +17987,18 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>3</v>
+      </c>
+      <c r="L22" t="n">
+        <v>92.59</v>
+      </c>
+      <c r="M22" t="n">
+        <v>46.3</v>
+      </c>
       <c r="N22" t="inlineStr">
         <is>
           <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -17387,12 +18045,18 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>11</v>
+      </c>
+      <c r="L23" t="n">
+        <v>100</v>
+      </c>
+      <c r="M23" t="n">
+        <v>50</v>
+      </c>
       <c r="N23" t="inlineStr">
         <is>
           <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -17439,12 +18103,18 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>9</v>
+      </c>
+      <c r="L24" t="n">
+        <v>90.91</v>
+      </c>
+      <c r="M24" t="n">
+        <v>45.45</v>
+      </c>
       <c r="N24" t="inlineStr">
         <is>
           <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -17491,12 +18161,18 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>6</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-50</v>
+      </c>
       <c r="N25" t="inlineStr">
         <is>
           <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -17543,12 +18219,18 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>5</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-50</v>
+      </c>
       <c r="N26" t="inlineStr">
         <is>
           <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -17595,12 +18277,18 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>15</v>
+      </c>
+      <c r="L27" t="n">
+        <v>86.20999999999999</v>
+      </c>
+      <c r="M27" t="n">
+        <v>43.1</v>
+      </c>
       <c r="N27" t="inlineStr">
         <is>
           <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -17647,12 +18335,18 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>11</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-50</v>
+      </c>
       <c r="N28" t="inlineStr">
         <is>
           <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -17699,12 +18393,18 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>7</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-50</v>
+      </c>
       <c r="N29" t="inlineStr">
         <is>
           <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -17751,12 +18451,18 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>4</v>
+      </c>
+      <c r="L30" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M30" t="n">
+        <v>-50</v>
+      </c>
       <c r="N30" t="inlineStr">
         <is>
           <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -17803,12 +18509,18 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>7</v>
+      </c>
+      <c r="L31" t="n">
+        <v>95.23999999999999</v>
+      </c>
+      <c r="M31" t="n">
+        <v>47.62</v>
+      </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -17855,12 +18567,18 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>7</v>
+      </c>
+      <c r="L32" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M32" t="n">
+        <v>-50</v>
+      </c>
       <c r="N32" t="inlineStr">
         <is>
           <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -17907,12 +18625,18 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>5</v>
+      </c>
+      <c r="L33" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M33" t="n">
+        <v>-50</v>
+      </c>
       <c r="N33" t="inlineStr">
         <is>
           <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits method errors; Add daily retrain scheduler and update launchd setup; Fix Opening Day date to March 25; Initial commit — baseball models pipeline</t>
@@ -17959,12 +18683,18 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>11</v>
+      </c>
+      <c r="L34" t="n">
+        <v>98.04000000000001</v>
+      </c>
+      <c r="M34" t="n">
+        <v>49.02</v>
+      </c>
       <c r="N34" t="inlineStr">
         <is>
           <t>Add model-status notification to 4 AM grader on success; Fix Python 3.9 incompatibility: replace Path | None union syntax; Fix window filtering: game_time stripped from odds wrappers, late-wake guard, sentinel deduplication; Fix grading pipeline: MLB API hydration, bad odds guard, Discord embed truncation; Refactor grade_daily.py orchestrator to spawn named specialist subagents; Auto-add 2026 to training once 20 games played (season gate); Scope runs to game windows, add dupe protection, move scheduler to 5 AM; Fix pick_date normalization — handle integers, datetimes, and strings; Fix pick_date format mismatch in _load_picks; Add pnl_50 column to picks.xlsx — $50 flat stake P&amp;L; Write last_run_summary.txt after each model run for remote agents; Add post-run error checks and per-model picks sheets; Model improvements: raise thresholds, fix bugs, add dated export folders; Update props fetching to Action Network v2 API; Fix props auth, false positive bets, silent Discord failures, tracker f-string; Fix scheduler reliability: replace time.sleep with launchd one-shot plists; Update grade_daily.py references from 9am to 4am; Add Discord status notifications and Opening Day fixes; Add 5 model improvements from deep audit: fi_fstrike_pct, park factor, sweet_spot_pct, umpire data, bullpen fatigue; Fix run_daily.py and tracker.py for Python 3.9 and runtime errors; Pre-Opening Day fixes: MODEL_DIR path, pandas import, Series truthiness; Fix API crash guards and FanGraphs splits met